--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="154">
   <si>
     <t>Tecnico</t>
   </si>
@@ -599,14 +599,12 @@
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -902,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H345"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -7636,7 +7634,7 @@
         <v>20</v>
       </c>
       <c r="F272" s="3">
-        <f t="shared" ref="F272:F338" si="6">D272-(D272*E272)/100</f>
+        <f t="shared" ref="F272:F336" si="6">D272-(D272*E272)/100</f>
         <v>36.681839742579442</v>
       </c>
       <c r="G272" s="1"/>
@@ -7647,22 +7645,22 @@
         <v>4</v>
       </c>
       <c r="B273" s="11">
-        <v>45979</v>
-      </c>
-      <c r="C273" s="12">
-        <v>60</v>
-      </c>
-      <c r="D273" s="13">
-        <v>29.346096938775499</v>
-      </c>
-      <c r="E273" s="14">
-        <v>20</v>
-      </c>
-      <c r="F273" s="15">
+        <v>45991</v>
+      </c>
+      <c r="C273" s="9">
+        <v>124</v>
+      </c>
+      <c r="D273" s="12">
+        <v>31.189142473118299</v>
+      </c>
+      <c r="E273" s="13">
+        <v>20</v>
+      </c>
+      <c r="F273" s="14">
         <f t="shared" si="6"/>
-        <v>23.476877551020401</v>
-      </c>
-      <c r="G273" s="10" t="s">
+        <v>24.951313978494639</v>
+      </c>
+      <c r="G273" s="15" t="s">
         <v>67</v>
       </c>
       <c r="H273" s="16" t="s">
@@ -7674,20 +7672,20 @@
         <v>5</v>
       </c>
       <c r="B274" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C274" s="9">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="D274" s="4">
-        <v>28.6650595515537</v>
+        <v>37.811625817847897</v>
       </c>
       <c r="E274" s="6">
         <v>20</v>
       </c>
       <c r="F274" s="3">
         <f t="shared" si="6"/>
-        <v>22.93204764124296</v>
+        <v>30.249300654278318</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>67</v>
@@ -7701,16 +7699,20 @@
         <v>139</v>
       </c>
       <c r="B275" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C275" s="9"/>
-      <c r="D275" s="4"/>
+        <v>45991</v>
+      </c>
+      <c r="C275" s="9">
+        <v>48</v>
+      </c>
+      <c r="D275" s="4">
+        <v>134.20636002328999</v>
+      </c>
       <c r="E275" s="6">
         <v>20</v>
       </c>
       <c r="F275" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>107.36508801863199</v>
       </c>
       <c r="G275" s="1"/>
       <c r="H275" s="8"/>
@@ -7720,20 +7722,20 @@
         <v>6</v>
       </c>
       <c r="B276" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C276" s="9">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="D276" s="4">
-        <v>43.425407592332903</v>
+        <v>31.485793439459201</v>
       </c>
       <c r="E276" s="6">
         <v>20</v>
       </c>
       <c r="F276" s="3">
         <f t="shared" si="6"/>
-        <v>34.740326073866321</v>
+        <v>25.18863475156736</v>
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="8" t="s">
@@ -7745,20 +7747,20 @@
         <v>7</v>
       </c>
       <c r="B277" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C277" s="9">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D277" s="4">
-        <v>791.60524999999996</v>
+        <v>203.80709722222201</v>
       </c>
       <c r="E277" s="6">
         <v>20</v>
       </c>
       <c r="F277" s="3">
         <f t="shared" si="6"/>
-        <v>633.28419999999994</v>
+        <v>163.0456777777776</v>
       </c>
       <c r="G277" s="1"/>
       <c r="H277" s="8" t="s">
@@ -7770,20 +7772,20 @@
         <v>8</v>
       </c>
       <c r="B278" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C278" s="9">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="D278" s="4">
-        <v>27.603030921459499</v>
+        <v>29.248444138400199</v>
       </c>
       <c r="E278" s="6">
         <v>20</v>
       </c>
       <c r="F278" s="3">
         <f t="shared" si="6"/>
-        <v>22.082424737167599</v>
+        <v>23.398755310720158</v>
       </c>
       <c r="G278" s="1"/>
       <c r="H278" s="8" t="s">
@@ -7795,20 +7797,20 @@
         <v>9</v>
       </c>
       <c r="B279" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C279" s="9">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="D279" s="4">
-        <v>32.3825986394558</v>
+        <v>39.744967680608397</v>
       </c>
       <c r="E279" s="6">
         <v>20</v>
       </c>
       <c r="F279" s="3">
         <f t="shared" si="6"/>
-        <v>25.906078911564641</v>
+        <v>31.795974144486717</v>
       </c>
       <c r="G279" s="1"/>
       <c r="H279" s="8" t="s">
@@ -7820,20 +7822,20 @@
         <v>10</v>
       </c>
       <c r="B280" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C280" s="9">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="D280" s="4">
-        <v>34.770215</v>
+        <v>35.579655487804899</v>
       </c>
       <c r="E280" s="6">
         <v>20</v>
       </c>
       <c r="F280" s="3">
         <f t="shared" si="6"/>
-        <v>27.816172000000002</v>
+        <v>28.463724390243918</v>
       </c>
       <c r="G280" s="1"/>
       <c r="H280" s="8" t="s">
@@ -7845,20 +7847,20 @@
         <v>11</v>
       </c>
       <c r="B281" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C281" s="9">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="D281" s="4">
-        <v>32.3825986394558</v>
+        <v>39.744967680608397</v>
       </c>
       <c r="E281" s="6">
         <v>20</v>
       </c>
       <c r="F281" s="3">
         <f t="shared" si="6"/>
-        <v>25.906078911564641</v>
+        <v>31.795974144486717</v>
       </c>
       <c r="G281" s="1"/>
       <c r="H281" s="8" t="s">
@@ -7870,20 +7872,20 @@
         <v>12</v>
       </c>
       <c r="B282" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C282" s="9">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="D282" s="4">
-        <v>24.5925847457627</v>
+        <v>56.329923570077497</v>
       </c>
       <c r="E282" s="6">
         <v>20</v>
       </c>
       <c r="F282" s="3">
         <f t="shared" si="6"/>
-        <v>19.67406779661016</v>
+        <v>45.063938856061995</v>
       </c>
       <c r="G282" s="1"/>
       <c r="H282" s="8" t="s">
@@ -7895,20 +7897,20 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C283" s="9">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="D283" s="4">
-        <v>24.5925847457627</v>
+        <v>56.329923570077497</v>
       </c>
       <c r="E283" s="6">
         <v>20</v>
       </c>
       <c r="F283" s="3">
         <f t="shared" si="6"/>
-        <v>19.67406779661016</v>
+        <v>45.063938856061995</v>
       </c>
       <c r="G283" s="1"/>
       <c r="H283" s="8" t="s">
@@ -7920,20 +7922,20 @@
         <v>14</v>
       </c>
       <c r="B284" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C284" s="9">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="D284" s="4">
-        <v>52.361870530303001</v>
+        <v>42.655002724037701</v>
       </c>
       <c r="E284" s="6">
         <v>20</v>
       </c>
       <c r="F284" s="3">
         <f t="shared" si="6"/>
-        <v>41.889496424242402</v>
+        <v>34.12400217923016</v>
       </c>
       <c r="G284" s="1"/>
       <c r="H284" s="8" t="s">
@@ -7942,1490 +7944,1456 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B285" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C285" s="9"/>
-      <c r="D285" s="4"/>
+        <v>45991</v>
+      </c>
+      <c r="C285" s="9">
+        <v>168</v>
+      </c>
+      <c r="D285" s="4">
+        <v>30.141696688279701</v>
+      </c>
       <c r="E285" s="6">
         <v>20</v>
       </c>
       <c r="F285" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>24.113357350623762</v>
       </c>
       <c r="G285" s="1"/>
       <c r="H285" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="1" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="B286" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C286" s="9">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="D286" s="4">
-        <v>27.748286422902499</v>
+        <v>118.816192483051</v>
       </c>
       <c r="E286" s="6">
         <v>20</v>
       </c>
       <c r="F286" s="3">
         <f t="shared" si="6"/>
-        <v>22.198629138321998</v>
+        <v>95.052953986440798</v>
       </c>
       <c r="G286" s="1"/>
-      <c r="H286" s="8" t="s">
-        <v>87</v>
-      </c>
+      <c r="H286" s="8"/>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="1" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="B287" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C287" s="9">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D287" s="4">
-        <v>98.040274962742203</v>
+        <v>37.687197916666697</v>
       </c>
       <c r="E287" s="6">
         <v>20</v>
       </c>
       <c r="F287" s="3">
         <f t="shared" si="6"/>
-        <v>78.432219970193756</v>
+        <v>30.149758333333359</v>
       </c>
       <c r="G287" s="1"/>
-      <c r="H287" s="8"/>
+      <c r="H287" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B288" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C288" s="9">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="D288" s="4">
-        <v>35.915104166666701</v>
+        <v>34.291203234185197</v>
       </c>
       <c r="E288" s="6">
         <v>20</v>
       </c>
       <c r="F288" s="3">
         <f t="shared" si="6"/>
-        <v>28.73208333333336</v>
+        <v>27.432962587348158</v>
       </c>
       <c r="G288" s="1"/>
       <c r="H288" s="8" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B289" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C289" s="9">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="D289" s="4">
-        <v>28.036716018884501</v>
+        <v>33.499415518672699</v>
       </c>
       <c r="E289" s="6">
         <v>20</v>
       </c>
       <c r="F289" s="3">
         <f t="shared" si="6"/>
-        <v>22.429372815107602</v>
+        <v>26.79953241493816</v>
       </c>
       <c r="G289" s="1"/>
       <c r="H289" s="8" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B290" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C290" s="9"/>
-      <c r="D290" s="4"/>
+        <v>45991</v>
+      </c>
+      <c r="C290" s="9">
+        <v>176</v>
+      </c>
+      <c r="D290" s="4">
+        <v>34.022932412626503</v>
+      </c>
       <c r="E290" s="6">
         <v>20</v>
       </c>
       <c r="F290" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>27.218345930101201</v>
       </c>
       <c r="G290" s="1"/>
       <c r="H290" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="291" spans="1:8">
-      <c r="A291" s="1" t="s">
-        <v>20</v>
+      <c r="A291" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="B291" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C291" s="9">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D291" s="4">
-        <v>32.164854642023002</v>
+        <v>61.609753215045302</v>
       </c>
       <c r="E291" s="6">
         <v>20</v>
       </c>
       <c r="F291" s="3">
         <f t="shared" si="6"/>
-        <v>25.731883713618402</v>
+        <v>49.287802572036242</v>
       </c>
       <c r="G291" s="1"/>
       <c r="H291" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B292" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C292" s="9">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="D292" s="4">
-        <v>34.249028517481499</v>
+        <v>33.456470827983601</v>
       </c>
       <c r="E292" s="6">
         <v>20</v>
       </c>
       <c r="F292" s="3">
         <f t="shared" si="6"/>
-        <v>27.399222813985197</v>
+        <v>26.765176662386882</v>
       </c>
       <c r="G292" s="1"/>
       <c r="H292" s="8" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B293" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C293" s="9">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="D293" s="4">
-        <v>56.364232531030197</v>
+        <v>64.038399660655003</v>
       </c>
       <c r="E293" s="6">
         <v>20</v>
       </c>
       <c r="F293" s="3">
         <f t="shared" si="6"/>
-        <v>45.09138602482416</v>
+        <v>51.230719728524001</v>
       </c>
       <c r="G293" s="1"/>
       <c r="H293" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B294" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C294" s="9">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D294" s="4">
-        <v>29.681458688447002</v>
+        <v>88.3928023255814</v>
       </c>
       <c r="E294" s="6">
         <v>20</v>
       </c>
       <c r="F294" s="3">
         <f t="shared" si="6"/>
-        <v>23.7451669507576</v>
+        <v>70.714241860465123</v>
       </c>
       <c r="G294" s="1"/>
       <c r="H294" s="8" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="295" spans="1:8">
-      <c r="A295" s="10" t="s">
-        <v>24</v>
+      <c r="A295" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B295" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C295" s="9">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="D295" s="4">
-        <v>66.424341818395206</v>
+        <v>38.881013321004197</v>
       </c>
       <c r="E295" s="6">
         <v>20</v>
       </c>
       <c r="F295" s="3">
         <f t="shared" si="6"/>
-        <v>53.139473454716168</v>
+        <v>31.104810656803359</v>
       </c>
       <c r="G295" s="1"/>
       <c r="H295" s="8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="296" spans="1:8">
-      <c r="A296" s="1" t="s">
-        <v>25</v>
+      <c r="A296" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="B296" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C296" s="9">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="D296" s="4">
-        <v>117.66158</v>
+        <v>52.267790172084403</v>
       </c>
       <c r="E296" s="6">
         <v>20</v>
       </c>
       <c r="F296" s="3">
         <f t="shared" si="6"/>
-        <v>94.129264000000006</v>
+        <v>41.814232137667524</v>
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B297" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C297" s="9">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D297" s="4">
-        <v>32.019694007464103</v>
+        <v>126.401940695297</v>
       </c>
       <c r="E297" s="6">
         <v>20</v>
       </c>
       <c r="F297" s="3">
         <f t="shared" si="6"/>
-        <v>25.615755205971283</v>
+        <v>101.1215525562376</v>
       </c>
       <c r="G297" s="1"/>
       <c r="H297" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="298" spans="1:8">
-      <c r="A298" s="10" t="s">
-        <v>27</v>
+      <c r="A298" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B298" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C298" s="9">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="D298" s="4">
-        <v>45.581570352003197</v>
+        <v>34.397298925667798</v>
       </c>
       <c r="E298" s="6">
         <v>20</v>
       </c>
       <c r="F298" s="3">
         <f t="shared" si="6"/>
-        <v>36.465256281602556</v>
+        <v>27.517839140534239</v>
       </c>
       <c r="G298" s="1"/>
       <c r="H298" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B299" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C299" s="9">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="D299" s="4">
-        <v>103.274454545455</v>
+        <v>31.755745670756699</v>
       </c>
       <c r="E299" s="6">
         <v>20</v>
       </c>
       <c r="F299" s="3">
         <f t="shared" si="6"/>
-        <v>82.619563636364006</v>
+        <v>25.404596536605361</v>
       </c>
       <c r="G299" s="1"/>
       <c r="H299" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="1" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="B300" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C300" s="9">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="D300" s="4">
-        <v>32.011510416666702</v>
+        <v>85.8098843963852</v>
       </c>
       <c r="E300" s="6">
         <v>20</v>
       </c>
       <c r="F300" s="3">
         <f t="shared" si="6"/>
-        <v>25.609208333333363</v>
+        <v>68.647907517108166</v>
       </c>
       <c r="G300" s="1"/>
       <c r="H300" s="8" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="301" spans="1:8">
-      <c r="A301" s="1" t="s">
-        <v>30</v>
+      <c r="A301" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B301" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C301" s="9">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D301" s="4">
-        <v>41.469765200222</v>
+        <v>51.640695707107703</v>
       </c>
       <c r="E301" s="6">
         <v>20</v>
       </c>
       <c r="F301" s="3">
         <f t="shared" si="6"/>
-        <v>33.1758121601776</v>
+        <v>41.312556565686165</v>
       </c>
       <c r="G301" s="1"/>
       <c r="H301" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="1" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="B302" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C302" s="9">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D302" s="4">
-        <v>98.080272611832598</v>
+        <v>73.009943662951798</v>
       </c>
       <c r="E302" s="6">
         <v>20</v>
       </c>
       <c r="F302" s="3">
         <f t="shared" si="6"/>
-        <v>78.464218089466073</v>
+        <v>58.407954930361441</v>
       </c>
       <c r="G302" s="1"/>
       <c r="H302" s="8" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="303" spans="1:8">
-      <c r="A303" s="10" t="s">
-        <v>31</v>
+      <c r="A303" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="B303" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C303" s="9">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="D303" s="4">
-        <v>44.8543698230323</v>
+        <v>126.401940695297</v>
       </c>
       <c r="E303" s="6">
         <v>20</v>
       </c>
       <c r="F303" s="3">
         <f t="shared" si="6"/>
-        <v>35.883495858425839</v>
+        <v>101.1215525562376</v>
       </c>
       <c r="G303" s="1"/>
-      <c r="H303" s="8" t="s">
-        <v>100</v>
-      </c>
+      <c r="H303" s="8"/>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B304" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C304" s="9">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="D304" s="4">
-        <v>63.363835227272702</v>
+        <v>31.188293255131999</v>
       </c>
       <c r="E304" s="6">
         <v>20</v>
       </c>
       <c r="F304" s="3">
         <f t="shared" si="6"/>
-        <v>50.69106818181816</v>
+        <v>24.950634604105598</v>
       </c>
       <c r="G304" s="1"/>
       <c r="H304" s="8" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="1" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="B305" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C305" s="9">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="D305" s="4">
-        <v>103.274454545455</v>
+        <v>87.665935013964102</v>
       </c>
       <c r="E305" s="6">
         <v>20</v>
       </c>
       <c r="F305" s="3">
         <f t="shared" si="6"/>
-        <v>82.619563636364006</v>
+        <v>70.132748011171287</v>
       </c>
       <c r="G305" s="1"/>
-      <c r="H305" s="8"/>
+      <c r="H305" s="8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B306" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C306" s="9">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="D306" s="4">
-        <v>28.126445652173899</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E306" s="6">
         <v>20</v>
       </c>
       <c r="F306" s="3">
         <f t="shared" si="6"/>
-        <v>22.501156521739119</v>
+        <v>55.482249295774636</v>
       </c>
       <c r="G306" s="1"/>
       <c r="H306" s="8" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B307" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C307" s="9">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="D307" s="4">
-        <v>115.874940343171</v>
+        <v>36.535145325203302</v>
       </c>
       <c r="E307" s="6">
         <v>20</v>
       </c>
       <c r="F307" s="3">
         <f t="shared" si="6"/>
-        <v>92.699952274536798</v>
+        <v>29.228116260162643</v>
       </c>
       <c r="G307" s="1"/>
       <c r="H307" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="308" spans="1:8">
-      <c r="A308" s="1" t="s">
-        <v>35</v>
+      <c r="A308" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="B308" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C308" s="9">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="D308" s="4">
-        <v>64.704009900990101</v>
+        <v>65.116759665642803</v>
       </c>
       <c r="E308" s="6">
         <v>20</v>
       </c>
       <c r="F308" s="3">
         <f t="shared" si="6"/>
-        <v>51.763207920792084</v>
+        <v>52.093407732514244</v>
       </c>
       <c r="G308" s="1"/>
       <c r="H308" s="8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B309" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C309" s="9">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D309" s="4">
-        <v>31.229027243589702</v>
+        <v>72.692134156806901</v>
       </c>
       <c r="E309" s="6">
         <v>20</v>
       </c>
       <c r="F309" s="3">
         <f t="shared" si="6"/>
-        <v>24.98322179487176</v>
+        <v>58.153707325445524</v>
       </c>
       <c r="G309" s="1"/>
       <c r="H309" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="310" spans="1:8">
-      <c r="A310" s="10" t="s">
-        <v>37</v>
+      <c r="A310" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B310" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C310" s="9">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D310" s="4">
-        <v>66.972437992236706</v>
+        <v>118.356012267064</v>
       </c>
       <c r="E310" s="6">
         <v>20</v>
       </c>
       <c r="F310" s="3">
         <f t="shared" si="6"/>
-        <v>53.577950393789365</v>
+        <v>94.684809813651199</v>
       </c>
       <c r="G310" s="1"/>
       <c r="H310" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B311" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C311" s="9">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="D311" s="4">
-        <v>63.363835227272702</v>
+        <v>43.0334627677342</v>
       </c>
       <c r="E311" s="6">
         <v>20</v>
       </c>
       <c r="F311" s="3">
         <f t="shared" si="6"/>
-        <v>50.69106818181816</v>
+        <v>34.426770214187357</v>
       </c>
       <c r="G311" s="1"/>
       <c r="H311" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B312" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C312" s="9">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="D312" s="4">
-        <v>93.173415097909398</v>
+        <v>29.255522727272702</v>
       </c>
       <c r="E312" s="6">
         <v>20</v>
       </c>
       <c r="F312" s="3">
         <f t="shared" si="6"/>
-        <v>74.538732078327513</v>
+        <v>23.404418181818162</v>
       </c>
       <c r="G312" s="1"/>
       <c r="H312" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B313" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C313" s="9">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="D313" s="4">
-        <v>69.129963316404897</v>
+        <v>39.122489596083199</v>
       </c>
       <c r="E313" s="6">
         <v>20</v>
       </c>
       <c r="F313" s="3">
         <f t="shared" si="6"/>
-        <v>55.303970653123919</v>
+        <v>31.297991676866559</v>
       </c>
       <c r="G313" s="1"/>
       <c r="H313" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B314" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C314" s="9">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D314" s="4">
-        <v>27.2976363636364</v>
+        <v>44.091314393939399</v>
       </c>
       <c r="E314" s="6">
         <v>20</v>
       </c>
       <c r="F314" s="3">
         <f t="shared" si="6"/>
-        <v>21.838109090909121</v>
+        <v>35.273051515151522</v>
       </c>
       <c r="G314" s="1"/>
       <c r="H314" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B315" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C315" s="9">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D315" s="4">
-        <v>38.761173333333304</v>
+        <v>138.055726689957</v>
       </c>
       <c r="E315" s="6">
         <v>20</v>
       </c>
       <c r="F315" s="3">
         <f t="shared" si="6"/>
-        <v>31.008938666666644</v>
+        <v>110.4445813519656</v>
       </c>
       <c r="G315" s="1"/>
       <c r="H315" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B316" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C316" s="9">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D316" s="4">
-        <v>36.366624999999999</v>
+        <v>33.228430586413999</v>
       </c>
       <c r="E316" s="6">
         <v>20</v>
       </c>
       <c r="F316" s="3">
         <f t="shared" si="6"/>
-        <v>29.093299999999999</v>
+        <v>26.5827444691312</v>
       </c>
       <c r="G316" s="1"/>
       <c r="H316" s="8" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B317" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C317" s="9"/>
-      <c r="D317" s="4"/>
+        <v>45991</v>
+      </c>
+      <c r="C317" s="9">
+        <v>176</v>
+      </c>
+      <c r="D317" s="4">
+        <v>42.893889259977797</v>
+      </c>
       <c r="E317" s="6">
         <v>20</v>
       </c>
       <c r="F317" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>34.315111407982236</v>
       </c>
       <c r="G317" s="1"/>
       <c r="H317" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="318" spans="1:8">
-      <c r="A318" s="1" t="s">
-        <v>45</v>
+      <c r="A318" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="B318" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C318" s="9">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="D318" s="4">
-        <v>30.1475120048019</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E318" s="6">
         <v>20</v>
       </c>
       <c r="F318" s="3">
         <f t="shared" si="6"/>
-        <v>24.118009603841521</v>
+        <v>55.482249295774636</v>
       </c>
       <c r="G318" s="1"/>
       <c r="H318" s="8" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
     </row>
     <row r="319" spans="1:8">
-      <c r="A319" s="1" t="s">
-        <v>46</v>
+      <c r="A319" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="B319" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C319" s="9">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="D319" s="4">
-        <v>49.737972826087002</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E319" s="6">
         <v>20</v>
       </c>
       <c r="F319" s="3">
         <f t="shared" si="6"/>
-        <v>39.790378260869602</v>
+        <v>55.482249295774636</v>
       </c>
       <c r="G319" s="1"/>
       <c r="H319" s="8" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="320" spans="1:8">
-      <c r="A320" s="10" t="s">
-        <v>47</v>
+      <c r="A320" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B320" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C320" s="9">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="D320" s="4">
-        <v>64.704009900990101</v>
+        <v>35.764634634387299</v>
       </c>
       <c r="E320" s="6">
         <v>20</v>
       </c>
       <c r="F320" s="3">
         <f t="shared" si="6"/>
-        <v>51.763207920792084</v>
+        <v>28.61170770750984</v>
       </c>
       <c r="G320" s="1"/>
       <c r="H320" s="8" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="321" spans="1:8">
-      <c r="A321" s="10" t="s">
-        <v>48</v>
+      <c r="A321" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="B321" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C321" s="9">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D321" s="4">
-        <v>64.704009900990101</v>
+        <v>53.564347826086902</v>
       </c>
       <c r="E321" s="6">
         <v>20</v>
       </c>
       <c r="F321" s="3">
         <f t="shared" si="6"/>
-        <v>51.763207920792084</v>
+        <v>42.85147826086952</v>
       </c>
       <c r="G321" s="1"/>
       <c r="H321" s="8" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B322" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C322" s="9">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="D322" s="4">
-        <v>29.926879464285701</v>
+        <v>35.448980113636303</v>
       </c>
       <c r="E322" s="6">
         <v>20</v>
       </c>
       <c r="F322" s="3">
         <f t="shared" si="6"/>
-        <v>23.941503571428562</v>
+        <v>28.359184090909043</v>
       </c>
       <c r="G322" s="1"/>
       <c r="H322" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B323" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C323" s="9">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="D323" s="4">
-        <v>48.371413043478199</v>
+        <v>47.900705877298499</v>
       </c>
       <c r="E323" s="6">
         <v>20</v>
       </c>
       <c r="F323" s="3">
         <f t="shared" si="6"/>
-        <v>38.697130434782558</v>
+        <v>38.320564701838798</v>
       </c>
       <c r="G323" s="1"/>
       <c r="H323" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B324" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C324" s="9">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="D324" s="4">
-        <v>29.447552884615401</v>
+        <v>35.043873962999797</v>
       </c>
       <c r="E324" s="6">
         <v>20</v>
       </c>
       <c r="F324" s="3">
         <f t="shared" si="6"/>
-        <v>23.558042307692322</v>
+        <v>28.035099170399839</v>
       </c>
       <c r="G324" s="1"/>
       <c r="H324" s="8" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B325" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C325" s="9">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="D325" s="4">
-        <v>46.492445652173899</v>
+        <v>34.037200887328602</v>
       </c>
       <c r="E325" s="6">
         <v>20</v>
       </c>
       <c r="F325" s="3">
         <f t="shared" si="6"/>
-        <v>37.193956521739118</v>
+        <v>27.22976070986288</v>
       </c>
       <c r="G325" s="1"/>
       <c r="H325" s="8" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="1" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="B326" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C326" s="9">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D326" s="4">
-        <v>32.176956559829101</v>
+        <v>126.401940695297</v>
       </c>
       <c r="E326" s="6">
         <v>20</v>
       </c>
       <c r="F326" s="3">
         <f t="shared" si="6"/>
-        <v>25.741565247863281</v>
+        <v>101.1215525562376</v>
       </c>
       <c r="G326" s="1"/>
-      <c r="H326" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="H326" s="8"/>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B327" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C327" s="9">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="D327" s="4">
-        <v>31.346785496470499</v>
+        <v>34.774626321423803</v>
       </c>
       <c r="E327" s="6">
         <v>20</v>
       </c>
       <c r="F327" s="3">
         <f t="shared" si="6"/>
-        <v>25.077428397176398</v>
+        <v>27.819701057139042</v>
       </c>
       <c r="G327" s="1"/>
       <c r="H327" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B328" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C328" s="9">
         <v>152</v>
       </c>
-      <c r="B328" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C328" s="9">
-        <v>13</v>
-      </c>
       <c r="D328" s="4">
-        <v>103.274454545455</v>
+        <v>32.023106772613403</v>
       </c>
       <c r="E328" s="6">
         <v>20</v>
       </c>
       <c r="F328" s="3">
         <f t="shared" si="6"/>
-        <v>82.619563636364006</v>
+        <v>25.618485418090721</v>
       </c>
       <c r="G328" s="1"/>
-      <c r="H328" s="8"/>
+      <c r="H328" s="8" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B329" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C329" s="9">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="D329" s="4">
-        <v>32.350611342992899</v>
+        <v>34.662226704545397</v>
       </c>
       <c r="E329" s="6">
         <v>20</v>
       </c>
       <c r="F329" s="3">
         <f t="shared" si="6"/>
-        <v>25.880489074394319</v>
+        <v>27.729781363636317</v>
       </c>
       <c r="G329" s="1"/>
       <c r="H329" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B330" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C330" s="9">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="D330" s="4">
-        <v>30.421940789473702</v>
+        <v>41.266697646467001</v>
       </c>
       <c r="E330" s="6">
         <v>20</v>
       </c>
       <c r="F330" s="3">
         <f t="shared" si="6"/>
-        <v>24.337552631578962</v>
+        <v>33.013358117173603</v>
       </c>
       <c r="G330" s="1"/>
       <c r="H330" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B331" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C331" s="9">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D331" s="4">
-        <v>32.660236742424303</v>
+        <v>32.388312499999998</v>
       </c>
       <c r="E331" s="6">
         <v>20</v>
       </c>
       <c r="F331" s="3">
         <f t="shared" si="6"/>
-        <v>26.128189393939444</v>
+        <v>25.910649999999997</v>
       </c>
       <c r="G331" s="1"/>
       <c r="H331" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B332" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C332" s="9">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D332" s="4">
-        <v>40.3757801390529</v>
+        <v>44.936636595744702</v>
       </c>
       <c r="E332" s="6">
         <v>20</v>
       </c>
       <c r="F332" s="3">
         <f t="shared" si="6"/>
-        <v>32.300624111242321</v>
+        <v>35.949309276595763</v>
       </c>
       <c r="G332" s="1"/>
       <c r="H332" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B333" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C333" s="9">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="D333" s="4">
-        <v>34.434678571428599</v>
+        <v>46.078225000000003</v>
       </c>
       <c r="E333" s="6">
         <v>20</v>
       </c>
       <c r="F333" s="3">
         <f t="shared" si="6"/>
-        <v>27.547742857142879</v>
+        <v>36.862580000000001</v>
       </c>
       <c r="G333" s="1"/>
       <c r="H333" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B334" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C334" s="9">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="D334" s="4">
-        <v>38.463169312169299</v>
+        <v>38.524439547383999</v>
       </c>
       <c r="E334" s="6">
         <v>20</v>
       </c>
       <c r="F334" s="3">
         <f t="shared" si="6"/>
-        <v>30.770535449735441</v>
+        <v>30.8195516379072</v>
       </c>
       <c r="G334" s="1"/>
       <c r="H334" s="8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B335" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C335" s="9">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D335" s="4">
-        <v>40.651797619047599</v>
+        <v>55.400851106519198</v>
       </c>
       <c r="E335" s="6">
         <v>20</v>
       </c>
       <c r="F335" s="3">
         <f t="shared" si="6"/>
-        <v>32.521438095238082</v>
+        <v>44.32068088521536</v>
       </c>
       <c r="G335" s="1"/>
       <c r="H335" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B336" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C336" s="9">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="D336" s="4">
-        <v>41.4668669481606</v>
+        <v>122.259504428672</v>
       </c>
       <c r="E336" s="6">
         <v>20</v>
       </c>
       <c r="F336" s="3">
         <f t="shared" si="6"/>
-        <v>33.173493558528477</v>
+        <v>97.807603542937599</v>
       </c>
       <c r="G336" s="1"/>
       <c r="H336" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="337" spans="1:8">
       <c r="A337" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B337" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C337" s="9">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="D337" s="4">
-        <v>56.425414381099102</v>
+        <v>42.763601458579302</v>
       </c>
       <c r="E337" s="6">
         <v>20</v>
       </c>
       <c r="F337" s="3">
-        <f t="shared" si="6"/>
-        <v>45.140331504879285</v>
+        <f t="shared" ref="F337:F342" si="7">D337-(D337*E337)/100</f>
+        <v>34.210881166863444</v>
       </c>
       <c r="G337" s="1"/>
       <c r="H337" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="338" spans="1:8">
-      <c r="A338" s="1" t="s">
-        <v>64</v>
+      <c r="A338" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="B338" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C338" s="9">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D338" s="4">
-        <v>107.8525579528</v>
+        <v>71.2247082005441</v>
       </c>
       <c r="E338" s="6">
         <v>20</v>
       </c>
       <c r="F338" s="3">
-        <f t="shared" si="6"/>
-        <v>86.282046362239996</v>
+        <f t="shared" si="7"/>
+        <v>56.97976656043528</v>
       </c>
       <c r="G338" s="1"/>
-      <c r="H338" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="H338" s="8"/>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="B339" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C339" s="9">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D339" s="4">
-        <v>38.006612446581201</v>
+        <v>29.255522727272702</v>
       </c>
       <c r="E339" s="6">
         <v>20</v>
       </c>
       <c r="F339" s="3">
-        <f t="shared" ref="F339:F344" si="7">D339-(D339*E339)/100</f>
-        <v>30.405289957264962</v>
+        <f t="shared" si="7"/>
+        <v>23.404418181818162</v>
       </c>
       <c r="G339" s="1"/>
-      <c r="H339" s="8" t="s">
-        <v>131</v>
-      </c>
+      <c r="H339" s="8"/>
     </row>
     <row r="340" spans="1:8">
-      <c r="A340" s="10" t="s">
-        <v>134</v>
+      <c r="A340" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B340" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C340" s="9">
-        <v>80</v>
-      </c>
-      <c r="D340" s="4">
-        <v>89.243906249999995</v>
-      </c>
+        <v>45991</v>
+      </c>
+      <c r="C340" s="9"/>
+      <c r="D340" s="4"/>
       <c r="E340" s="6">
         <v>20</v>
       </c>
       <c r="F340" s="3">
         <f t="shared" si="7"/>
-        <v>71.395124999999993</v>
+        <v>0</v>
       </c>
       <c r="G340" s="1"/>
       <c r="H340" s="8"/>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B341" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C341" s="9">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="D341" s="4">
-        <v>27.2976363636364</v>
+        <v>43.976640382483303</v>
       </c>
       <c r="E341" s="6">
         <v>20</v>
       </c>
       <c r="F341" s="3">
         <f t="shared" si="7"/>
-        <v>21.838109090909121</v>
+        <v>35.181312305986644</v>
       </c>
       <c r="G341" s="1"/>
       <c r="H341" s="8"/>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B342" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C342" s="9"/>
-      <c r="D342" s="4"/>
+        <v>45991</v>
+      </c>
+      <c r="C342" s="9">
+        <v>24</v>
+      </c>
+      <c r="D342" s="4">
+        <v>178.00537837991399</v>
+      </c>
       <c r="E342" s="6">
         <v>20</v>
       </c>
       <c r="F342" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>142.40430270393119</v>
       </c>
       <c r="G342" s="1"/>
       <c r="H342" s="8"/>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="1" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B343" s="7">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C343" s="9">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D343" s="4">
-        <v>50.264938719342197</v>
+        <v>126.401940695297</v>
       </c>
       <c r="E343" s="6">
         <v>20</v>
       </c>
       <c r="F343" s="3">
-        <f t="shared" si="7"/>
-        <v>40.211950975473755</v>
+        <f t="shared" ref="F343" si="8">D343-(D343*E343)/100</f>
+        <v>101.1215525562376</v>
       </c>
       <c r="G343" s="1"/>
       <c r="H343" s="8"/>
-    </row>
-    <row r="344" spans="1:8">
-      <c r="A344" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B344" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C344" s="9"/>
-      <c r="D344" s="4"/>
-      <c r="E344" s="6">
-        <v>20</v>
-      </c>
-      <c r="F344" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G344" s="1"/>
-      <c r="H344" s="8"/>
-    </row>
-    <row r="345" spans="1:8">
-      <c r="A345" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B345" s="7">
-        <v>45979</v>
-      </c>
-      <c r="C345" s="9">
-        <v>37</v>
-      </c>
-      <c r="D345" s="4">
-        <v>103.274454545455</v>
-      </c>
-      <c r="E345" s="6">
-        <v>20</v>
-      </c>
-      <c r="F345" s="3">
-        <f t="shared" ref="F345" si="8">D345-(D345*E345)/100</f>
-        <v>82.619563636364006</v>
-      </c>
-      <c r="G345" s="1"/>
-      <c r="H345" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G272"/>
@@ -9697,7 +9665,7 @@
     <hyperlink ref="H283" r:id="rId265"/>
     <hyperlink ref="H284" r:id="rId266"/>
     <hyperlink ref="H285" r:id="rId267"/>
-    <hyperlink ref="H286" r:id="rId268"/>
+    <hyperlink ref="H287" r:id="rId268"/>
     <hyperlink ref="H288" r:id="rId269"/>
     <hyperlink ref="H289" r:id="rId270"/>
     <hyperlink ref="H290" r:id="rId271"/>
@@ -9710,10 +9678,10 @@
     <hyperlink ref="H297" r:id="rId278"/>
     <hyperlink ref="H298" r:id="rId279"/>
     <hyperlink ref="H299" r:id="rId280"/>
-    <hyperlink ref="H300" r:id="rId281"/>
-    <hyperlink ref="H301" r:id="rId282"/>
-    <hyperlink ref="H303" r:id="rId283"/>
-    <hyperlink ref="H304" r:id="rId284"/>
+    <hyperlink ref="H301" r:id="rId281"/>
+    <hyperlink ref="H302" r:id="rId282"/>
+    <hyperlink ref="H304" r:id="rId283"/>
+    <hyperlink ref="H305" r:id="rId284"/>
     <hyperlink ref="H306" r:id="rId285"/>
     <hyperlink ref="H307" r:id="rId286"/>
     <hyperlink ref="H308" r:id="rId287"/>
@@ -9734,8 +9702,8 @@
     <hyperlink ref="H323" r:id="rId302"/>
     <hyperlink ref="H324" r:id="rId303"/>
     <hyperlink ref="H325" r:id="rId304"/>
-    <hyperlink ref="H326" r:id="rId305"/>
-    <hyperlink ref="H327" r:id="rId306"/>
+    <hyperlink ref="H327" r:id="rId305"/>
+    <hyperlink ref="H328" r:id="rId306"/>
     <hyperlink ref="H329" r:id="rId307"/>
     <hyperlink ref="H330" r:id="rId308"/>
     <hyperlink ref="H331" r:id="rId309"/>
@@ -9745,9 +9713,7 @@
     <hyperlink ref="H335" r:id="rId313"/>
     <hyperlink ref="H336" r:id="rId314"/>
     <hyperlink ref="H337" r:id="rId315"/>
-    <hyperlink ref="H338" r:id="rId316"/>
-    <hyperlink ref="H339" r:id="rId317"/>
-    <hyperlink ref="H302" r:id="rId318" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="H300" r:id="rId316" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="155">
   <si>
     <t>Tecnico</t>
   </si>
@@ -481,6 +481,9 @@
   </si>
   <si>
     <t>IRTE0000115 - LA PIANA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
   </si>
 </sst>
 </file>
@@ -900,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H414"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -7678,14 +7681,14 @@
         <v>128</v>
       </c>
       <c r="D274" s="4">
-        <v>37.811625817847897</v>
+        <v>40.800815245361299</v>
       </c>
       <c r="E274" s="6">
         <v>20</v>
       </c>
       <c r="F274" s="3">
         <f t="shared" si="6"/>
-        <v>30.249300654278318</v>
+        <v>32.640652196289039</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>67</v>
@@ -7705,14 +7708,14 @@
         <v>48</v>
       </c>
       <c r="D275" s="4">
-        <v>134.20636002328999</v>
+        <v>135.02601646500801</v>
       </c>
       <c r="E275" s="6">
         <v>20</v>
       </c>
       <c r="F275" s="3">
         <f t="shared" si="6"/>
-        <v>107.36508801863199</v>
+        <v>108.02081317200641</v>
       </c>
       <c r="G275" s="1"/>
       <c r="H275" s="8"/>
@@ -7728,14 +7731,14 @@
         <v>141</v>
       </c>
       <c r="D276" s="4">
-        <v>31.485793439459201</v>
+        <v>31.3221358219987</v>
       </c>
       <c r="E276" s="6">
         <v>20</v>
       </c>
       <c r="F276" s="3">
         <f t="shared" si="6"/>
-        <v>25.18863475156736</v>
+        <v>25.057708657598958</v>
       </c>
       <c r="G276" s="1"/>
       <c r="H276" s="8" t="s">
@@ -7803,14 +7806,14 @@
         <v>135</v>
       </c>
       <c r="D279" s="4">
-        <v>39.744967680608397</v>
+        <v>39.740131178707202</v>
       </c>
       <c r="E279" s="6">
         <v>20</v>
       </c>
       <c r="F279" s="3">
         <f t="shared" si="6"/>
-        <v>31.795974144486717</v>
+        <v>31.792104942965761</v>
       </c>
       <c r="G279" s="1"/>
       <c r="H279" s="8" t="s">
@@ -7853,14 +7856,14 @@
         <v>159</v>
       </c>
       <c r="D281" s="4">
-        <v>39.744967680608397</v>
+        <v>39.740131178707202</v>
       </c>
       <c r="E281" s="6">
         <v>20</v>
       </c>
       <c r="F281" s="3">
         <f t="shared" si="6"/>
-        <v>31.795974144486717</v>
+        <v>31.792104942965761</v>
       </c>
       <c r="G281" s="1"/>
       <c r="H281" s="8" t="s">
@@ -7878,14 +7881,14 @@
         <v>182</v>
       </c>
       <c r="D282" s="4">
-        <v>56.329923570077497</v>
+        <v>57.692955767948099</v>
       </c>
       <c r="E282" s="6">
         <v>20</v>
       </c>
       <c r="F282" s="3">
         <f t="shared" si="6"/>
-        <v>45.063938856061995</v>
+        <v>46.154364614358478</v>
       </c>
       <c r="G282" s="1"/>
       <c r="H282" s="8" t="s">
@@ -7903,14 +7906,14 @@
         <v>182</v>
       </c>
       <c r="D283" s="4">
-        <v>56.329923570077497</v>
+        <v>57.692955767948099</v>
       </c>
       <c r="E283" s="6">
         <v>20</v>
       </c>
       <c r="F283" s="3">
         <f t="shared" si="6"/>
-        <v>45.063938856061995</v>
+        <v>46.154364614358478</v>
       </c>
       <c r="G283" s="1"/>
       <c r="H283" s="8" t="s">
@@ -7928,14 +7931,14 @@
         <v>160</v>
       </c>
       <c r="D284" s="4">
-        <v>42.655002724037701</v>
+        <v>43.218896010424999</v>
       </c>
       <c r="E284" s="6">
         <v>20</v>
       </c>
       <c r="F284" s="3">
         <f t="shared" si="6"/>
-        <v>34.12400217923016</v>
+        <v>34.575116808339999</v>
       </c>
       <c r="G284" s="1"/>
       <c r="H284" s="8" t="s">
@@ -7953,14 +7956,14 @@
         <v>168</v>
       </c>
       <c r="D285" s="4">
-        <v>30.141696688279701</v>
+        <v>30.141236069051001</v>
       </c>
       <c r="E285" s="6">
         <v>20</v>
       </c>
       <c r="F285" s="3">
         <f t="shared" si="6"/>
-        <v>24.113357350623762</v>
+        <v>24.1129888552408</v>
       </c>
       <c r="G285" s="1"/>
       <c r="H285" s="8" t="s">
@@ -7978,14 +7981,14 @@
         <v>61</v>
       </c>
       <c r="D286" s="4">
-        <v>118.816192483051</v>
+        <v>123.08915557266199</v>
       </c>
       <c r="E286" s="6">
         <v>20</v>
       </c>
       <c r="F286" s="3">
         <f t="shared" si="6"/>
-        <v>95.052953986440798</v>
+        <v>98.471324458129601</v>
       </c>
       <c r="G286" s="1"/>
       <c r="H286" s="8"/>
@@ -8051,14 +8054,14 @@
         <v>172</v>
       </c>
       <c r="D289" s="4">
-        <v>33.499415518672699</v>
+        <v>33.496389610872797</v>
       </c>
       <c r="E289" s="6">
         <v>20</v>
       </c>
       <c r="F289" s="3">
         <f t="shared" si="6"/>
-        <v>26.79953241493816</v>
+        <v>26.797111688698237</v>
       </c>
       <c r="G289" s="1"/>
       <c r="H289" s="8" t="s">
@@ -8101,14 +8104,14 @@
         <v>129</v>
       </c>
       <c r="D291" s="4">
-        <v>61.609753215045302</v>
+        <v>61.601600296300099</v>
       </c>
       <c r="E291" s="6">
         <v>20</v>
       </c>
       <c r="F291" s="3">
         <f t="shared" si="6"/>
-        <v>49.287802572036242</v>
+        <v>49.281280237040079</v>
       </c>
       <c r="G291" s="1"/>
       <c r="H291" s="8" t="s">
@@ -8151,14 +8154,14 @@
         <v>139</v>
       </c>
       <c r="D293" s="4">
-        <v>64.038399660655003</v>
+        <v>64.034912881533003</v>
       </c>
       <c r="E293" s="6">
         <v>20</v>
       </c>
       <c r="F293" s="3">
         <f t="shared" si="6"/>
-        <v>51.230719728524001</v>
+        <v>51.227930305226401</v>
       </c>
       <c r="G293" s="1"/>
       <c r="H293" s="8" t="s">
@@ -8176,14 +8179,14 @@
         <v>86</v>
       </c>
       <c r="D294" s="4">
-        <v>88.3928023255814</v>
+        <v>87.691933139534896</v>
       </c>
       <c r="E294" s="6">
         <v>20</v>
       </c>
       <c r="F294" s="3">
         <f t="shared" si="6"/>
-        <v>70.714241860465123</v>
+        <v>70.153546511627923</v>
       </c>
       <c r="G294" s="1"/>
       <c r="H294" s="8" t="s">
@@ -8201,14 +8204,14 @@
         <v>160</v>
       </c>
       <c r="D295" s="4">
-        <v>38.881013321004197</v>
+        <v>38.876902294388202</v>
       </c>
       <c r="E295" s="6">
         <v>20</v>
       </c>
       <c r="F295" s="3">
         <f t="shared" si="6"/>
-        <v>31.104810656803359</v>
+        <v>31.10152183551056</v>
       </c>
       <c r="G295" s="1"/>
       <c r="H295" s="8" t="s">
@@ -8226,14 +8229,14 @@
         <v>139</v>
       </c>
       <c r="D296" s="4">
-        <v>52.267790172084403</v>
+        <v>52.252847876867698</v>
       </c>
       <c r="E296" s="6">
         <v>20</v>
       </c>
       <c r="F296" s="3">
         <f t="shared" si="6"/>
-        <v>41.814232137667524</v>
+        <v>41.802278301494155</v>
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="8" t="s">
@@ -8251,14 +8254,14 @@
         <v>117</v>
       </c>
       <c r="D297" s="4">
-        <v>126.401940695297</v>
+        <v>131.319879345603</v>
       </c>
       <c r="E297" s="6">
         <v>20</v>
       </c>
       <c r="F297" s="3">
         <f t="shared" si="6"/>
-        <v>101.1215525562376</v>
+        <v>105.0559034764824</v>
       </c>
       <c r="G297" s="1"/>
       <c r="H297" s="8" t="s">
@@ -8301,14 +8304,14 @@
         <v>156</v>
       </c>
       <c r="D299" s="4">
-        <v>31.755745670756699</v>
+        <v>31.601682689636799</v>
       </c>
       <c r="E299" s="6">
         <v>20</v>
       </c>
       <c r="F299" s="3">
         <f t="shared" si="6"/>
-        <v>25.404596536605361</v>
+        <v>25.281346151709439</v>
       </c>
       <c r="G299" s="1"/>
       <c r="H299" s="8" t="s">
@@ -8326,14 +8329,14 @@
         <v>42</v>
       </c>
       <c r="D300" s="4">
-        <v>85.8098843963852</v>
+        <v>86.950255825442696</v>
       </c>
       <c r="E300" s="6">
         <v>20</v>
       </c>
       <c r="F300" s="3">
         <f t="shared" si="6"/>
-        <v>68.647907517108166</v>
+        <v>69.56020466035416</v>
       </c>
       <c r="G300" s="1"/>
       <c r="H300" s="8" t="s">
@@ -8351,14 +8354,14 @@
         <v>141</v>
       </c>
       <c r="D301" s="4">
-        <v>51.640695707107703</v>
+        <v>51.625046106299003</v>
       </c>
       <c r="E301" s="6">
         <v>20</v>
       </c>
       <c r="F301" s="3">
         <f t="shared" si="6"/>
-        <v>41.312556565686165</v>
+        <v>41.300036885039205</v>
       </c>
       <c r="G301" s="1"/>
       <c r="H301" s="8" t="s">
@@ -8376,14 +8379,14 @@
         <v>104</v>
       </c>
       <c r="D302" s="4">
-        <v>73.009943662951798</v>
+        <v>73.388246636052401</v>
       </c>
       <c r="E302" s="6">
         <v>20</v>
       </c>
       <c r="F302" s="3">
         <f t="shared" si="6"/>
-        <v>58.407954930361441</v>
+        <v>58.710597308841919</v>
       </c>
       <c r="G302" s="1"/>
       <c r="H302" s="8" t="s">
@@ -8401,14 +8404,14 @@
         <v>16</v>
       </c>
       <c r="D303" s="4">
-        <v>126.401940695297</v>
+        <v>131.319879345603</v>
       </c>
       <c r="E303" s="6">
         <v>20</v>
       </c>
       <c r="F303" s="3">
         <f t="shared" si="6"/>
-        <v>101.1215525562376</v>
+        <v>105.0559034764824</v>
       </c>
       <c r="G303" s="1"/>
       <c r="H303" s="8"/>
@@ -8449,14 +8452,14 @@
         <v>166</v>
       </c>
       <c r="D305" s="4">
-        <v>87.665935013964102</v>
+        <v>86.971927575464505</v>
       </c>
       <c r="E305" s="6">
         <v>20</v>
       </c>
       <c r="F305" s="3">
         <f t="shared" si="6"/>
-        <v>70.132748011171287</v>
+        <v>69.577542060371599</v>
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="8" t="s">
@@ -8524,14 +8527,14 @@
         <v>163</v>
       </c>
       <c r="D308" s="4">
-        <v>65.116759665642803</v>
+        <v>65.114581459390905</v>
       </c>
       <c r="E308" s="6">
         <v>20</v>
       </c>
       <c r="F308" s="3">
         <f t="shared" si="6"/>
-        <v>52.093407732514244</v>
+        <v>52.091665167512723</v>
       </c>
       <c r="G308" s="1"/>
       <c r="H308" s="8" t="s">
@@ -8549,14 +8552,14 @@
         <v>112</v>
       </c>
       <c r="D309" s="4">
-        <v>72.692134156806901</v>
+        <v>73.043415488971604</v>
       </c>
       <c r="E309" s="6">
         <v>20</v>
       </c>
       <c r="F309" s="3">
         <f t="shared" si="6"/>
-        <v>58.153707325445524</v>
+        <v>58.434732391177285</v>
       </c>
       <c r="G309" s="1"/>
       <c r="H309" s="8" t="s">
@@ -8574,14 +8577,14 @@
         <v>110</v>
       </c>
       <c r="D310" s="4">
-        <v>118.356012267064</v>
+        <v>122.86082778001099</v>
       </c>
       <c r="E310" s="6">
         <v>20</v>
       </c>
       <c r="F310" s="3">
         <f t="shared" si="6"/>
-        <v>94.684809813651199</v>
+        <v>98.288662224008789</v>
       </c>
       <c r="G310" s="1"/>
       <c r="H310" s="8" t="s">
@@ -8599,14 +8602,14 @@
         <v>156</v>
       </c>
       <c r="D311" s="4">
-        <v>43.0334627677342</v>
+        <v>42.955545565289299</v>
       </c>
       <c r="E311" s="6">
         <v>20</v>
       </c>
       <c r="F311" s="3">
         <f t="shared" si="6"/>
-        <v>34.426770214187357</v>
+        <v>34.364436452231438</v>
       </c>
       <c r="G311" s="1"/>
       <c r="H311" s="8" t="s">
@@ -8624,14 +8627,14 @@
         <v>154</v>
       </c>
       <c r="D312" s="4">
-        <v>29.255522727272702</v>
+        <v>29.326201298701299</v>
       </c>
       <c r="E312" s="6">
         <v>20</v>
       </c>
       <c r="F312" s="3">
         <f t="shared" si="6"/>
-        <v>23.404418181818162</v>
+        <v>23.460961038961038</v>
       </c>
       <c r="G312" s="1"/>
       <c r="H312" s="8" t="s">
@@ -8649,14 +8652,14 @@
         <v>152</v>
       </c>
       <c r="D313" s="4">
-        <v>39.122489596083199</v>
+        <v>39.0856017441861</v>
       </c>
       <c r="E313" s="6">
         <v>20</v>
       </c>
       <c r="F313" s="3">
         <f t="shared" si="6"/>
-        <v>31.297991676866559</v>
+        <v>31.268481395348878</v>
       </c>
       <c r="G313" s="1"/>
       <c r="H313" s="8" t="s">
@@ -8699,14 +8702,14 @@
         <v>48</v>
       </c>
       <c r="D315" s="4">
-        <v>138.055726689957</v>
+        <v>138.87538313167499</v>
       </c>
       <c r="E315" s="6">
         <v>20</v>
       </c>
       <c r="F315" s="3">
         <f t="shared" si="6"/>
-        <v>110.4445813519656</v>
+        <v>111.10030650534</v>
       </c>
       <c r="G315" s="1"/>
       <c r="H315" s="8" t="s">
@@ -8949,14 +8952,14 @@
         <v>176</v>
       </c>
       <c r="D325" s="4">
-        <v>34.037200887328602</v>
+        <v>34.0364644402894</v>
       </c>
       <c r="E325" s="6">
         <v>20</v>
       </c>
       <c r="F325" s="3">
         <f t="shared" si="6"/>
-        <v>27.22976070986288</v>
+        <v>27.22917155223152</v>
       </c>
       <c r="G325" s="1"/>
       <c r="H325" s="8" t="s">
@@ -8974,14 +8977,14 @@
         <v>13</v>
       </c>
       <c r="D326" s="4">
-        <v>126.401940695297</v>
+        <v>131.319879345603</v>
       </c>
       <c r="E326" s="6">
         <v>20</v>
       </c>
       <c r="F326" s="3">
         <f t="shared" si="6"/>
-        <v>101.1215525562376</v>
+        <v>105.0559034764824</v>
       </c>
       <c r="G326" s="1"/>
       <c r="H326" s="8"/>
@@ -9072,14 +9075,14 @@
         <v>160</v>
       </c>
       <c r="D330" s="4">
-        <v>41.266697646467001</v>
+        <v>41.537577078982302</v>
       </c>
       <c r="E330" s="6">
         <v>20</v>
       </c>
       <c r="F330" s="3">
         <f t="shared" si="6"/>
-        <v>33.013358117173603</v>
+        <v>33.230061663185843</v>
       </c>
       <c r="G330" s="1"/>
       <c r="H330" s="8" t="s">
@@ -9097,14 +9100,14 @@
         <v>128</v>
       </c>
       <c r="D331" s="4">
-        <v>32.388312499999998</v>
+        <v>32.718628906249997</v>
       </c>
       <c r="E331" s="6">
         <v>20</v>
       </c>
       <c r="F331" s="3">
         <f t="shared" si="6"/>
-        <v>25.910649999999997</v>
+        <v>26.174903124999997</v>
       </c>
       <c r="G331" s="1"/>
       <c r="H331" s="8" t="s">
@@ -9122,14 +9125,14 @@
         <v>120</v>
       </c>
       <c r="D332" s="4">
-        <v>44.936636595744702</v>
+        <v>45.014359929077997</v>
       </c>
       <c r="E332" s="6">
         <v>20</v>
       </c>
       <c r="F332" s="3">
         <f t="shared" si="6"/>
-        <v>35.949309276595763</v>
+        <v>36.011487943262395</v>
       </c>
       <c r="G332" s="1"/>
       <c r="H332" s="8" t="s">
@@ -9147,14 +9150,14 @@
         <v>152</v>
       </c>
       <c r="D333" s="4">
-        <v>46.078225000000003</v>
+        <v>46.161499999999997</v>
       </c>
       <c r="E333" s="6">
         <v>20</v>
       </c>
       <c r="F333" s="3">
         <f t="shared" si="6"/>
-        <v>36.862580000000001</v>
+        <v>36.929199999999994</v>
       </c>
       <c r="G333" s="1"/>
       <c r="H333" s="8" t="s">
@@ -9197,14 +9200,14 @@
         <v>120</v>
       </c>
       <c r="D335" s="4">
-        <v>55.400851106519198</v>
+        <v>58.903540317882197</v>
       </c>
       <c r="E335" s="6">
         <v>20</v>
       </c>
       <c r="F335" s="3">
         <f t="shared" si="6"/>
-        <v>44.32068088521536</v>
+        <v>47.122832254305756</v>
       </c>
       <c r="G335" s="1"/>
       <c r="H335" s="8" t="s">
@@ -9222,14 +9225,14 @@
         <v>29</v>
       </c>
       <c r="D336" s="4">
-        <v>122.259504428672</v>
+        <v>124.950204349591</v>
       </c>
       <c r="E336" s="6">
         <v>20</v>
       </c>
       <c r="F336" s="3">
         <f t="shared" si="6"/>
-        <v>97.807603542937599</v>
+        <v>99.960163479672801</v>
       </c>
       <c r="G336" s="1"/>
       <c r="H336" s="8" t="s">
@@ -9272,14 +9275,14 @@
         <v>144</v>
       </c>
       <c r="D338" s="4">
-        <v>71.2247082005441</v>
+        <v>71.206216137052095</v>
       </c>
       <c r="E338" s="6">
         <v>20</v>
       </c>
       <c r="F338" s="3">
         <f t="shared" si="7"/>
-        <v>56.97976656043528</v>
+        <v>56.964972909641673</v>
       </c>
       <c r="G338" s="1"/>
       <c r="H338" s="8"/>
@@ -9295,14 +9298,14 @@
         <v>154</v>
       </c>
       <c r="D339" s="4">
-        <v>29.255522727272702</v>
+        <v>29.326201298701299</v>
       </c>
       <c r="E339" s="6">
         <v>20</v>
       </c>
       <c r="F339" s="3">
         <f t="shared" si="7"/>
-        <v>23.404418181818162</v>
+        <v>23.460961038961038</v>
       </c>
       <c r="G339" s="1"/>
       <c r="H339" s="8"/>
@@ -9360,14 +9363,14 @@
         <v>24</v>
       </c>
       <c r="D342" s="4">
-        <v>178.00537837991399</v>
+        <v>179.64469126334899</v>
       </c>
       <c r="E342" s="6">
         <v>20</v>
       </c>
       <c r="F342" s="3">
         <f t="shared" si="7"/>
-        <v>142.40430270393119</v>
+        <v>143.71575301067918</v>
       </c>
       <c r="G342" s="1"/>
       <c r="H342" s="8"/>
@@ -9383,17 +9386,1752 @@
         <v>37</v>
       </c>
       <c r="D343" s="4">
-        <v>126.401940695297</v>
+        <v>131.319879345603</v>
       </c>
       <c r="E343" s="6">
         <v>20</v>
       </c>
       <c r="F343" s="3">
-        <f t="shared" ref="F343" si="8">D343-(D343*E343)/100</f>
-        <v>101.1215525562376</v>
+        <f t="shared" ref="F343:F406" si="8">D343-(D343*E343)/100</f>
+        <v>105.0559034764824</v>
       </c>
       <c r="G343" s="1"/>
       <c r="H343" s="8"/>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B344" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C344" s="9">
+        <v>116</v>
+      </c>
+      <c r="D344" s="12">
+        <v>35.1365432098765</v>
+      </c>
+      <c r="E344" s="13">
+        <v>20</v>
+      </c>
+      <c r="F344" s="14">
+        <f t="shared" si="8"/>
+        <v>28.109234567901201</v>
+      </c>
+      <c r="G344" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H344" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B345" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C345" s="9">
+        <v>29</v>
+      </c>
+      <c r="D345" s="4">
+        <v>48.984647486176499</v>
+      </c>
+      <c r="E345" s="6">
+        <v>20</v>
+      </c>
+      <c r="F345" s="3">
+        <f t="shared" si="8"/>
+        <v>39.187717988941202</v>
+      </c>
+      <c r="G345" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H345" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B346" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C346" s="9">
+        <v>104</v>
+      </c>
+      <c r="D346" s="4">
+        <v>18.3408644018151</v>
+      </c>
+      <c r="E346" s="6">
+        <v>20</v>
+      </c>
+      <c r="F346" s="3">
+        <f t="shared" si="8"/>
+        <v>14.67269152145208</v>
+      </c>
+      <c r="G346" s="1"/>
+      <c r="H346" s="8"/>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B347" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C347" s="9">
+        <v>97</v>
+      </c>
+      <c r="D347" s="4">
+        <v>27.686624270940701</v>
+      </c>
+      <c r="E347" s="6">
+        <v>20</v>
+      </c>
+      <c r="F347" s="3">
+        <f t="shared" si="8"/>
+        <v>22.149299416752562</v>
+      </c>
+      <c r="G347" s="1"/>
+      <c r="H347" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B348" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C348" s="9">
+        <v>72</v>
+      </c>
+      <c r="D348" s="4">
+        <v>93.622258278145694</v>
+      </c>
+      <c r="E348" s="6">
+        <v>20</v>
+      </c>
+      <c r="F348" s="3">
+        <f t="shared" si="8"/>
+        <v>74.897806622516555</v>
+      </c>
+      <c r="G348" s="1"/>
+      <c r="H348" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B349" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C349" s="9">
+        <v>112</v>
+      </c>
+      <c r="D349" s="4">
+        <v>35.253587837837799</v>
+      </c>
+      <c r="E349" s="6">
+        <v>20</v>
+      </c>
+      <c r="F349" s="3">
+        <f t="shared" si="8"/>
+        <v>28.202870270270239</v>
+      </c>
+      <c r="G349" s="1"/>
+      <c r="H349" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B350" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C350" s="9">
+        <v>104</v>
+      </c>
+      <c r="D350" s="4">
+        <v>32.856121275074599</v>
+      </c>
+      <c r="E350" s="6">
+        <v>20</v>
+      </c>
+      <c r="F350" s="3">
+        <f t="shared" si="8"/>
+        <v>26.284897020059681</v>
+      </c>
+      <c r="G350" s="1"/>
+      <c r="H350" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B351" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C351" s="9">
+        <v>120</v>
+      </c>
+      <c r="D351" s="4">
+        <v>41.062986607142903</v>
+      </c>
+      <c r="E351" s="6">
+        <v>20</v>
+      </c>
+      <c r="F351" s="3">
+        <f t="shared" si="8"/>
+        <v>32.850389285714321</v>
+      </c>
+      <c r="G351" s="1"/>
+      <c r="H351" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B352" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C352" s="9">
+        <v>120</v>
+      </c>
+      <c r="D352" s="4">
+        <v>33.0241870087116</v>
+      </c>
+      <c r="E352" s="6">
+        <v>20</v>
+      </c>
+      <c r="F352" s="3">
+        <f t="shared" si="8"/>
+        <v>26.419349606969281</v>
+      </c>
+      <c r="G352" s="1"/>
+      <c r="H352" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B353" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C353" s="9">
+        <v>91</v>
+      </c>
+      <c r="D353" s="4">
+        <v>41.623448430493298</v>
+      </c>
+      <c r="E353" s="6">
+        <v>20</v>
+      </c>
+      <c r="F353" s="3">
+        <f t="shared" si="8"/>
+        <v>33.29875874439464</v>
+      </c>
+      <c r="G353" s="1"/>
+      <c r="H353" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B354" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C354" s="9">
+        <v>108</v>
+      </c>
+      <c r="D354" s="4">
+        <v>45.165530398604901</v>
+      </c>
+      <c r="E354" s="6">
+        <v>20</v>
+      </c>
+      <c r="F354" s="3">
+        <f t="shared" si="8"/>
+        <v>36.13242431888392</v>
+      </c>
+      <c r="G354" s="1"/>
+      <c r="H354" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B355" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C355" s="9">
+        <v>109</v>
+      </c>
+      <c r="D355" s="4">
+        <v>38.283576648631701</v>
+      </c>
+      <c r="E355" s="6">
+        <v>20</v>
+      </c>
+      <c r="F355" s="3">
+        <f t="shared" si="8"/>
+        <v>30.626861318905362</v>
+      </c>
+      <c r="G355" s="1"/>
+      <c r="H355" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B356" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C356" s="9">
+        <v>112</v>
+      </c>
+      <c r="D356" s="4">
+        <v>35.253587837837799</v>
+      </c>
+      <c r="E356" s="6">
+        <v>20</v>
+      </c>
+      <c r="F356" s="3">
+        <f t="shared" si="8"/>
+        <v>28.202870270270239</v>
+      </c>
+      <c r="G356" s="1"/>
+      <c r="H356" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B357" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C357" s="9">
+        <v>79</v>
+      </c>
+      <c r="D357" s="4">
+        <v>93.622258278145694</v>
+      </c>
+      <c r="E357" s="6">
+        <v>20</v>
+      </c>
+      <c r="F357" s="3">
+        <f t="shared" si="8"/>
+        <v>74.897806622516555</v>
+      </c>
+      <c r="G357" s="1"/>
+      <c r="H357" s="8"/>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B358" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C358" s="9">
+        <v>128</v>
+      </c>
+      <c r="D358" s="4">
+        <v>44.589509943181802</v>
+      </c>
+      <c r="E358" s="6">
+        <v>20</v>
+      </c>
+      <c r="F358" s="3">
+        <f t="shared" si="8"/>
+        <v>35.671607954545443</v>
+      </c>
+      <c r="G358" s="1"/>
+      <c r="H358" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B359" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C359" s="9">
+        <v>136</v>
+      </c>
+      <c r="D359" s="4">
+        <v>37.248636718749999</v>
+      </c>
+      <c r="E359" s="6">
+        <v>20</v>
+      </c>
+      <c r="F359" s="3">
+        <f t="shared" si="8"/>
+        <v>29.798909375000001</v>
+      </c>
+      <c r="G359" s="1"/>
+      <c r="H359" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B360" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C360" s="9">
+        <v>116</v>
+      </c>
+      <c r="D360" s="4">
+        <v>35.1365432098765</v>
+      </c>
+      <c r="E360" s="6">
+        <v>20</v>
+      </c>
+      <c r="F360" s="3">
+        <f t="shared" si="8"/>
+        <v>28.109234567901201</v>
+      </c>
+      <c r="G360" s="1"/>
+      <c r="H360" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B361" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C361" s="9">
+        <v>136</v>
+      </c>
+      <c r="D361" s="4">
+        <v>32.110759081935903</v>
+      </c>
+      <c r="E361" s="6">
+        <v>20</v>
+      </c>
+      <c r="F361" s="3">
+        <f t="shared" si="8"/>
+        <v>25.688607265548722</v>
+      </c>
+      <c r="G361" s="1"/>
+      <c r="H361" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B362" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C362" s="9">
+        <v>118</v>
+      </c>
+      <c r="D362" s="4">
+        <v>72.360395992404605</v>
+      </c>
+      <c r="E362" s="6">
+        <v>20</v>
+      </c>
+      <c r="F362" s="3">
+        <f t="shared" si="8"/>
+        <v>57.888316793923686</v>
+      </c>
+      <c r="G362" s="1"/>
+      <c r="H362" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B363" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C363" s="9">
+        <v>112</v>
+      </c>
+      <c r="D363" s="4">
+        <v>32.661591346153898</v>
+      </c>
+      <c r="E363" s="6">
+        <v>20</v>
+      </c>
+      <c r="F363" s="3">
+        <f t="shared" si="8"/>
+        <v>26.12927307692312</v>
+      </c>
+      <c r="G363" s="1"/>
+      <c r="H363" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B364" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C364" s="9">
+        <v>115</v>
+      </c>
+      <c r="D364" s="4">
+        <v>64.305845646890504</v>
+      </c>
+      <c r="E364" s="6">
+        <v>20</v>
+      </c>
+      <c r="F364" s="3">
+        <f t="shared" si="8"/>
+        <v>51.444676517512406</v>
+      </c>
+      <c r="G364" s="1"/>
+      <c r="H364" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B365" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C365" s="9">
+        <v>109</v>
+      </c>
+      <c r="D365" s="4">
+        <v>36.331231268348603</v>
+      </c>
+      <c r="E365" s="6">
+        <v>20</v>
+      </c>
+      <c r="F365" s="3">
+        <f t="shared" si="8"/>
+        <v>29.064985014678882</v>
+      </c>
+      <c r="G365" s="1"/>
+      <c r="H365" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B366" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C366" s="9">
+        <v>104</v>
+      </c>
+      <c r="D366" s="4">
+        <v>33.397336589587198</v>
+      </c>
+      <c r="E366" s="6">
+        <v>20</v>
+      </c>
+      <c r="F366" s="3">
+        <f t="shared" si="8"/>
+        <v>26.717869271669759</v>
+      </c>
+      <c r="G366" s="1"/>
+      <c r="H366" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B367" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C367" s="9">
+        <v>108</v>
+      </c>
+      <c r="D367" s="4">
+        <v>52.224931685452802</v>
+      </c>
+      <c r="E367" s="6">
+        <v>20</v>
+      </c>
+      <c r="F367" s="3">
+        <f t="shared" si="8"/>
+        <v>41.77994534836224</v>
+      </c>
+      <c r="G367" s="1"/>
+      <c r="H367" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B368" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C368" s="9">
+        <v>88</v>
+      </c>
+      <c r="D368" s="4">
+        <v>84.681672909090906</v>
+      </c>
+      <c r="E368" s="6">
+        <v>20</v>
+      </c>
+      <c r="F368" s="3">
+        <f t="shared" si="8"/>
+        <v>67.745338327272719</v>
+      </c>
+      <c r="G368" s="1"/>
+      <c r="H368" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B369" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C369" s="9">
+        <v>120</v>
+      </c>
+      <c r="D369" s="4">
+        <v>39.903595833333299</v>
+      </c>
+      <c r="E369" s="6">
+        <v>20</v>
+      </c>
+      <c r="F369" s="3">
+        <f t="shared" si="8"/>
+        <v>31.922876666666639</v>
+      </c>
+      <c r="G369" s="1"/>
+      <c r="H369" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B370" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C370" s="9">
+        <v>94</v>
+      </c>
+      <c r="D370" s="4">
+        <v>27.713579741356401</v>
+      </c>
+      <c r="E370" s="6">
+        <v>20</v>
+      </c>
+      <c r="F370" s="3">
+        <f t="shared" si="8"/>
+        <v>22.170863793085122</v>
+      </c>
+      <c r="G370" s="1"/>
+      <c r="H370" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B371" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C371" s="9">
+        <v>24</v>
+      </c>
+      <c r="D371" s="4">
+        <v>71.988653999999997</v>
+      </c>
+      <c r="E371" s="6">
+        <v>20</v>
+      </c>
+      <c r="F371" s="3">
+        <f t="shared" si="8"/>
+        <v>57.590923199999999</v>
+      </c>
+      <c r="G371" s="1"/>
+      <c r="H371" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B372" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C372" s="9">
+        <v>100</v>
+      </c>
+      <c r="D372" s="4">
+        <v>49.6150039023427</v>
+      </c>
+      <c r="E372" s="6">
+        <v>20</v>
+      </c>
+      <c r="F372" s="3">
+        <f t="shared" si="8"/>
+        <v>39.692003121874158</v>
+      </c>
+      <c r="G372" s="1"/>
+      <c r="H372" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B373" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C373" s="9"/>
+      <c r="D373" s="4"/>
+      <c r="E373" s="6">
+        <v>20</v>
+      </c>
+      <c r="F373" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G373" s="1"/>
+      <c r="H373" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B374" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C374" s="9"/>
+      <c r="D374" s="4"/>
+      <c r="E374" s="6">
+        <v>20</v>
+      </c>
+      <c r="F374" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G374" s="1"/>
+      <c r="H374" s="8"/>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B375" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C375" s="9">
+        <v>136</v>
+      </c>
+      <c r="D375" s="4">
+        <v>33.361180147058803</v>
+      </c>
+      <c r="E375" s="6">
+        <v>20</v>
+      </c>
+      <c r="F375" s="3">
+        <f t="shared" si="8"/>
+        <v>26.688944117647043</v>
+      </c>
+      <c r="G375" s="1"/>
+      <c r="H375" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B376" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C376" s="9">
+        <v>109</v>
+      </c>
+      <c r="D376" s="4">
+        <v>37.082852000000003</v>
+      </c>
+      <c r="E376" s="6">
+        <v>20</v>
+      </c>
+      <c r="F376" s="3">
+        <f t="shared" si="8"/>
+        <v>29.666281600000001</v>
+      </c>
+      <c r="G376" s="1"/>
+      <c r="H376" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B377" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C377" s="9">
+        <v>96</v>
+      </c>
+      <c r="D377" s="4">
+        <v>76.324502906976804</v>
+      </c>
+      <c r="E377" s="6">
+        <v>20</v>
+      </c>
+      <c r="F377" s="3">
+        <f t="shared" si="8"/>
+        <v>61.059602325581444</v>
+      </c>
+      <c r="G377" s="1"/>
+      <c r="H377" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B378" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C378" s="9">
+        <v>120</v>
+      </c>
+      <c r="D378" s="4">
+        <v>39.478974940476199</v>
+      </c>
+      <c r="E378" s="6">
+        <v>20</v>
+      </c>
+      <c r="F378" s="3">
+        <f t="shared" si="8"/>
+        <v>31.583179952380959</v>
+      </c>
+      <c r="G378" s="1"/>
+      <c r="H378" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B379" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C379" s="9">
+        <v>114</v>
+      </c>
+      <c r="D379" s="4">
+        <v>64.293517519123</v>
+      </c>
+      <c r="E379" s="6">
+        <v>20</v>
+      </c>
+      <c r="F379" s="3">
+        <f t="shared" si="8"/>
+        <v>51.4348140152984</v>
+      </c>
+      <c r="G379" s="1"/>
+      <c r="H379" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B380" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C380" s="9"/>
+      <c r="D380" s="4"/>
+      <c r="E380" s="6">
+        <v>20</v>
+      </c>
+      <c r="F380" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G380" s="1"/>
+      <c r="H380" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B381" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C381" s="9">
+        <v>88</v>
+      </c>
+      <c r="D381" s="4">
+        <v>84.681672909090906</v>
+      </c>
+      <c r="E381" s="6">
+        <v>20</v>
+      </c>
+      <c r="F381" s="3">
+        <f t="shared" si="8"/>
+        <v>67.745338327272719</v>
+      </c>
+      <c r="G381" s="1"/>
+      <c r="H381" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B382" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C382" s="9">
+        <v>65</v>
+      </c>
+      <c r="D382" s="4">
+        <v>26.842019531249999</v>
+      </c>
+      <c r="E382" s="6">
+        <v>20</v>
+      </c>
+      <c r="F382" s="3">
+        <f t="shared" si="8"/>
+        <v>21.473615625000001</v>
+      </c>
+      <c r="G382" s="1"/>
+      <c r="H382" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B383" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C383" s="9">
+        <v>87</v>
+      </c>
+      <c r="D383" s="4">
+        <v>28.136091954023001</v>
+      </c>
+      <c r="E383" s="6">
+        <v>20</v>
+      </c>
+      <c r="F383" s="3">
+        <f t="shared" si="8"/>
+        <v>22.508873563218401</v>
+      </c>
+      <c r="G383" s="1"/>
+      <c r="H383" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B384" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C384" s="9">
+        <v>120</v>
+      </c>
+      <c r="D384" s="4">
+        <v>36.1158966666667</v>
+      </c>
+      <c r="E384" s="6">
+        <v>20</v>
+      </c>
+      <c r="F384" s="3">
+        <f t="shared" si="8"/>
+        <v>28.892717333333358</v>
+      </c>
+      <c r="G384" s="1"/>
+      <c r="H384" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B385" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C385" s="9">
+        <v>136</v>
+      </c>
+      <c r="D385" s="4">
+        <v>43.092284090909097</v>
+      </c>
+      <c r="E385" s="6">
+        <v>20</v>
+      </c>
+      <c r="F385" s="3">
+        <f t="shared" si="8"/>
+        <v>34.473827272727277</v>
+      </c>
+      <c r="G385" s="1"/>
+      <c r="H385" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B386" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C386" s="9">
+        <v>120</v>
+      </c>
+      <c r="D386" s="4">
+        <v>24.200622362231599</v>
+      </c>
+      <c r="E386" s="6">
+        <v>20</v>
+      </c>
+      <c r="F386" s="3">
+        <f t="shared" si="8"/>
+        <v>19.360497889785279</v>
+      </c>
+      <c r="G386" s="1"/>
+      <c r="H386" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B387" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C387" s="9">
+        <v>116</v>
+      </c>
+      <c r="D387" s="4">
+        <v>33.9616288846318</v>
+      </c>
+      <c r="E387" s="6">
+        <v>20</v>
+      </c>
+      <c r="F387" s="3">
+        <f t="shared" si="8"/>
+        <v>27.169303107705439</v>
+      </c>
+      <c r="G387" s="1"/>
+      <c r="H387" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B388" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C388" s="9">
+        <v>120</v>
+      </c>
+      <c r="D388" s="4">
+        <v>34.340737500000003</v>
+      </c>
+      <c r="E388" s="6">
+        <v>20</v>
+      </c>
+      <c r="F388" s="3">
+        <f t="shared" si="8"/>
+        <v>27.472590000000004</v>
+      </c>
+      <c r="G388" s="1"/>
+      <c r="H388" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B389" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C389" s="9">
+        <v>104</v>
+      </c>
+      <c r="D389" s="4">
+        <v>76.324502906976804</v>
+      </c>
+      <c r="E389" s="6">
+        <v>20</v>
+      </c>
+      <c r="F389" s="3">
+        <f t="shared" si="8"/>
+        <v>61.059602325581444</v>
+      </c>
+      <c r="G389" s="1"/>
+      <c r="H389" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B390" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C390" s="9">
+        <v>104</v>
+      </c>
+      <c r="D390" s="4">
+        <v>76.324502906976804</v>
+      </c>
+      <c r="E390" s="6">
+        <v>20</v>
+      </c>
+      <c r="F390" s="3">
+        <f t="shared" si="8"/>
+        <v>61.059602325581444</v>
+      </c>
+      <c r="G390" s="1"/>
+      <c r="H390" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B391" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C391" s="9">
+        <v>104</v>
+      </c>
+      <c r="D391" s="4">
+        <v>34.364038461538499</v>
+      </c>
+      <c r="E391" s="6">
+        <v>20</v>
+      </c>
+      <c r="F391" s="3">
+        <f t="shared" si="8"/>
+        <v>27.4912307692308</v>
+      </c>
+      <c r="G391" s="1"/>
+      <c r="H391" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B392" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C392" s="9"/>
+      <c r="D392" s="4"/>
+      <c r="E392" s="6">
+        <v>20</v>
+      </c>
+      <c r="F392" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G392" s="1"/>
+      <c r="H392" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B393" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C393" s="9">
+        <v>96</v>
+      </c>
+      <c r="D393" s="4">
+        <v>33.831854967948701</v>
+      </c>
+      <c r="E393" s="6">
+        <v>20</v>
+      </c>
+      <c r="F393" s="3">
+        <f t="shared" si="8"/>
+        <v>27.065483974358962</v>
+      </c>
+      <c r="G393" s="1"/>
+      <c r="H393" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B394" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C394" s="9">
+        <v>128</v>
+      </c>
+      <c r="D394" s="4">
+        <v>31.7292916666667</v>
+      </c>
+      <c r="E394" s="6">
+        <v>20</v>
+      </c>
+      <c r="F394" s="3">
+        <f t="shared" si="8"/>
+        <v>25.383433333333361</v>
+      </c>
+      <c r="G394" s="1"/>
+      <c r="H394" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B395" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C395" s="9">
+        <v>144</v>
+      </c>
+      <c r="D395" s="4">
+        <v>36.2851210842109</v>
+      </c>
+      <c r="E395" s="6">
+        <v>20</v>
+      </c>
+      <c r="F395" s="3">
+        <f t="shared" si="8"/>
+        <v>29.028096867368721</v>
+      </c>
+      <c r="G395" s="1"/>
+      <c r="H395" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B396" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C396" s="9">
+        <v>120</v>
+      </c>
+      <c r="D396" s="4">
+        <v>34.998192345207798</v>
+      </c>
+      <c r="E396" s="6">
+        <v>20</v>
+      </c>
+      <c r="F396" s="3">
+        <f t="shared" si="8"/>
+        <v>27.998553876166238</v>
+      </c>
+      <c r="G396" s="1"/>
+      <c r="H396" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B397" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C397" s="9"/>
+      <c r="D397" s="4"/>
+      <c r="E397" s="6">
+        <v>20</v>
+      </c>
+      <c r="F397" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G397" s="1"/>
+      <c r="H397" s="8"/>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B398" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C398" s="9">
+        <v>120</v>
+      </c>
+      <c r="D398" s="4">
+        <v>33.286357415786803</v>
+      </c>
+      <c r="E398" s="6">
+        <v>20</v>
+      </c>
+      <c r="F398" s="3">
+        <f t="shared" si="8"/>
+        <v>26.629085932629444</v>
+      </c>
+      <c r="G398" s="1"/>
+      <c r="H398" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B399" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C399" s="9">
+        <v>128</v>
+      </c>
+      <c r="D399" s="4">
+        <v>35.2772221354167</v>
+      </c>
+      <c r="E399" s="6">
+        <v>20</v>
+      </c>
+      <c r="F399" s="3">
+        <f t="shared" si="8"/>
+        <v>28.221777708333359</v>
+      </c>
+      <c r="G399" s="1"/>
+      <c r="H399" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B400" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C400" s="9">
+        <v>104</v>
+      </c>
+      <c r="D400" s="4">
+        <v>39.903595833333299</v>
+      </c>
+      <c r="E400" s="6">
+        <v>20</v>
+      </c>
+      <c r="F400" s="3">
+        <f t="shared" si="8"/>
+        <v>31.922876666666639</v>
+      </c>
+      <c r="G400" s="1"/>
+      <c r="H400" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B401" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C401" s="9">
+        <v>88</v>
+      </c>
+      <c r="D401" s="4">
+        <v>35.636584028714701</v>
+      </c>
+      <c r="E401" s="6">
+        <v>20</v>
+      </c>
+      <c r="F401" s="3">
+        <f t="shared" si="8"/>
+        <v>28.509267222971761</v>
+      </c>
+      <c r="G401" s="1"/>
+      <c r="H401" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B402" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C402" s="9">
+        <v>117</v>
+      </c>
+      <c r="D402" s="4">
+        <v>32.489529914529903</v>
+      </c>
+      <c r="E402" s="6">
+        <v>20</v>
+      </c>
+      <c r="F402" s="3">
+        <f t="shared" si="8"/>
+        <v>25.991623931623923</v>
+      </c>
+      <c r="G402" s="1"/>
+      <c r="H402" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B403" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C403" s="9">
+        <v>104</v>
+      </c>
+      <c r="D403" s="4">
+        <v>43.817596153846203</v>
+      </c>
+      <c r="E403" s="6">
+        <v>20</v>
+      </c>
+      <c r="F403" s="3">
+        <f t="shared" si="8"/>
+        <v>35.054076923076963</v>
+      </c>
+      <c r="G403" s="1"/>
+      <c r="H403" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B404" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C404" s="9">
+        <v>104</v>
+      </c>
+      <c r="D404" s="4">
+        <v>43.817596153846203</v>
+      </c>
+      <c r="E404" s="6">
+        <v>20</v>
+      </c>
+      <c r="F404" s="3">
+        <f t="shared" si="8"/>
+        <v>35.054076923076963</v>
+      </c>
+      <c r="G404" s="1"/>
+      <c r="H404" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B405" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C405" s="9">
+        <v>128</v>
+      </c>
+      <c r="D405" s="4">
+        <v>38.795750948660697</v>
+      </c>
+      <c r="E405" s="6">
+        <v>20</v>
+      </c>
+      <c r="F405" s="3">
+        <f t="shared" si="8"/>
+        <v>31.036600758928557</v>
+      </c>
+      <c r="G405" s="1"/>
+      <c r="H405" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B406" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C406" s="9">
+        <v>37</v>
+      </c>
+      <c r="D406" s="4">
+        <v>72.8261341348245</v>
+      </c>
+      <c r="E406" s="6">
+        <v>20</v>
+      </c>
+      <c r="F406" s="3">
+        <f t="shared" si="8"/>
+        <v>58.260907307859597</v>
+      </c>
+      <c r="G406" s="1"/>
+      <c r="H406" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B407" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C407" s="9">
+        <v>8</v>
+      </c>
+      <c r="D407" s="4">
+        <v>111.433416666667</v>
+      </c>
+      <c r="E407" s="6">
+        <v>20</v>
+      </c>
+      <c r="F407" s="3">
+        <f t="shared" ref="F407:F414" si="9">D407-(D407*E407)/100</f>
+        <v>89.1467333333336</v>
+      </c>
+      <c r="G407" s="1"/>
+      <c r="H407" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B408" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C408" s="9">
+        <v>144</v>
+      </c>
+      <c r="D408" s="4">
+        <v>42.042984659090898</v>
+      </c>
+      <c r="E408" s="6">
+        <v>20</v>
+      </c>
+      <c r="F408" s="3">
+        <f t="shared" si="9"/>
+        <v>33.634387727272717</v>
+      </c>
+      <c r="G408" s="1"/>
+      <c r="H408" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B409" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C409" s="9">
+        <v>101</v>
+      </c>
+      <c r="D409" s="4">
+        <v>88.492330346601506</v>
+      </c>
+      <c r="E409" s="6">
+        <v>20</v>
+      </c>
+      <c r="F409" s="3">
+        <f t="shared" si="9"/>
+        <v>70.793864277281202</v>
+      </c>
+      <c r="G409" s="1"/>
+      <c r="H409" s="8"/>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B410" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C410" s="9">
+        <v>87</v>
+      </c>
+      <c r="D410" s="4">
+        <v>28.136091954023001</v>
+      </c>
+      <c r="E410" s="6">
+        <v>20</v>
+      </c>
+      <c r="F410" s="3">
+        <f t="shared" si="9"/>
+        <v>22.508873563218401</v>
+      </c>
+      <c r="G410" s="1"/>
+      <c r="H410" s="8"/>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B411" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C411" s="9">
+        <v>64</v>
+      </c>
+      <c r="D411" s="4">
+        <v>34.340737500000003</v>
+      </c>
+      <c r="E411" s="6">
+        <v>20</v>
+      </c>
+      <c r="F411" s="3">
+        <f t="shared" si="9"/>
+        <v>27.472590000000004</v>
+      </c>
+      <c r="G411" s="1"/>
+      <c r="H411" s="8"/>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B412" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C412" s="9">
+        <v>96</v>
+      </c>
+      <c r="D412" s="4">
+        <v>33.937659107906001</v>
+      </c>
+      <c r="E412" s="6">
+        <v>20</v>
+      </c>
+      <c r="F412" s="3">
+        <f t="shared" si="9"/>
+        <v>27.1501272863248</v>
+      </c>
+      <c r="G412" s="1"/>
+      <c r="H412" s="8"/>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B413" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C413" s="9">
+        <v>16</v>
+      </c>
+      <c r="D413" s="4">
+        <v>32.489529914529903</v>
+      </c>
+      <c r="E413" s="6">
+        <v>20</v>
+      </c>
+      <c r="F413" s="3">
+        <f t="shared" si="9"/>
+        <v>25.991623931623923</v>
+      </c>
+      <c r="G413" s="1"/>
+      <c r="H413" s="8"/>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B414" s="11">
+        <v>46013</v>
+      </c>
+      <c r="C414" s="9"/>
+      <c r="D414" s="4"/>
+      <c r="E414" s="6">
+        <v>20</v>
+      </c>
+      <c r="F414" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G414" s="1"/>
+      <c r="H414" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G272"/>
@@ -9714,6 +11452,68 @@
     <hyperlink ref="H336" r:id="rId314"/>
     <hyperlink ref="H337" r:id="rId315"/>
     <hyperlink ref="H300" r:id="rId316" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="G344" r:id="rId317"/>
+    <hyperlink ref="H344" r:id="rId318"/>
+    <hyperlink ref="H345" r:id="rId319"/>
+    <hyperlink ref="H347" r:id="rId320"/>
+    <hyperlink ref="H348" r:id="rId321"/>
+    <hyperlink ref="H349" r:id="rId322"/>
+    <hyperlink ref="H350" r:id="rId323"/>
+    <hyperlink ref="H351" r:id="rId324"/>
+    <hyperlink ref="H352" r:id="rId325"/>
+    <hyperlink ref="H353" r:id="rId326"/>
+    <hyperlink ref="H354" r:id="rId327"/>
+    <hyperlink ref="H355" r:id="rId328"/>
+    <hyperlink ref="H356" r:id="rId329"/>
+    <hyperlink ref="H358" r:id="rId330"/>
+    <hyperlink ref="H359" r:id="rId331"/>
+    <hyperlink ref="H360" r:id="rId332"/>
+    <hyperlink ref="H361" r:id="rId333"/>
+    <hyperlink ref="H362" r:id="rId334"/>
+    <hyperlink ref="H363" r:id="rId335"/>
+    <hyperlink ref="H364" r:id="rId336"/>
+    <hyperlink ref="H365" r:id="rId337"/>
+    <hyperlink ref="H366" r:id="rId338"/>
+    <hyperlink ref="H367" r:id="rId339"/>
+    <hyperlink ref="H368" r:id="rId340"/>
+    <hyperlink ref="H369" r:id="rId341"/>
+    <hyperlink ref="H370" r:id="rId342"/>
+    <hyperlink ref="H372" r:id="rId343"/>
+    <hyperlink ref="H373" r:id="rId344"/>
+    <hyperlink ref="H375" r:id="rId345"/>
+    <hyperlink ref="H376" r:id="rId346"/>
+    <hyperlink ref="H377" r:id="rId347"/>
+    <hyperlink ref="H378" r:id="rId348"/>
+    <hyperlink ref="H379" r:id="rId349"/>
+    <hyperlink ref="H380" r:id="rId350"/>
+    <hyperlink ref="H381" r:id="rId351"/>
+    <hyperlink ref="H382" r:id="rId352"/>
+    <hyperlink ref="H383" r:id="rId353"/>
+    <hyperlink ref="H384" r:id="rId354"/>
+    <hyperlink ref="H385" r:id="rId355"/>
+    <hyperlink ref="H386" r:id="rId356"/>
+    <hyperlink ref="H387" r:id="rId357"/>
+    <hyperlink ref="H388" r:id="rId358"/>
+    <hyperlink ref="H389" r:id="rId359"/>
+    <hyperlink ref="H390" r:id="rId360"/>
+    <hyperlink ref="H391" r:id="rId361"/>
+    <hyperlink ref="H392" r:id="rId362"/>
+    <hyperlink ref="H393" r:id="rId363"/>
+    <hyperlink ref="H394" r:id="rId364"/>
+    <hyperlink ref="H395" r:id="rId365"/>
+    <hyperlink ref="H396" r:id="rId366"/>
+    <hyperlink ref="H398" r:id="rId367"/>
+    <hyperlink ref="H399" r:id="rId368"/>
+    <hyperlink ref="H400" r:id="rId369"/>
+    <hyperlink ref="H401" r:id="rId370"/>
+    <hyperlink ref="H402" r:id="rId371"/>
+    <hyperlink ref="H403" r:id="rId372"/>
+    <hyperlink ref="H404" r:id="rId373"/>
+    <hyperlink ref="H405" r:id="rId374"/>
+    <hyperlink ref="H406" r:id="rId375"/>
+    <hyperlink ref="H407" r:id="rId376"/>
+    <hyperlink ref="H408" r:id="rId377"/>
+    <hyperlink ref="H371" r:id="rId378" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="154">
   <si>
     <t>Tecnico</t>
   </si>
@@ -481,9 +481,6 @@
   </si>
   <si>
     <t>IRTE0000115 - LA PIANA GIUSEPPE</t>
-  </si>
-  <si>
-    <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
   </si>
 </sst>
 </file>
@@ -9392,7 +9389,7 @@
         <v>20</v>
       </c>
       <c r="F343" s="3">
-        <f t="shared" ref="F343:F406" si="8">D343-(D343*E343)/100</f>
+        <f t="shared" ref="F343:F357" si="8">D343-(D343*E343)/100</f>
         <v>105.0559034764824</v>
       </c>
       <c r="G343" s="1"/>
@@ -9403,20 +9400,20 @@
         <v>4</v>
       </c>
       <c r="B344" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C344" s="9">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D344" s="12">
-        <v>35.1365432098765</v>
+        <v>31.189142473118299</v>
       </c>
       <c r="E344" s="13">
         <v>20</v>
       </c>
       <c r="F344" s="14">
         <f t="shared" si="8"/>
-        <v>28.109234567901201</v>
+        <v>24.951313978494639</v>
       </c>
       <c r="G344" s="15" t="s">
         <v>67</v>
@@ -9430,20 +9427,20 @@
         <v>5</v>
       </c>
       <c r="B345" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C345" s="9">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="D345" s="4">
-        <v>48.984647486176499</v>
+        <v>40.789290597474</v>
       </c>
       <c r="E345" s="6">
         <v>20</v>
       </c>
       <c r="F345" s="3">
         <f t="shared" si="8"/>
-        <v>39.187717988941202</v>
+        <v>32.631432477979203</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>67</v>
@@ -9457,20 +9454,20 @@
         <v>139</v>
       </c>
       <c r="B346" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C346" s="9">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="D346" s="4">
-        <v>18.3408644018151</v>
+        <v>135.02601646500801</v>
       </c>
       <c r="E346" s="6">
         <v>20</v>
       </c>
       <c r="F346" s="3">
         <f t="shared" si="8"/>
-        <v>14.67269152145208</v>
+        <v>108.02081317200641</v>
       </c>
       <c r="G346" s="1"/>
       <c r="H346" s="8"/>
@@ -9480,20 +9477,20 @@
         <v>6</v>
       </c>
       <c r="B347" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C347" s="9">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="D347" s="4">
-        <v>27.686624270940701</v>
+        <v>31.3221358219987</v>
       </c>
       <c r="E347" s="6">
         <v>20</v>
       </c>
       <c r="F347" s="3">
         <f t="shared" si="8"/>
-        <v>22.149299416752562</v>
+        <v>25.057708657598958</v>
       </c>
       <c r="G347" s="1"/>
       <c r="H347" s="8" t="s">
@@ -9505,20 +9502,20 @@
         <v>7</v>
       </c>
       <c r="B348" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C348" s="9">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D348" s="4">
-        <v>93.622258278145694</v>
+        <v>203.80709722222201</v>
       </c>
       <c r="E348" s="6">
         <v>20</v>
       </c>
       <c r="F348" s="3">
         <f t="shared" si="8"/>
-        <v>74.897806622516555</v>
+        <v>163.0456777777776</v>
       </c>
       <c r="G348" s="1"/>
       <c r="H348" s="8" t="s">
@@ -9530,20 +9527,20 @@
         <v>8</v>
       </c>
       <c r="B349" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C349" s="9">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="D349" s="4">
-        <v>35.253587837837799</v>
+        <v>29.248444138400199</v>
       </c>
       <c r="E349" s="6">
         <v>20</v>
       </c>
       <c r="F349" s="3">
         <f t="shared" si="8"/>
-        <v>28.202870270270239</v>
+        <v>23.398755310720158</v>
       </c>
       <c r="G349" s="1"/>
       <c r="H349" s="8" t="s">
@@ -9555,20 +9552,20 @@
         <v>9</v>
       </c>
       <c r="B350" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C350" s="9">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D350" s="4">
-        <v>32.856121275074599</v>
+        <v>39.740131178707202</v>
       </c>
       <c r="E350" s="6">
         <v>20</v>
       </c>
       <c r="F350" s="3">
         <f t="shared" si="8"/>
-        <v>26.284897020059681</v>
+        <v>31.792104942965761</v>
       </c>
       <c r="G350" s="1"/>
       <c r="H350" s="8" t="s">
@@ -9580,20 +9577,20 @@
         <v>10</v>
       </c>
       <c r="B351" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C351" s="9">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="D351" s="4">
-        <v>41.062986607142903</v>
+        <v>35.579655487804899</v>
       </c>
       <c r="E351" s="6">
         <v>20</v>
       </c>
       <c r="F351" s="3">
         <f t="shared" si="8"/>
-        <v>32.850389285714321</v>
+        <v>28.463724390243918</v>
       </c>
       <c r="G351" s="1"/>
       <c r="H351" s="8" t="s">
@@ -9605,20 +9602,20 @@
         <v>11</v>
       </c>
       <c r="B352" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C352" s="9">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D352" s="4">
-        <v>33.0241870087116</v>
+        <v>39.740131178707202</v>
       </c>
       <c r="E352" s="6">
         <v>20</v>
       </c>
       <c r="F352" s="3">
         <f t="shared" si="8"/>
-        <v>26.419349606969281</v>
+        <v>31.792104942965761</v>
       </c>
       <c r="G352" s="1"/>
       <c r="H352" s="8" t="s">
@@ -9630,20 +9627,20 @@
         <v>12</v>
       </c>
       <c r="B353" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C353" s="9">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="D353" s="4">
-        <v>41.623448430493298</v>
+        <v>57.557192882945799</v>
       </c>
       <c r="E353" s="6">
         <v>20</v>
       </c>
       <c r="F353" s="3">
         <f t="shared" si="8"/>
-        <v>33.29875874439464</v>
+        <v>46.045754306356642</v>
       </c>
       <c r="G353" s="1"/>
       <c r="H353" s="8" t="s">
@@ -9655,20 +9652,20 @@
         <v>13</v>
       </c>
       <c r="B354" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C354" s="9">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="D354" s="4">
-        <v>45.165530398604901</v>
+        <v>57.557192882945799</v>
       </c>
       <c r="E354" s="6">
         <v>20</v>
       </c>
       <c r="F354" s="3">
         <f t="shared" si="8"/>
-        <v>36.13242431888392</v>
+        <v>46.045754306356642</v>
       </c>
       <c r="G354" s="1"/>
       <c r="H354" s="8" t="s">
@@ -9680,20 +9677,20 @@
         <v>14</v>
       </c>
       <c r="B355" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C355" s="9">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="D355" s="4">
-        <v>38.283576648631701</v>
+        <v>43.046664760425003</v>
       </c>
       <c r="E355" s="6">
         <v>20</v>
       </c>
       <c r="F355" s="3">
         <f t="shared" si="8"/>
-        <v>30.626861318905362</v>
+        <v>34.437331808340005</v>
       </c>
       <c r="G355" s="1"/>
       <c r="H355" s="8" t="s">
@@ -9705,20 +9702,20 @@
         <v>16</v>
       </c>
       <c r="B356" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C356" s="9">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="D356" s="4">
-        <v>35.253587837837799</v>
+        <v>30.141236069051001</v>
       </c>
       <c r="E356" s="6">
         <v>20</v>
       </c>
       <c r="F356" s="3">
         <f t="shared" si="8"/>
-        <v>28.202870270270239</v>
+        <v>24.1129888552408</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="8" t="s">
@@ -9727,23 +9724,23 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B357" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C357" s="9">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D357" s="4">
-        <v>93.622258278145694</v>
+        <v>123.08915557266199</v>
       </c>
       <c r="E357" s="6">
         <v>20</v>
       </c>
       <c r="F357" s="3">
         <f t="shared" si="8"/>
-        <v>74.897806622516555</v>
+        <v>98.471324458129601</v>
       </c>
       <c r="G357" s="1"/>
       <c r="H357" s="8"/>
@@ -9753,20 +9750,20 @@
         <v>17</v>
       </c>
       <c r="B358" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C358" s="9">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D358" s="4">
-        <v>44.589509943181802</v>
+        <v>37.687197916666697</v>
       </c>
       <c r="E358" s="6">
         <v>20</v>
       </c>
       <c r="F358" s="3">
-        <f t="shared" si="8"/>
-        <v>35.671607954545443</v>
+        <f>D358-(D358*E358)/100</f>
+        <v>30.149758333333359</v>
       </c>
       <c r="G358" s="1"/>
       <c r="H358" s="8" t="s">
@@ -9778,20 +9775,20 @@
         <v>18</v>
       </c>
       <c r="B359" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C359" s="9">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D359" s="4">
-        <v>37.248636718749999</v>
+        <v>34.291203234185197</v>
       </c>
       <c r="E359" s="6">
         <v>20</v>
       </c>
       <c r="F359" s="3">
-        <f t="shared" si="8"/>
-        <v>29.798909375000001</v>
+        <f>D359-(D359*E359)/100</f>
+        <v>27.432962587348158</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="8" t="s">
@@ -9803,20 +9800,20 @@
         <v>20</v>
       </c>
       <c r="B360" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C360" s="9">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="D360" s="4">
-        <v>35.1365432098765</v>
+        <v>33.496389610872797</v>
       </c>
       <c r="E360" s="6">
         <v>20</v>
       </c>
       <c r="F360" s="3">
-        <f t="shared" si="8"/>
-        <v>28.109234567901201</v>
+        <f>D360-(D360*E360)/100</f>
+        <v>26.797111688698237</v>
       </c>
       <c r="G360" s="1"/>
       <c r="H360" s="8" t="s">
@@ -9828,20 +9825,20 @@
         <v>21</v>
       </c>
       <c r="B361" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C361" s="9">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D361" s="4">
-        <v>32.110759081935903</v>
+        <v>34.022932412626503</v>
       </c>
       <c r="E361" s="6">
         <v>20</v>
       </c>
       <c r="F361" s="3">
-        <f t="shared" si="8"/>
-        <v>25.688607265548722</v>
+        <f>D361-(D361*E361)/100</f>
+        <v>27.218345930101201</v>
       </c>
       <c r="G361" s="1"/>
       <c r="H361" s="8" t="s">
@@ -9853,20 +9850,20 @@
         <v>22</v>
       </c>
       <c r="B362" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C362" s="9">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D362" s="4">
-        <v>72.360395992404605</v>
+        <v>61.601600296300099</v>
       </c>
       <c r="E362" s="6">
         <v>20</v>
       </c>
       <c r="F362" s="3">
-        <f t="shared" si="8"/>
-        <v>57.888316793923686</v>
+        <f>D362-(D362*E362)/100</f>
+        <v>49.281280237040079</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="8" t="s">
@@ -9878,20 +9875,20 @@
         <v>23</v>
       </c>
       <c r="B363" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C363" s="9">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D363" s="4">
-        <v>32.661591346153898</v>
+        <v>33.456470827983601</v>
       </c>
       <c r="E363" s="6">
         <v>20</v>
       </c>
       <c r="F363" s="3">
-        <f t="shared" si="8"/>
-        <v>26.12927307692312</v>
+        <f>D363-(D363*E363)/100</f>
+        <v>26.765176662386882</v>
       </c>
       <c r="G363" s="1"/>
       <c r="H363" s="8" t="s">
@@ -9903,20 +9900,20 @@
         <v>24</v>
       </c>
       <c r="B364" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C364" s="9">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D364" s="4">
-        <v>64.305845646890504</v>
+        <v>64.034912881533003</v>
       </c>
       <c r="E364" s="6">
         <v>20</v>
       </c>
       <c r="F364" s="3">
-        <f t="shared" si="8"/>
-        <v>51.444676517512406</v>
+        <f>D364-(D364*E364)/100</f>
+        <v>51.227930305226401</v>
       </c>
       <c r="G364" s="1"/>
       <c r="H364" s="8" t="s">
@@ -9928,20 +9925,20 @@
         <v>25</v>
       </c>
       <c r="B365" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C365" s="9">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D365" s="4">
-        <v>36.331231268348603</v>
+        <v>87.691933139534896</v>
       </c>
       <c r="E365" s="6">
         <v>20</v>
       </c>
       <c r="F365" s="3">
-        <f t="shared" si="8"/>
-        <v>29.064985014678882</v>
+        <f>D365-(D365*E365)/100</f>
+        <v>70.153546511627923</v>
       </c>
       <c r="G365" s="1"/>
       <c r="H365" s="8" t="s">
@@ -9953,20 +9950,20 @@
         <v>26</v>
       </c>
       <c r="B366" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C366" s="9">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="D366" s="4">
-        <v>33.397336589587198</v>
+        <v>38.876902294388202</v>
       </c>
       <c r="E366" s="6">
         <v>20</v>
       </c>
       <c r="F366" s="3">
-        <f t="shared" si="8"/>
-        <v>26.717869271669759</v>
+        <f>D366-(D366*E366)/100</f>
+        <v>31.10152183551056</v>
       </c>
       <c r="G366" s="1"/>
       <c r="H366" s="8" t="s">
@@ -9978,20 +9975,20 @@
         <v>27</v>
       </c>
       <c r="B367" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C367" s="9">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D367" s="4">
-        <v>52.224931685452802</v>
+        <v>52.252847876867698</v>
       </c>
       <c r="E367" s="6">
         <v>20</v>
       </c>
       <c r="F367" s="3">
-        <f t="shared" si="8"/>
-        <v>41.77994534836224</v>
+        <f>D367-(D367*E367)/100</f>
+        <v>41.802278301494155</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="8" t="s">
@@ -10003,20 +10000,20 @@
         <v>28</v>
       </c>
       <c r="B368" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C368" s="9">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D368" s="4">
-        <v>84.681672909090906</v>
+        <v>131.319879345603</v>
       </c>
       <c r="E368" s="6">
         <v>20</v>
       </c>
       <c r="F368" s="3">
-        <f t="shared" si="8"/>
-        <v>67.745338327272719</v>
+        <f>D368-(D368*E368)/100</f>
+        <v>105.0559034764824</v>
       </c>
       <c r="G368" s="1"/>
       <c r="H368" s="8" t="s">
@@ -10028,20 +10025,20 @@
         <v>29</v>
       </c>
       <c r="B369" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C369" s="9">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="D369" s="4">
-        <v>39.903595833333299</v>
+        <v>34.397298925667798</v>
       </c>
       <c r="E369" s="6">
         <v>20</v>
       </c>
       <c r="F369" s="3">
-        <f t="shared" si="8"/>
-        <v>31.922876666666639</v>
+        <f>D369-(D369*E369)/100</f>
+        <v>27.517839140534239</v>
       </c>
       <c r="G369" s="1"/>
       <c r="H369" s="8" t="s">
@@ -10053,20 +10050,20 @@
         <v>30</v>
       </c>
       <c r="B370" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C370" s="9">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D370" s="4">
-        <v>27.713579741356401</v>
+        <v>31.601682689636799</v>
       </c>
       <c r="E370" s="6">
         <v>20</v>
       </c>
       <c r="F370" s="3">
-        <f t="shared" si="8"/>
-        <v>22.170863793085122</v>
+        <f>D370-(D370*E370)/100</f>
+        <v>25.281346151709439</v>
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="8" t="s">
@@ -10078,20 +10075,20 @@
         <v>137</v>
       </c>
       <c r="B371" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C371" s="9">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D371" s="4">
-        <v>71.988653999999997</v>
+        <v>86.950255825442696</v>
       </c>
       <c r="E371" s="6">
         <v>20</v>
       </c>
       <c r="F371" s="3">
-        <f t="shared" si="8"/>
-        <v>57.590923199999999</v>
+        <f>D371-(D371*E371)/100</f>
+        <v>69.56020466035416</v>
       </c>
       <c r="G371" s="1"/>
       <c r="H371" s="8" t="s">
@@ -10103,20 +10100,20 @@
         <v>31</v>
       </c>
       <c r="B372" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C372" s="9">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="D372" s="4">
-        <v>49.6150039023427</v>
+        <v>51.625046106299003</v>
       </c>
       <c r="E372" s="6">
         <v>20</v>
       </c>
       <c r="F372" s="3">
-        <f t="shared" si="8"/>
-        <v>39.692003121874158</v>
+        <f>D372-(D372*E372)/100</f>
+        <v>41.300036885039205</v>
       </c>
       <c r="G372" s="1"/>
       <c r="H372" s="8" t="s">
@@ -10128,16 +10125,20 @@
         <v>32</v>
       </c>
       <c r="B373" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C373" s="9"/>
-      <c r="D373" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C373" s="9">
+        <v>104</v>
+      </c>
+      <c r="D373" s="4">
+        <v>73.388246636052401</v>
+      </c>
       <c r="E373" s="6">
         <v>20</v>
       </c>
       <c r="F373" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>D373-(D373*E373)/100</f>
+        <v>58.710597308841919</v>
       </c>
       <c r="G373" s="1"/>
       <c r="H373" s="8" t="s">
@@ -10149,16 +10150,20 @@
         <v>141</v>
       </c>
       <c r="B374" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C374" s="9"/>
-      <c r="D374" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C374" s="9">
+        <v>16</v>
+      </c>
+      <c r="D374" s="4">
+        <v>131.319879345603</v>
+      </c>
       <c r="E374" s="6">
         <v>20</v>
       </c>
       <c r="F374" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>D374-(D374*E374)/100</f>
+        <v>105.0559034764824</v>
       </c>
       <c r="G374" s="1"/>
       <c r="H374" s="8"/>
@@ -10168,20 +10173,20 @@
         <v>33</v>
       </c>
       <c r="B375" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C375" s="9">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D375" s="4">
-        <v>33.361180147058803</v>
+        <v>31.188293255131999</v>
       </c>
       <c r="E375" s="6">
         <v>20</v>
       </c>
       <c r="F375" s="3">
-        <f t="shared" si="8"/>
-        <v>26.688944117647043</v>
+        <f>D375-(D375*E375)/100</f>
+        <v>24.950634604105598</v>
       </c>
       <c r="G375" s="1"/>
       <c r="H375" s="8" t="s">
@@ -10193,20 +10198,20 @@
         <v>34</v>
       </c>
       <c r="B376" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C376" s="9">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="D376" s="4">
-        <v>37.082852000000003</v>
+        <v>86.971927575464505</v>
       </c>
       <c r="E376" s="6">
         <v>20</v>
       </c>
       <c r="F376" s="3">
-        <f t="shared" si="8"/>
-        <v>29.666281600000001</v>
+        <f>D376-(D376*E376)/100</f>
+        <v>69.577542060371599</v>
       </c>
       <c r="G376" s="1"/>
       <c r="H376" s="8" t="s">
@@ -10218,20 +10223,20 @@
         <v>35</v>
       </c>
       <c r="B377" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C377" s="9">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="D377" s="4">
-        <v>76.324502906976804</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E377" s="6">
         <v>20</v>
       </c>
       <c r="F377" s="3">
-        <f t="shared" si="8"/>
-        <v>61.059602325581444</v>
+        <f>D377-(D377*E377)/100</f>
+        <v>55.482249295774636</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="8" t="s">
@@ -10243,20 +10248,20 @@
         <v>36</v>
       </c>
       <c r="B378" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C378" s="9">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="D378" s="4">
-        <v>39.478974940476199</v>
+        <v>36.535145325203302</v>
       </c>
       <c r="E378" s="6">
         <v>20</v>
       </c>
       <c r="F378" s="3">
-        <f t="shared" si="8"/>
-        <v>31.583179952380959</v>
+        <f>D378-(D378*E378)/100</f>
+        <v>29.228116260162643</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="8" t="s">
@@ -10268,20 +10273,20 @@
         <v>37</v>
       </c>
       <c r="B379" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C379" s="9">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="D379" s="4">
-        <v>64.293517519123</v>
+        <v>65.114581459390905</v>
       </c>
       <c r="E379" s="6">
         <v>20</v>
       </c>
       <c r="F379" s="3">
-        <f t="shared" si="8"/>
-        <v>51.4348140152984</v>
+        <f>D379-(D379*E379)/100</f>
+        <v>52.091665167512723</v>
       </c>
       <c r="G379" s="1"/>
       <c r="H379" s="8" t="s">
@@ -10293,16 +10298,20 @@
         <v>38</v>
       </c>
       <c r="B380" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C380" s="9"/>
-      <c r="D380" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C380" s="9">
+        <v>112</v>
+      </c>
+      <c r="D380" s="4">
+        <v>73.043415488971604</v>
+      </c>
       <c r="E380" s="6">
         <v>20</v>
       </c>
       <c r="F380" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>D380-(D380*E380)/100</f>
+        <v>58.434732391177285</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="8" t="s">
@@ -10314,20 +10323,20 @@
         <v>39</v>
       </c>
       <c r="B381" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C381" s="9">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D381" s="4">
-        <v>84.681672909090906</v>
+        <v>122.86082778001099</v>
       </c>
       <c r="E381" s="6">
         <v>20</v>
       </c>
       <c r="F381" s="3">
-        <f t="shared" si="8"/>
-        <v>67.745338327272719</v>
+        <f>D381-(D381*E381)/100</f>
+        <v>98.288662224008789</v>
       </c>
       <c r="G381" s="1"/>
       <c r="H381" s="8" t="s">
@@ -10339,20 +10348,20 @@
         <v>40</v>
       </c>
       <c r="B382" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C382" s="9">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="D382" s="4">
-        <v>26.842019531249999</v>
+        <v>42.955545565289299</v>
       </c>
       <c r="E382" s="6">
         <v>20</v>
       </c>
       <c r="F382" s="3">
-        <f t="shared" si="8"/>
-        <v>21.473615625000001</v>
+        <f>D382-(D382*E382)/100</f>
+        <v>34.364436452231438</v>
       </c>
       <c r="G382" s="1"/>
       <c r="H382" s="8" t="s">
@@ -10364,20 +10373,20 @@
         <v>41</v>
       </c>
       <c r="B383" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C383" s="9">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="D383" s="4">
-        <v>28.136091954023001</v>
+        <v>29.326201298701299</v>
       </c>
       <c r="E383" s="6">
         <v>20</v>
       </c>
       <c r="F383" s="3">
-        <f t="shared" si="8"/>
-        <v>22.508873563218401</v>
+        <f>D383-(D383*E383)/100</f>
+        <v>23.460961038961038</v>
       </c>
       <c r="G383" s="1"/>
       <c r="H383" s="8" t="s">
@@ -10389,20 +10398,20 @@
         <v>42</v>
       </c>
       <c r="B384" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C384" s="9">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D384" s="4">
-        <v>36.1158966666667</v>
+        <v>39.0856017441861</v>
       </c>
       <c r="E384" s="6">
         <v>20</v>
       </c>
       <c r="F384" s="3">
-        <f t="shared" si="8"/>
-        <v>28.892717333333358</v>
+        <f>D384-(D384*E384)/100</f>
+        <v>31.268481395348878</v>
       </c>
       <c r="G384" s="1"/>
       <c r="H384" s="8" t="s">
@@ -10414,20 +10423,20 @@
         <v>43</v>
       </c>
       <c r="B385" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C385" s="9">
         <v>136</v>
       </c>
       <c r="D385" s="4">
-        <v>43.092284090909097</v>
+        <v>44.091314393939399</v>
       </c>
       <c r="E385" s="6">
         <v>20</v>
       </c>
       <c r="F385" s="3">
-        <f t="shared" si="8"/>
-        <v>34.473827272727277</v>
+        <f>D385-(D385*E385)/100</f>
+        <v>35.273051515151522</v>
       </c>
       <c r="G385" s="1"/>
       <c r="H385" s="8" t="s">
@@ -10439,20 +10448,20 @@
         <v>44</v>
       </c>
       <c r="B386" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C386" s="9">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="D386" s="4">
-        <v>24.200622362231599</v>
+        <v>138.87538313167499</v>
       </c>
       <c r="E386" s="6">
         <v>20</v>
       </c>
       <c r="F386" s="3">
-        <f t="shared" si="8"/>
-        <v>19.360497889785279</v>
+        <f>D386-(D386*E386)/100</f>
+        <v>111.10030650534</v>
       </c>
       <c r="G386" s="1"/>
       <c r="H386" s="8" t="s">
@@ -10464,20 +10473,20 @@
         <v>45</v>
       </c>
       <c r="B387" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C387" s="9">
         <v>116</v>
       </c>
       <c r="D387" s="4">
-        <v>33.9616288846318</v>
+        <v>33.228430586413999</v>
       </c>
       <c r="E387" s="6">
         <v>20</v>
       </c>
       <c r="F387" s="3">
-        <f t="shared" si="8"/>
-        <v>27.169303107705439</v>
+        <f>D387-(D387*E387)/100</f>
+        <v>26.5827444691312</v>
       </c>
       <c r="G387" s="1"/>
       <c r="H387" s="8" t="s">
@@ -10489,20 +10498,20 @@
         <v>46</v>
       </c>
       <c r="B388" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C388" s="9">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="D388" s="4">
-        <v>34.340737500000003</v>
+        <v>42.893889259977797</v>
       </c>
       <c r="E388" s="6">
         <v>20</v>
       </c>
       <c r="F388" s="3">
-        <f t="shared" si="8"/>
-        <v>27.472590000000004</v>
+        <f>D388-(D388*E388)/100</f>
+        <v>34.315111407982236</v>
       </c>
       <c r="G388" s="1"/>
       <c r="H388" s="8" t="s">
@@ -10514,20 +10523,20 @@
         <v>47</v>
       </c>
       <c r="B389" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C389" s="9">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="D389" s="4">
-        <v>76.324502906976804</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E389" s="6">
         <v>20</v>
       </c>
       <c r="F389" s="3">
-        <f t="shared" si="8"/>
-        <v>61.059602325581444</v>
+        <f>D389-(D389*E389)/100</f>
+        <v>55.482249295774636</v>
       </c>
       <c r="G389" s="1"/>
       <c r="H389" s="8" t="s">
@@ -10539,20 +10548,20 @@
         <v>48</v>
       </c>
       <c r="B390" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C390" s="9">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="D390" s="4">
-        <v>76.324502906976804</v>
+        <v>69.352811619718295</v>
       </c>
       <c r="E390" s="6">
         <v>20</v>
       </c>
       <c r="F390" s="3">
-        <f t="shared" si="8"/>
-        <v>61.059602325581444</v>
+        <f>D390-(D390*E390)/100</f>
+        <v>55.482249295774636</v>
       </c>
       <c r="G390" s="1"/>
       <c r="H390" s="8" t="s">
@@ -10564,20 +10573,20 @@
         <v>49</v>
       </c>
       <c r="B391" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C391" s="9">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="D391" s="4">
-        <v>34.364038461538499</v>
+        <v>35.764634634387299</v>
       </c>
       <c r="E391" s="6">
         <v>20</v>
       </c>
       <c r="F391" s="3">
-        <f t="shared" si="8"/>
-        <v>27.4912307692308</v>
+        <f>D391-(D391*E391)/100</f>
+        <v>28.61170770750984</v>
       </c>
       <c r="G391" s="1"/>
       <c r="H391" s="8" t="s">
@@ -10589,16 +10598,20 @@
         <v>50</v>
       </c>
       <c r="B392" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C392" s="9"/>
-      <c r="D392" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C392" s="9">
+        <v>96</v>
+      </c>
+      <c r="D392" s="4">
+        <v>53.564347826086902</v>
+      </c>
       <c r="E392" s="6">
         <v>20</v>
       </c>
       <c r="F392" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>D392-(D392*E392)/100</f>
+        <v>42.85147826086952</v>
       </c>
       <c r="G392" s="1"/>
       <c r="H392" s="8" t="s">
@@ -10610,20 +10623,20 @@
         <v>51</v>
       </c>
       <c r="B393" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C393" s="9">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="D393" s="4">
-        <v>33.831854967948701</v>
+        <v>35.448980113636303</v>
       </c>
       <c r="E393" s="6">
         <v>20</v>
       </c>
       <c r="F393" s="3">
-        <f t="shared" si="8"/>
-        <v>27.065483974358962</v>
+        <f>D393-(D393*E393)/100</f>
+        <v>28.359184090909043</v>
       </c>
       <c r="G393" s="1"/>
       <c r="H393" s="8" t="s">
@@ -10635,20 +10648,20 @@
         <v>52</v>
       </c>
       <c r="B394" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C394" s="9">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="D394" s="4">
-        <v>31.7292916666667</v>
+        <v>47.900705877298499</v>
       </c>
       <c r="E394" s="6">
         <v>20</v>
       </c>
       <c r="F394" s="3">
-        <f t="shared" si="8"/>
-        <v>25.383433333333361</v>
+        <f>D394-(D394*E394)/100</f>
+        <v>38.320564701838798</v>
       </c>
       <c r="G394" s="1"/>
       <c r="H394" s="8" t="s">
@@ -10660,20 +10673,20 @@
         <v>53</v>
       </c>
       <c r="B395" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C395" s="9">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D395" s="4">
-        <v>36.2851210842109</v>
+        <v>35.043873962999797</v>
       </c>
       <c r="E395" s="6">
         <v>20</v>
       </c>
       <c r="F395" s="3">
-        <f t="shared" si="8"/>
-        <v>29.028096867368721</v>
+        <f>D395-(D395*E395)/100</f>
+        <v>28.035099170399839</v>
       </c>
       <c r="G395" s="1"/>
       <c r="H395" s="8" t="s">
@@ -10685,20 +10698,20 @@
         <v>54</v>
       </c>
       <c r="B396" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C396" s="9">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="D396" s="4">
-        <v>34.998192345207798</v>
+        <v>34.0364644402894</v>
       </c>
       <c r="E396" s="6">
         <v>20</v>
       </c>
       <c r="F396" s="3">
-        <f t="shared" si="8"/>
-        <v>27.998553876166238</v>
+        <f>D396-(D396*E396)/100</f>
+        <v>27.22917155223152</v>
       </c>
       <c r="G396" s="1"/>
       <c r="H396" s="8" t="s">
@@ -10710,16 +10723,20 @@
         <v>152</v>
       </c>
       <c r="B397" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C397" s="9"/>
-      <c r="D397" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C397" s="9">
+        <v>13</v>
+      </c>
+      <c r="D397" s="4">
+        <v>131.319879345603</v>
+      </c>
       <c r="E397" s="6">
         <v>20</v>
       </c>
       <c r="F397" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>D397-(D397*E397)/100</f>
+        <v>105.0559034764824</v>
       </c>
       <c r="G397" s="1"/>
       <c r="H397" s="8"/>
@@ -10729,20 +10746,20 @@
         <v>55</v>
       </c>
       <c r="B398" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C398" s="9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D398" s="4">
-        <v>33.286357415786803</v>
+        <v>34.774626321423803</v>
       </c>
       <c r="E398" s="6">
         <v>20</v>
       </c>
       <c r="F398" s="3">
-        <f t="shared" si="8"/>
-        <v>26.629085932629444</v>
+        <f>D398-(D398*E398)/100</f>
+        <v>27.819701057139042</v>
       </c>
       <c r="G398" s="1"/>
       <c r="H398" s="8" t="s">
@@ -10754,20 +10771,20 @@
         <v>56</v>
       </c>
       <c r="B399" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C399" s="9">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D399" s="4">
-        <v>35.2772221354167</v>
+        <v>32.023106772613403</v>
       </c>
       <c r="E399" s="6">
         <v>20</v>
       </c>
       <c r="F399" s="3">
-        <f t="shared" si="8"/>
-        <v>28.221777708333359</v>
+        <f>D399-(D399*E399)/100</f>
+        <v>25.618485418090721</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="8" t="s">
@@ -10779,20 +10796,20 @@
         <v>57</v>
       </c>
       <c r="B400" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C400" s="9">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="D400" s="4">
-        <v>39.903595833333299</v>
+        <v>34.662226704545397</v>
       </c>
       <c r="E400" s="6">
         <v>20</v>
       </c>
       <c r="F400" s="3">
-        <f t="shared" si="8"/>
-        <v>31.922876666666639</v>
+        <f>D400-(D400*E400)/100</f>
+        <v>27.729781363636317</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="8" t="s">
@@ -10804,20 +10821,20 @@
         <v>58</v>
       </c>
       <c r="B401" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C401" s="9">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="D401" s="4">
-        <v>35.636584028714701</v>
+        <v>41.537577078982302</v>
       </c>
       <c r="E401" s="6">
         <v>20</v>
       </c>
       <c r="F401" s="3">
-        <f t="shared" si="8"/>
-        <v>28.509267222971761</v>
+        <f>D401-(D401*E401)/100</f>
+        <v>33.230061663185843</v>
       </c>
       <c r="G401" s="1"/>
       <c r="H401" s="8" t="s">
@@ -10829,20 +10846,20 @@
         <v>59</v>
       </c>
       <c r="B402" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C402" s="9">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D402" s="4">
-        <v>32.489529914529903</v>
+        <v>32.503339843749998</v>
       </c>
       <c r="E402" s="6">
         <v>20</v>
       </c>
       <c r="F402" s="3">
-        <f t="shared" si="8"/>
-        <v>25.991623931623923</v>
+        <f>D402-(D402*E402)/100</f>
+        <v>26.002671874999997</v>
       </c>
       <c r="G402" s="1"/>
       <c r="H402" s="8" t="s">
@@ -10854,20 +10871,20 @@
         <v>60</v>
       </c>
       <c r="B403" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C403" s="9">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D403" s="4">
-        <v>43.817596153846203</v>
+        <v>45.014359929077997</v>
       </c>
       <c r="E403" s="6">
         <v>20</v>
       </c>
       <c r="F403" s="3">
-        <f t="shared" si="8"/>
-        <v>35.054076923076963</v>
+        <f>D403-(D403*E403)/100</f>
+        <v>36.011487943262395</v>
       </c>
       <c r="G403" s="1"/>
       <c r="H403" s="8" t="s">
@@ -10879,20 +10896,20 @@
         <v>61</v>
       </c>
       <c r="B404" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C404" s="9">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="D404" s="4">
-        <v>43.817596153846203</v>
+        <v>46.161499999999997</v>
       </c>
       <c r="E404" s="6">
         <v>20</v>
       </c>
       <c r="F404" s="3">
-        <f t="shared" si="8"/>
-        <v>35.054076923076963</v>
+        <f>D404-(D404*E404)/100</f>
+        <v>36.929199999999994</v>
       </c>
       <c r="G404" s="1"/>
       <c r="H404" s="8" t="s">
@@ -10904,20 +10921,20 @@
         <v>62</v>
       </c>
       <c r="B405" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C405" s="9">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="D405" s="4">
-        <v>38.795750948660697</v>
+        <v>38.524439547383999</v>
       </c>
       <c r="E405" s="6">
         <v>20</v>
       </c>
       <c r="F405" s="3">
-        <f t="shared" si="8"/>
-        <v>31.036600758928557</v>
+        <f>D405-(D405*E405)/100</f>
+        <v>30.8195516379072</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="8" t="s">
@@ -10929,20 +10946,20 @@
         <v>63</v>
       </c>
       <c r="B406" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C406" s="9">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="D406" s="4">
-        <v>72.8261341348245</v>
+        <v>58.891247360135701</v>
       </c>
       <c r="E406" s="6">
         <v>20</v>
       </c>
       <c r="F406" s="3">
-        <f t="shared" si="8"/>
-        <v>58.260907307859597</v>
+        <f>D406-(D406*E406)/100</f>
+        <v>47.112997888108559</v>
       </c>
       <c r="G406" s="1"/>
       <c r="H406" s="8" t="s">
@@ -10954,20 +10971,20 @@
         <v>64</v>
       </c>
       <c r="B407" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C407" s="9">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D407" s="4">
-        <v>111.433416666667</v>
+        <v>124.950204349591</v>
       </c>
       <c r="E407" s="6">
         <v>20</v>
       </c>
       <c r="F407" s="3">
-        <f t="shared" ref="F407:F414" si="9">D407-(D407*E407)/100</f>
-        <v>89.1467333333336</v>
+        <f>D407-(D407*E407)/100</f>
+        <v>99.960163479672801</v>
       </c>
       <c r="G407" s="1"/>
       <c r="H407" s="8" t="s">
@@ -10979,20 +10996,20 @@
         <v>65</v>
       </c>
       <c r="B408" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C408" s="9">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D408" s="4">
-        <v>42.042984659090898</v>
+        <v>42.763601458579302</v>
       </c>
       <c r="E408" s="6">
         <v>20</v>
       </c>
       <c r="F408" s="3">
-        <f t="shared" si="9"/>
-        <v>33.634387727272717</v>
+        <f>D408-(D408*E408)/100</f>
+        <v>34.210881166863444</v>
       </c>
       <c r="G408" s="1"/>
       <c r="H408" s="8" t="s">
@@ -11004,20 +11021,20 @@
         <v>134</v>
       </c>
       <c r="B409" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C409" s="9">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D409" s="4">
-        <v>88.492330346601506</v>
+        <v>71.206216137052095</v>
       </c>
       <c r="E409" s="6">
         <v>20</v>
       </c>
       <c r="F409" s="3">
-        <f t="shared" si="9"/>
-        <v>70.793864277281202</v>
+        <f>D409-(D409*E409)/100</f>
+        <v>56.964972909641673</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="8"/>
@@ -11027,20 +11044,20 @@
         <v>133</v>
       </c>
       <c r="B410" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C410" s="9">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="D410" s="4">
-        <v>28.136091954023001</v>
+        <v>29.326201298701299</v>
       </c>
       <c r="E410" s="6">
         <v>20</v>
       </c>
       <c r="F410" s="3">
-        <f t="shared" si="9"/>
-        <v>22.508873563218401</v>
+        <f>D410-(D410*E410)/100</f>
+        <v>23.460961038961038</v>
       </c>
       <c r="G410" s="1"/>
       <c r="H410" s="8"/>
@@ -11050,20 +11067,16 @@
         <v>135</v>
       </c>
       <c r="B411" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C411" s="9">
-        <v>64</v>
-      </c>
-      <c r="D411" s="4">
-        <v>34.340737500000003</v>
-      </c>
+        <v>46021</v>
+      </c>
+      <c r="C411" s="9"/>
+      <c r="D411" s="4"/>
       <c r="E411" s="6">
         <v>20</v>
       </c>
       <c r="F411" s="3">
-        <f t="shared" si="9"/>
-        <v>27.472590000000004</v>
+        <f t="shared" ref="F411:F414" si="9">D411-(D411*E411)/100</f>
+        <v>0</v>
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="8"/>
@@ -11073,20 +11086,20 @@
         <v>136</v>
       </c>
       <c r="B412" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C412" s="9">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="D412" s="4">
-        <v>33.937659107906001</v>
+        <v>43.976640382483303</v>
       </c>
       <c r="E412" s="6">
         <v>20</v>
       </c>
       <c r="F412" s="3">
         <f t="shared" si="9"/>
-        <v>27.1501272863248</v>
+        <v>35.181312305986644</v>
       </c>
       <c r="G412" s="1"/>
       <c r="H412" s="8"/>
@@ -11096,20 +11109,20 @@
         <v>140</v>
       </c>
       <c r="B413" s="11">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C413" s="9">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D413" s="4">
-        <v>32.489529914529903</v>
+        <v>179.64469126334899</v>
       </c>
       <c r="E413" s="6">
         <v>20</v>
       </c>
       <c r="F413" s="3">
         <f t="shared" si="9"/>
-        <v>25.991623931623923</v>
+        <v>143.71575301067918</v>
       </c>
       <c r="G413" s="1"/>
       <c r="H413" s="8"/>
@@ -11119,16 +11132,20 @@
         <v>153</v>
       </c>
       <c r="B414" s="11">
-        <v>46013</v>
-      </c>
-      <c r="C414" s="9"/>
-      <c r="D414" s="4"/>
+        <v>46021</v>
+      </c>
+      <c r="C414" s="9">
+        <v>37</v>
+      </c>
+      <c r="D414" s="4">
+        <v>131.319879345603</v>
+      </c>
       <c r="E414" s="6">
         <v>20</v>
       </c>
       <c r="F414" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>105.0559034764824</v>
       </c>
       <c r="G414" s="1"/>
       <c r="H414" s="8"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="154">
   <si>
     <t>Tecnico</t>
   </si>
@@ -900,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H414"/>
+  <dimension ref="A1:H411"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -9400,20 +9400,20 @@
         <v>4</v>
       </c>
       <c r="B344" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C344" s="9">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D344" s="12">
-        <v>31.189142473118299</v>
+        <v>35.775566502463001</v>
       </c>
       <c r="E344" s="13">
         <v>20</v>
       </c>
       <c r="F344" s="14">
         <f t="shared" si="8"/>
-        <v>24.951313978494639</v>
+        <v>28.620453201970399</v>
       </c>
       <c r="G344" s="15" t="s">
         <v>67</v>
@@ -9427,20 +9427,20 @@
         <v>5</v>
       </c>
       <c r="B345" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C345" s="9">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="D345" s="4">
-        <v>40.789290597474</v>
+        <v>24.4746569796324</v>
       </c>
       <c r="E345" s="6">
         <v>20</v>
       </c>
       <c r="F345" s="3">
         <f t="shared" si="8"/>
-        <v>32.631432477979203</v>
+        <v>19.579725583705919</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>67</v>
@@ -9454,20 +9454,20 @@
         <v>139</v>
       </c>
       <c r="B346" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C346" s="9">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="D346" s="4">
-        <v>135.02601646500801</v>
+        <v>13.1692001683502</v>
       </c>
       <c r="E346" s="6">
         <v>20</v>
       </c>
       <c r="F346" s="3">
         <f t="shared" si="8"/>
-        <v>108.02081317200641</v>
+        <v>10.535360134680159</v>
       </c>
       <c r="G346" s="1"/>
       <c r="H346" s="8"/>
@@ -9477,20 +9477,20 @@
         <v>6</v>
       </c>
       <c r="B347" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C347" s="9">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D347" s="4">
-        <v>31.3221358219987</v>
+        <v>25.525050344334201</v>
       </c>
       <c r="E347" s="6">
         <v>20</v>
       </c>
       <c r="F347" s="3">
         <f t="shared" si="8"/>
-        <v>25.057708657598958</v>
+        <v>20.420040275467361</v>
       </c>
       <c r="G347" s="1"/>
       <c r="H347" s="8" t="s">
@@ -9502,20 +9502,20 @@
         <v>7</v>
       </c>
       <c r="B348" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C348" s="9">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="D348" s="4">
-        <v>203.80709722222201</v>
+        <v>73.655240155677603</v>
       </c>
       <c r="E348" s="6">
         <v>20</v>
       </c>
       <c r="F348" s="3">
         <f t="shared" si="8"/>
-        <v>163.0456777777776</v>
+        <v>58.924192124542081</v>
       </c>
       <c r="G348" s="1"/>
       <c r="H348" s="8" t="s">
@@ -9527,20 +9527,20 @@
         <v>8</v>
       </c>
       <c r="B349" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C349" s="9">
         <v>152</v>
       </c>
       <c r="D349" s="4">
-        <v>29.248444138400199</v>
+        <v>32.478216836734703</v>
       </c>
       <c r="E349" s="6">
         <v>20</v>
       </c>
       <c r="F349" s="3">
         <f t="shared" si="8"/>
-        <v>23.398755310720158</v>
+        <v>25.982573469387763</v>
       </c>
       <c r="G349" s="1"/>
       <c r="H349" s="8" t="s">
@@ -9552,20 +9552,20 @@
         <v>9</v>
       </c>
       <c r="B350" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C350" s="9">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D350" s="4">
-        <v>39.740131178707202</v>
+        <v>34.441048869520699</v>
       </c>
       <c r="E350" s="6">
         <v>20</v>
       </c>
       <c r="F350" s="3">
         <f t="shared" si="8"/>
-        <v>31.792104942965761</v>
+        <v>27.552839095616559</v>
       </c>
       <c r="G350" s="1"/>
       <c r="H350" s="8" t="s">
@@ -9577,20 +9577,20 @@
         <v>10</v>
       </c>
       <c r="B351" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C351" s="9">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="D351" s="4">
-        <v>35.579655487804899</v>
+        <v>42.239571969697003</v>
       </c>
       <c r="E351" s="6">
         <v>20</v>
       </c>
       <c r="F351" s="3">
         <f t="shared" si="8"/>
-        <v>28.463724390243918</v>
+        <v>33.791657575757604</v>
       </c>
       <c r="G351" s="1"/>
       <c r="H351" s="8" t="s">
@@ -9602,20 +9602,20 @@
         <v>11</v>
       </c>
       <c r="B352" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C352" s="9">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="D352" s="4">
-        <v>39.740131178707202</v>
+        <v>32.640037651850697</v>
       </c>
       <c r="E352" s="6">
         <v>20</v>
       </c>
       <c r="F352" s="3">
         <f t="shared" si="8"/>
-        <v>31.792104942965761</v>
+        <v>26.112030121480558</v>
       </c>
       <c r="G352" s="1"/>
       <c r="H352" s="8" t="s">
@@ -9627,20 +9627,20 @@
         <v>12</v>
       </c>
       <c r="B353" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C353" s="9">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="D353" s="4">
-        <v>57.557192882945799</v>
+        <v>35.005030303030303</v>
       </c>
       <c r="E353" s="6">
         <v>20</v>
       </c>
       <c r="F353" s="3">
         <f t="shared" si="8"/>
-        <v>46.045754306356642</v>
+        <v>28.004024242424244</v>
       </c>
       <c r="G353" s="1"/>
       <c r="H353" s="8" t="s">
@@ -9652,20 +9652,20 @@
         <v>13</v>
       </c>
       <c r="B354" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C354" s="9">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="D354" s="4">
-        <v>57.557192882945799</v>
+        <v>38.129028768970599</v>
       </c>
       <c r="E354" s="6">
         <v>20</v>
       </c>
       <c r="F354" s="3">
         <f t="shared" si="8"/>
-        <v>46.045754306356642</v>
+        <v>30.503223015176481</v>
       </c>
       <c r="G354" s="1"/>
       <c r="H354" s="8" t="s">
@@ -9677,20 +9677,20 @@
         <v>14</v>
       </c>
       <c r="B355" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C355" s="9">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D355" s="4">
-        <v>43.046664760425003</v>
+        <v>33.669544527352798</v>
       </c>
       <c r="E355" s="6">
         <v>20</v>
       </c>
       <c r="F355" s="3">
         <f t="shared" si="8"/>
-        <v>34.437331808340005</v>
+        <v>26.935635621882238</v>
       </c>
       <c r="G355" s="1"/>
       <c r="H355" s="8" t="s">
@@ -9702,20 +9702,20 @@
         <v>16</v>
       </c>
       <c r="B356" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C356" s="9">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D356" s="4">
-        <v>30.141236069051001</v>
+        <v>32.478216836734703</v>
       </c>
       <c r="E356" s="6">
         <v>20</v>
       </c>
       <c r="F356" s="3">
         <f t="shared" si="8"/>
-        <v>24.1129888552408</v>
+        <v>25.982573469387763</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="8" t="s">
@@ -9727,20 +9727,20 @@
         <v>151</v>
       </c>
       <c r="B357" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C357" s="9">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="D357" s="4">
-        <v>123.08915557266199</v>
+        <v>75.002930172068801</v>
       </c>
       <c r="E357" s="6">
         <v>20</v>
       </c>
       <c r="F357" s="3">
         <f t="shared" si="8"/>
-        <v>98.471324458129601</v>
+        <v>60.002344137655044</v>
       </c>
       <c r="G357" s="1"/>
       <c r="H357" s="8"/>
@@ -9750,20 +9750,20 @@
         <v>17</v>
       </c>
       <c r="B358" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C358" s="9">
         <v>136</v>
       </c>
       <c r="D358" s="4">
-        <v>37.687197916666697</v>
+        <v>45.794366004094002</v>
       </c>
       <c r="E358" s="6">
         <v>20</v>
       </c>
       <c r="F358" s="3">
-        <f>D358-(D358*E358)/100</f>
-        <v>30.149758333333359</v>
+        <f t="shared" ref="F358:F388" si="9">D358-(D358*E358)/100</f>
+        <v>36.635492803275199</v>
       </c>
       <c r="G358" s="1"/>
       <c r="H358" s="8" t="s">
@@ -9775,20 +9775,20 @@
         <v>18</v>
       </c>
       <c r="B359" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C359" s="9">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D359" s="4">
-        <v>34.291203234185197</v>
+        <v>39.97243125</v>
       </c>
       <c r="E359" s="6">
         <v>20</v>
       </c>
       <c r="F359" s="3">
-        <f>D359-(D359*E359)/100</f>
-        <v>27.432962587348158</v>
+        <f t="shared" si="9"/>
+        <v>31.977944999999998</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="8" t="s">
@@ -9800,20 +9800,20 @@
         <v>20</v>
       </c>
       <c r="B360" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C360" s="9">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D360" s="4">
-        <v>33.496389610872797</v>
+        <v>35.341841067813</v>
       </c>
       <c r="E360" s="6">
         <v>20</v>
       </c>
       <c r="F360" s="3">
-        <f>D360-(D360*E360)/100</f>
-        <v>26.797111688698237</v>
+        <f t="shared" si="9"/>
+        <v>28.2734728542504</v>
       </c>
       <c r="G360" s="1"/>
       <c r="H360" s="8" t="s">
@@ -9825,20 +9825,20 @@
         <v>21</v>
       </c>
       <c r="B361" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C361" s="9">
         <v>176</v>
       </c>
       <c r="D361" s="4">
-        <v>34.022932412626503</v>
+        <v>31.8962839646465</v>
       </c>
       <c r="E361" s="6">
         <v>20</v>
       </c>
       <c r="F361" s="3">
-        <f>D361-(D361*E361)/100</f>
-        <v>27.218345930101201</v>
+        <f t="shared" si="9"/>
+        <v>25.517027171717199</v>
       </c>
       <c r="G361" s="1"/>
       <c r="H361" s="8" t="s">
@@ -9850,20 +9850,20 @@
         <v>22</v>
       </c>
       <c r="B362" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C362" s="9">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D362" s="4">
-        <v>61.601600296300099</v>
+        <v>63.709436208725002</v>
       </c>
       <c r="E362" s="6">
         <v>20</v>
       </c>
       <c r="F362" s="3">
-        <f>D362-(D362*E362)/100</f>
-        <v>49.281280237040079</v>
+        <f t="shared" si="9"/>
+        <v>50.967548966980004</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="8" t="s">
@@ -9875,20 +9875,20 @@
         <v>23</v>
       </c>
       <c r="B363" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C363" s="9">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D363" s="4">
-        <v>33.456470827983601</v>
+        <v>32.779111842105301</v>
       </c>
       <c r="E363" s="6">
         <v>20</v>
       </c>
       <c r="F363" s="3">
-        <f>D363-(D363*E363)/100</f>
-        <v>26.765176662386882</v>
+        <f t="shared" si="9"/>
+        <v>26.22328947368424</v>
       </c>
       <c r="G363" s="1"/>
       <c r="H363" s="8" t="s">
@@ -9900,20 +9900,20 @@
         <v>24</v>
       </c>
       <c r="B364" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C364" s="9">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D364" s="4">
-        <v>64.034912881533003</v>
+        <v>64.917773263771807</v>
       </c>
       <c r="E364" s="6">
         <v>20</v>
       </c>
       <c r="F364" s="3">
-        <f>D364-(D364*E364)/100</f>
-        <v>51.227930305226401</v>
+        <f t="shared" si="9"/>
+        <v>51.934218611017442</v>
       </c>
       <c r="G364" s="1"/>
       <c r="H364" s="8" t="s">
@@ -9925,20 +9925,20 @@
         <v>25</v>
       </c>
       <c r="B365" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C365" s="9">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="D365" s="4">
-        <v>87.691933139534896</v>
+        <v>36.446089200666698</v>
       </c>
       <c r="E365" s="6">
         <v>20</v>
       </c>
       <c r="F365" s="3">
-        <f>D365-(D365*E365)/100</f>
-        <v>70.153546511627923</v>
+        <f t="shared" si="9"/>
+        <v>29.156871360533358</v>
       </c>
       <c r="G365" s="1"/>
       <c r="H365" s="8" t="s">
@@ -9950,20 +9950,20 @@
         <v>26</v>
       </c>
       <c r="B366" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C366" s="9">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D366" s="4">
-        <v>38.876902294388202</v>
+        <v>36.268250262094597</v>
       </c>
       <c r="E366" s="6">
         <v>20</v>
       </c>
       <c r="F366" s="3">
-        <f>D366-(D366*E366)/100</f>
-        <v>31.10152183551056</v>
+        <f t="shared" si="9"/>
+        <v>29.014600209675677</v>
       </c>
       <c r="G366" s="1"/>
       <c r="H366" s="8" t="s">
@@ -9975,20 +9975,20 @@
         <v>27</v>
       </c>
       <c r="B367" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C367" s="9">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D367" s="4">
-        <v>52.252847876867698</v>
+        <v>49.270387424388403</v>
       </c>
       <c r="E367" s="6">
         <v>20</v>
       </c>
       <c r="F367" s="3">
-        <f>D367-(D367*E367)/100</f>
-        <v>41.802278301494155</v>
+        <f t="shared" si="9"/>
+        <v>39.416309939510725</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="8" t="s">
@@ -10000,20 +10000,20 @@
         <v>28</v>
       </c>
       <c r="B368" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C368" s="9">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D368" s="4">
-        <v>131.319879345603</v>
+        <v>84.606319710017999</v>
       </c>
       <c r="E368" s="6">
         <v>20</v>
       </c>
       <c r="F368" s="3">
-        <f>D368-(D368*E368)/100</f>
-        <v>105.0559034764824</v>
+        <f t="shared" si="9"/>
+        <v>67.685055768014394</v>
       </c>
       <c r="G368" s="1"/>
       <c r="H368" s="8" t="s">
@@ -10025,20 +10025,20 @@
         <v>29</v>
       </c>
       <c r="B369" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C369" s="9">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D369" s="4">
-        <v>34.397298925667798</v>
+        <v>38.547943113772398</v>
       </c>
       <c r="E369" s="6">
         <v>20</v>
       </c>
       <c r="F369" s="3">
-        <f>D369-(D369*E369)/100</f>
-        <v>27.517839140534239</v>
+        <f t="shared" si="9"/>
+        <v>30.838354491017917</v>
       </c>
       <c r="G369" s="1"/>
       <c r="H369" s="8" t="s">
@@ -10050,20 +10050,20 @@
         <v>30</v>
       </c>
       <c r="B370" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C370" s="9">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="D370" s="4">
-        <v>31.601682689636799</v>
+        <v>25.508038155418699</v>
       </c>
       <c r="E370" s="6">
         <v>20</v>
       </c>
       <c r="F370" s="3">
-        <f>D370-(D370*E370)/100</f>
-        <v>25.281346151709439</v>
+        <f t="shared" si="9"/>
+        <v>20.406430524334958</v>
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="8" t="s">
@@ -10075,20 +10075,20 @@
         <v>137</v>
       </c>
       <c r="B371" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C371" s="9">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D371" s="4">
-        <v>86.950255825442696</v>
+        <v>71.615705302551106</v>
       </c>
       <c r="E371" s="6">
         <v>20</v>
       </c>
       <c r="F371" s="3">
-        <f>D371-(D371*E371)/100</f>
-        <v>69.56020466035416</v>
+        <f t="shared" si="9"/>
+        <v>57.292564242040882</v>
       </c>
       <c r="G371" s="1"/>
       <c r="H371" s="8" t="s">
@@ -10100,20 +10100,20 @@
         <v>31</v>
       </c>
       <c r="B372" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C372" s="9">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D372" s="4">
-        <v>51.625046106299003</v>
+        <v>47.491338336460302</v>
       </c>
       <c r="E372" s="6">
         <v>20</v>
       </c>
       <c r="F372" s="3">
-        <f>D372-(D372*E372)/100</f>
-        <v>41.300036885039205</v>
+        <f t="shared" si="9"/>
+        <v>37.99307066916824</v>
       </c>
       <c r="G372" s="1"/>
       <c r="H372" s="8" t="s">
@@ -10125,20 +10125,20 @@
         <v>32</v>
       </c>
       <c r="B373" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C373" s="9">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="D373" s="4">
-        <v>73.388246636052401</v>
+        <v>30.789425559947301</v>
       </c>
       <c r="E373" s="6">
         <v>20</v>
       </c>
       <c r="F373" s="3">
-        <f>D373-(D373*E373)/100</f>
-        <v>58.710597308841919</v>
+        <f t="shared" si="9"/>
+        <v>24.631540447957839</v>
       </c>
       <c r="G373" s="1"/>
       <c r="H373" s="8" t="s">
@@ -10147,1008 +10147,943 @@
     </row>
     <row r="374" spans="1:8">
       <c r="A374" s="1" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="B374" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C374" s="9">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="D374" s="4">
-        <v>131.319879345603</v>
+        <v>33.184156250000001</v>
       </c>
       <c r="E374" s="6">
         <v>20</v>
       </c>
       <c r="F374" s="3">
-        <f>D374-(D374*E374)/100</f>
-        <v>105.0559034764824</v>
+        <f t="shared" si="9"/>
+        <v>26.547325000000001</v>
       </c>
       <c r="G374" s="1"/>
-      <c r="H374" s="8"/>
+      <c r="H374" s="8" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="375" spans="1:8">
       <c r="A375" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B375" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C375" s="9">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="D375" s="4">
-        <v>31.188293255131999</v>
+        <v>37.840107843137197</v>
       </c>
       <c r="E375" s="6">
         <v>20</v>
       </c>
       <c r="F375" s="3">
-        <f>D375-(D375*E375)/100</f>
-        <v>24.950634604105598</v>
+        <f t="shared" si="9"/>
+        <v>30.272086274509757</v>
       </c>
       <c r="G375" s="1"/>
       <c r="H375" s="8" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="376" spans="1:8">
       <c r="A376" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B376" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C376" s="9">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="D376" s="4">
-        <v>86.971927575464505</v>
+        <v>71.335528301886796</v>
       </c>
       <c r="E376" s="6">
         <v>20</v>
       </c>
       <c r="F376" s="3">
-        <f>D376-(D376*E376)/100</f>
-        <v>69.577542060371599</v>
+        <f t="shared" si="9"/>
+        <v>57.068422641509436</v>
       </c>
       <c r="G376" s="1"/>
       <c r="H376" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="377" spans="1:8">
       <c r="A377" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B377" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C377" s="9">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D377" s="4">
-        <v>69.352811619718295</v>
+        <v>41.7438490300325</v>
       </c>
       <c r="E377" s="6">
         <v>20</v>
       </c>
       <c r="F377" s="3">
-        <f>D377-(D377*E377)/100</f>
-        <v>55.482249295774636</v>
+        <f t="shared" si="9"/>
+        <v>33.395079224025999</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="8" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="378" spans="1:8">
-      <c r="A378" s="1" t="s">
-        <v>36</v>
+      <c r="A378" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="B378" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C378" s="9">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D378" s="4">
-        <v>36.535145325203302</v>
+        <v>64.905633548887195</v>
       </c>
       <c r="E378" s="6">
         <v>20</v>
       </c>
       <c r="F378" s="3">
-        <f>D378-(D378*E378)/100</f>
-        <v>29.228116260162643</v>
+        <f t="shared" si="9"/>
+        <v>51.924506839109753</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="379" spans="1:8">
-      <c r="A379" s="10" t="s">
-        <v>37</v>
+      <c r="A379" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B379" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C379" s="9">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="D379" s="4">
-        <v>65.114581459390905</v>
+        <v>28.541103030302999</v>
       </c>
       <c r="E379" s="6">
         <v>20</v>
       </c>
       <c r="F379" s="3">
-        <f>D379-(D379*E379)/100</f>
-        <v>52.091665167512723</v>
+        <f t="shared" si="9"/>
+        <v>22.832882424242399</v>
       </c>
       <c r="G379" s="1"/>
       <c r="H379" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="380" spans="1:8">
       <c r="A380" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B380" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C380" s="9">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D380" s="4">
-        <v>73.043415488971604</v>
+        <v>84.281554349831296</v>
       </c>
       <c r="E380" s="6">
         <v>20</v>
       </c>
       <c r="F380" s="3">
-        <f>D380-(D380*E380)/100</f>
-        <v>58.434732391177285</v>
+        <f t="shared" si="9"/>
+        <v>67.425243479865031</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="381" spans="1:8">
       <c r="A381" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B381" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C381" s="9">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D381" s="4">
-        <v>122.86082778001099</v>
+        <v>24.612980407666601</v>
       </c>
       <c r="E381" s="6">
         <v>20</v>
       </c>
       <c r="F381" s="3">
-        <f>D381-(D381*E381)/100</f>
-        <v>98.288662224008789</v>
+        <f t="shared" si="9"/>
+        <v>19.69038432613328</v>
       </c>
       <c r="G381" s="1"/>
       <c r="H381" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="382" spans="1:8">
       <c r="A382" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B382" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C382" s="9">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D382" s="4">
-        <v>42.955545565289299</v>
+        <v>22.9888100775194</v>
       </c>
       <c r="E382" s="6">
         <v>20</v>
       </c>
       <c r="F382" s="3">
-        <f>D382-(D382*E382)/100</f>
-        <v>34.364436452231438</v>
+        <f t="shared" si="9"/>
+        <v>18.391048062015521</v>
       </c>
       <c r="G382" s="1"/>
       <c r="H382" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="383" spans="1:8">
       <c r="A383" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B383" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C383" s="9">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D383" s="4">
-        <v>29.326201298701299</v>
+        <v>36.1170913690476</v>
       </c>
       <c r="E383" s="6">
         <v>20</v>
       </c>
       <c r="F383" s="3">
-        <f>D383-(D383*E383)/100</f>
-        <v>23.460961038961038</v>
+        <f t="shared" si="9"/>
+        <v>28.893673095238078</v>
       </c>
       <c r="G383" s="1"/>
       <c r="H383" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="384" spans="1:8">
       <c r="A384" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B384" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C384" s="9">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D384" s="4">
-        <v>39.0856017441861</v>
+        <v>46.248983974359</v>
       </c>
       <c r="E384" s="6">
         <v>20</v>
       </c>
       <c r="F384" s="3">
-        <f>D384-(D384*E384)/100</f>
-        <v>31.268481395348878</v>
+        <f t="shared" si="9"/>
+        <v>36.999187179487201</v>
       </c>
       <c r="G384" s="1"/>
       <c r="H384" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="385" spans="1:8">
       <c r="A385" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B385" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C385" s="9">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D385" s="4">
-        <v>44.091314393939399</v>
+        <v>22.161195577953698</v>
       </c>
       <c r="E385" s="6">
         <v>20</v>
       </c>
       <c r="F385" s="3">
-        <f>D385-(D385*E385)/100</f>
-        <v>35.273051515151522</v>
+        <f t="shared" si="9"/>
+        <v>17.728956462362959</v>
       </c>
       <c r="G385" s="1"/>
       <c r="H385" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="386" spans="1:8">
       <c r="A386" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B386" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C386" s="9">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="D386" s="4">
-        <v>138.87538313167499</v>
+        <v>32.588220876751798</v>
       </c>
       <c r="E386" s="6">
         <v>20</v>
       </c>
       <c r="F386" s="3">
-        <f>D386-(D386*E386)/100</f>
-        <v>111.10030650534</v>
+        <f t="shared" si="9"/>
+        <v>26.070576701401439</v>
       </c>
       <c r="G386" s="1"/>
       <c r="H386" s="8" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="387" spans="1:8">
       <c r="A387" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B387" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C387" s="9">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="D387" s="4">
-        <v>33.228430586413999</v>
+        <v>33.698501863353997</v>
       </c>
       <c r="E387" s="6">
         <v>20</v>
       </c>
       <c r="F387" s="3">
-        <f>D387-(D387*E387)/100</f>
-        <v>26.5827444691312</v>
+        <f t="shared" si="9"/>
+        <v>26.958801490683197</v>
       </c>
       <c r="G387" s="1"/>
       <c r="H387" s="8" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="388" spans="1:8">
-      <c r="A388" s="1" t="s">
-        <v>46</v>
+      <c r="A388" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="B388" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C388" s="9">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D388" s="4">
-        <v>42.893889259977797</v>
+        <v>71.335528301886796</v>
       </c>
       <c r="E388" s="6">
         <v>20</v>
       </c>
       <c r="F388" s="3">
-        <f>D388-(D388*E388)/100</f>
-        <v>34.315111407982236</v>
+        <f t="shared" si="9"/>
+        <v>57.068422641509436</v>
       </c>
       <c r="G388" s="1"/>
       <c r="H388" s="8" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="389" spans="1:8">
       <c r="A389" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B389" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C389" s="9">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D389" s="4">
-        <v>69.352811619718295</v>
+        <v>71.335528301886796</v>
       </c>
       <c r="E389" s="6">
         <v>20</v>
       </c>
       <c r="F389" s="3">
-        <f>D389-(D389*E389)/100</f>
-        <v>55.482249295774636</v>
+        <f t="shared" ref="F389:F408" si="10">D389-(D389*E389)/100</f>
+        <v>57.068422641509436</v>
       </c>
       <c r="G389" s="1"/>
       <c r="H389" s="8" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
     </row>
     <row r="390" spans="1:8">
-      <c r="A390" s="10" t="s">
-        <v>48</v>
+      <c r="A390" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B390" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C390" s="9">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="D390" s="4">
-        <v>69.352811619718295</v>
+        <v>32.199673611111102</v>
       </c>
       <c r="E390" s="6">
         <v>20</v>
       </c>
       <c r="F390" s="3">
-        <f>D390-(D390*E390)/100</f>
-        <v>55.482249295774636</v>
+        <f t="shared" si="10"/>
+        <v>25.759738888888883</v>
       </c>
       <c r="G390" s="1"/>
       <c r="H390" s="8" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="391" spans="1:8">
       <c r="A391" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B391" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C391" s="9">
-        <v>184</v>
+        <v>55</v>
       </c>
       <c r="D391" s="4">
-        <v>35.764634634387299</v>
+        <v>21.2992298850575</v>
       </c>
       <c r="E391" s="6">
         <v>20</v>
       </c>
       <c r="F391" s="3">
-        <f>D391-(D391*E391)/100</f>
-        <v>28.61170770750984</v>
+        <f t="shared" si="10"/>
+        <v>17.039383908045998</v>
       </c>
       <c r="G391" s="1"/>
       <c r="H391" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="392" spans="1:8">
       <c r="A392" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B392" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C392" s="9">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D392" s="4">
-        <v>53.564347826086902</v>
+        <v>30.044605140619499</v>
       </c>
       <c r="E392" s="6">
         <v>20</v>
       </c>
       <c r="F392" s="3">
-        <f>D392-(D392*E392)/100</f>
-        <v>42.85147826086952</v>
+        <f t="shared" si="10"/>
+        <v>24.035684112495598</v>
       </c>
       <c r="G392" s="1"/>
       <c r="H392" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="393" spans="1:8">
       <c r="A393" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B393" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C393" s="9">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D393" s="4">
-        <v>35.448980113636303</v>
+        <v>31.176832702816299</v>
       </c>
       <c r="E393" s="6">
         <v>20</v>
       </c>
       <c r="F393" s="3">
-        <f>D393-(D393*E393)/100</f>
-        <v>28.359184090909043</v>
+        <f t="shared" si="10"/>
+        <v>24.94146616225304</v>
       </c>
       <c r="G393" s="1"/>
       <c r="H393" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="394" spans="1:8">
       <c r="A394" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B394" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C394" s="9">
         <v>184</v>
       </c>
       <c r="D394" s="4">
-        <v>47.900705877298499</v>
+        <v>38.688061252687</v>
       </c>
       <c r="E394" s="6">
         <v>20</v>
       </c>
       <c r="F394" s="3">
-        <f>D394-(D394*E394)/100</f>
-        <v>38.320564701838798</v>
+        <f t="shared" si="10"/>
+        <v>30.9504490021496</v>
       </c>
       <c r="G394" s="1"/>
       <c r="H394" s="8" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="395" spans="1:8">
       <c r="A395" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B395" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C395" s="9">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D395" s="4">
-        <v>35.043873962999797</v>
+        <v>33.210764142738199</v>
       </c>
       <c r="E395" s="6">
         <v>20</v>
       </c>
       <c r="F395" s="3">
-        <f>D395-(D395*E395)/100</f>
-        <v>28.035099170399839</v>
+        <f t="shared" si="10"/>
+        <v>26.568611314190559</v>
       </c>
       <c r="G395" s="1"/>
       <c r="H395" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="396" spans="1:8">
       <c r="A396" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B396" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C396" s="9">
         <v>176</v>
       </c>
       <c r="D396" s="4">
-        <v>34.0364644402894</v>
+        <v>33.515705679682199</v>
       </c>
       <c r="E396" s="6">
         <v>20</v>
       </c>
       <c r="F396" s="3">
-        <f>D396-(D396*E396)/100</f>
-        <v>27.22917155223152</v>
+        <f t="shared" si="10"/>
+        <v>26.812564543745758</v>
       </c>
       <c r="G396" s="1"/>
       <c r="H396" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="397" spans="1:8">
       <c r="A397" s="1" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="B397" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C397" s="9">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="D397" s="4">
-        <v>131.319879345603</v>
+        <v>33.111744631252002</v>
       </c>
       <c r="E397" s="6">
         <v>20</v>
       </c>
       <c r="F397" s="3">
-        <f>D397-(D397*E397)/100</f>
-        <v>105.0559034764824</v>
+        <f t="shared" si="10"/>
+        <v>26.489395705001602</v>
       </c>
       <c r="G397" s="1"/>
-      <c r="H397" s="8"/>
+      <c r="H397" s="8" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B398" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C398" s="9">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D398" s="4">
-        <v>34.774626321423803</v>
+        <v>36.608423963393903</v>
       </c>
       <c r="E398" s="6">
         <v>20</v>
       </c>
       <c r="F398" s="3">
-        <f>D398-(D398*E398)/100</f>
-        <v>27.819701057139042</v>
+        <f t="shared" si="10"/>
+        <v>29.286739170715123</v>
       </c>
       <c r="G398" s="1"/>
       <c r="H398" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="399" spans="1:8">
       <c r="A399" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B399" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C399" s="9">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="D399" s="4">
-        <v>32.023106772613403</v>
+        <v>32.443847650833398</v>
       </c>
       <c r="E399" s="6">
         <v>20</v>
       </c>
       <c r="F399" s="3">
-        <f>D399-(D399*E399)/100</f>
-        <v>25.618485418090721</v>
+        <f t="shared" si="10"/>
+        <v>25.95507812066672</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="400" spans="1:8">
       <c r="A400" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B400" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C400" s="9">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D400" s="4">
-        <v>34.662226704545397</v>
+        <v>29.257409937888202</v>
       </c>
       <c r="E400" s="6">
         <v>20</v>
       </c>
       <c r="F400" s="3">
-        <f>D400-(D400*E400)/100</f>
-        <v>27.729781363636317</v>
+        <f t="shared" si="10"/>
+        <v>23.405927950310563</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="401" spans="1:8">
       <c r="A401" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B401" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C401" s="9">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D401" s="4">
-        <v>41.537577078982302</v>
+        <v>42.699784722222198</v>
       </c>
       <c r="E401" s="6">
         <v>20</v>
       </c>
       <c r="F401" s="3">
-        <f>D401-(D401*E401)/100</f>
-        <v>33.230061663185843</v>
+        <f t="shared" si="10"/>
+        <v>34.159827777777757</v>
       </c>
       <c r="G401" s="1"/>
       <c r="H401" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="402" spans="1:8">
       <c r="A402" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B402" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C402" s="9">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D402" s="4">
-        <v>32.503339843749998</v>
+        <v>42.699784722222198</v>
       </c>
       <c r="E402" s="6">
         <v>20</v>
       </c>
       <c r="F402" s="3">
-        <f>D402-(D402*E402)/100</f>
-        <v>26.002671874999997</v>
+        <f t="shared" si="10"/>
+        <v>34.159827777777757</v>
       </c>
       <c r="G402" s="1"/>
       <c r="H402" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="403" spans="1:8">
       <c r="A403" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B403" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C403" s="9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D403" s="4">
-        <v>45.014359929077997</v>
+        <v>39.628265434149199</v>
       </c>
       <c r="E403" s="6">
         <v>20</v>
       </c>
       <c r="F403" s="3">
-        <f>D403-(D403*E403)/100</f>
-        <v>36.011487943262395</v>
+        <f t="shared" si="10"/>
+        <v>31.702612347319359</v>
       </c>
       <c r="G403" s="1"/>
       <c r="H403" s="8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="404" spans="1:8">
       <c r="A404" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B404" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C404" s="9">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="D404" s="4">
-        <v>46.161499999999997</v>
+        <v>40.759553607604801</v>
       </c>
       <c r="E404" s="6">
         <v>20</v>
       </c>
       <c r="F404" s="3">
-        <f>D404-(D404*E404)/100</f>
-        <v>36.929199999999994</v>
+        <f t="shared" si="10"/>
+        <v>32.607642886083838</v>
       </c>
       <c r="G404" s="1"/>
       <c r="H404" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="405" spans="1:8">
       <c r="A405" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B405" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C405" s="9">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="D405" s="4">
-        <v>38.524439547383999</v>
+        <v>99.968460349462404</v>
       </c>
       <c r="E405" s="6">
         <v>20</v>
       </c>
       <c r="F405" s="3">
-        <f>D405-(D405*E405)/100</f>
-        <v>30.8195516379072</v>
+        <f t="shared" si="10"/>
+        <v>79.974768279569929</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="406" spans="1:8">
       <c r="A406" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B406" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C406" s="9">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="D406" s="4">
-        <v>58.891247360135701</v>
+        <v>45.044318038112699</v>
       </c>
       <c r="E406" s="6">
         <v>20</v>
       </c>
       <c r="F406" s="3">
-        <f>D406-(D406*E406)/100</f>
-        <v>47.112997888108559</v>
+        <f t="shared" si="10"/>
+        <v>36.035454430490162</v>
       </c>
       <c r="G406" s="1"/>
       <c r="H406" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="407" spans="1:8">
-      <c r="A407" s="1" t="s">
-        <v>64</v>
+      <c r="A407" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="B407" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C407" s="9">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="D407" s="4">
-        <v>124.950204349591</v>
+        <v>73.852854568325398</v>
       </c>
       <c r="E407" s="6">
         <v>20</v>
       </c>
       <c r="F407" s="3">
-        <f>D407-(D407*E407)/100</f>
-        <v>99.960163479672801</v>
+        <f t="shared" si="10"/>
+        <v>59.082283654660316</v>
       </c>
       <c r="G407" s="1"/>
-      <c r="H407" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="H407" s="8"/>
     </row>
     <row r="408" spans="1:8">
       <c r="A408" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="B408" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C408" s="9">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="D408" s="4">
-        <v>42.763601458579302</v>
+        <v>22.9888100775194</v>
       </c>
       <c r="E408" s="6">
         <v>20</v>
       </c>
       <c r="F408" s="3">
-        <f>D408-(D408*E408)/100</f>
-        <v>34.210881166863444</v>
+        <f t="shared" si="10"/>
+        <v>18.391048062015521</v>
       </c>
       <c r="G408" s="1"/>
-      <c r="H408" s="8" t="s">
-        <v>131</v>
-      </c>
+      <c r="H408" s="8"/>
     </row>
     <row r="409" spans="1:8">
-      <c r="A409" s="10" t="s">
-        <v>134</v>
+      <c r="A409" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B409" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C409" s="9">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D409" s="4">
-        <v>71.206216137052095</v>
+        <v>33.755016741071401</v>
       </c>
       <c r="E409" s="6">
         <v>20</v>
       </c>
       <c r="F409" s="3">
-        <f>D409-(D409*E409)/100</f>
-        <v>56.964972909641673</v>
+        <f t="shared" ref="F409:F411" si="11">D409-(D409*E409)/100</f>
+        <v>27.004013392857122</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="8"/>
     </row>
     <row r="410" spans="1:8">
       <c r="A410" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B410" s="11">
-        <v>46021</v>
+        <v>46387</v>
       </c>
       <c r="C410" s="9">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D410" s="4">
-        <v>29.326201298701299</v>
+        <v>32.173319999236902</v>
       </c>
       <c r="E410" s="6">
         <v>20</v>
       </c>
       <c r="F410" s="3">
-        <f>D410-(D410*E410)/100</f>
-        <v>23.460961038961038</v>
+        <f t="shared" si="11"/>
+        <v>25.738655999389522</v>
       </c>
       <c r="G410" s="1"/>
       <c r="H410" s="8"/>
     </row>
     <row r="411" spans="1:8">
       <c r="A411" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B411" s="11">
-        <v>46021</v>
-      </c>
-      <c r="C411" s="9"/>
-      <c r="D411" s="4"/>
+        <v>46387</v>
+      </c>
+      <c r="C411" s="9">
+        <v>24</v>
+      </c>
+      <c r="D411" s="4">
+        <v>49.006107969344797</v>
+      </c>
       <c r="E411" s="6">
         <v>20</v>
       </c>
       <c r="F411" s="3">
-        <f t="shared" ref="F411:F414" si="9">D411-(D411*E411)/100</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>39.204886375475837</v>
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="8"/>
-    </row>
-    <row r="412" spans="1:8">
-      <c r="A412" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B412" s="11">
-        <v>46021</v>
-      </c>
-      <c r="C412" s="9">
-        <v>184</v>
-      </c>
-      <c r="D412" s="4">
-        <v>43.976640382483303</v>
-      </c>
-      <c r="E412" s="6">
-        <v>20</v>
-      </c>
-      <c r="F412" s="3">
-        <f t="shared" si="9"/>
-        <v>35.181312305986644</v>
-      </c>
-      <c r="G412" s="1"/>
-      <c r="H412" s="8"/>
-    </row>
-    <row r="413" spans="1:8">
-      <c r="A413" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B413" s="11">
-        <v>46021</v>
-      </c>
-      <c r="C413" s="9">
-        <v>24</v>
-      </c>
-      <c r="D413" s="4">
-        <v>179.64469126334899</v>
-      </c>
-      <c r="E413" s="6">
-        <v>20</v>
-      </c>
-      <c r="F413" s="3">
-        <f t="shared" si="9"/>
-        <v>143.71575301067918</v>
-      </c>
-      <c r="G413" s="1"/>
-      <c r="H413" s="8"/>
-    </row>
-    <row r="414" spans="1:8">
-      <c r="A414" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B414" s="11">
-        <v>46021</v>
-      </c>
-      <c r="C414" s="9">
-        <v>37</v>
-      </c>
-      <c r="D414" s="4">
-        <v>131.319879345603</v>
-      </c>
-      <c r="E414" s="6">
-        <v>20</v>
-      </c>
-      <c r="F414" s="3">
-        <f t="shared" si="9"/>
-        <v>105.0559034764824</v>
-      </c>
-      <c r="G414" s="1"/>
-      <c r="H414" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G272"/>
@@ -11497,39 +11432,39 @@
     <hyperlink ref="H370" r:id="rId342"/>
     <hyperlink ref="H372" r:id="rId343"/>
     <hyperlink ref="H373" r:id="rId344"/>
-    <hyperlink ref="H375" r:id="rId345"/>
-    <hyperlink ref="H376" r:id="rId346"/>
-    <hyperlink ref="H377" r:id="rId347"/>
-    <hyperlink ref="H378" r:id="rId348"/>
-    <hyperlink ref="H379" r:id="rId349"/>
-    <hyperlink ref="H380" r:id="rId350"/>
-    <hyperlink ref="H381" r:id="rId351"/>
-    <hyperlink ref="H382" r:id="rId352"/>
-    <hyperlink ref="H383" r:id="rId353"/>
-    <hyperlink ref="H384" r:id="rId354"/>
-    <hyperlink ref="H385" r:id="rId355"/>
-    <hyperlink ref="H386" r:id="rId356"/>
-    <hyperlink ref="H387" r:id="rId357"/>
-    <hyperlink ref="H388" r:id="rId358"/>
-    <hyperlink ref="H389" r:id="rId359"/>
-    <hyperlink ref="H390" r:id="rId360"/>
-    <hyperlink ref="H391" r:id="rId361"/>
-    <hyperlink ref="H392" r:id="rId362"/>
-    <hyperlink ref="H393" r:id="rId363"/>
-    <hyperlink ref="H394" r:id="rId364"/>
-    <hyperlink ref="H395" r:id="rId365"/>
-    <hyperlink ref="H396" r:id="rId366"/>
-    <hyperlink ref="H398" r:id="rId367"/>
-    <hyperlink ref="H399" r:id="rId368"/>
-    <hyperlink ref="H400" r:id="rId369"/>
-    <hyperlink ref="H401" r:id="rId370"/>
-    <hyperlink ref="H402" r:id="rId371"/>
-    <hyperlink ref="H403" r:id="rId372"/>
-    <hyperlink ref="H404" r:id="rId373"/>
-    <hyperlink ref="H405" r:id="rId374"/>
-    <hyperlink ref="H406" r:id="rId375"/>
-    <hyperlink ref="H407" r:id="rId376"/>
-    <hyperlink ref="H408" r:id="rId377"/>
+    <hyperlink ref="H374" r:id="rId345"/>
+    <hyperlink ref="H375" r:id="rId346"/>
+    <hyperlink ref="H376" r:id="rId347"/>
+    <hyperlink ref="H377" r:id="rId348"/>
+    <hyperlink ref="H378" r:id="rId349"/>
+    <hyperlink ref="H379" r:id="rId350"/>
+    <hyperlink ref="H380" r:id="rId351"/>
+    <hyperlink ref="H381" r:id="rId352"/>
+    <hyperlink ref="H382" r:id="rId353"/>
+    <hyperlink ref="H383" r:id="rId354"/>
+    <hyperlink ref="H384" r:id="rId355"/>
+    <hyperlink ref="H385" r:id="rId356"/>
+    <hyperlink ref="H386" r:id="rId357"/>
+    <hyperlink ref="H387" r:id="rId358"/>
+    <hyperlink ref="H388" r:id="rId359"/>
+    <hyperlink ref="H389" r:id="rId360"/>
+    <hyperlink ref="H390" r:id="rId361"/>
+    <hyperlink ref="H391" r:id="rId362"/>
+    <hyperlink ref="H392" r:id="rId363"/>
+    <hyperlink ref="H393" r:id="rId364"/>
+    <hyperlink ref="H394" r:id="rId365"/>
+    <hyperlink ref="H395" r:id="rId366"/>
+    <hyperlink ref="H396" r:id="rId367"/>
+    <hyperlink ref="H397" r:id="rId368"/>
+    <hyperlink ref="H398" r:id="rId369"/>
+    <hyperlink ref="H399" r:id="rId370"/>
+    <hyperlink ref="H400" r:id="rId371"/>
+    <hyperlink ref="H401" r:id="rId372"/>
+    <hyperlink ref="H402" r:id="rId373"/>
+    <hyperlink ref="H403" r:id="rId374"/>
+    <hyperlink ref="H404" r:id="rId375"/>
+    <hyperlink ref="H405" r:id="rId376"/>
+    <hyperlink ref="H406" r:id="rId377"/>
     <hyperlink ref="H371" r:id="rId378" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -9400,7 +9400,7 @@
         <v>4</v>
       </c>
       <c r="B344" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C344" s="9">
         <v>146</v>
@@ -9427,7 +9427,7 @@
         <v>5</v>
       </c>
       <c r="B345" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C345" s="9">
         <v>61</v>
@@ -9454,7 +9454,7 @@
         <v>139</v>
       </c>
       <c r="B346" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C346" s="9">
         <v>120</v>
@@ -9477,7 +9477,7 @@
         <v>6</v>
       </c>
       <c r="B347" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C347" s="9">
         <v>127</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="B348" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C348" s="9">
         <v>104</v>
@@ -9527,7 +9527,7 @@
         <v>8</v>
       </c>
       <c r="B349" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C349" s="9">
         <v>152</v>
@@ -9552,7 +9552,7 @@
         <v>9</v>
       </c>
       <c r="B350" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C350" s="9">
         <v>128</v>
@@ -9577,7 +9577,7 @@
         <v>10</v>
       </c>
       <c r="B351" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C351" s="9">
         <v>144</v>
@@ -9602,7 +9602,7 @@
         <v>11</v>
       </c>
       <c r="B352" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C352" s="9">
         <v>136</v>
@@ -9627,7 +9627,7 @@
         <v>12</v>
       </c>
       <c r="B353" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C353" s="9">
         <v>114</v>
@@ -9652,7 +9652,7 @@
         <v>13</v>
       </c>
       <c r="B354" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C354" s="9">
         <v>137</v>
@@ -9677,7 +9677,7 @@
         <v>14</v>
       </c>
       <c r="B355" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C355" s="9">
         <v>149</v>
@@ -9702,7 +9702,7 @@
         <v>16</v>
       </c>
       <c r="B356" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C356" s="9">
         <v>152</v>
@@ -9727,7 +9727,7 @@
         <v>151</v>
       </c>
       <c r="B357" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C357" s="9">
         <v>119</v>
@@ -9750,7 +9750,7 @@
         <v>17</v>
       </c>
       <c r="B358" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C358" s="9">
         <v>136</v>
@@ -9775,7 +9775,7 @@
         <v>18</v>
       </c>
       <c r="B359" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C359" s="9">
         <v>168</v>
@@ -9800,7 +9800,7 @@
         <v>20</v>
       </c>
       <c r="B360" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C360" s="9">
         <v>152</v>
@@ -9825,7 +9825,7 @@
         <v>21</v>
       </c>
       <c r="B361" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C361" s="9">
         <v>176</v>
@@ -9850,7 +9850,7 @@
         <v>22</v>
       </c>
       <c r="B362" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C362" s="9">
         <v>147</v>
@@ -9875,7 +9875,7 @@
         <v>23</v>
       </c>
       <c r="B363" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C363" s="9">
         <v>160</v>
@@ -9900,7 +9900,7 @@
         <v>24</v>
       </c>
       <c r="B364" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C364" s="9">
         <v>151</v>
@@ -9925,7 +9925,7 @@
         <v>25</v>
       </c>
       <c r="B365" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C365" s="9">
         <v>143</v>
@@ -9950,7 +9950,7 @@
         <v>26</v>
       </c>
       <c r="B366" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C366" s="9">
         <v>144</v>
@@ -9975,7 +9975,7 @@
         <v>27</v>
       </c>
       <c r="B367" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C367" s="9">
         <v>143</v>
@@ -10000,7 +10000,7 @@
         <v>28</v>
       </c>
       <c r="B368" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C368" s="9">
         <v>104</v>
@@ -10025,7 +10025,7 @@
         <v>29</v>
       </c>
       <c r="B369" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C369" s="9">
         <v>167</v>
@@ -10050,7 +10050,7 @@
         <v>30</v>
       </c>
       <c r="B370" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C370" s="9">
         <v>130</v>
@@ -10075,7 +10075,7 @@
         <v>137</v>
       </c>
       <c r="B371" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C371" s="9">
         <v>24</v>
@@ -10100,7 +10100,7 @@
         <v>31</v>
       </c>
       <c r="B372" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C372" s="9">
         <v>130</v>
@@ -10125,7 +10125,7 @@
         <v>32</v>
       </c>
       <c r="B373" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C373" s="9">
         <v>23</v>
@@ -10150,7 +10150,7 @@
         <v>33</v>
       </c>
       <c r="B374" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C374" s="9">
         <v>176</v>
@@ -10175,7 +10175,7 @@
         <v>34</v>
       </c>
       <c r="B375" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C375" s="9">
         <v>137</v>
@@ -10200,7 +10200,7 @@
         <v>35</v>
       </c>
       <c r="B376" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C376" s="9">
         <v>112</v>
@@ -10225,7 +10225,7 @@
         <v>36</v>
       </c>
       <c r="B377" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C377" s="9">
         <v>160</v>
@@ -10250,7 +10250,7 @@
         <v>37</v>
       </c>
       <c r="B378" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C378" s="9">
         <v>150</v>
@@ -10275,7 +10275,7 @@
         <v>38</v>
       </c>
       <c r="B379" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C379" s="9">
         <v>15</v>
@@ -10300,7 +10300,7 @@
         <v>39</v>
       </c>
       <c r="B380" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C380" s="9">
         <v>96</v>
@@ -10325,7 +10325,7 @@
         <v>40</v>
       </c>
       <c r="B381" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C381" s="9">
         <v>95</v>
@@ -10350,7 +10350,7 @@
         <v>41</v>
       </c>
       <c r="B382" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C382" s="9">
         <v>123</v>
@@ -10375,7 +10375,7 @@
         <v>42</v>
       </c>
       <c r="B383" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C383" s="9">
         <v>160</v>
@@ -10400,7 +10400,7 @@
         <v>43</v>
       </c>
       <c r="B384" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C384" s="9">
         <v>160</v>
@@ -10425,7 +10425,7 @@
         <v>44</v>
       </c>
       <c r="B385" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C385" s="9">
         <v>152</v>
@@ -10450,7 +10450,7 @@
         <v>45</v>
       </c>
       <c r="B386" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C386" s="9">
         <v>152</v>
@@ -10475,7 +10475,7 @@
         <v>46</v>
       </c>
       <c r="B387" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C387" s="9">
         <v>184</v>
@@ -10500,7 +10500,7 @@
         <v>47</v>
       </c>
       <c r="B388" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C388" s="9">
         <v>136</v>
@@ -10525,7 +10525,7 @@
         <v>48</v>
       </c>
       <c r="B389" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C389" s="9">
         <v>136</v>
@@ -10550,7 +10550,7 @@
         <v>49</v>
       </c>
       <c r="B390" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C390" s="9">
         <v>144</v>
@@ -10575,7 +10575,7 @@
         <v>50</v>
       </c>
       <c r="B391" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C391" s="9">
         <v>55</v>
@@ -10600,7 +10600,7 @@
         <v>51</v>
       </c>
       <c r="B392" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C392" s="9">
         <v>136</v>
@@ -10625,7 +10625,7 @@
         <v>52</v>
       </c>
       <c r="B393" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C393" s="9">
         <v>183</v>
@@ -10650,7 +10650,7 @@
         <v>53</v>
       </c>
       <c r="B394" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C394" s="9">
         <v>184</v>
@@ -10675,7 +10675,7 @@
         <v>54</v>
       </c>
       <c r="B395" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C395" s="9">
         <v>151</v>
@@ -10700,7 +10700,7 @@
         <v>55</v>
       </c>
       <c r="B396" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C396" s="9">
         <v>176</v>
@@ -10725,7 +10725,7 @@
         <v>56</v>
       </c>
       <c r="B397" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C397" s="9">
         <v>159</v>
@@ -10750,7 +10750,7 @@
         <v>57</v>
       </c>
       <c r="B398" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C398" s="9">
         <v>159</v>
@@ -10775,7 +10775,7 @@
         <v>58</v>
       </c>
       <c r="B399" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C399" s="9">
         <v>112</v>
@@ -10800,7 +10800,7 @@
         <v>59</v>
       </c>
       <c r="B400" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C400" s="9">
         <v>157</v>
@@ -10825,7 +10825,7 @@
         <v>60</v>
       </c>
       <c r="B401" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C401" s="9">
         <v>144</v>
@@ -10850,7 +10850,7 @@
         <v>61</v>
       </c>
       <c r="B402" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C402" s="9">
         <v>144</v>
@@ -10875,7 +10875,7 @@
         <v>62</v>
       </c>
       <c r="B403" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C403" s="9">
         <v>160</v>
@@ -10900,7 +10900,7 @@
         <v>63</v>
       </c>
       <c r="B404" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C404" s="9">
         <v>69</v>
@@ -10925,7 +10925,7 @@
         <v>64</v>
       </c>
       <c r="B405" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C405" s="9">
         <v>16</v>
@@ -10950,7 +10950,7 @@
         <v>65</v>
       </c>
       <c r="B406" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C406" s="9">
         <v>168</v>
@@ -10975,7 +10975,7 @@
         <v>134</v>
       </c>
       <c r="B407" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C407" s="9">
         <v>138</v>
@@ -10998,7 +10998,7 @@
         <v>133</v>
       </c>
       <c r="B408" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C408" s="9">
         <v>123</v>
@@ -11021,7 +11021,7 @@
         <v>135</v>
       </c>
       <c r="B409" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C409" s="9">
         <v>128</v>
@@ -11044,7 +11044,7 @@
         <v>136</v>
       </c>
       <c r="B410" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C410" s="9">
         <v>160</v>
@@ -11067,7 +11067,7 @@
         <v>140</v>
       </c>
       <c r="B411" s="11">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="C411" s="9">
         <v>24</v>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="155">
   <si>
     <t>Tecnico</t>
   </si>
@@ -481,6 +481,9 @@
   </si>
   <si>
     <t>IRTE0000115 - LA PIANA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
   </si>
 </sst>
 </file>
@@ -9433,14 +9436,14 @@
         <v>61</v>
       </c>
       <c r="D345" s="4">
-        <v>24.4746569796324</v>
+        <v>27.809242971410502</v>
       </c>
       <c r="E345" s="6">
         <v>20</v>
       </c>
       <c r="F345" s="3">
         <f t="shared" si="8"/>
-        <v>19.579725583705919</v>
+        <v>22.247394377128401</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>67</v>
@@ -9460,14 +9463,14 @@
         <v>120</v>
       </c>
       <c r="D346" s="4">
-        <v>13.1692001683502</v>
+        <v>13.7804308373591</v>
       </c>
       <c r="E346" s="6">
         <v>20</v>
       </c>
       <c r="F346" s="3">
         <f t="shared" si="8"/>
-        <v>10.535360134680159</v>
+        <v>11.024344669887281</v>
       </c>
       <c r="G346" s="1"/>
       <c r="H346" s="8"/>
@@ -9483,14 +9486,14 @@
         <v>127</v>
       </c>
       <c r="D347" s="4">
-        <v>25.525050344334201</v>
+        <v>25.525801138138899</v>
       </c>
       <c r="E347" s="6">
         <v>20</v>
       </c>
       <c r="F347" s="3">
         <f t="shared" si="8"/>
-        <v>20.420040275467361</v>
+        <v>20.420640910511118</v>
       </c>
       <c r="G347" s="1"/>
       <c r="H347" s="8" t="s">
@@ -9508,14 +9511,14 @@
         <v>104</v>
       </c>
       <c r="D348" s="4">
-        <v>73.655240155677603</v>
+        <v>62.888621062271099</v>
       </c>
       <c r="E348" s="6">
         <v>20</v>
       </c>
       <c r="F348" s="3">
         <f t="shared" si="8"/>
-        <v>58.924192124542081</v>
+        <v>50.310896849816878</v>
       </c>
       <c r="G348" s="1"/>
       <c r="H348" s="8" t="s">
@@ -9533,14 +9536,14 @@
         <v>152</v>
       </c>
       <c r="D349" s="4">
-        <v>32.478216836734703</v>
+        <v>32.308418367346903</v>
       </c>
       <c r="E349" s="6">
         <v>20</v>
       </c>
       <c r="F349" s="3">
         <f t="shared" si="8"/>
-        <v>25.982573469387763</v>
+        <v>25.846734693877522</v>
       </c>
       <c r="G349" s="1"/>
       <c r="H349" s="8" t="s">
@@ -9558,14 +9561,14 @@
         <v>128</v>
       </c>
       <c r="D350" s="4">
-        <v>34.441048869520699</v>
+        <v>34.539974325249901</v>
       </c>
       <c r="E350" s="6">
         <v>20</v>
       </c>
       <c r="F350" s="3">
         <f t="shared" si="8"/>
-        <v>27.552839095616559</v>
+        <v>27.631979460199922</v>
       </c>
       <c r="G350" s="1"/>
       <c r="H350" s="8" t="s">
@@ -9608,14 +9611,14 @@
         <v>136</v>
       </c>
       <c r="D352" s="4">
-        <v>32.640037651850697</v>
+        <v>32.736390286654597</v>
       </c>
       <c r="E352" s="6">
         <v>20</v>
       </c>
       <c r="F352" s="3">
         <f t="shared" si="8"/>
-        <v>26.112030121480558</v>
+        <v>26.189112229323676</v>
       </c>
       <c r="G352" s="1"/>
       <c r="H352" s="8" t="s">
@@ -9633,14 +9636,14 @@
         <v>114</v>
       </c>
       <c r="D353" s="4">
-        <v>35.005030303030303</v>
+        <v>41.2832222222222</v>
       </c>
       <c r="E353" s="6">
         <v>20</v>
       </c>
       <c r="F353" s="3">
         <f t="shared" si="8"/>
-        <v>28.004024242424244</v>
+        <v>33.02657777777776</v>
       </c>
       <c r="G353" s="1"/>
       <c r="H353" s="8" t="s">
@@ -9658,14 +9661,14 @@
         <v>137</v>
       </c>
       <c r="D354" s="4">
-        <v>38.129028768970599</v>
+        <v>44.193727964837898</v>
       </c>
       <c r="E354" s="6">
         <v>20</v>
       </c>
       <c r="F354" s="3">
         <f t="shared" si="8"/>
-        <v>30.503223015176481</v>
+        <v>35.354982371870321</v>
       </c>
       <c r="G354" s="1"/>
       <c r="H354" s="8" t="s">
@@ -9683,14 +9686,14 @@
         <v>149</v>
       </c>
       <c r="D355" s="4">
-        <v>33.669544527352798</v>
+        <v>34.198853592618804</v>
       </c>
       <c r="E355" s="6">
         <v>20</v>
       </c>
       <c r="F355" s="3">
         <f t="shared" si="8"/>
-        <v>26.935635621882238</v>
+        <v>27.359082874095044</v>
       </c>
       <c r="G355" s="1"/>
       <c r="H355" s="8" t="s">
@@ -9708,14 +9711,14 @@
         <v>152</v>
       </c>
       <c r="D356" s="4">
-        <v>32.478216836734703</v>
+        <v>32.308418367346903</v>
       </c>
       <c r="E356" s="6">
         <v>20</v>
       </c>
       <c r="F356" s="3">
         <f t="shared" si="8"/>
-        <v>25.982573469387763</v>
+        <v>25.846734693877522</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="8" t="s">
@@ -9724,7 +9727,7 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B357" s="11">
         <v>46022</v>
@@ -9733,14 +9736,14 @@
         <v>119</v>
       </c>
       <c r="D357" s="4">
-        <v>75.002930172068801</v>
+        <v>63.825521648659503</v>
       </c>
       <c r="E357" s="6">
         <v>20</v>
       </c>
       <c r="F357" s="3">
         <f t="shared" si="8"/>
-        <v>60.002344137655044</v>
+        <v>51.060417318927605</v>
       </c>
       <c r="G357" s="1"/>
       <c r="H357" s="8"/>
@@ -9856,14 +9859,14 @@
         <v>147</v>
       </c>
       <c r="D362" s="4">
-        <v>63.709436208725002</v>
+        <v>63.624319235106299</v>
       </c>
       <c r="E362" s="6">
         <v>20</v>
       </c>
       <c r="F362" s="3">
         <f t="shared" si="9"/>
-        <v>50.967548966980004</v>
+        <v>50.899455388085038</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="8" t="s">
@@ -9906,14 +9909,14 @@
         <v>151</v>
       </c>
       <c r="D364" s="4">
-        <v>64.917773263771807</v>
+        <v>64.859462813117602</v>
       </c>
       <c r="E364" s="6">
         <v>20</v>
       </c>
       <c r="F364" s="3">
         <f t="shared" si="9"/>
-        <v>51.934218611017442</v>
+        <v>51.887570250494079</v>
       </c>
       <c r="G364" s="1"/>
       <c r="H364" s="8" t="s">
@@ -9931,14 +9934,14 @@
         <v>143</v>
       </c>
       <c r="D365" s="4">
-        <v>36.446089200666698</v>
+        <v>36.469688199706901</v>
       </c>
       <c r="E365" s="6">
         <v>20</v>
       </c>
       <c r="F365" s="3">
         <f t="shared" si="9"/>
-        <v>29.156871360533358</v>
+        <v>29.175750559765522</v>
       </c>
       <c r="G365" s="1"/>
       <c r="H365" s="8" t="s">
@@ -9956,14 +9959,14 @@
         <v>144</v>
       </c>
       <c r="D366" s="4">
-        <v>36.268250262094597</v>
+        <v>36.282797137094597</v>
       </c>
       <c r="E366" s="6">
         <v>20</v>
       </c>
       <c r="F366" s="3">
         <f t="shared" si="9"/>
-        <v>29.014600209675677</v>
+        <v>29.026237709675677</v>
       </c>
       <c r="G366" s="1"/>
       <c r="H366" s="8" t="s">
@@ -9981,14 +9984,14 @@
         <v>143</v>
       </c>
       <c r="D367" s="4">
-        <v>49.270387424388403</v>
+        <v>48.923351954776699</v>
       </c>
       <c r="E367" s="6">
         <v>20</v>
       </c>
       <c r="F367" s="3">
         <f t="shared" si="9"/>
-        <v>39.416309939510725</v>
+        <v>39.138681563821358</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="8" t="s">
@@ -10006,14 +10009,14 @@
         <v>104</v>
       </c>
       <c r="D368" s="4">
-        <v>84.606319710017999</v>
+        <v>87.028758826773</v>
       </c>
       <c r="E368" s="6">
         <v>20</v>
       </c>
       <c r="F368" s="3">
         <f t="shared" si="9"/>
-        <v>67.685055768014394</v>
+        <v>69.623007061418406</v>
       </c>
       <c r="G368" s="1"/>
       <c r="H368" s="8" t="s">
@@ -10056,14 +10059,14 @@
         <v>130</v>
       </c>
       <c r="D370" s="4">
-        <v>25.508038155418699</v>
+        <v>25.5087716232125</v>
       </c>
       <c r="E370" s="6">
         <v>20</v>
       </c>
       <c r="F370" s="3">
         <f t="shared" si="9"/>
-        <v>20.406430524334958</v>
+        <v>20.40701729857</v>
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="8" t="s">
@@ -10081,14 +10084,14 @@
         <v>24</v>
       </c>
       <c r="D371" s="4">
-        <v>71.615705302551106</v>
+        <v>73.3725113676295</v>
       </c>
       <c r="E371" s="6">
         <v>20</v>
       </c>
       <c r="F371" s="3">
         <f t="shared" si="9"/>
-        <v>57.292564242040882</v>
+        <v>58.698009094103597</v>
       </c>
       <c r="G371" s="1"/>
       <c r="H371" s="8" t="s">
@@ -10106,14 +10109,14 @@
         <v>130</v>
       </c>
       <c r="D372" s="4">
-        <v>47.491338336460302</v>
+        <v>47.045434216697899</v>
       </c>
       <c r="E372" s="6">
         <v>20</v>
       </c>
       <c r="F372" s="3">
         <f t="shared" si="9"/>
-        <v>37.99307066916824</v>
+        <v>37.636347373358319</v>
       </c>
       <c r="G372" s="1"/>
       <c r="H372" s="8" t="s">
@@ -10131,14 +10134,14 @@
         <v>23</v>
       </c>
       <c r="D373" s="4">
-        <v>30.789425559947301</v>
+        <v>35.889209199747903</v>
       </c>
       <c r="E373" s="6">
         <v>20</v>
       </c>
       <c r="F373" s="3">
         <f t="shared" si="9"/>
-        <v>24.631540447957839</v>
+        <v>28.711367359798324</v>
       </c>
       <c r="G373" s="1"/>
       <c r="H373" s="8" t="s">
@@ -10181,14 +10184,14 @@
         <v>137</v>
       </c>
       <c r="D375" s="4">
-        <v>37.840107843137197</v>
+        <v>37.866267973856203</v>
       </c>
       <c r="E375" s="6">
         <v>20</v>
       </c>
       <c r="F375" s="3">
         <f t="shared" si="9"/>
-        <v>30.272086274509757</v>
+        <v>30.293014379084962</v>
       </c>
       <c r="G375" s="1"/>
       <c r="H375" s="8" t="s">
@@ -10256,14 +10259,14 @@
         <v>150</v>
       </c>
       <c r="D378" s="4">
-        <v>64.905633548887195</v>
+        <v>64.846934361895407</v>
       </c>
       <c r="E378" s="6">
         <v>20</v>
       </c>
       <c r="F378" s="3">
         <f t="shared" si="9"/>
-        <v>51.924506839109753</v>
+        <v>51.877547489516324</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="8" t="s">
@@ -10281,14 +10284,14 @@
         <v>15</v>
       </c>
       <c r="D379" s="4">
-        <v>28.541103030302999</v>
+        <v>33.012402254428302</v>
       </c>
       <c r="E379" s="6">
         <v>20</v>
       </c>
       <c r="F379" s="3">
         <f t="shared" si="9"/>
-        <v>22.832882424242399</v>
+        <v>26.409921803542641</v>
       </c>
       <c r="G379" s="1"/>
       <c r="H379" s="8" t="s">
@@ -10306,14 +10309,14 @@
         <v>96</v>
       </c>
       <c r="D380" s="4">
-        <v>84.281554349831296</v>
+        <v>86.687352640294407</v>
       </c>
       <c r="E380" s="6">
         <v>20</v>
       </c>
       <c r="F380" s="3">
         <f t="shared" si="9"/>
-        <v>67.425243479865031</v>
+        <v>69.34988211223552</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="8" t="s">
@@ -10356,14 +10359,14 @@
         <v>123</v>
       </c>
       <c r="D382" s="4">
-        <v>22.9888100775194</v>
+        <v>22.969821705426401</v>
       </c>
       <c r="E382" s="6">
         <v>20</v>
       </c>
       <c r="F382" s="3">
         <f t="shared" si="9"/>
-        <v>18.391048062015521</v>
+        <v>18.375857364341122</v>
       </c>
       <c r="G382" s="1"/>
       <c r="H382" s="8" t="s">
@@ -10431,14 +10434,14 @@
         <v>152</v>
       </c>
       <c r="D385" s="4">
-        <v>22.161195577953698</v>
+        <v>22.9197596884616</v>
       </c>
       <c r="E385" s="6">
         <v>20</v>
       </c>
       <c r="F385" s="3">
         <f t="shared" si="9"/>
-        <v>17.728956462362959</v>
+        <v>18.33580775076928</v>
       </c>
       <c r="G385" s="1"/>
       <c r="H385" s="8" t="s">
@@ -10681,14 +10684,14 @@
         <v>151</v>
       </c>
       <c r="D395" s="4">
-        <v>33.210764142738199</v>
+        <v>33.121763981213398</v>
       </c>
       <c r="E395" s="6">
         <v>20</v>
       </c>
       <c r="F395" s="3">
         <f t="shared" si="10"/>
-        <v>26.568611314190559</v>
+        <v>26.497411184970719</v>
       </c>
       <c r="G395" s="1"/>
       <c r="H395" s="8" t="s">
@@ -10781,14 +10784,14 @@
         <v>112</v>
       </c>
       <c r="D399" s="4">
-        <v>32.443847650833398</v>
+        <v>32.782156577240102</v>
       </c>
       <c r="E399" s="6">
         <v>20</v>
       </c>
       <c r="F399" s="3">
         <f t="shared" si="10"/>
-        <v>25.95507812066672</v>
+        <v>26.225725261792082</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="8" t="s">
@@ -10806,14 +10809,14 @@
         <v>157</v>
       </c>
       <c r="D400" s="4">
-        <v>29.257409937888202</v>
+        <v>29.477649068323</v>
       </c>
       <c r="E400" s="6">
         <v>20</v>
       </c>
       <c r="F400" s="3">
         <f t="shared" si="10"/>
-        <v>23.405927950310563</v>
+        <v>23.582119254658402</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="8" t="s">
@@ -10906,14 +10909,14 @@
         <v>69</v>
       </c>
       <c r="D404" s="4">
-        <v>40.759553607604801</v>
+        <v>43.976576444363097</v>
       </c>
       <c r="E404" s="6">
         <v>20</v>
       </c>
       <c r="F404" s="3">
         <f t="shared" si="10"/>
-        <v>32.607642886083838</v>
+        <v>35.181261155490475</v>
       </c>
       <c r="G404" s="1"/>
       <c r="H404" s="8" t="s">
@@ -10931,14 +10934,14 @@
         <v>16</v>
       </c>
       <c r="D405" s="4">
-        <v>99.968460349462404</v>
+        <v>104.267858198925</v>
       </c>
       <c r="E405" s="6">
         <v>20</v>
       </c>
       <c r="F405" s="3">
         <f t="shared" si="10"/>
-        <v>79.974768279569929</v>
+        <v>83.414286559139995</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="8" t="s">
@@ -11004,14 +11007,14 @@
         <v>123</v>
       </c>
       <c r="D408" s="4">
-        <v>22.9888100775194</v>
+        <v>22.969821705426401</v>
       </c>
       <c r="E408" s="6">
         <v>20</v>
       </c>
       <c r="F408" s="3">
         <f t="shared" si="10"/>
-        <v>18.391048062015521</v>
+        <v>18.375857364341122</v>
       </c>
       <c r="G408" s="1"/>
       <c r="H408" s="8"/>
@@ -11073,14 +11076,14 @@
         <v>24</v>
       </c>
       <c r="D411" s="4">
-        <v>49.006107969344797</v>
+        <v>50.026977067053998</v>
       </c>
       <c r="E411" s="6">
         <v>20</v>
       </c>
       <c r="F411" s="3">
         <f t="shared" si="11"/>
-        <v>39.204886375475837</v>
+        <v>40.021581653643196</v>
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="8"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="159">
   <si>
     <t>Tecnico</t>
   </si>
@@ -484,18 +484,32 @@
   </si>
   <si>
     <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
+  </si>
+  <si>
+    <t>Matricola e Nominativo Dipendente</t>
+  </si>
+  <si>
+    <t>Tot. Ore</t>
+  </si>
+  <si>
+    <t>Tot.</t>
+  </si>
+  <si>
+    <t>IRTE0000117 - FERRANTI GIANLUCA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.0\ &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="#,###,###,##0&quot; h.&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,###,###,##0.00&quot; h.&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,###,###,##0.00&quot; €/h.&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,8 +536,14 @@
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8.25"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -539,6 +559,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0FFC0"/>
       </patternFill>
     </fill>
   </fills>
@@ -588,7 +623,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -608,6 +643,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -903,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H411"/>
+  <dimension ref="A1:L479"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -914,6 +961,9 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="24.28515625" customWidth="1"/>
     <col min="8" max="8" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10823,7 +10873,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:12">
       <c r="A401" s="1" t="s">
         <v>60</v>
       </c>
@@ -10848,7 +10898,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:12">
       <c r="A402" s="1" t="s">
         <v>61</v>
       </c>
@@ -10873,7 +10923,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:12">
       <c r="A403" s="1" t="s">
         <v>62</v>
       </c>
@@ -10898,7 +10948,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" spans="1:12">
       <c r="A404" s="1" t="s">
         <v>63</v>
       </c>
@@ -10923,7 +10973,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" spans="1:12">
       <c r="A405" s="1" t="s">
         <v>64</v>
       </c>
@@ -10948,7 +10998,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" spans="1:12">
       <c r="A406" s="1" t="s">
         <v>65</v>
       </c>
@@ -10973,7 +11023,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" spans="1:12">
       <c r="A407" s="10" t="s">
         <v>134</v>
       </c>
@@ -10996,7 +11046,7 @@
       <c r="G407" s="1"/>
       <c r="H407" s="8"/>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:12">
       <c r="A408" s="1" t="s">
         <v>133</v>
       </c>
@@ -11019,7 +11069,7 @@
       <c r="G408" s="1"/>
       <c r="H408" s="8"/>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:12">
       <c r="A409" s="1" t="s">
         <v>135</v>
       </c>
@@ -11036,13 +11086,13 @@
         <v>20</v>
       </c>
       <c r="F409" s="3">
-        <f t="shared" ref="F409:F411" si="11">D409-(D409*E409)/100</f>
+        <f t="shared" ref="F409:F472" si="11">D409-(D409*E409)/100</f>
         <v>27.004013392857122</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="8"/>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:12">
       <c r="A410" s="1" t="s">
         <v>136</v>
       </c>
@@ -11065,7 +11115,7 @@
       <c r="G410" s="1"/>
       <c r="H410" s="8"/>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:12">
       <c r="A411" s="1" t="s">
         <v>140</v>
       </c>
@@ -11087,6 +11137,2317 @@
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="8"/>
+      <c r="J411" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="K411" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="L411" s="17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12">
+      <c r="A412" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B412" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C412" s="9">
+        <v>88</v>
+      </c>
+      <c r="D412" s="12">
+        <v>37.604112903225797</v>
+      </c>
+      <c r="E412" s="13">
+        <v>20</v>
+      </c>
+      <c r="F412" s="14">
+        <f t="shared" si="11"/>
+        <v>30.083290322580638</v>
+      </c>
+      <c r="G412" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H412" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J412" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K412" s="19">
+        <v>88</v>
+      </c>
+      <c r="L412" s="20">
+        <v>37.604112903225797</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12">
+      <c r="A413" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B413" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C413" s="9">
+        <v>63.5</v>
+      </c>
+      <c r="D413" s="4">
+        <v>38.479831632710201</v>
+      </c>
+      <c r="E413" s="6">
+        <v>20</v>
+      </c>
+      <c r="F413" s="3">
+        <f t="shared" si="11"/>
+        <v>30.78386530616816</v>
+      </c>
+      <c r="G413" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H413" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J413" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="K413" s="19">
+        <v>63.5</v>
+      </c>
+      <c r="L413" s="20">
+        <v>38.479831632710201</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12">
+      <c r="A414" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B414" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C414" s="9">
+        <v>16</v>
+      </c>
+      <c r="D414" s="4">
+        <v>43.527846283783802</v>
+      </c>
+      <c r="E414" s="6">
+        <v>20</v>
+      </c>
+      <c r="F414" s="3">
+        <f t="shared" si="11"/>
+        <v>34.822277027027042</v>
+      </c>
+      <c r="G414" s="1"/>
+      <c r="H414" s="8"/>
+      <c r="J414" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="K414" s="19">
+        <v>16</v>
+      </c>
+      <c r="L414" s="20">
+        <v>43.527846283783802</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12">
+      <c r="A415" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B415" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C415" s="9">
+        <v>88</v>
+      </c>
+      <c r="D415" s="4">
+        <v>22.541478490259699</v>
+      </c>
+      <c r="E415" s="6">
+        <v>20</v>
+      </c>
+      <c r="F415" s="3">
+        <f t="shared" si="11"/>
+        <v>18.033182792207761</v>
+      </c>
+      <c r="G415" s="1"/>
+      <c r="H415" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J415" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="K415" s="19">
+        <v>88</v>
+      </c>
+      <c r="L415" s="20">
+        <v>22.541478490259699</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12">
+      <c r="A416" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B416" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C416" s="9">
+        <v>88</v>
+      </c>
+      <c r="D416" s="4">
+        <v>73.332048526228704</v>
+      </c>
+      <c r="E416" s="6">
+        <v>20</v>
+      </c>
+      <c r="F416" s="3">
+        <f t="shared" si="11"/>
+        <v>58.665638820982963</v>
+      </c>
+      <c r="G416" s="1"/>
+      <c r="H416" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J416" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="K416" s="19">
+        <v>88</v>
+      </c>
+      <c r="L416" s="20">
+        <v>73.332048526228704</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12">
+      <c r="A417" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B417" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C417" s="9">
+        <v>96</v>
+      </c>
+      <c r="D417" s="4">
+        <v>27.902842741935501</v>
+      </c>
+      <c r="E417" s="6">
+        <v>20</v>
+      </c>
+      <c r="F417" s="3">
+        <f t="shared" si="11"/>
+        <v>22.322274193548402</v>
+      </c>
+      <c r="G417" s="1"/>
+      <c r="H417" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J417" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K417" s="19">
+        <v>96</v>
+      </c>
+      <c r="L417" s="20">
+        <v>27.902842741935501</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12">
+      <c r="A418" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C418" s="9">
+        <v>80</v>
+      </c>
+      <c r="D418" s="4">
+        <v>37.276177700049097</v>
+      </c>
+      <c r="E418" s="6">
+        <v>20</v>
+      </c>
+      <c r="F418" s="3">
+        <f t="shared" si="11"/>
+        <v>29.820942160039277</v>
+      </c>
+      <c r="G418" s="1"/>
+      <c r="H418" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J418" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K418" s="19">
+        <v>80</v>
+      </c>
+      <c r="L418" s="20">
+        <v>37.276177700049097</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12">
+      <c r="A419" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B419" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C419" s="9">
+        <v>120</v>
+      </c>
+      <c r="D419" s="4">
+        <v>36.273470833333398</v>
+      </c>
+      <c r="E419" s="6">
+        <v>20</v>
+      </c>
+      <c r="F419" s="3">
+        <f t="shared" si="11"/>
+        <v>29.018776666666717</v>
+      </c>
+      <c r="G419" s="1"/>
+      <c r="H419" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J419" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="K419" s="19">
+        <v>120</v>
+      </c>
+      <c r="L419" s="20">
+        <v>36.273470833333398</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12">
+      <c r="A420" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B420" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C420" s="9">
+        <v>64</v>
+      </c>
+      <c r="D420" s="4">
+        <v>37.344654761904799</v>
+      </c>
+      <c r="E420" s="6">
+        <v>20</v>
+      </c>
+      <c r="F420" s="3">
+        <f t="shared" si="11"/>
+        <v>29.875723809523841</v>
+      </c>
+      <c r="G420" s="1"/>
+      <c r="H420" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J420" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K420" s="19">
+        <v>64</v>
+      </c>
+      <c r="L420" s="20">
+        <v>37.344654761904799</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12">
+      <c r="A421" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B421" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C421" s="9">
+        <v>64</v>
+      </c>
+      <c r="D421" s="4">
+        <v>90.817939644607804</v>
+      </c>
+      <c r="E421" s="6">
+        <v>20</v>
+      </c>
+      <c r="F421" s="3">
+        <f t="shared" si="11"/>
+        <v>72.654351715686246</v>
+      </c>
+      <c r="G421" s="1"/>
+      <c r="H421" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J421" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="K421" s="19">
+        <v>64</v>
+      </c>
+      <c r="L421" s="20">
+        <v>90.817939644607804</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12">
+      <c r="A422" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B422" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C422" s="9">
+        <v>72</v>
+      </c>
+      <c r="D422" s="4">
+        <v>101.36440105301401</v>
+      </c>
+      <c r="E422" s="6">
+        <v>20</v>
+      </c>
+      <c r="F422" s="3">
+        <f t="shared" si="11"/>
+        <v>81.0915208424112</v>
+      </c>
+      <c r="G422" s="1"/>
+      <c r="H422" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="J422" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="K422" s="19">
+        <v>72</v>
+      </c>
+      <c r="L422" s="20">
+        <v>101.36440105301401</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12">
+      <c r="A423" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B423" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C423" s="9">
+        <v>78</v>
+      </c>
+      <c r="D423" s="4">
+        <v>35.874131238633602</v>
+      </c>
+      <c r="E423" s="6">
+        <v>20</v>
+      </c>
+      <c r="F423" s="3">
+        <f t="shared" si="11"/>
+        <v>28.699304990906882</v>
+      </c>
+      <c r="G423" s="1"/>
+      <c r="H423" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J423" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K423" s="19">
+        <v>78</v>
+      </c>
+      <c r="L423" s="20">
+        <v>35.874131238633602</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12">
+      <c r="A424" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B424" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C424" s="9">
+        <v>104</v>
+      </c>
+      <c r="D424" s="4">
+        <v>27.902842741935501</v>
+      </c>
+      <c r="E424" s="6">
+        <v>20</v>
+      </c>
+      <c r="F424" s="3">
+        <f t="shared" si="11"/>
+        <v>22.322274193548402</v>
+      </c>
+      <c r="G424" s="1"/>
+      <c r="H424" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J424" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K424" s="19">
+        <v>104</v>
+      </c>
+      <c r="L424" s="20">
+        <v>27.902842741935501</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12">
+      <c r="A425" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B425" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C425" s="9">
+        <v>72</v>
+      </c>
+      <c r="D425" s="4">
+        <v>65.784042114067901</v>
+      </c>
+      <c r="E425" s="6">
+        <v>20</v>
+      </c>
+      <c r="F425" s="3">
+        <f t="shared" si="11"/>
+        <v>52.627233691254318</v>
+      </c>
+      <c r="G425" s="1"/>
+      <c r="H425" s="8"/>
+      <c r="J425" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="K425" s="19">
+        <v>72</v>
+      </c>
+      <c r="L425" s="20">
+        <v>65.784042114067901</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12">
+      <c r="A426" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B426" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C426" s="9">
+        <v>104</v>
+      </c>
+      <c r="D426" s="4">
+        <v>36.4920336538462</v>
+      </c>
+      <c r="E426" s="6">
+        <v>20</v>
+      </c>
+      <c r="F426" s="3">
+        <f t="shared" si="11"/>
+        <v>29.193626923076959</v>
+      </c>
+      <c r="G426" s="1"/>
+      <c r="H426" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J426" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K426" s="19">
+        <v>104</v>
+      </c>
+      <c r="L426" s="20">
+        <v>36.4920336538462</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12">
+      <c r="A427" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B427" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C427" s="9">
+        <v>128</v>
+      </c>
+      <c r="D427" s="4">
+        <v>32.8449294704861</v>
+      </c>
+      <c r="E427" s="6">
+        <v>20</v>
+      </c>
+      <c r="F427" s="3">
+        <f t="shared" si="11"/>
+        <v>26.27594357638888</v>
+      </c>
+      <c r="G427" s="1"/>
+      <c r="H427" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J427" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K427" s="19">
+        <v>128</v>
+      </c>
+      <c r="L427" s="20">
+        <v>32.8449294704861</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12">
+      <c r="A428" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B428" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C428" s="9">
+        <v>88</v>
+      </c>
+      <c r="D428" s="4">
+        <v>37.604112903225797</v>
+      </c>
+      <c r="E428" s="6">
+        <v>20</v>
+      </c>
+      <c r="F428" s="3">
+        <f t="shared" si="11"/>
+        <v>30.083290322580638</v>
+      </c>
+      <c r="G428" s="1"/>
+      <c r="H428" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J428" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K428" s="19">
+        <v>88</v>
+      </c>
+      <c r="L428" s="20">
+        <v>37.604112903225797</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12">
+      <c r="A429" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B429" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C429" s="9">
+        <v>120</v>
+      </c>
+      <c r="D429" s="4">
+        <v>29.6908361111111</v>
+      </c>
+      <c r="E429" s="6">
+        <v>20</v>
+      </c>
+      <c r="F429" s="3">
+        <f t="shared" si="11"/>
+        <v>23.752668888888881</v>
+      </c>
+      <c r="G429" s="1"/>
+      <c r="H429" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J429" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K429" s="19">
+        <v>120</v>
+      </c>
+      <c r="L429" s="20">
+        <v>29.6908361111111</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12">
+      <c r="A430" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B430" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C430" s="9">
+        <v>103</v>
+      </c>
+      <c r="D430" s="4">
+        <v>48.722940437538497</v>
+      </c>
+      <c r="E430" s="6">
+        <v>20</v>
+      </c>
+      <c r="F430" s="3">
+        <f t="shared" si="11"/>
+        <v>38.978352350030796</v>
+      </c>
+      <c r="G430" s="1"/>
+      <c r="H430" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J430" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K430" s="19">
+        <v>103</v>
+      </c>
+      <c r="L430" s="20">
+        <v>48.722940437538497</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12">
+      <c r="A431" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B431" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C431" s="9">
+        <v>120</v>
+      </c>
+      <c r="D431" s="4">
+        <v>31.0014254734849</v>
+      </c>
+      <c r="E431" s="6">
+        <v>20</v>
+      </c>
+      <c r="F431" s="3">
+        <f t="shared" si="11"/>
+        <v>24.80114037878792</v>
+      </c>
+      <c r="G431" s="1"/>
+      <c r="H431" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J431" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K431" s="19">
+        <v>120</v>
+      </c>
+      <c r="L431" s="20">
+        <v>31.0014254734849</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12">
+      <c r="A432" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B432" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C432" s="9">
+        <v>95</v>
+      </c>
+      <c r="D432" s="4">
+        <v>53.5923998587432</v>
+      </c>
+      <c r="E432" s="6">
+        <v>20</v>
+      </c>
+      <c r="F432" s="3">
+        <f t="shared" si="11"/>
+        <v>42.873919886994557</v>
+      </c>
+      <c r="G432" s="1"/>
+      <c r="H432" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J432" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K432" s="19">
+        <v>95</v>
+      </c>
+      <c r="L432" s="20">
+        <v>53.5923998587432</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12">
+      <c r="A433" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B433" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C433" s="9">
+        <v>72</v>
+      </c>
+      <c r="D433" s="4">
+        <v>45.699325694444397</v>
+      </c>
+      <c r="E433" s="6">
+        <v>20</v>
+      </c>
+      <c r="F433" s="3">
+        <f t="shared" si="11"/>
+        <v>36.559460555555518</v>
+      </c>
+      <c r="G433" s="1"/>
+      <c r="H433" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J433" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K433" s="19">
+        <v>72</v>
+      </c>
+      <c r="L433" s="20">
+        <v>45.699325694444397</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12">
+      <c r="A434" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B434" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C434" s="9">
+        <v>96</v>
+      </c>
+      <c r="D434" s="4">
+        <v>34.394302544476503</v>
+      </c>
+      <c r="E434" s="6">
+        <v>20</v>
+      </c>
+      <c r="F434" s="3">
+        <f t="shared" si="11"/>
+        <v>27.515442035581202</v>
+      </c>
+      <c r="G434" s="1"/>
+      <c r="H434" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J434" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K434" s="19">
+        <v>96</v>
+      </c>
+      <c r="L434" s="20">
+        <v>34.394302544476503</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12">
+      <c r="A435" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B435" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C435" s="9">
+        <v>101</v>
+      </c>
+      <c r="D435" s="4">
+        <v>58.825565263804002</v>
+      </c>
+      <c r="E435" s="6">
+        <v>20</v>
+      </c>
+      <c r="F435" s="3">
+        <f t="shared" si="11"/>
+        <v>47.060452211043199</v>
+      </c>
+      <c r="G435" s="1"/>
+      <c r="H435" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J435" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K435" s="19">
+        <v>101</v>
+      </c>
+      <c r="L435" s="20">
+        <v>58.825565263804002</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12">
+      <c r="A436" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B436" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C436" s="9">
+        <v>72</v>
+      </c>
+      <c r="D436" s="4">
+        <v>85.515069444444407</v>
+      </c>
+      <c r="E436" s="6">
+        <v>20</v>
+      </c>
+      <c r="F436" s="3">
+        <f t="shared" si="11"/>
+        <v>68.412055555555526</v>
+      </c>
+      <c r="G436" s="1"/>
+      <c r="H436" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J436" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K436" s="19">
+        <v>72</v>
+      </c>
+      <c r="L436" s="20">
+        <v>85.515069444444407</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12">
+      <c r="A437" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B437" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C437" s="9">
+        <v>64</v>
+      </c>
+      <c r="D437" s="4">
+        <v>31.138515625</v>
+      </c>
+      <c r="E437" s="6">
+        <v>20</v>
+      </c>
+      <c r="F437" s="3">
+        <f t="shared" si="11"/>
+        <v>24.910812499999999</v>
+      </c>
+      <c r="G437" s="1"/>
+      <c r="H437" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J437" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K437" s="19">
+        <v>64</v>
+      </c>
+      <c r="L437" s="20">
+        <v>31.138515625</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12">
+      <c r="A438" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B438" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C438" s="9">
+        <v>72</v>
+      </c>
+      <c r="D438" s="4">
+        <v>22.814334821428599</v>
+      </c>
+      <c r="E438" s="6">
+        <v>20</v>
+      </c>
+      <c r="F438" s="3">
+        <f t="shared" si="11"/>
+        <v>18.251467857142877</v>
+      </c>
+      <c r="G438" s="1"/>
+      <c r="H438" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J438" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K438" s="19">
+        <v>72</v>
+      </c>
+      <c r="L438" s="20">
+        <v>22.814334821428599</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12">
+      <c r="A439" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B439" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C439" s="9">
+        <v>8</v>
+      </c>
+      <c r="D439" s="4">
+        <v>52.666668749999999</v>
+      </c>
+      <c r="E439" s="6">
+        <v>20</v>
+      </c>
+      <c r="F439" s="3">
+        <f t="shared" si="11"/>
+        <v>42.133335000000002</v>
+      </c>
+      <c r="G439" s="1"/>
+      <c r="H439" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="J439" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="K439" s="19">
+        <v>8</v>
+      </c>
+      <c r="L439" s="20">
+        <v>52.666668749999999</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12">
+      <c r="A440" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B440" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C440" s="9">
+        <v>109</v>
+      </c>
+      <c r="D440" s="4">
+        <v>58.917153619031097</v>
+      </c>
+      <c r="E440" s="6">
+        <v>20</v>
+      </c>
+      <c r="F440" s="3">
+        <f t="shared" si="11"/>
+        <v>47.133722895224878</v>
+      </c>
+      <c r="G440" s="1"/>
+      <c r="H440" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="J440" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K440" s="19">
+        <v>109</v>
+      </c>
+      <c r="L440" s="20">
+        <v>58.917153619031097</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12">
+      <c r="A441" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B441" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C441" s="9">
+        <v>96</v>
+      </c>
+      <c r="D441" s="4">
+        <v>60.347925273764503</v>
+      </c>
+      <c r="E441" s="6">
+        <v>20</v>
+      </c>
+      <c r="F441" s="3">
+        <f t="shared" si="11"/>
+        <v>48.278340219011604</v>
+      </c>
+      <c r="G441" s="1"/>
+      <c r="H441" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J441" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K441" s="19">
+        <v>96</v>
+      </c>
+      <c r="L441" s="20">
+        <v>60.347925273764503</v>
+      </c>
+    </row>
+    <row r="442" spans="1:12">
+      <c r="A442" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B442" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C442" s="9">
+        <v>128</v>
+      </c>
+      <c r="D442" s="4">
+        <v>29.894890624999999</v>
+      </c>
+      <c r="E442" s="6">
+        <v>20</v>
+      </c>
+      <c r="F442" s="3">
+        <f t="shared" si="11"/>
+        <v>23.915912499999997</v>
+      </c>
+      <c r="G442" s="1"/>
+      <c r="H442" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J442" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K442" s="19">
+        <v>128</v>
+      </c>
+      <c r="L442" s="20">
+        <v>29.894890624999999</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12">
+      <c r="A443" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B443" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C443" s="9">
+        <v>88</v>
+      </c>
+      <c r="D443" s="4">
+        <v>49.990725309917401</v>
+      </c>
+      <c r="E443" s="6">
+        <v>20</v>
+      </c>
+      <c r="F443" s="3">
+        <f t="shared" si="11"/>
+        <v>39.992580247933923</v>
+      </c>
+      <c r="G443" s="1"/>
+      <c r="H443" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J443" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K443" s="19">
+        <v>88</v>
+      </c>
+      <c r="L443" s="20">
+        <v>49.990725309917401</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12">
+      <c r="A444" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B444" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C444" s="9">
+        <v>96</v>
+      </c>
+      <c r="D444" s="4">
+        <v>68.987288235294102</v>
+      </c>
+      <c r="E444" s="6">
+        <v>20</v>
+      </c>
+      <c r="F444" s="3">
+        <f t="shared" si="11"/>
+        <v>55.189830588235282</v>
+      </c>
+      <c r="G444" s="1"/>
+      <c r="H444" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J444" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K444" s="19">
+        <v>96</v>
+      </c>
+      <c r="L444" s="20">
+        <v>68.987288235294102</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12">
+      <c r="A445" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B445" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C445" s="9">
+        <v>128</v>
+      </c>
+      <c r="D445" s="4">
+        <v>21.692925925925898</v>
+      </c>
+      <c r="E445" s="6">
+        <v>20</v>
+      </c>
+      <c r="F445" s="3">
+        <f t="shared" si="11"/>
+        <v>17.354340740740717</v>
+      </c>
+      <c r="G445" s="1"/>
+      <c r="H445" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J445" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K445" s="19">
+        <v>128</v>
+      </c>
+      <c r="L445" s="20">
+        <v>21.692925925925898</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12">
+      <c r="A446" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B446" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C446" s="9">
+        <v>110</v>
+      </c>
+      <c r="D446" s="4">
+        <v>55.287511072487298</v>
+      </c>
+      <c r="E446" s="6">
+        <v>20</v>
+      </c>
+      <c r="F446" s="3">
+        <f t="shared" si="11"/>
+        <v>44.230008857989837</v>
+      </c>
+      <c r="G446" s="1"/>
+      <c r="H446" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J446" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K446" s="19">
+        <v>110</v>
+      </c>
+      <c r="L446" s="20">
+        <v>55.287511072487298</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12">
+      <c r="A447" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B447" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C447" s="9">
+        <v>96</v>
+      </c>
+      <c r="D447" s="4">
+        <v>60.347925273764503</v>
+      </c>
+      <c r="E447" s="6">
+        <v>20</v>
+      </c>
+      <c r="F447" s="3">
+        <f t="shared" si="11"/>
+        <v>48.278340219011604</v>
+      </c>
+      <c r="G447" s="1"/>
+      <c r="H447" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J447" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K447" s="19">
+        <v>96</v>
+      </c>
+      <c r="L447" s="20">
+        <v>60.347925273764503</v>
+      </c>
+    </row>
+    <row r="448" spans="1:12">
+      <c r="A448" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B448" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C448" s="9">
+        <v>72</v>
+      </c>
+      <c r="D448" s="4">
+        <v>87.400534404502594</v>
+      </c>
+      <c r="E448" s="6">
+        <v>20</v>
+      </c>
+      <c r="F448" s="3">
+        <f t="shared" si="11"/>
+        <v>69.920427523602072</v>
+      </c>
+      <c r="G448" s="1"/>
+      <c r="H448" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J448" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="K448" s="19">
+        <v>72</v>
+      </c>
+      <c r="L448" s="20">
+        <v>87.400534404502594</v>
+      </c>
+    </row>
+    <row r="449" spans="1:12">
+      <c r="A449" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B449" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C449" s="9">
+        <v>88</v>
+      </c>
+      <c r="D449" s="4">
+        <v>25.255327029220801</v>
+      </c>
+      <c r="E449" s="6">
+        <v>20</v>
+      </c>
+      <c r="F449" s="3">
+        <f t="shared" si="11"/>
+        <v>20.204261623376642</v>
+      </c>
+      <c r="G449" s="1"/>
+      <c r="H449" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J449" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="K449" s="19">
+        <v>88</v>
+      </c>
+      <c r="L449" s="20">
+        <v>25.255327029220801</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12">
+      <c r="A450" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B450" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C450" s="9">
+        <v>106</v>
+      </c>
+      <c r="D450" s="4">
+        <v>23.231290909090902</v>
+      </c>
+      <c r="E450" s="6">
+        <v>20</v>
+      </c>
+      <c r="F450" s="3">
+        <f t="shared" si="11"/>
+        <v>18.585032727272722</v>
+      </c>
+      <c r="G450" s="1"/>
+      <c r="H450" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J450" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K450" s="19">
+        <v>106</v>
+      </c>
+      <c r="L450" s="20">
+        <v>23.231290909090902</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12">
+      <c r="A451" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B451" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C451" s="9">
+        <v>112</v>
+      </c>
+      <c r="D451" s="4">
+        <v>34.184946428571401</v>
+      </c>
+      <c r="E451" s="6">
+        <v>20</v>
+      </c>
+      <c r="F451" s="3">
+        <f t="shared" si="11"/>
+        <v>27.347957142857119</v>
+      </c>
+      <c r="G451" s="1"/>
+      <c r="H451" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J451" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="K451" s="19">
+        <v>112</v>
+      </c>
+      <c r="L451" s="20">
+        <v>34.184946428571401</v>
+      </c>
+    </row>
+    <row r="452" spans="1:12">
+      <c r="A452" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B452" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C452" s="9">
+        <v>144</v>
+      </c>
+      <c r="D452" s="4">
+        <v>35.723969091961301</v>
+      </c>
+      <c r="E452" s="6">
+        <v>20</v>
+      </c>
+      <c r="F452" s="3">
+        <f t="shared" si="11"/>
+        <v>28.579175273569042</v>
+      </c>
+      <c r="G452" s="1"/>
+      <c r="H452" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J452" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K452" s="19">
+        <v>144</v>
+      </c>
+      <c r="L452" s="20">
+        <v>35.723969091961301</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12">
+      <c r="A453" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B453" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C453" s="9">
+        <v>8</v>
+      </c>
+      <c r="D453" s="4">
+        <v>30.648550632911402</v>
+      </c>
+      <c r="E453" s="6">
+        <v>20</v>
+      </c>
+      <c r="F453" s="3">
+        <f t="shared" si="11"/>
+        <v>24.51884050632912</v>
+      </c>
+      <c r="G453" s="1"/>
+      <c r="H453" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J453" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="K453" s="19">
+        <v>8</v>
+      </c>
+      <c r="L453" s="20">
+        <v>30.648550632911402</v>
+      </c>
+    </row>
+    <row r="454" spans="1:12">
+      <c r="A454" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B454" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C454" s="9">
+        <v>88</v>
+      </c>
+      <c r="D454" s="4">
+        <v>37.006373374329002</v>
+      </c>
+      <c r="E454" s="6">
+        <v>20</v>
+      </c>
+      <c r="F454" s="3">
+        <f t="shared" si="11"/>
+        <v>29.605098699463202</v>
+      </c>
+      <c r="G454" s="1"/>
+      <c r="H454" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J454" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K454" s="19">
+        <v>88</v>
+      </c>
+      <c r="L454" s="20">
+        <v>37.006373374329002</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12">
+      <c r="A455" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B455" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C455" s="9">
+        <v>112</v>
+      </c>
+      <c r="D455" s="4">
+        <v>25.078375000000001</v>
+      </c>
+      <c r="E455" s="6">
+        <v>20</v>
+      </c>
+      <c r="F455" s="3">
+        <f t="shared" si="11"/>
+        <v>20.0627</v>
+      </c>
+      <c r="G455" s="1"/>
+      <c r="H455" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J455" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="K455" s="19">
+        <v>112</v>
+      </c>
+      <c r="L455" s="20">
+        <v>25.078375000000001</v>
+      </c>
+    </row>
+    <row r="456" spans="1:12">
+      <c r="A456" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B456" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C456" s="9">
+        <v>90</v>
+      </c>
+      <c r="D456" s="4">
+        <v>68.987288235294102</v>
+      </c>
+      <c r="E456" s="6">
+        <v>20</v>
+      </c>
+      <c r="F456" s="3">
+        <f t="shared" si="11"/>
+        <v>55.189830588235282</v>
+      </c>
+      <c r="G456" s="1"/>
+      <c r="H456" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J456" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K456" s="19">
+        <v>90</v>
+      </c>
+      <c r="L456" s="20">
+        <v>68.987288235294102</v>
+      </c>
+    </row>
+    <row r="457" spans="1:12">
+      <c r="A457" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B457" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C457" s="9">
+        <v>98</v>
+      </c>
+      <c r="D457" s="4">
+        <v>68.987288235294102</v>
+      </c>
+      <c r="E457" s="6">
+        <v>20</v>
+      </c>
+      <c r="F457" s="3">
+        <f t="shared" si="11"/>
+        <v>55.189830588235282</v>
+      </c>
+      <c r="G457" s="1"/>
+      <c r="H457" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J457" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="K457" s="19">
+        <v>98</v>
+      </c>
+      <c r="L457" s="20">
+        <v>68.987288235294102</v>
+      </c>
+    </row>
+    <row r="458" spans="1:12">
+      <c r="A458" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B458" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C458" s="9">
+        <v>112</v>
+      </c>
+      <c r="D458" s="4">
+        <v>32.626603571428603</v>
+      </c>
+      <c r="E458" s="6">
+        <v>20</v>
+      </c>
+      <c r="F458" s="3">
+        <f t="shared" si="11"/>
+        <v>26.101282857142884</v>
+      </c>
+      <c r="G458" s="1"/>
+      <c r="H458" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J458" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K458" s="19">
+        <v>112</v>
+      </c>
+      <c r="L458" s="20">
+        <v>32.626603571428603</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12">
+      <c r="A459" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B459" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C459" s="9">
+        <v>104</v>
+      </c>
+      <c r="D459" s="4">
+        <v>22.692030510355</v>
+      </c>
+      <c r="E459" s="6">
+        <v>20</v>
+      </c>
+      <c r="F459" s="3">
+        <f t="shared" si="11"/>
+        <v>18.153624408283999</v>
+      </c>
+      <c r="G459" s="1"/>
+      <c r="H459" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J459" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="K459" s="19">
+        <v>104</v>
+      </c>
+      <c r="L459" s="20">
+        <v>22.692030510355</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12">
+      <c r="A460" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B460" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C460" s="9">
+        <v>96</v>
+      </c>
+      <c r="D460" s="4">
+        <v>31.437741185897401</v>
+      </c>
+      <c r="E460" s="6">
+        <v>20</v>
+      </c>
+      <c r="F460" s="3">
+        <f t="shared" si="11"/>
+        <v>25.150192948717923</v>
+      </c>
+      <c r="G460" s="1"/>
+      <c r="H460" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J460" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K460" s="19">
+        <v>96</v>
+      </c>
+      <c r="L460" s="20">
+        <v>31.437741185897401</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12">
+      <c r="A461" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B461" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C461" s="9">
+        <v>112</v>
+      </c>
+      <c r="D461" s="4">
+        <v>25.911191964285699</v>
+      </c>
+      <c r="E461" s="6">
+        <v>20</v>
+      </c>
+      <c r="F461" s="3">
+        <f t="shared" si="11"/>
+        <v>20.728953571428558</v>
+      </c>
+      <c r="G461" s="1"/>
+      <c r="H461" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J461" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K461" s="19">
+        <v>112</v>
+      </c>
+      <c r="L461" s="20">
+        <v>25.911191964285699</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12">
+      <c r="A462" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B462" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C462" s="9">
+        <v>136</v>
+      </c>
+      <c r="D462" s="4">
+        <v>26.066781735863501</v>
+      </c>
+      <c r="E462" s="6">
+        <v>20</v>
+      </c>
+      <c r="F462" s="3">
+        <f t="shared" si="11"/>
+        <v>20.853425388690802</v>
+      </c>
+      <c r="G462" s="1"/>
+      <c r="H462" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J462" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K462" s="19">
+        <v>136</v>
+      </c>
+      <c r="L462" s="20">
+        <v>26.066781735863501</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12">
+      <c r="A463" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B463" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C463" s="9">
+        <v>64</v>
+      </c>
+      <c r="D463" s="4">
+        <v>31.585208170832502</v>
+      </c>
+      <c r="E463" s="6">
+        <v>20</v>
+      </c>
+      <c r="F463" s="3">
+        <f t="shared" si="11"/>
+        <v>25.268166536666001</v>
+      </c>
+      <c r="G463" s="1"/>
+      <c r="H463" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="J463" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K463" s="19">
+        <v>64</v>
+      </c>
+      <c r="L463" s="20">
+        <v>31.585208170832502</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12">
+      <c r="A464" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B464" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C464" s="9">
+        <v>120</v>
+      </c>
+      <c r="D464" s="4">
+        <v>33.273441222319398</v>
+      </c>
+      <c r="E464" s="6">
+        <v>20</v>
+      </c>
+      <c r="F464" s="3">
+        <f t="shared" si="11"/>
+        <v>26.618752977855518</v>
+      </c>
+      <c r="G464" s="1"/>
+      <c r="H464" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J464" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K464" s="19">
+        <v>120</v>
+      </c>
+      <c r="L464" s="20">
+        <v>33.273441222319398</v>
+      </c>
+    </row>
+    <row r="465" spans="1:12">
+      <c r="A465" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B465" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C465" s="9">
+        <v>96</v>
+      </c>
+      <c r="D465" s="4">
+        <v>28.651272916666699</v>
+      </c>
+      <c r="E465" s="6">
+        <v>20</v>
+      </c>
+      <c r="F465" s="3">
+        <f t="shared" si="11"/>
+        <v>22.921018333333357</v>
+      </c>
+      <c r="G465" s="1"/>
+      <c r="H465" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J465" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K465" s="19">
+        <v>96</v>
+      </c>
+      <c r="L465" s="20">
+        <v>28.651272916666699</v>
+      </c>
+    </row>
+    <row r="466" spans="1:12">
+      <c r="A466" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B466" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C466" s="9">
+        <v>80</v>
+      </c>
+      <c r="D466" s="4">
+        <v>30.175071875</v>
+      </c>
+      <c r="E466" s="6">
+        <v>20</v>
+      </c>
+      <c r="F466" s="3">
+        <f t="shared" si="11"/>
+        <v>24.140057500000001</v>
+      </c>
+      <c r="G466" s="1"/>
+      <c r="H466" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J466" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K466" s="19">
+        <v>80</v>
+      </c>
+      <c r="L466" s="20">
+        <v>30.175071875</v>
+      </c>
+    </row>
+    <row r="467" spans="1:12">
+      <c r="A467" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B467" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C467" s="9">
+        <v>71.5</v>
+      </c>
+      <c r="D467" s="4">
+        <v>35.2410749227233</v>
+      </c>
+      <c r="E467" s="6">
+        <v>20</v>
+      </c>
+      <c r="F467" s="3">
+        <f t="shared" si="11"/>
+        <v>28.192859938178639</v>
+      </c>
+      <c r="G467" s="1"/>
+      <c r="H467" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="J467" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K467" s="19">
+        <v>71.5</v>
+      </c>
+      <c r="L467" s="20">
+        <v>35.2410749227233</v>
+      </c>
+    </row>
+    <row r="468" spans="1:12">
+      <c r="A468" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B468" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C468" s="9">
+        <v>80</v>
+      </c>
+      <c r="D468" s="4">
+        <v>30.2568398423372</v>
+      </c>
+      <c r="E468" s="6">
+        <v>20</v>
+      </c>
+      <c r="F468" s="3">
+        <f t="shared" si="11"/>
+        <v>24.205471873869762</v>
+      </c>
+      <c r="G468" s="1"/>
+      <c r="H468" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="J468" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K468" s="19">
+        <v>80</v>
+      </c>
+      <c r="L468" s="20">
+        <v>30.2568398423372</v>
+      </c>
+    </row>
+    <row r="469" spans="1:12">
+      <c r="A469" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B469" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C469" s="9">
+        <v>88</v>
+      </c>
+      <c r="D469" s="4">
+        <v>40.3872897727273</v>
+      </c>
+      <c r="E469" s="6">
+        <v>20</v>
+      </c>
+      <c r="F469" s="3">
+        <f t="shared" si="11"/>
+        <v>32.309831818181841</v>
+      </c>
+      <c r="G469" s="1"/>
+      <c r="H469" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J469" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="K469" s="19">
+        <v>88</v>
+      </c>
+      <c r="L469" s="20">
+        <v>40.3872897727273</v>
+      </c>
+    </row>
+    <row r="470" spans="1:12">
+      <c r="A470" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B470" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C470" s="9">
+        <v>88</v>
+      </c>
+      <c r="D470" s="4">
+        <v>40.3872897727273</v>
+      </c>
+      <c r="E470" s="6">
+        <v>20</v>
+      </c>
+      <c r="F470" s="3">
+        <f t="shared" si="11"/>
+        <v>32.309831818181841</v>
+      </c>
+      <c r="G470" s="1"/>
+      <c r="H470" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J470" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K470" s="19">
+        <v>88</v>
+      </c>
+      <c r="L470" s="20">
+        <v>40.3872897727273</v>
+      </c>
+    </row>
+    <row r="471" spans="1:12">
+      <c r="A471" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B471" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C471" s="9">
+        <v>136</v>
+      </c>
+      <c r="D471" s="4">
+        <v>35.015775245097998</v>
+      </c>
+      <c r="E471" s="6">
+        <v>20</v>
+      </c>
+      <c r="F471" s="3">
+        <f t="shared" si="11"/>
+        <v>28.012620196078398</v>
+      </c>
+      <c r="G471" s="1"/>
+      <c r="H471" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J471" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K471" s="19">
+        <v>136</v>
+      </c>
+      <c r="L471" s="20">
+        <v>35.015775245097998</v>
+      </c>
+    </row>
+    <row r="472" spans="1:12">
+      <c r="A472" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B472" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C472" s="9">
+        <v>40</v>
+      </c>
+      <c r="D472" s="4">
+        <v>39.402925284494998</v>
+      </c>
+      <c r="E472" s="6">
+        <v>20</v>
+      </c>
+      <c r="F472" s="3">
+        <f t="shared" si="11"/>
+        <v>31.522340227595997</v>
+      </c>
+      <c r="G472" s="1"/>
+      <c r="H472" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J472" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K472" s="19">
+        <v>40</v>
+      </c>
+      <c r="L472" s="20">
+        <v>39.402925284494998</v>
+      </c>
+    </row>
+    <row r="473" spans="1:12">
+      <c r="A473" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B473" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C473" s="9">
+        <v>16</v>
+      </c>
+      <c r="D473" s="4">
+        <v>58.081810038677901</v>
+      </c>
+      <c r="E473" s="6">
+        <v>20</v>
+      </c>
+      <c r="F473" s="3">
+        <f t="shared" ref="F473:F479" si="12">D473-(D473*E473)/100</f>
+        <v>46.465448030942319</v>
+      </c>
+      <c r="G473" s="1"/>
+      <c r="H473" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J473" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K473" s="19">
+        <v>16</v>
+      </c>
+      <c r="L473" s="20">
+        <v>58.081810038677901</v>
+      </c>
+    </row>
+    <row r="474" spans="1:12">
+      <c r="A474" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B474" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C474" s="9">
+        <v>136</v>
+      </c>
+      <c r="D474" s="4">
+        <v>36.896736881684497</v>
+      </c>
+      <c r="E474" s="6">
+        <v>20</v>
+      </c>
+      <c r="F474" s="3">
+        <f t="shared" si="12"/>
+        <v>29.517389505347598</v>
+      </c>
+      <c r="G474" s="1"/>
+      <c r="H474" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="J474" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K474" s="19">
+        <v>136</v>
+      </c>
+      <c r="L474" s="20">
+        <v>36.896736881684497</v>
+      </c>
+    </row>
+    <row r="475" spans="1:12">
+      <c r="A475" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B475" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C475" s="9">
+        <v>104</v>
+      </c>
+      <c r="D475" s="4">
+        <v>79.134148259850704</v>
+      </c>
+      <c r="E475" s="6">
+        <v>20</v>
+      </c>
+      <c r="F475" s="3">
+        <f t="shared" si="12"/>
+        <v>63.307318607880561</v>
+      </c>
+      <c r="G475" s="1"/>
+      <c r="H475" s="8"/>
+      <c r="J475" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="K475" s="19">
+        <v>104</v>
+      </c>
+      <c r="L475" s="20">
+        <v>79.134148259850704</v>
+      </c>
+    </row>
+    <row r="476" spans="1:12">
+      <c r="A476" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B476" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C476" s="9">
+        <v>106</v>
+      </c>
+      <c r="D476" s="4">
+        <v>23.231290909090902</v>
+      </c>
+      <c r="E476" s="6">
+        <v>20</v>
+      </c>
+      <c r="F476" s="3">
+        <f t="shared" si="12"/>
+        <v>18.585032727272722</v>
+      </c>
+      <c r="G476" s="1"/>
+      <c r="H476" s="8"/>
+      <c r="J476" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="K476" s="19">
+        <v>106</v>
+      </c>
+      <c r="L476" s="20">
+        <v>23.231290909090902</v>
+      </c>
+    </row>
+    <row r="477" spans="1:12">
+      <c r="A477" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B477" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C477" s="9">
+        <v>104</v>
+      </c>
+      <c r="D477" s="4">
+        <v>25.078375000000001</v>
+      </c>
+      <c r="E477" s="6">
+        <v>20</v>
+      </c>
+      <c r="F477" s="3">
+        <f t="shared" si="12"/>
+        <v>20.0627</v>
+      </c>
+      <c r="G477" s="1"/>
+      <c r="H477" s="8"/>
+      <c r="J477" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="K477" s="19">
+        <v>104</v>
+      </c>
+      <c r="L477" s="20">
+        <v>25.078375000000001</v>
+      </c>
+    </row>
+    <row r="478" spans="1:12">
+      <c r="A478" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B478" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C478" s="9">
+        <v>96</v>
+      </c>
+      <c r="D478" s="4">
+        <v>29.137684070877</v>
+      </c>
+      <c r="E478" s="6">
+        <v>20</v>
+      </c>
+      <c r="F478" s="3">
+        <f t="shared" si="12"/>
+        <v>23.310147256701601</v>
+      </c>
+      <c r="G478" s="1"/>
+      <c r="H478" s="8"/>
+      <c r="J478" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="K478" s="19">
+        <v>96</v>
+      </c>
+      <c r="L478" s="20">
+        <v>29.137684070877</v>
+      </c>
+    </row>
+    <row r="479" spans="1:12">
+      <c r="A479" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B479" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C479" s="9">
+        <v>94</v>
+      </c>
+      <c r="D479" s="4">
+        <v>58.157057626555698</v>
+      </c>
+      <c r="E479" s="6">
+        <v>20</v>
+      </c>
+      <c r="F479" s="3">
+        <f t="shared" si="12"/>
+        <v>46.525646101244561</v>
+      </c>
+      <c r="G479" s="1"/>
+      <c r="H479" s="8"/>
+      <c r="J479" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="K479" s="19">
+        <v>94</v>
+      </c>
+      <c r="L479" s="20">
+        <v>58.157057626555698</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G272"/>
@@ -11469,6 +13830,68 @@
     <hyperlink ref="H405" r:id="rId376"/>
     <hyperlink ref="H406" r:id="rId377"/>
     <hyperlink ref="H371" r:id="rId378" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="G412" r:id="rId379"/>
+    <hyperlink ref="H412" r:id="rId380"/>
+    <hyperlink ref="H413" r:id="rId381"/>
+    <hyperlink ref="H415" r:id="rId382"/>
+    <hyperlink ref="H416" r:id="rId383"/>
+    <hyperlink ref="H417" r:id="rId384"/>
+    <hyperlink ref="H418" r:id="rId385"/>
+    <hyperlink ref="H419" r:id="rId386"/>
+    <hyperlink ref="H420" r:id="rId387"/>
+    <hyperlink ref="H421" r:id="rId388"/>
+    <hyperlink ref="H422" r:id="rId389"/>
+    <hyperlink ref="H423" r:id="rId390"/>
+    <hyperlink ref="H424" r:id="rId391"/>
+    <hyperlink ref="H426" r:id="rId392"/>
+    <hyperlink ref="H427" r:id="rId393"/>
+    <hyperlink ref="H428" r:id="rId394"/>
+    <hyperlink ref="H429" r:id="rId395"/>
+    <hyperlink ref="H430" r:id="rId396"/>
+    <hyperlink ref="H431" r:id="rId397"/>
+    <hyperlink ref="H432" r:id="rId398"/>
+    <hyperlink ref="H433" r:id="rId399"/>
+    <hyperlink ref="H434" r:id="rId400"/>
+    <hyperlink ref="H435" r:id="rId401"/>
+    <hyperlink ref="H436" r:id="rId402"/>
+    <hyperlink ref="H437" r:id="rId403"/>
+    <hyperlink ref="H438" r:id="rId404"/>
+    <hyperlink ref="H440" r:id="rId405"/>
+    <hyperlink ref="H441" r:id="rId406"/>
+    <hyperlink ref="H442" r:id="rId407"/>
+    <hyperlink ref="H443" r:id="rId408"/>
+    <hyperlink ref="H444" r:id="rId409"/>
+    <hyperlink ref="H445" r:id="rId410"/>
+    <hyperlink ref="H446" r:id="rId411"/>
+    <hyperlink ref="H447" r:id="rId412"/>
+    <hyperlink ref="H448" r:id="rId413"/>
+    <hyperlink ref="H449" r:id="rId414"/>
+    <hyperlink ref="H450" r:id="rId415"/>
+    <hyperlink ref="H451" r:id="rId416"/>
+    <hyperlink ref="H452" r:id="rId417"/>
+    <hyperlink ref="H453" r:id="rId418"/>
+    <hyperlink ref="H454" r:id="rId419"/>
+    <hyperlink ref="H455" r:id="rId420"/>
+    <hyperlink ref="H456" r:id="rId421"/>
+    <hyperlink ref="H457" r:id="rId422"/>
+    <hyperlink ref="H458" r:id="rId423"/>
+    <hyperlink ref="H459" r:id="rId424"/>
+    <hyperlink ref="H460" r:id="rId425"/>
+    <hyperlink ref="H461" r:id="rId426"/>
+    <hyperlink ref="H462" r:id="rId427"/>
+    <hyperlink ref="H463" r:id="rId428"/>
+    <hyperlink ref="H464" r:id="rId429"/>
+    <hyperlink ref="H465" r:id="rId430"/>
+    <hyperlink ref="H466" r:id="rId431"/>
+    <hyperlink ref="H467" r:id="rId432"/>
+    <hyperlink ref="H468" r:id="rId433"/>
+    <hyperlink ref="H469" r:id="rId434"/>
+    <hyperlink ref="H470" r:id="rId435"/>
+    <hyperlink ref="H471" r:id="rId436"/>
+    <hyperlink ref="H472" r:id="rId437"/>
+    <hyperlink ref="H473" r:id="rId438"/>
+    <hyperlink ref="H474" r:id="rId439"/>
+    <hyperlink ref="H439" r:id="rId440" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="157">
   <si>
     <t>Tecnico</t>
   </si>
@@ -486,30 +486,22 @@
     <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
   </si>
   <si>
-    <t>Matricola e Nominativo Dipendente</t>
-  </si>
-  <si>
-    <t>Tot. Ore</t>
-  </si>
-  <si>
-    <t>Tot.</t>
-  </si>
-  <si>
     <t>IRTE0000117 - FERRANTI GIANLUCA</t>
+  </si>
+  <si>
+    <t>IRTE0000116 - GARANTE GIUSEPPE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.0\ &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="#,###,###,##0&quot; h.&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,###,###,##0.00&quot; h.&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,###,###,##0.00&quot; €/h.&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,14 +528,8 @@
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8.25"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,21 +545,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFC0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0FFC0"/>
       </patternFill>
     </fill>
   </fills>
@@ -623,7 +594,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -643,18 +614,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -950,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L479"/>
+  <dimension ref="A1:H480"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -961,9 +920,6 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="24.28515625" customWidth="1"/>
     <col min="8" max="8" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10873,7 +10829,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="401" spans="1:12">
+    <row r="401" spans="1:8">
       <c r="A401" s="1" t="s">
         <v>60</v>
       </c>
@@ -10898,7 +10854,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="402" spans="1:12">
+    <row r="402" spans="1:8">
       <c r="A402" s="1" t="s">
         <v>61</v>
       </c>
@@ -10923,7 +10879,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="403" spans="1:12">
+    <row r="403" spans="1:8">
       <c r="A403" s="1" t="s">
         <v>62</v>
       </c>
@@ -10948,7 +10904,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="404" spans="1:12">
+    <row r="404" spans="1:8">
       <c r="A404" s="1" t="s">
         <v>63</v>
       </c>
@@ -10973,7 +10929,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="405" spans="1:12">
+    <row r="405" spans="1:8">
       <c r="A405" s="1" t="s">
         <v>64</v>
       </c>
@@ -10998,7 +10954,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="406" spans="1:12">
+    <row r="406" spans="1:8">
       <c r="A406" s="1" t="s">
         <v>65</v>
       </c>
@@ -11023,7 +10979,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="407" spans="1:12">
+    <row r="407" spans="1:8">
       <c r="A407" s="10" t="s">
         <v>134</v>
       </c>
@@ -11046,7 +11002,7 @@
       <c r="G407" s="1"/>
       <c r="H407" s="8"/>
     </row>
-    <row r="408" spans="1:12">
+    <row r="408" spans="1:8">
       <c r="A408" s="1" t="s">
         <v>133</v>
       </c>
@@ -11069,7 +11025,7 @@
       <c r="G408" s="1"/>
       <c r="H408" s="8"/>
     </row>
-    <row r="409" spans="1:12">
+    <row r="409" spans="1:8">
       <c r="A409" s="1" t="s">
         <v>135</v>
       </c>
@@ -11092,7 +11048,7 @@
       <c r="G409" s="1"/>
       <c r="H409" s="8"/>
     </row>
-    <row r="410" spans="1:12">
+    <row r="410" spans="1:8">
       <c r="A410" s="1" t="s">
         <v>136</v>
       </c>
@@ -11115,7 +11071,7 @@
       <c r="G410" s="1"/>
       <c r="H410" s="8"/>
     </row>
-    <row r="411" spans="1:12">
+    <row r="411" spans="1:8">
       <c r="A411" s="1" t="s">
         <v>140</v>
       </c>
@@ -11137,35 +11093,26 @@
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="8"/>
-      <c r="J411" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="K411" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="L411" s="17" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12">
+    </row>
+    <row r="412" spans="1:8">
       <c r="A412" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B412" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C412" s="9">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D412" s="12">
-        <v>37.604112903225797</v>
+        <v>34.926737804878101</v>
       </c>
       <c r="E412" s="13">
         <v>20</v>
       </c>
       <c r="F412" s="14">
         <f t="shared" si="11"/>
-        <v>30.083290322580638</v>
+        <v>27.941390243902482</v>
       </c>
       <c r="G412" s="15" t="s">
         <v>67</v>
@@ -11173,35 +11120,26 @@
       <c r="H412" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J412" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="K412" s="19">
-        <v>88</v>
-      </c>
-      <c r="L412" s="20">
-        <v>37.604112903225797</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12">
+    </row>
+    <row r="413" spans="1:8">
       <c r="A413" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B413" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C413" s="9">
-        <v>63.5</v>
+        <v>87.5</v>
       </c>
       <c r="D413" s="4">
-        <v>38.479831632710201</v>
+        <v>42.202444669387702</v>
       </c>
       <c r="E413" s="6">
         <v>20</v>
       </c>
       <c r="F413" s="3">
         <f t="shared" si="11"/>
-        <v>30.78386530616816</v>
+        <v>33.761955735510163</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>67</v>
@@ -11209,2245 +11147,1665 @@
       <c r="H413" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="J413" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="K413" s="19">
-        <v>63.5</v>
-      </c>
-      <c r="L413" s="20">
-        <v>38.479831632710201</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12">
+    </row>
+    <row r="414" spans="1:8">
       <c r="A414" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B414" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C414" s="9">
         <v>16</v>
       </c>
       <c r="D414" s="4">
-        <v>43.527846283783802</v>
+        <v>43.336609642857098</v>
       </c>
       <c r="E414" s="6">
         <v>20</v>
       </c>
       <c r="F414" s="3">
         <f t="shared" si="11"/>
-        <v>34.822277027027042</v>
+        <v>34.66928771428568</v>
       </c>
       <c r="G414" s="1"/>
       <c r="H414" s="8"/>
-      <c r="J414" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="K414" s="19">
-        <v>16</v>
-      </c>
-      <c r="L414" s="20">
-        <v>43.527846283783802</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12">
+    </row>
+    <row r="415" spans="1:8">
       <c r="A415" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B415" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C415" s="9">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D415" s="4">
-        <v>22.541478490259699</v>
+        <v>22.536746287878799</v>
       </c>
       <c r="E415" s="6">
         <v>20</v>
       </c>
       <c r="F415" s="3">
         <f t="shared" si="11"/>
-        <v>18.033182792207761</v>
+        <v>18.029397030303038</v>
       </c>
       <c r="G415" s="1"/>
       <c r="H415" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J415" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="K415" s="19">
-        <v>88</v>
-      </c>
-      <c r="L415" s="20">
-        <v>22.541478490259699</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12">
+    </row>
+    <row r="416" spans="1:8">
       <c r="A416" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B416" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C416" s="9">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D416" s="4">
-        <v>73.332048526228704</v>
+        <v>67.812777057926795</v>
       </c>
       <c r="E416" s="6">
         <v>20</v>
       </c>
       <c r="F416" s="3">
         <f t="shared" si="11"/>
-        <v>58.665638820982963</v>
+        <v>54.250221646341437</v>
       </c>
       <c r="G416" s="1"/>
       <c r="H416" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J416" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="K416" s="19">
-        <v>88</v>
-      </c>
-      <c r="L416" s="20">
-        <v>73.332048526228704</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12">
+    </row>
+    <row r="417" spans="1:8">
       <c r="A417" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B417" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C417" s="9">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D417" s="4">
-        <v>27.902842741935501</v>
+        <v>25.796163888888898</v>
       </c>
       <c r="E417" s="6">
         <v>20</v>
       </c>
       <c r="F417" s="3">
         <f t="shared" si="11"/>
-        <v>22.322274193548402</v>
+        <v>20.636931111111117</v>
       </c>
       <c r="G417" s="1"/>
       <c r="H417" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J417" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="K417" s="19">
-        <v>96</v>
-      </c>
-      <c r="L417" s="20">
-        <v>27.902842741935501</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12">
+    </row>
+    <row r="418" spans="1:8">
       <c r="A418" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B418" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C418" s="9">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D418" s="4">
-        <v>37.276177700049097</v>
+        <v>34.5041824513428</v>
       </c>
       <c r="E418" s="6">
         <v>20</v>
       </c>
       <c r="F418" s="3">
         <f t="shared" si="11"/>
-        <v>29.820942160039277</v>
+        <v>27.60334596107424</v>
       </c>
       <c r="G418" s="1"/>
       <c r="H418" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J418" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="K418" s="19">
-        <v>80</v>
-      </c>
-      <c r="L418" s="20">
-        <v>37.276177700049097</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12">
+    </row>
+    <row r="419" spans="1:8">
       <c r="A419" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B419" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C419" s="9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D419" s="4">
-        <v>36.273470833333398</v>
+        <v>39.2927051282051</v>
       </c>
       <c r="E419" s="6">
         <v>20</v>
       </c>
       <c r="F419" s="3">
         <f t="shared" si="11"/>
-        <v>29.018776666666717</v>
+        <v>31.434164102564079</v>
       </c>
       <c r="G419" s="1"/>
       <c r="H419" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J419" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="K419" s="19">
-        <v>120</v>
-      </c>
-      <c r="L419" s="20">
-        <v>36.273470833333398</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12">
+    </row>
+    <row r="420" spans="1:8">
       <c r="A420" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B420" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C420" s="9">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D420" s="4">
-        <v>37.344654761904799</v>
+        <v>35.765437499999997</v>
       </c>
       <c r="E420" s="6">
         <v>20</v>
       </c>
       <c r="F420" s="3">
         <f t="shared" si="11"/>
-        <v>29.875723809523841</v>
+        <v>28.612349999999999</v>
       </c>
       <c r="G420" s="1"/>
       <c r="H420" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="J420" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K420" s="19">
-        <v>64</v>
-      </c>
-      <c r="L420" s="20">
-        <v>37.344654761904799</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12">
+    </row>
+    <row r="421" spans="1:8">
       <c r="A421" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B421" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C421" s="9">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D421" s="4">
-        <v>90.817939644607804</v>
+        <v>87.082881097561</v>
       </c>
       <c r="E421" s="6">
         <v>20</v>
       </c>
       <c r="F421" s="3">
         <f t="shared" si="11"/>
-        <v>72.654351715686246</v>
+        <v>69.666304878048805</v>
       </c>
       <c r="G421" s="1"/>
       <c r="H421" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J421" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="K421" s="19">
-        <v>64</v>
-      </c>
-      <c r="L421" s="20">
-        <v>90.817939644607804</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12">
+    </row>
+    <row r="422" spans="1:8">
       <c r="A422" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B422" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C422" s="9">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D422" s="4">
-        <v>101.36440105301401</v>
+        <v>97.689130335365903</v>
       </c>
       <c r="E422" s="6">
         <v>20</v>
       </c>
       <c r="F422" s="3">
         <f t="shared" si="11"/>
-        <v>81.0915208424112</v>
+        <v>78.151304268292719</v>
       </c>
       <c r="G422" s="1"/>
       <c r="H422" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J422" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="K422" s="19">
-        <v>72</v>
-      </c>
-      <c r="L422" s="20">
-        <v>101.36440105301401</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12">
+    </row>
+    <row r="423" spans="1:8">
       <c r="A423" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B423" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C423" s="9">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D423" s="4">
-        <v>35.874131238633602</v>
+        <v>32.238172860810998</v>
       </c>
       <c r="E423" s="6">
         <v>20</v>
       </c>
       <c r="F423" s="3">
         <f t="shared" si="11"/>
-        <v>28.699304990906882</v>
+        <v>25.790538288648797</v>
       </c>
       <c r="G423" s="1"/>
       <c r="H423" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J423" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="K423" s="19">
-        <v>78</v>
-      </c>
-      <c r="L423" s="20">
-        <v>35.874131238633602</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12">
+    </row>
+    <row r="424" spans="1:8">
       <c r="A424" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B424" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C424" s="9">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="D424" s="4">
-        <v>27.902842741935501</v>
+        <v>25.796163888888898</v>
       </c>
       <c r="E424" s="6">
         <v>20</v>
       </c>
       <c r="F424" s="3">
         <f t="shared" si="11"/>
-        <v>22.322274193548402</v>
+        <v>20.636931111111117</v>
       </c>
       <c r="G424" s="1"/>
       <c r="H424" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J424" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K424" s="19">
-        <v>104</v>
-      </c>
-      <c r="L424" s="20">
-        <v>27.902842741935501</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12">
+    </row>
+    <row r="425" spans="1:8">
       <c r="A425" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B425" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C425" s="9">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D425" s="4">
-        <v>65.784042114067901</v>
+        <v>58.556289851916397</v>
       </c>
       <c r="E425" s="6">
         <v>20</v>
       </c>
       <c r="F425" s="3">
         <f t="shared" si="11"/>
-        <v>52.627233691254318</v>
+        <v>46.845031881533117</v>
       </c>
       <c r="G425" s="1"/>
       <c r="H425" s="8"/>
-      <c r="J425" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="K425" s="19">
-        <v>72</v>
-      </c>
-      <c r="L425" s="20">
-        <v>65.784042114067901</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12">
+    </row>
+    <row r="426" spans="1:8">
       <c r="A426" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B426" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C426" s="9">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="D426" s="4">
-        <v>36.4920336538462</v>
+        <v>39.409404411764697</v>
       </c>
       <c r="E426" s="6">
         <v>20</v>
       </c>
       <c r="F426" s="3">
         <f t="shared" si="11"/>
-        <v>29.193626923076959</v>
+        <v>31.527523529411759</v>
       </c>
       <c r="G426" s="1"/>
       <c r="H426" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="J426" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K426" s="19">
-        <v>104</v>
-      </c>
-      <c r="L426" s="20">
-        <v>36.4920336538462</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12">
+    </row>
+    <row r="427" spans="1:8">
       <c r="A427" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B427" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C427" s="9">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D427" s="4">
-        <v>32.8449294704861</v>
+        <v>34.535883767887498</v>
       </c>
       <c r="E427" s="6">
         <v>20</v>
       </c>
       <c r="F427" s="3">
         <f t="shared" si="11"/>
-        <v>26.27594357638888</v>
+        <v>27.628707014309999</v>
       </c>
       <c r="G427" s="1"/>
       <c r="H427" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J427" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K427" s="19">
-        <v>128</v>
-      </c>
-      <c r="L427" s="20">
-        <v>32.8449294704861</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12">
+    </row>
+    <row r="428" spans="1:8">
       <c r="A428" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B428" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C428" s="9">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D428" s="4">
-        <v>37.604112903225797</v>
+        <v>34.926737804878101</v>
       </c>
       <c r="E428" s="6">
         <v>20</v>
       </c>
       <c r="F428" s="3">
         <f t="shared" si="11"/>
-        <v>30.083290322580638</v>
+        <v>27.941390243902482</v>
       </c>
       <c r="G428" s="1"/>
       <c r="H428" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="J428" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K428" s="19">
-        <v>88</v>
-      </c>
-      <c r="L428" s="20">
-        <v>37.604112903225797</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12">
+    </row>
+    <row r="429" spans="1:8">
       <c r="A429" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B429" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C429" s="9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D429" s="4">
-        <v>29.6908361111111</v>
+        <v>34.471468407258101</v>
       </c>
       <c r="E429" s="6">
         <v>20</v>
       </c>
       <c r="F429" s="3">
         <f t="shared" si="11"/>
-        <v>23.752668888888881</v>
+        <v>27.577174725806479</v>
       </c>
       <c r="G429" s="1"/>
       <c r="H429" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="J429" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="K429" s="19">
-        <v>120</v>
-      </c>
-      <c r="L429" s="20">
-        <v>29.6908361111111</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12">
+    </row>
+    <row r="430" spans="1:8">
       <c r="A430" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B430" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C430" s="9">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D430" s="4">
-        <v>48.722940437538497</v>
+        <v>48.2411620189297</v>
       </c>
       <c r="E430" s="6">
         <v>20</v>
       </c>
       <c r="F430" s="3">
         <f t="shared" si="11"/>
-        <v>38.978352350030796</v>
+        <v>38.59292961514376</v>
       </c>
       <c r="G430" s="1"/>
       <c r="H430" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="J430" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="K430" s="19">
-        <v>103</v>
-      </c>
-      <c r="L430" s="20">
-        <v>48.722940437538497</v>
-      </c>
-    </row>
-    <row r="431" spans="1:12">
+    </row>
+    <row r="431" spans="1:8">
       <c r="A431" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B431" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C431" s="9">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D431" s="4">
-        <v>31.0014254734849</v>
+        <v>37.519305620081397</v>
       </c>
       <c r="E431" s="6">
         <v>20</v>
       </c>
       <c r="F431" s="3">
         <f t="shared" si="11"/>
-        <v>24.80114037878792</v>
+        <v>30.015444496065118</v>
       </c>
       <c r="G431" s="1"/>
       <c r="H431" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J431" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K431" s="19">
-        <v>120</v>
-      </c>
-      <c r="L431" s="20">
-        <v>31.0014254734849</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12">
+    </row>
+    <row r="432" spans="1:8">
       <c r="A432" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B432" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C432" s="9">
-        <v>95</v>
+        <v>135.5</v>
       </c>
       <c r="D432" s="4">
-        <v>53.5923998587432</v>
+        <v>50.360186906318503</v>
       </c>
       <c r="E432" s="6">
         <v>20</v>
       </c>
       <c r="F432" s="3">
         <f t="shared" si="11"/>
-        <v>42.873919886994557</v>
+        <v>40.288149525054806</v>
       </c>
       <c r="G432" s="1"/>
       <c r="H432" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="J432" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="K432" s="19">
-        <v>95</v>
-      </c>
-      <c r="L432" s="20">
-        <v>53.5923998587432</v>
-      </c>
-    </row>
-    <row r="433" spans="1:12">
+    </row>
+    <row r="433" spans="1:8">
       <c r="A433" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B433" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C433" s="9">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D433" s="4">
-        <v>45.699325694444397</v>
+        <v>35.755218592171701</v>
       </c>
       <c r="E433" s="6">
         <v>20</v>
       </c>
       <c r="F433" s="3">
         <f t="shared" si="11"/>
-        <v>36.559460555555518</v>
+        <v>28.60417487373736</v>
       </c>
       <c r="G433" s="1"/>
       <c r="H433" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J433" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K433" s="19">
-        <v>72</v>
-      </c>
-      <c r="L433" s="20">
-        <v>45.699325694444397</v>
-      </c>
-    </row>
-    <row r="434" spans="1:12">
+    </row>
+    <row r="434" spans="1:8">
       <c r="A434" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B434" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C434" s="9">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D434" s="4">
-        <v>34.394302544476503</v>
+        <v>33.188081165098197</v>
       </c>
       <c r="E434" s="6">
         <v>20</v>
       </c>
       <c r="F434" s="3">
         <f t="shared" si="11"/>
-        <v>27.515442035581202</v>
+        <v>26.550464932078558</v>
       </c>
       <c r="G434" s="1"/>
       <c r="H434" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J434" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K434" s="19">
-        <v>96</v>
-      </c>
-      <c r="L434" s="20">
-        <v>34.394302544476503</v>
-      </c>
-    </row>
-    <row r="435" spans="1:12">
+    </row>
+    <row r="435" spans="1:8">
       <c r="A435" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B435" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C435" s="9">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="D435" s="4">
-        <v>58.825565263804002</v>
+        <v>55.786484071767902</v>
       </c>
       <c r="E435" s="6">
         <v>20</v>
       </c>
       <c r="F435" s="3">
         <f t="shared" si="11"/>
-        <v>47.060452211043199</v>
+        <v>44.629187257414323</v>
       </c>
       <c r="G435" s="1"/>
       <c r="H435" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="J435" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K435" s="19">
-        <v>101</v>
-      </c>
-      <c r="L435" s="20">
-        <v>58.825565263804002</v>
-      </c>
-    </row>
-    <row r="436" spans="1:12">
+    </row>
+    <row r="436" spans="1:8">
       <c r="A436" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B436" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C436" s="9">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D436" s="4">
-        <v>85.515069444444407</v>
+        <v>83.905483231707294</v>
       </c>
       <c r="E436" s="6">
         <v>20</v>
       </c>
       <c r="F436" s="3">
         <f t="shared" si="11"/>
-        <v>68.412055555555526</v>
+        <v>67.124386585365841</v>
       </c>
       <c r="G436" s="1"/>
       <c r="H436" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="J436" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K436" s="19">
-        <v>72</v>
-      </c>
-      <c r="L436" s="20">
-        <v>85.515069444444407</v>
-      </c>
-    </row>
-    <row r="437" spans="1:12">
+    </row>
+    <row r="437" spans="1:8">
       <c r="A437" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B437" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C437" s="9">
         <v>64</v>
       </c>
       <c r="D437" s="4">
-        <v>31.138515625</v>
+        <v>53.360546874999997</v>
       </c>
       <c r="E437" s="6">
         <v>20</v>
       </c>
       <c r="F437" s="3">
         <f t="shared" si="11"/>
-        <v>24.910812499999999</v>
+        <v>42.688437499999999</v>
       </c>
       <c r="G437" s="1"/>
       <c r="H437" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="J437" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K437" s="19">
-        <v>64</v>
-      </c>
-      <c r="L437" s="20">
-        <v>31.138515625</v>
-      </c>
-    </row>
-    <row r="438" spans="1:12">
+    </row>
+    <row r="438" spans="1:8">
       <c r="A438" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B438" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C438" s="9">
         <v>72</v>
       </c>
       <c r="D438" s="4">
-        <v>22.814334821428599</v>
+        <v>22.36840625</v>
       </c>
       <c r="E438" s="6">
         <v>20</v>
       </c>
       <c r="F438" s="3">
         <f t="shared" si="11"/>
-        <v>18.251467857142877</v>
+        <v>17.894725000000001</v>
       </c>
       <c r="G438" s="1"/>
       <c r="H438" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J438" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K438" s="19">
-        <v>72</v>
-      </c>
-      <c r="L438" s="20">
-        <v>22.814334821428599</v>
-      </c>
-    </row>
-    <row r="439" spans="1:12">
+    </row>
+    <row r="439" spans="1:8">
       <c r="A439" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B439" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C439" s="9">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D439" s="4">
-        <v>52.666668749999999</v>
+        <v>45.174571969696999</v>
       </c>
       <c r="E439" s="6">
         <v>20</v>
       </c>
       <c r="F439" s="3">
         <f t="shared" si="11"/>
-        <v>42.133335000000002</v>
+        <v>36.139657575757596</v>
       </c>
       <c r="G439" s="1"/>
       <c r="H439" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="J439" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="K439" s="19">
-        <v>8</v>
-      </c>
-      <c r="L439" s="20">
-        <v>52.666668749999999</v>
-      </c>
-    </row>
-    <row r="440" spans="1:12">
+    </row>
+    <row r="440" spans="1:8">
       <c r="A440" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B440" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C440" s="9">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="D440" s="4">
-        <v>58.917153619031097</v>
+        <v>55.8542804988287</v>
       </c>
       <c r="E440" s="6">
         <v>20</v>
       </c>
       <c r="F440" s="3">
         <f t="shared" si="11"/>
-        <v>47.133722895224878</v>
+        <v>44.683424399062957</v>
       </c>
       <c r="G440" s="1"/>
       <c r="H440" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J440" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="K440" s="19">
-        <v>109</v>
-      </c>
-      <c r="L440" s="20">
-        <v>58.917153619031097</v>
-      </c>
-    </row>
-    <row r="441" spans="1:12">
+    </row>
+    <row r="441" spans="1:8">
       <c r="A441" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B441" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C441" s="9">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D441" s="4">
-        <v>60.347925273764503</v>
+        <v>53.310188888284003</v>
       </c>
       <c r="E441" s="6">
         <v>20</v>
       </c>
       <c r="F441" s="3">
         <f t="shared" si="11"/>
-        <v>48.278340219011604</v>
+        <v>42.648151110627204</v>
       </c>
       <c r="G441" s="1"/>
       <c r="H441" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J441" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K441" s="19">
-        <v>96</v>
-      </c>
-      <c r="L441" s="20">
-        <v>60.347925273764503</v>
-      </c>
-    </row>
-    <row r="442" spans="1:12">
+    </row>
+    <row r="442" spans="1:8">
       <c r="A442" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B442" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C442" s="9">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="D442" s="4">
-        <v>29.894890624999999</v>
+        <v>34.624721874999999</v>
       </c>
       <c r="E442" s="6">
         <v>20</v>
       </c>
       <c r="F442" s="3">
         <f t="shared" si="11"/>
-        <v>23.915912499999997</v>
+        <v>27.6997775</v>
       </c>
       <c r="G442" s="1"/>
       <c r="H442" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J442" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K442" s="19">
-        <v>128</v>
-      </c>
-      <c r="L442" s="20">
-        <v>29.894890624999999</v>
-      </c>
-    </row>
-    <row r="443" spans="1:12">
+    </row>
+    <row r="443" spans="1:8">
       <c r="A443" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B443" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C443" s="9">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D443" s="4">
-        <v>49.990725309917401</v>
+        <v>44.310356951871697</v>
       </c>
       <c r="E443" s="6">
         <v>20</v>
       </c>
       <c r="F443" s="3">
         <f t="shared" si="11"/>
-        <v>39.992580247933923</v>
+        <v>35.448285561497357</v>
       </c>
       <c r="G443" s="1"/>
       <c r="H443" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="J443" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="K443" s="19">
-        <v>88</v>
-      </c>
-      <c r="L443" s="20">
-        <v>49.990725309917401</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12">
+    </row>
+    <row r="444" spans="1:8">
       <c r="A444" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B444" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C444" s="9">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D444" s="4">
-        <v>68.987288235294102</v>
+        <v>62.755560743464002</v>
       </c>
       <c r="E444" s="6">
         <v>20</v>
       </c>
       <c r="F444" s="3">
         <f t="shared" si="11"/>
-        <v>55.189830588235282</v>
+        <v>50.2044485947712</v>
       </c>
       <c r="G444" s="1"/>
       <c r="H444" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J444" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="K444" s="19">
-        <v>96</v>
-      </c>
-      <c r="L444" s="20">
-        <v>68.987288235294102</v>
-      </c>
-    </row>
-    <row r="445" spans="1:12">
+    </row>
+    <row r="445" spans="1:8">
       <c r="A445" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B445" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C445" s="9">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="D445" s="4">
-        <v>21.692925925925898</v>
+        <v>27.674382142857201</v>
       </c>
       <c r="E445" s="6">
         <v>20</v>
       </c>
       <c r="F445" s="3">
         <f t="shared" si="11"/>
-        <v>17.354340740740717</v>
+        <v>22.139505714285761</v>
       </c>
       <c r="G445" s="1"/>
       <c r="H445" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="J445" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="K445" s="19">
-        <v>128</v>
-      </c>
-      <c r="L445" s="20">
-        <v>21.692925925925898</v>
-      </c>
-    </row>
-    <row r="446" spans="1:12">
+    </row>
+    <row r="446" spans="1:8">
       <c r="A446" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B446" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C446" s="9">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D446" s="4">
-        <v>55.287511072487298</v>
+        <v>55.823776157998402</v>
       </c>
       <c r="E446" s="6">
         <v>20</v>
       </c>
       <c r="F446" s="3">
         <f t="shared" si="11"/>
-        <v>44.230008857989837</v>
+        <v>44.659020926398725</v>
       </c>
       <c r="G446" s="1"/>
       <c r="H446" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J446" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K446" s="19">
-        <v>110</v>
-      </c>
-      <c r="L446" s="20">
-        <v>55.287511072487298</v>
-      </c>
-    </row>
-    <row r="447" spans="1:12">
+    </row>
+    <row r="447" spans="1:8">
       <c r="A447" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B447" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C447" s="9">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D447" s="4">
-        <v>60.347925273764503</v>
+        <v>53.310188888284003</v>
       </c>
       <c r="E447" s="6">
         <v>20</v>
       </c>
       <c r="F447" s="3">
         <f t="shared" si="11"/>
-        <v>48.278340219011604</v>
+        <v>42.648151110627204</v>
       </c>
       <c r="G447" s="1"/>
       <c r="H447" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J447" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K447" s="19">
-        <v>96</v>
-      </c>
-      <c r="L447" s="20">
-        <v>60.347925273764503</v>
-      </c>
-    </row>
-    <row r="448" spans="1:12">
+    </row>
+    <row r="448" spans="1:8">
       <c r="A448" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B448" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C448" s="9">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D448" s="4">
-        <v>87.400534404502594</v>
+        <v>85.435341463414602</v>
       </c>
       <c r="E448" s="6">
         <v>20</v>
       </c>
       <c r="F448" s="3">
         <f t="shared" si="11"/>
-        <v>69.920427523602072</v>
+        <v>68.348273170731687</v>
       </c>
       <c r="G448" s="1"/>
       <c r="H448" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J448" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="K448" s="19">
-        <v>72</v>
-      </c>
-      <c r="L448" s="20">
-        <v>87.400534404502594</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12">
+    </row>
+    <row r="449" spans="1:8">
       <c r="A449" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B449" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C449" s="9">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D449" s="4">
-        <v>25.255327029220801</v>
+        <v>23.984021464646499</v>
       </c>
       <c r="E449" s="6">
         <v>20</v>
       </c>
       <c r="F449" s="3">
         <f t="shared" si="11"/>
-        <v>20.204261623376642</v>
+        <v>19.187217171717201</v>
       </c>
       <c r="G449" s="1"/>
       <c r="H449" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J449" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="K449" s="19">
-        <v>88</v>
-      </c>
-      <c r="L449" s="20">
-        <v>25.255327029220801</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12">
+    </row>
+    <row r="450" spans="1:8">
       <c r="A450" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B450" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C450" s="9">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D450" s="4">
-        <v>23.231290909090902</v>
+        <v>30.4829166666667</v>
       </c>
       <c r="E450" s="6">
         <v>20</v>
       </c>
       <c r="F450" s="3">
         <f t="shared" si="11"/>
-        <v>18.585032727272722</v>
+        <v>24.386333333333361</v>
       </c>
       <c r="G450" s="1"/>
       <c r="H450" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J450" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K450" s="19">
-        <v>106</v>
-      </c>
-      <c r="L450" s="20">
-        <v>23.231290909090902</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12">
+    </row>
+    <row r="451" spans="1:8">
       <c r="A451" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B451" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C451" s="9">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D451" s="4">
-        <v>34.184946428571401</v>
+        <v>38.682580453574197</v>
       </c>
       <c r="E451" s="6">
         <v>20</v>
       </c>
       <c r="F451" s="3">
         <f t="shared" si="11"/>
-        <v>27.347957142857119</v>
+        <v>30.946064362859357</v>
       </c>
       <c r="G451" s="1"/>
       <c r="H451" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J451" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="K451" s="19">
-        <v>112</v>
-      </c>
-      <c r="L451" s="20">
-        <v>34.184946428571401</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12">
+    </row>
+    <row r="452" spans="1:8">
       <c r="A452" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B452" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C452" s="9">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="D452" s="4">
-        <v>35.723969091961301</v>
+        <v>38.506148753544402</v>
       </c>
       <c r="E452" s="6">
         <v>20</v>
       </c>
       <c r="F452" s="3">
         <f t="shared" si="11"/>
-        <v>28.579175273569042</v>
+        <v>30.804919002835522</v>
       </c>
       <c r="G452" s="1"/>
       <c r="H452" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J452" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K452" s="19">
-        <v>144</v>
-      </c>
-      <c r="L452" s="20">
-        <v>35.723969091961301</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12">
+    </row>
+    <row r="453" spans="1:8">
       <c r="A453" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B453" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C453" s="9">
         <v>8</v>
       </c>
       <c r="D453" s="4">
-        <v>30.648550632911402</v>
+        <v>28.5604495798319</v>
       </c>
       <c r="E453" s="6">
         <v>20</v>
       </c>
       <c r="F453" s="3">
         <f t="shared" si="11"/>
-        <v>24.51884050632912</v>
+        <v>22.848359663865519</v>
       </c>
       <c r="G453" s="1"/>
       <c r="H453" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="J453" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K453" s="19">
-        <v>8</v>
-      </c>
-      <c r="L453" s="20">
-        <v>30.648550632911402</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12">
+    </row>
+    <row r="454" spans="1:8">
       <c r="A454" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B454" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C454" s="9">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D454" s="4">
-        <v>37.006373374329002</v>
+        <v>34.956656470864502</v>
       </c>
       <c r="E454" s="6">
         <v>20</v>
       </c>
       <c r="F454" s="3">
         <f t="shared" si="11"/>
-        <v>29.605098699463202</v>
+        <v>27.9653251766916</v>
       </c>
       <c r="G454" s="1"/>
       <c r="H454" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J454" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K454" s="19">
-        <v>88</v>
-      </c>
-      <c r="L454" s="20">
-        <v>37.006373374329002</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12">
+    </row>
+    <row r="455" spans="1:8">
       <c r="A455" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B455" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C455" s="9">
         <v>112</v>
       </c>
       <c r="D455" s="4">
-        <v>25.078375000000001</v>
+        <v>34.708821428571397</v>
       </c>
       <c r="E455" s="6">
         <v>20</v>
       </c>
       <c r="F455" s="3">
         <f t="shared" si="11"/>
-        <v>20.0627</v>
+        <v>27.767057142857119</v>
       </c>
       <c r="G455" s="1"/>
       <c r="H455" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J455" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K455" s="19">
-        <v>112</v>
-      </c>
-      <c r="L455" s="20">
-        <v>25.078375000000001</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12">
+    </row>
+    <row r="456" spans="1:8">
       <c r="A456" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B456" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C456" s="9">
         <v>90</v>
       </c>
       <c r="D456" s="4">
-        <v>68.987288235294102</v>
+        <v>68.570641176470602</v>
       </c>
       <c r="E456" s="6">
         <v>20</v>
       </c>
       <c r="F456" s="3">
         <f t="shared" si="11"/>
-        <v>55.189830588235282</v>
+        <v>54.856512941176483</v>
       </c>
       <c r="G456" s="1"/>
       <c r="H456" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J456" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K456" s="19">
-        <v>90</v>
-      </c>
-      <c r="L456" s="20">
-        <v>68.987288235294102</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12">
+    </row>
+    <row r="457" spans="1:8">
       <c r="A457" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B457" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C457" s="9">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D457" s="4">
-        <v>68.987288235294102</v>
+        <v>62.845023519356403</v>
       </c>
       <c r="E457" s="6">
         <v>20</v>
       </c>
       <c r="F457" s="3">
         <f t="shared" si="11"/>
-        <v>55.189830588235282</v>
+        <v>50.276018815485124</v>
       </c>
       <c r="G457" s="1"/>
       <c r="H457" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J457" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K457" s="19">
-        <v>98</v>
-      </c>
-      <c r="L457" s="20">
-        <v>68.987288235294102</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12">
+    </row>
+    <row r="458" spans="1:8">
       <c r="A458" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B458" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C458" s="9">
         <v>112</v>
       </c>
       <c r="D458" s="4">
-        <v>32.626603571428603</v>
+        <v>49.238255357142798</v>
       </c>
       <c r="E458" s="6">
         <v>20</v>
       </c>
       <c r="F458" s="3">
         <f t="shared" si="11"/>
-        <v>26.101282857142884</v>
+        <v>39.39060428571424</v>
       </c>
       <c r="G458" s="1"/>
       <c r="H458" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J458" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="K458" s="19">
-        <v>112</v>
-      </c>
-      <c r="L458" s="20">
-        <v>32.626603571428603</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12">
+    </row>
+    <row r="459" spans="1:8">
       <c r="A459" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B459" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C459" s="9">
         <v>104</v>
       </c>
       <c r="D459" s="4">
-        <v>22.692030510355</v>
+        <v>37.3064931165299</v>
       </c>
       <c r="E459" s="6">
         <v>20</v>
       </c>
       <c r="F459" s="3">
         <f t="shared" si="11"/>
-        <v>18.153624408283999</v>
+        <v>29.845194493223921</v>
       </c>
       <c r="G459" s="1"/>
       <c r="H459" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J459" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="K459" s="19">
-        <v>104</v>
-      </c>
-      <c r="L459" s="20">
-        <v>22.692030510355</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12">
+    </row>
+    <row r="460" spans="1:8">
       <c r="A460" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B460" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C460" s="9">
         <v>96</v>
       </c>
       <c r="D460" s="4">
-        <v>31.437741185897401</v>
+        <v>52.285287259615401</v>
       </c>
       <c r="E460" s="6">
         <v>20</v>
       </c>
       <c r="F460" s="3">
         <f t="shared" si="11"/>
-        <v>25.150192948717923</v>
+        <v>41.828229807692324</v>
       </c>
       <c r="G460" s="1"/>
       <c r="H460" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J460" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="K460" s="19">
-        <v>96</v>
-      </c>
-      <c r="L460" s="20">
-        <v>31.437741185897401</v>
-      </c>
-    </row>
-    <row r="461" spans="1:12">
+    </row>
+    <row r="461" spans="1:8">
       <c r="A461" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B461" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C461" s="9">
         <v>112</v>
       </c>
       <c r="D461" s="4">
-        <v>25.911191964285699</v>
+        <v>38.512924107142901</v>
       </c>
       <c r="E461" s="6">
         <v>20</v>
       </c>
       <c r="F461" s="3">
         <f t="shared" si="11"/>
-        <v>20.728953571428558</v>
+        <v>30.810339285714321</v>
       </c>
       <c r="G461" s="1"/>
       <c r="H461" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="J461" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K461" s="19">
-        <v>112</v>
-      </c>
-      <c r="L461" s="20">
-        <v>25.911191964285699</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12">
+    </row>
+    <row r="462" spans="1:8">
       <c r="A462" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B462" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C462" s="9">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D462" s="4">
-        <v>26.066781735863501</v>
+        <v>29.4018927861344</v>
       </c>
       <c r="E462" s="6">
         <v>20</v>
       </c>
       <c r="F462" s="3">
         <f t="shared" si="11"/>
-        <v>20.853425388690802</v>
+        <v>23.52151422890752</v>
       </c>
       <c r="G462" s="1"/>
       <c r="H462" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J462" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="K462" s="19">
-        <v>136</v>
-      </c>
-      <c r="L462" s="20">
-        <v>26.066781735863501</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12">
+    </row>
+    <row r="463" spans="1:8">
       <c r="A463" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B463" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C463" s="9">
         <v>64</v>
       </c>
       <c r="D463" s="4">
-        <v>31.585208170832502</v>
+        <v>52.498907049813603</v>
       </c>
       <c r="E463" s="6">
         <v>20</v>
       </c>
       <c r="F463" s="3">
         <f t="shared" si="11"/>
-        <v>25.268166536666001</v>
+        <v>41.999125639850881</v>
       </c>
       <c r="G463" s="1"/>
       <c r="H463" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J463" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="K463" s="19">
-        <v>64</v>
-      </c>
-      <c r="L463" s="20">
-        <v>31.585208170832502</v>
-      </c>
-    </row>
-    <row r="464" spans="1:12">
+    </row>
+    <row r="464" spans="1:8">
       <c r="A464" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B464" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C464" s="9">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D464" s="4">
-        <v>33.273441222319398</v>
+        <v>36.976850232618801</v>
       </c>
       <c r="E464" s="6">
         <v>20</v>
       </c>
       <c r="F464" s="3">
         <f t="shared" si="11"/>
-        <v>26.618752977855518</v>
+        <v>29.581480186095042</v>
       </c>
       <c r="G464" s="1"/>
       <c r="H464" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J464" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K464" s="19">
-        <v>120</v>
-      </c>
-      <c r="L464" s="20">
-        <v>33.273441222319398</v>
-      </c>
-    </row>
-    <row r="465" spans="1:12">
+    </row>
+    <row r="465" spans="1:8">
       <c r="A465" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B465" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C465" s="9">
         <v>96</v>
       </c>
       <c r="D465" s="4">
-        <v>28.651272916666699</v>
+        <v>43.054450000000003</v>
       </c>
       <c r="E465" s="6">
         <v>20</v>
       </c>
       <c r="F465" s="3">
         <f t="shared" si="11"/>
-        <v>22.921018333333357</v>
+        <v>34.443560000000005</v>
       </c>
       <c r="G465" s="1"/>
       <c r="H465" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J465" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="K465" s="19">
-        <v>96</v>
-      </c>
-      <c r="L465" s="20">
-        <v>28.651272916666699</v>
-      </c>
-    </row>
-    <row r="466" spans="1:12">
+    </row>
+    <row r="466" spans="1:8">
       <c r="A466" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B466" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C466" s="9">
         <v>80</v>
       </c>
       <c r="D466" s="4">
-        <v>30.175071875</v>
+        <v>50.410741517857197</v>
       </c>
       <c r="E466" s="6">
         <v>20</v>
       </c>
       <c r="F466" s="3">
         <f t="shared" si="11"/>
-        <v>24.140057500000001</v>
+        <v>40.32859321428576</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="J466" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K466" s="19">
-        <v>80</v>
-      </c>
-      <c r="L466" s="20">
-        <v>30.175071875</v>
-      </c>
-    </row>
-    <row r="467" spans="1:12">
+    </row>
+    <row r="467" spans="1:8">
       <c r="A467" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B467" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C467" s="9">
-        <v>71.5</v>
+        <v>111.5</v>
       </c>
       <c r="D467" s="4">
-        <v>35.2410749227233</v>
+        <v>31.561763113777101</v>
       </c>
       <c r="E467" s="6">
         <v>20</v>
       </c>
       <c r="F467" s="3">
         <f t="shared" si="11"/>
-        <v>28.192859938178639</v>
+        <v>25.249410491021681</v>
       </c>
       <c r="G467" s="1"/>
       <c r="H467" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="J467" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K467" s="19">
-        <v>71.5</v>
-      </c>
-      <c r="L467" s="20">
-        <v>35.2410749227233</v>
-      </c>
-    </row>
-    <row r="468" spans="1:12">
+    </row>
+    <row r="468" spans="1:8">
       <c r="A468" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B468" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C468" s="9">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D468" s="4">
-        <v>30.2568398423372</v>
+        <v>28.817259970785202</v>
       </c>
       <c r="E468" s="6">
         <v>20</v>
       </c>
       <c r="F468" s="3">
         <f t="shared" si="11"/>
-        <v>24.205471873869762</v>
+        <v>23.053807976628161</v>
       </c>
       <c r="G468" s="1"/>
       <c r="H468" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J468" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="K468" s="19">
-        <v>80</v>
-      </c>
-      <c r="L468" s="20">
-        <v>30.2568398423372</v>
-      </c>
-    </row>
-    <row r="469" spans="1:12">
+    </row>
+    <row r="469" spans="1:8">
       <c r="A469" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B469" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C469" s="9">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D469" s="4">
-        <v>40.3872897727273</v>
+        <v>43.48629296875</v>
       </c>
       <c r="E469" s="6">
         <v>20</v>
       </c>
       <c r="F469" s="3">
         <f t="shared" si="11"/>
-        <v>32.309831818181841</v>
+        <v>34.789034375</v>
       </c>
       <c r="G469" s="1"/>
       <c r="H469" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="J469" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="K469" s="19">
-        <v>88</v>
-      </c>
-      <c r="L469" s="20">
-        <v>40.3872897727273</v>
-      </c>
-    </row>
-    <row r="470" spans="1:12">
+    </row>
+    <row r="470" spans="1:8">
       <c r="A470" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B470" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C470" s="9">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="D470" s="4">
-        <v>40.3872897727273</v>
+        <v>43.48629296875</v>
       </c>
       <c r="E470" s="6">
         <v>20</v>
       </c>
       <c r="F470" s="3">
         <f t="shared" si="11"/>
-        <v>32.309831818181841</v>
+        <v>34.789034375</v>
       </c>
       <c r="G470" s="1"/>
       <c r="H470" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J470" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="K470" s="19">
-        <v>88</v>
-      </c>
-      <c r="L470" s="20">
-        <v>40.3872897727273</v>
-      </c>
-    </row>
-    <row r="471" spans="1:12">
+    </row>
+    <row r="471" spans="1:8">
       <c r="A471" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B471" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C471" s="9">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D471" s="4">
-        <v>35.015775245097998</v>
+        <v>37.510418065268098</v>
       </c>
       <c r="E471" s="6">
         <v>20</v>
       </c>
       <c r="F471" s="3">
         <f t="shared" si="11"/>
-        <v>28.012620196078398</v>
+        <v>30.008334452214477</v>
       </c>
       <c r="G471" s="1"/>
       <c r="H471" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="J471" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="K471" s="19">
-        <v>136</v>
-      </c>
-      <c r="L471" s="20">
-        <v>35.015775245097998</v>
-      </c>
-    </row>
-    <row r="472" spans="1:12">
+    </row>
+    <row r="472" spans="1:8">
       <c r="A472" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B472" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C472" s="9">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D472" s="4">
-        <v>39.402925284494998</v>
+        <v>43.0140421428571</v>
       </c>
       <c r="E472" s="6">
         <v>20</v>
       </c>
       <c r="F472" s="3">
         <f t="shared" si="11"/>
-        <v>31.522340227595997</v>
+        <v>34.411233714285679</v>
       </c>
       <c r="G472" s="1"/>
       <c r="H472" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="J472" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="K472" s="19">
-        <v>40</v>
-      </c>
-      <c r="L472" s="20">
-        <v>39.402925284494998</v>
-      </c>
-    </row>
-    <row r="473" spans="1:12">
+    </row>
+    <row r="473" spans="1:8">
       <c r="A473" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B473" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C473" s="9">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D473" s="4">
-        <v>58.081810038677901</v>
+        <v>71.981547608372594</v>
       </c>
       <c r="E473" s="6">
         <v>20</v>
       </c>
       <c r="F473" s="3">
-        <f t="shared" ref="F473:F479" si="12">D473-(D473*E473)/100</f>
-        <v>46.465448030942319</v>
+        <f t="shared" ref="F473:F480" si="12">D473-(D473*E473)/100</f>
+        <v>57.585238086698077</v>
       </c>
       <c r="G473" s="1"/>
       <c r="H473" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J473" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="K473" s="19">
-        <v>16</v>
-      </c>
-      <c r="L473" s="20">
-        <v>58.081810038677901</v>
-      </c>
-    </row>
-    <row r="474" spans="1:12">
+    </row>
+    <row r="474" spans="1:8">
       <c r="A474" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B474" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C474" s="9">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D474" s="4">
-        <v>36.896736881684497</v>
+        <v>39.702951679841902</v>
       </c>
       <c r="E474" s="6">
         <v>20</v>
       </c>
       <c r="F474" s="3">
         <f t="shared" si="12"/>
-        <v>29.517389505347598</v>
+        <v>31.762361343873522</v>
       </c>
       <c r="G474" s="1"/>
       <c r="H474" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J474" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K474" s="19">
-        <v>136</v>
-      </c>
-      <c r="L474" s="20">
-        <v>36.896736881684497</v>
-      </c>
-    </row>
-    <row r="475" spans="1:12">
+    </row>
+    <row r="475" spans="1:8">
       <c r="A475" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B475" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C475" s="9">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="D475" s="4">
-        <v>79.134148259850704</v>
+        <v>71.091197088886602</v>
       </c>
       <c r="E475" s="6">
         <v>20</v>
       </c>
       <c r="F475" s="3">
         <f t="shared" si="12"/>
-        <v>63.307318607880561</v>
+        <v>56.872957671109283</v>
       </c>
       <c r="G475" s="1"/>
       <c r="H475" s="8"/>
-      <c r="J475" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="K475" s="19">
-        <v>104</v>
-      </c>
-      <c r="L475" s="20">
-        <v>79.134148259850704</v>
-      </c>
-    </row>
-    <row r="476" spans="1:12">
+    </row>
+    <row r="476" spans="1:8">
       <c r="A476" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B476" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C476" s="9">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D476" s="4">
-        <v>23.231290909090902</v>
+        <v>30.4829166666667</v>
       </c>
       <c r="E476" s="6">
         <v>20</v>
       </c>
       <c r="F476" s="3">
         <f t="shared" si="12"/>
-        <v>18.585032727272722</v>
+        <v>24.386333333333361</v>
       </c>
       <c r="G476" s="1"/>
       <c r="H476" s="8"/>
-      <c r="J476" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="K476" s="19">
-        <v>106</v>
-      </c>
-      <c r="L476" s="20">
-        <v>23.231290909090902</v>
-      </c>
-    </row>
-    <row r="477" spans="1:12">
+    </row>
+    <row r="477" spans="1:8">
       <c r="A477" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B477" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C477" s="9">
         <v>104</v>
       </c>
       <c r="D477" s="4">
-        <v>25.078375000000001</v>
+        <v>34.708821428571397</v>
       </c>
       <c r="E477" s="6">
         <v>20</v>
       </c>
       <c r="F477" s="3">
         <f t="shared" si="12"/>
-        <v>20.0627</v>
+        <v>27.767057142857119</v>
       </c>
       <c r="G477" s="1"/>
       <c r="H477" s="8"/>
-      <c r="J477" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="K477" s="19">
-        <v>104</v>
-      </c>
-      <c r="L477" s="20">
-        <v>25.078375000000001</v>
-      </c>
-    </row>
-    <row r="478" spans="1:12">
+    </row>
+    <row r="478" spans="1:8">
       <c r="A478" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B478" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C478" s="9">
         <v>96</v>
       </c>
       <c r="D478" s="4">
-        <v>29.137684070877</v>
+        <v>44.4461330572394</v>
       </c>
       <c r="E478" s="6">
         <v>20</v>
       </c>
       <c r="F478" s="3">
         <f t="shared" si="12"/>
-        <v>23.310147256701601</v>
+        <v>35.556906445791519</v>
       </c>
       <c r="G478" s="1"/>
       <c r="H478" s="8"/>
-      <c r="J478" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="K478" s="19">
-        <v>96</v>
-      </c>
-      <c r="L478" s="20">
-        <v>29.137684070877</v>
-      </c>
-    </row>
-    <row r="479" spans="1:12">
+    </row>
+    <row r="479" spans="1:8">
       <c r="A479" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B479" s="11">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="C479" s="9">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D479" s="4">
-        <v>58.157057626555698</v>
+        <v>88.495057926829304</v>
       </c>
       <c r="E479" s="6">
         <v>20</v>
       </c>
       <c r="F479" s="3">
-        <f t="shared" si="12"/>
-        <v>46.525646101244561</v>
+        <f t="shared" ref="F479" si="13">D479-(D479*E479)/100</f>
+        <v>70.796046341463438</v>
       </c>
       <c r="G479" s="1"/>
       <c r="H479" s="8"/>
-      <c r="J479" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="K479" s="19">
-        <v>94</v>
-      </c>
-      <c r="L479" s="20">
-        <v>58.157057626555698</v>
-      </c>
+    </row>
+    <row r="480" spans="1:8">
+      <c r="A480" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B480" s="11">
+        <v>46053</v>
+      </c>
+      <c r="C480" s="9">
+        <v>134</v>
+      </c>
+      <c r="D480" s="4">
+        <v>57.045771597709198</v>
+      </c>
+      <c r="E480" s="6">
+        <v>20</v>
+      </c>
+      <c r="F480" s="3">
+        <f t="shared" si="12"/>
+        <v>45.636617278167357</v>
+      </c>
+      <c r="G480" s="1"/>
+      <c r="H480" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G272"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$272</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$480</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -529,7 +529,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,6 +544,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,7 +606,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -614,12 +626,39 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -11272,7 +11311,7 @@
       </c>
     </row>
     <row r="419" spans="1:8">
-      <c r="A419" s="1" t="s">
+      <c r="A419" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B419" s="11">
@@ -11445,7 +11484,7 @@
       <c r="H425" s="8"/>
     </row>
     <row r="426" spans="1:8">
-      <c r="A426" s="1" t="s">
+      <c r="A426" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B426" s="11">
@@ -11470,7 +11509,7 @@
       </c>
     </row>
     <row r="427" spans="1:8">
-      <c r="A427" s="1" t="s">
+      <c r="A427" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B427" s="11">
@@ -11520,7 +11559,7 @@
       </c>
     </row>
     <row r="429" spans="1:8">
-      <c r="A429" s="1" t="s">
+      <c r="A429" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B429" s="11">
@@ -11570,7 +11609,7 @@
       </c>
     </row>
     <row r="431" spans="1:8">
-      <c r="A431" s="1" t="s">
+      <c r="A431" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B431" s="11">
@@ -11720,7 +11759,7 @@
       </c>
     </row>
     <row r="437" spans="1:8">
-      <c r="A437" s="1" t="s">
+      <c r="A437" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B437" s="11">
@@ -11845,7 +11884,7 @@
       </c>
     </row>
     <row r="442" spans="1:8">
-      <c r="A442" s="1" t="s">
+      <c r="A442" s="17" t="s">
         <v>33</v>
       </c>
       <c r="B442" s="11">
@@ -11920,7 +11959,7 @@
       </c>
     </row>
     <row r="445" spans="1:8">
-      <c r="A445" s="1" t="s">
+      <c r="A445" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B445" s="11">
@@ -12070,7 +12109,7 @@
       </c>
     </row>
     <row r="451" spans="1:8">
-      <c r="A451" s="1" t="s">
+      <c r="A451" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B451" s="11">
@@ -12095,7 +12134,7 @@
       </c>
     </row>
     <row r="452" spans="1:8">
-      <c r="A452" s="1" t="s">
+      <c r="A452" s="17" t="s">
         <v>43</v>
       </c>
       <c r="B452" s="11">
@@ -12170,7 +12209,7 @@
       </c>
     </row>
     <row r="455" spans="1:8">
-      <c r="A455" s="1" t="s">
+      <c r="A455" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B455" s="11">
@@ -12245,7 +12284,7 @@
       </c>
     </row>
     <row r="458" spans="1:8">
-      <c r="A458" s="1" t="s">
+      <c r="A458" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B458" s="11">
@@ -12270,7 +12309,7 @@
       </c>
     </row>
     <row r="459" spans="1:8">
-      <c r="A459" s="1" t="s">
+      <c r="A459" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B459" s="11">
@@ -12295,7 +12334,7 @@
       </c>
     </row>
     <row r="460" spans="1:8">
-      <c r="A460" s="1" t="s">
+      <c r="A460" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B460" s="11">
@@ -12320,7 +12359,7 @@
       </c>
     </row>
     <row r="461" spans="1:8">
-      <c r="A461" s="1" t="s">
+      <c r="A461" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B461" s="11">
@@ -12345,7 +12384,7 @@
       </c>
     </row>
     <row r="462" spans="1:8">
-      <c r="A462" s="1" t="s">
+      <c r="A462" s="17" t="s">
         <v>53</v>
       </c>
       <c r="B462" s="11">
@@ -12370,7 +12409,7 @@
       </c>
     </row>
     <row r="463" spans="1:8">
-      <c r="A463" s="1" t="s">
+      <c r="A463" s="18" t="s">
         <v>54</v>
       </c>
       <c r="B463" s="11">
@@ -12395,7 +12434,7 @@
       </c>
     </row>
     <row r="464" spans="1:8">
-      <c r="A464" s="1" t="s">
+      <c r="A464" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B464" s="11">
@@ -12420,7 +12459,7 @@
       </c>
     </row>
     <row r="465" spans="1:8">
-      <c r="A465" s="1" t="s">
+      <c r="A465" s="18" t="s">
         <v>56</v>
       </c>
       <c r="B465" s="11">
@@ -12445,7 +12484,7 @@
       </c>
     </row>
     <row r="466" spans="1:8">
-      <c r="A466" s="1" t="s">
+      <c r="A466" s="18" t="s">
         <v>57</v>
       </c>
       <c r="B466" s="11">
@@ -12570,7 +12609,7 @@
       </c>
     </row>
     <row r="471" spans="1:8">
-      <c r="A471" s="1" t="s">
+      <c r="A471" s="17" t="s">
         <v>62</v>
       </c>
       <c r="B471" s="11">
@@ -12645,7 +12684,7 @@
       </c>
     </row>
     <row r="474" spans="1:8">
-      <c r="A474" s="1" t="s">
+      <c r="A474" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B474" s="11">
@@ -12716,7 +12755,7 @@
       <c r="H476" s="8"/>
     </row>
     <row r="477" spans="1:8">
-      <c r="A477" s="1" t="s">
+      <c r="A477" s="18" t="s">
         <v>135</v>
       </c>
       <c r="B477" s="11">
@@ -12739,7 +12778,7 @@
       <c r="H477" s="8"/>
     </row>
     <row r="478" spans="1:8">
-      <c r="A478" s="1" t="s">
+      <c r="A478" s="18" t="s">
         <v>136</v>
       </c>
       <c r="B478" s="11">
@@ -12808,7 +12847,7 @@
       <c r="H480" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G272"/>
+  <autoFilter ref="A1:G480"/>
   <hyperlinks>
     <hyperlink ref="G74" r:id="rId1"/>
     <hyperlink ref="H74" r:id="rId2"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$551</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="160">
   <si>
     <t>Tecnico</t>
   </si>
@@ -490,6 +490,15 @@
   </si>
   <si>
     <t>IRTE0000116 - GARANTE GIUSEPPE</t>
+  </si>
+  <si>
+    <t>IRTE0000017 - CATANIA GIUSEPPE</t>
+  </si>
+  <si>
+    <t>IRTE0000119 - INGALISO ANTONIO</t>
+  </si>
+  <si>
+    <t>IRTE0000120 - AMORE GIORGIO</t>
   </si>
 </sst>
 </file>
@@ -633,23 +642,7 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -948,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H480"/>
+  <dimension ref="A1:H551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -12675,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="F473" s="3">
-        <f t="shared" ref="F473:F480" si="12">D473-(D473*E473)/100</f>
+        <f t="shared" ref="F473:F536" si="12">D473-(D473*E473)/100</f>
         <v>57.585238086698077</v>
       </c>
       <c r="G473" s="1"/>
@@ -12846,8 +12839,1765 @@
       <c r="G480" s="1"/>
       <c r="H480" s="8"/>
     </row>
+    <row r="481" spans="1:8">
+      <c r="A481" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B481" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C481" s="9">
+        <v>159</v>
+      </c>
+      <c r="D481" s="12">
+        <v>31.369738297872299</v>
+      </c>
+      <c r="E481" s="13">
+        <v>20</v>
+      </c>
+      <c r="F481" s="14">
+        <f t="shared" si="12"/>
+        <v>25.095790638297839</v>
+      </c>
+      <c r="G481" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H481" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B482" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C482" s="9">
+        <v>112</v>
+      </c>
+      <c r="D482" s="4">
+        <v>68.427141715896894</v>
+      </c>
+      <c r="E482" s="6">
+        <v>20</v>
+      </c>
+      <c r="F482" s="3">
+        <f t="shared" si="12"/>
+        <v>54.741713372717513</v>
+      </c>
+      <c r="G482" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H482" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B483" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C483" s="9">
+        <v>48</v>
+      </c>
+      <c r="D483" s="4">
+        <v>62.524824470029202</v>
+      </c>
+      <c r="E483" s="6">
+        <v>20</v>
+      </c>
+      <c r="F483" s="3">
+        <f t="shared" si="12"/>
+        <v>50.019859576023364</v>
+      </c>
+      <c r="G483" s="1"/>
+      <c r="H483" s="8"/>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B484" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C484" s="9">
+        <v>144</v>
+      </c>
+      <c r="D484" s="4">
+        <v>27.291165827366999</v>
+      </c>
+      <c r="E484" s="6">
+        <v>20</v>
+      </c>
+      <c r="F484" s="3">
+        <f t="shared" si="12"/>
+        <v>21.832932661893601</v>
+      </c>
+      <c r="G484" s="1"/>
+      <c r="H484" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B485" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C485" s="9">
+        <v>128</v>
+      </c>
+      <c r="D485" s="4">
+        <v>55.180107829944198</v>
+      </c>
+      <c r="E485" s="6">
+        <v>20</v>
+      </c>
+      <c r="F485" s="3">
+        <f t="shared" si="12"/>
+        <v>44.144086263955359</v>
+      </c>
+      <c r="G485" s="1"/>
+      <c r="H485" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B486" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C486" s="9">
+        <v>144</v>
+      </c>
+      <c r="D486" s="4">
+        <v>27.698004984567898</v>
+      </c>
+      <c r="E486" s="6">
+        <v>20</v>
+      </c>
+      <c r="F486" s="3">
+        <f t="shared" si="12"/>
+        <v>22.158403987654317</v>
+      </c>
+      <c r="G486" s="1"/>
+      <c r="H486" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B487" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C487" s="9">
+        <v>120</v>
+      </c>
+      <c r="D487" s="4">
+        <v>37.553407178451202</v>
+      </c>
+      <c r="E487" s="6">
+        <v>20</v>
+      </c>
+      <c r="F487" s="3">
+        <f t="shared" si="12"/>
+        <v>30.042725742760961</v>
+      </c>
+      <c r="G487" s="1"/>
+      <c r="H487" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
+      <c r="A488" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B488" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C488" s="9">
+        <v>144</v>
+      </c>
+      <c r="D488" s="4">
+        <v>32.971718333333399</v>
+      </c>
+      <c r="E488" s="6">
+        <v>20</v>
+      </c>
+      <c r="F488" s="3">
+        <f t="shared" si="12"/>
+        <v>26.377374666666718</v>
+      </c>
+      <c r="G488" s="1"/>
+      <c r="H488" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B489" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C489" s="9">
+        <v>160</v>
+      </c>
+      <c r="D489" s="4">
+        <v>27.7307202238174</v>
+      </c>
+      <c r="E489" s="6">
+        <v>20</v>
+      </c>
+      <c r="F489" s="3">
+        <f t="shared" si="12"/>
+        <v>22.18457617905392</v>
+      </c>
+      <c r="G489" s="1"/>
+      <c r="H489" s="8"/>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="A490" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B490" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C490" s="9">
+        <v>128</v>
+      </c>
+      <c r="D490" s="4">
+        <v>36.1157055555556</v>
+      </c>
+      <c r="E490" s="6">
+        <v>20</v>
+      </c>
+      <c r="F490" s="3">
+        <f t="shared" si="12"/>
+        <v>28.892564444444481</v>
+      </c>
+      <c r="G490" s="1"/>
+      <c r="H490" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B491" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C491" s="9">
+        <v>112</v>
+      </c>
+      <c r="D491" s="4">
+        <v>90.0277420183983</v>
+      </c>
+      <c r="E491" s="6">
+        <v>20</v>
+      </c>
+      <c r="F491" s="3">
+        <f t="shared" si="12"/>
+        <v>72.022193614718645</v>
+      </c>
+      <c r="G491" s="1"/>
+      <c r="H491" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B492" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C492" s="9">
+        <v>132</v>
+      </c>
+      <c r="D492" s="4">
+        <v>85.482263166956599</v>
+      </c>
+      <c r="E492" s="6">
+        <v>20</v>
+      </c>
+      <c r="F492" s="3">
+        <f t="shared" si="12"/>
+        <v>68.385810533565277</v>
+      </c>
+      <c r="G492" s="1"/>
+      <c r="H492" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B493" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C493" s="9">
+        <v>109</v>
+      </c>
+      <c r="D493" s="4">
+        <v>41.0361639829488</v>
+      </c>
+      <c r="E493" s="6">
+        <v>20</v>
+      </c>
+      <c r="F493" s="3">
+        <f t="shared" si="12"/>
+        <v>32.828931186359043</v>
+      </c>
+      <c r="G493" s="1"/>
+      <c r="H493" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B494" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C494" s="9">
+        <v>140</v>
+      </c>
+      <c r="D494" s="4">
+        <v>27.8431319126984</v>
+      </c>
+      <c r="E494" s="6">
+        <v>20</v>
+      </c>
+      <c r="F494" s="3">
+        <f t="shared" si="12"/>
+        <v>22.27450553015872</v>
+      </c>
+      <c r="G494" s="1"/>
+      <c r="H494" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B495" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C495" s="9">
+        <v>144</v>
+      </c>
+      <c r="D495" s="4">
+        <v>54.1322669989367</v>
+      </c>
+      <c r="E495" s="6">
+        <v>20</v>
+      </c>
+      <c r="F495" s="3">
+        <f t="shared" si="12"/>
+        <v>43.30581359914936</v>
+      </c>
+      <c r="G495" s="1"/>
+      <c r="H495" s="8"/>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B496" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C496" s="9">
+        <v>152</v>
+      </c>
+      <c r="D496" s="4">
+        <v>36.1098</v>
+      </c>
+      <c r="E496" s="6">
+        <v>20</v>
+      </c>
+      <c r="F496" s="3">
+        <f t="shared" si="12"/>
+        <v>28.887840000000001</v>
+      </c>
+      <c r="G496" s="1"/>
+      <c r="H496" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B497" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C497" s="9">
+        <v>176</v>
+      </c>
+      <c r="D497" s="4">
+        <v>31.924892655502401</v>
+      </c>
+      <c r="E497" s="6">
+        <v>20</v>
+      </c>
+      <c r="F497" s="3">
+        <f t="shared" si="12"/>
+        <v>25.539914124401921</v>
+      </c>
+      <c r="G497" s="1"/>
+      <c r="H497" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B498" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C498" s="9">
+        <v>159</v>
+      </c>
+      <c r="D498" s="4">
+        <v>31.369738297872299</v>
+      </c>
+      <c r="E498" s="6">
+        <v>20</v>
+      </c>
+      <c r="F498" s="3">
+        <f t="shared" si="12"/>
+        <v>25.095790638297839</v>
+      </c>
+      <c r="G498" s="1"/>
+      <c r="H498" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B499" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C499" s="9">
+        <v>168</v>
+      </c>
+      <c r="D499" s="4">
+        <v>34.4356642342984</v>
+      </c>
+      <c r="E499" s="6">
+        <v>20</v>
+      </c>
+      <c r="F499" s="3">
+        <f t="shared" si="12"/>
+        <v>27.548531387438722</v>
+      </c>
+      <c r="G499" s="1"/>
+      <c r="H499" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B500" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C500" s="9">
+        <v>158</v>
+      </c>
+      <c r="D500" s="4">
+        <v>58.702747191011198</v>
+      </c>
+      <c r="E500" s="6">
+        <v>20</v>
+      </c>
+      <c r="F500" s="3">
+        <f t="shared" si="12"/>
+        <v>46.962197752808962</v>
+      </c>
+      <c r="G500" s="1"/>
+      <c r="H500" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B501" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C501" s="9">
+        <v>160</v>
+      </c>
+      <c r="D501" s="4">
+        <v>40.473494282834103</v>
+      </c>
+      <c r="E501" s="6">
+        <v>20</v>
+      </c>
+      <c r="F501" s="3">
+        <f t="shared" si="12"/>
+        <v>32.378795426267281</v>
+      </c>
+      <c r="G501" s="1"/>
+      <c r="H501" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B502" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C502" s="9">
+        <v>136</v>
+      </c>
+      <c r="D502" s="4">
+        <v>33.5808769455844</v>
+      </c>
+      <c r="E502" s="6">
+        <v>20</v>
+      </c>
+      <c r="F502" s="3">
+        <f t="shared" si="12"/>
+        <v>26.864701556467519</v>
+      </c>
+      <c r="G502" s="1"/>
+      <c r="H502" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B503" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C503" s="9">
+        <v>160</v>
+      </c>
+      <c r="D503" s="4">
+        <v>33.605256443048901</v>
+      </c>
+      <c r="E503" s="6">
+        <v>20</v>
+      </c>
+      <c r="F503" s="3">
+        <f t="shared" si="12"/>
+        <v>26.884205154439123</v>
+      </c>
+      <c r="G503" s="1"/>
+      <c r="H503" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8">
+      <c r="A504" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B504" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C504" s="9">
+        <v>133</v>
+      </c>
+      <c r="D504" s="4">
+        <v>44.996793451486703</v>
+      </c>
+      <c r="E504" s="6">
+        <v>20</v>
+      </c>
+      <c r="F504" s="3">
+        <f t="shared" si="12"/>
+        <v>35.997434761189361</v>
+      </c>
+      <c r="G504" s="1"/>
+      <c r="H504" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B505" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C505" s="9">
+        <v>128</v>
+      </c>
+      <c r="D505" s="4">
+        <v>93.406500236742403</v>
+      </c>
+      <c r="E505" s="6">
+        <v>20</v>
+      </c>
+      <c r="F505" s="3">
+        <f t="shared" si="12"/>
+        <v>74.725200189393917</v>
+      </c>
+      <c r="G505" s="1"/>
+      <c r="H505" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="A506" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B506" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C506" s="9">
+        <v>88</v>
+      </c>
+      <c r="D506" s="4">
+        <v>35.171477272727302</v>
+      </c>
+      <c r="E506" s="6">
+        <v>20</v>
+      </c>
+      <c r="F506" s="3">
+        <f t="shared" si="12"/>
+        <v>28.13718181818184</v>
+      </c>
+      <c r="G506" s="1"/>
+      <c r="H506" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B507" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C507" s="9">
+        <v>103</v>
+      </c>
+      <c r="D507" s="4">
+        <v>25.610488888888899</v>
+      </c>
+      <c r="E507" s="6">
+        <v>20</v>
+      </c>
+      <c r="F507" s="3">
+        <f t="shared" si="12"/>
+        <v>20.48839111111112</v>
+      </c>
+      <c r="G507" s="1"/>
+      <c r="H507" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8">
+      <c r="A508" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B508" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C508" s="9">
+        <v>68</v>
+      </c>
+      <c r="D508" s="4">
+        <v>31.418000797993599</v>
+      </c>
+      <c r="E508" s="6">
+        <v>20</v>
+      </c>
+      <c r="F508" s="3">
+        <f t="shared" si="12"/>
+        <v>25.134400638394879</v>
+      </c>
+      <c r="G508" s="1"/>
+      <c r="H508" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8">
+      <c r="A509" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B509" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C509" s="9">
+        <v>127</v>
+      </c>
+      <c r="D509" s="4">
+        <v>40.823227272727301</v>
+      </c>
+      <c r="E509" s="6">
+        <v>20</v>
+      </c>
+      <c r="F509" s="3">
+        <f t="shared" si="12"/>
+        <v>32.658581818181844</v>
+      </c>
+      <c r="G509" s="1"/>
+      <c r="H509" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8">
+      <c r="A510" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B510" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C510" s="9">
+        <v>112</v>
+      </c>
+      <c r="D510" s="4">
+        <v>45.039889158163298</v>
+      </c>
+      <c r="E510" s="6">
+        <v>20</v>
+      </c>
+      <c r="F510" s="3">
+        <f t="shared" si="12"/>
+        <v>36.03191132653064</v>
+      </c>
+      <c r="G510" s="1"/>
+      <c r="H510" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8">
+      <c r="A511" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B511" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C511" s="9">
+        <v>160</v>
+      </c>
+      <c r="D511" s="4">
+        <v>37.453238338870399</v>
+      </c>
+      <c r="E511" s="6">
+        <v>20</v>
+      </c>
+      <c r="F511" s="3">
+        <f t="shared" si="12"/>
+        <v>29.962590671096319</v>
+      </c>
+      <c r="G511" s="1"/>
+      <c r="H511" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8">
+      <c r="A512" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B512" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C512" s="9">
+        <v>160</v>
+      </c>
+      <c r="D512" s="4">
+        <v>34.756645348837203</v>
+      </c>
+      <c r="E512" s="6">
+        <v>20</v>
+      </c>
+      <c r="F512" s="3">
+        <f t="shared" si="12"/>
+        <v>27.805316279069764</v>
+      </c>
+      <c r="G512" s="1"/>
+      <c r="H512" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8">
+      <c r="A513" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B513" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C513" s="9">
+        <v>136</v>
+      </c>
+      <c r="D513" s="4">
+        <v>56.388075359016803</v>
+      </c>
+      <c r="E513" s="6">
+        <v>20</v>
+      </c>
+      <c r="F513" s="3">
+        <f t="shared" si="12"/>
+        <v>45.110460287213442</v>
+      </c>
+      <c r="G513" s="1"/>
+      <c r="H513" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8">
+      <c r="A514" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B514" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C514" s="9">
+        <v>168</v>
+      </c>
+      <c r="D514" s="4">
+        <v>25.395943537415</v>
+      </c>
+      <c r="E514" s="6">
+        <v>20</v>
+      </c>
+      <c r="F514" s="3">
+        <f t="shared" si="12"/>
+        <v>20.316754829932002</v>
+      </c>
+      <c r="G514" s="1"/>
+      <c r="H514" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8">
+      <c r="A515" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B515" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C515" s="9">
+        <v>144</v>
+      </c>
+      <c r="D515" s="4">
+        <v>45.133217675061402</v>
+      </c>
+      <c r="E515" s="6">
+        <v>20</v>
+      </c>
+      <c r="F515" s="3">
+        <f t="shared" si="12"/>
+        <v>36.106574140049119</v>
+      </c>
+      <c r="G515" s="1"/>
+      <c r="H515" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8">
+      <c r="A516" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B516" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C516" s="9">
+        <v>152</v>
+      </c>
+      <c r="D516" s="4">
+        <v>43.885611309523803</v>
+      </c>
+      <c r="E516" s="6">
+        <v>20</v>
+      </c>
+      <c r="F516" s="3">
+        <f t="shared" si="12"/>
+        <v>35.108489047619045</v>
+      </c>
+      <c r="G516" s="1"/>
+      <c r="H516" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8">
+      <c r="A517" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B517" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C517" s="9">
+        <v>120</v>
+      </c>
+      <c r="D517" s="4">
+        <v>93.932084848484905</v>
+      </c>
+      <c r="E517" s="6">
+        <v>20</v>
+      </c>
+      <c r="F517" s="3">
+        <f t="shared" si="12"/>
+        <v>75.145667878787918</v>
+      </c>
+      <c r="G517" s="1"/>
+      <c r="H517" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8">
+      <c r="A518" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B518" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C518" s="9">
+        <v>136</v>
+      </c>
+      <c r="D518" s="4">
+        <v>26.5068125816993</v>
+      </c>
+      <c r="E518" s="6">
+        <v>20</v>
+      </c>
+      <c r="F518" s="3">
+        <f t="shared" si="12"/>
+        <v>21.20545006535944</v>
+      </c>
+      <c r="G518" s="1"/>
+      <c r="H518" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8">
+      <c r="A519" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B519" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C519" s="9">
+        <v>138</v>
+      </c>
+      <c r="D519" s="4">
+        <v>40.364205663083901</v>
+      </c>
+      <c r="E519" s="6">
+        <v>20</v>
+      </c>
+      <c r="F519" s="3">
+        <f t="shared" si="12"/>
+        <v>32.291364530467121</v>
+      </c>
+      <c r="G519" s="1"/>
+      <c r="H519" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8">
+      <c r="A520" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B520" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C520" s="9">
+        <v>160</v>
+      </c>
+      <c r="D520" s="4">
+        <v>36.1998541424419</v>
+      </c>
+      <c r="E520" s="6">
+        <v>20</v>
+      </c>
+      <c r="F520" s="3">
+        <f t="shared" si="12"/>
+        <v>28.959883313953519</v>
+      </c>
+      <c r="G520" s="1"/>
+      <c r="H520" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8">
+      <c r="A521" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B521" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C521" s="9">
+        <v>144</v>
+      </c>
+      <c r="D521" s="4">
+        <v>40.717765624999998</v>
+      </c>
+      <c r="E521" s="6">
+        <v>20</v>
+      </c>
+      <c r="F521" s="3">
+        <f t="shared" si="12"/>
+        <v>32.574212500000002</v>
+      </c>
+      <c r="G521" s="1"/>
+      <c r="H521" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8">
+      <c r="A522" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B522" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C522" s="9">
+        <v>40</v>
+      </c>
+      <c r="D522" s="4">
+        <v>73.754156030701793</v>
+      </c>
+      <c r="E522" s="6">
+        <v>20</v>
+      </c>
+      <c r="F522" s="3">
+        <f t="shared" si="12"/>
+        <v>59.003324824561432</v>
+      </c>
+      <c r="G522" s="1"/>
+      <c r="H522" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8">
+      <c r="A523" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B523" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C523" s="9">
+        <v>152</v>
+      </c>
+      <c r="D523" s="4">
+        <v>31.569829822864701</v>
+      </c>
+      <c r="E523" s="6">
+        <v>20</v>
+      </c>
+      <c r="F523" s="3">
+        <f t="shared" si="12"/>
+        <v>25.255863858291761</v>
+      </c>
+      <c r="G523" s="1"/>
+      <c r="H523" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8">
+      <c r="A524" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B524" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C524" s="9">
+        <v>120</v>
+      </c>
+      <c r="D524" s="4">
+        <v>65.886603448275807</v>
+      </c>
+      <c r="E524" s="6">
+        <v>20</v>
+      </c>
+      <c r="F524" s="3">
+        <f t="shared" si="12"/>
+        <v>52.709282758620645</v>
+      </c>
+      <c r="G524" s="1"/>
+      <c r="H524" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8">
+      <c r="A525" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B525" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C525" s="9">
+        <v>88</v>
+      </c>
+      <c r="D525" s="4">
+        <v>57.412687526675199</v>
+      </c>
+      <c r="E525" s="6">
+        <v>20</v>
+      </c>
+      <c r="F525" s="3">
+        <f t="shared" si="12"/>
+        <v>45.930150021340161</v>
+      </c>
+      <c r="G525" s="1"/>
+      <c r="H525" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8">
+      <c r="A526" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B526" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C526" s="9">
+        <v>128</v>
+      </c>
+      <c r="D526" s="4">
+        <v>56.505478836560997</v>
+      </c>
+      <c r="E526" s="6">
+        <v>20</v>
+      </c>
+      <c r="F526" s="3">
+        <f t="shared" si="12"/>
+        <v>45.204383069248799</v>
+      </c>
+      <c r="G526" s="1"/>
+      <c r="H526" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8">
+      <c r="A527" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B527" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C527" s="9">
+        <v>144</v>
+      </c>
+      <c r="D527" s="4">
+        <v>39.297410062406101</v>
+      </c>
+      <c r="E527" s="6">
+        <v>20</v>
+      </c>
+      <c r="F527" s="3">
+        <f t="shared" si="12"/>
+        <v>31.437928049924881</v>
+      </c>
+      <c r="G527" s="1"/>
+      <c r="H527" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8">
+      <c r="A528" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B528" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C528" s="9">
+        <v>152</v>
+      </c>
+      <c r="D528" s="4">
+        <v>27.168310810810802</v>
+      </c>
+      <c r="E528" s="6">
+        <v>20</v>
+      </c>
+      <c r="F528" s="3">
+        <f t="shared" si="12"/>
+        <v>21.734648648648641</v>
+      </c>
+      <c r="G528" s="1"/>
+      <c r="H528" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8">
+      <c r="A529" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B529" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C529" s="9">
+        <v>160</v>
+      </c>
+      <c r="D529" s="4">
+        <v>38.808745310991803</v>
+      </c>
+      <c r="E529" s="6">
+        <v>20</v>
+      </c>
+      <c r="F529" s="3">
+        <f t="shared" si="12"/>
+        <v>31.046996248793441</v>
+      </c>
+      <c r="G529" s="1"/>
+      <c r="H529" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="A530" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B530" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C530" s="9">
+        <v>152</v>
+      </c>
+      <c r="D530" s="4">
+        <v>32.504854196301601</v>
+      </c>
+      <c r="E530" s="6">
+        <v>20</v>
+      </c>
+      <c r="F530" s="3">
+        <f t="shared" si="12"/>
+        <v>26.003883357041282</v>
+      </c>
+      <c r="G530" s="1"/>
+      <c r="H530" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B531" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C531" s="9">
+        <v>160</v>
+      </c>
+      <c r="D531" s="4">
+        <v>33.8817909610705</v>
+      </c>
+      <c r="E531" s="6">
+        <v>20</v>
+      </c>
+      <c r="F531" s="3">
+        <f t="shared" si="12"/>
+        <v>27.105432768856399</v>
+      </c>
+      <c r="G531" s="1"/>
+      <c r="H531" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B532" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C532" s="9">
+        <v>120</v>
+      </c>
+      <c r="D532" s="4">
+        <v>36.205773563218401</v>
+      </c>
+      <c r="E532" s="6">
+        <v>20</v>
+      </c>
+      <c r="F532" s="3">
+        <f t="shared" si="12"/>
+        <v>28.96461885057472</v>
+      </c>
+      <c r="G532" s="1"/>
+      <c r="H532" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B533" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C533" s="9">
+        <v>160</v>
+      </c>
+      <c r="D533" s="4">
+        <v>35.133196965479499</v>
+      </c>
+      <c r="E533" s="6">
+        <v>20</v>
+      </c>
+      <c r="F533" s="3">
+        <f t="shared" si="12"/>
+        <v>28.106557572383601</v>
+      </c>
+      <c r="G533" s="1"/>
+      <c r="H533" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8">
+      <c r="A534" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B534" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C534" s="9">
+        <v>112</v>
+      </c>
+      <c r="D534" s="4">
+        <v>34.085714285714303</v>
+      </c>
+      <c r="E534" s="6">
+        <v>20</v>
+      </c>
+      <c r="F534" s="3">
+        <f t="shared" si="12"/>
+        <v>27.268571428571441</v>
+      </c>
+      <c r="G534" s="1"/>
+      <c r="H534" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8">
+      <c r="A535" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B535" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C535" s="9">
+        <v>136</v>
+      </c>
+      <c r="D535" s="4">
+        <v>34.841180916969101</v>
+      </c>
+      <c r="E535" s="6">
+        <v>20</v>
+      </c>
+      <c r="F535" s="3">
+        <f t="shared" si="12"/>
+        <v>27.872944733575281</v>
+      </c>
+      <c r="G535" s="1"/>
+      <c r="H535" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8">
+      <c r="A536" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B536" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C536" s="9">
+        <v>80</v>
+      </c>
+      <c r="D536" s="4">
+        <v>461.84753124999997</v>
+      </c>
+      <c r="E536" s="6">
+        <v>20</v>
+      </c>
+      <c r="F536" s="3">
+        <f t="shared" si="12"/>
+        <v>369.478025</v>
+      </c>
+      <c r="G536" s="1"/>
+      <c r="H536" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8">
+      <c r="A537" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B537" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C537" s="9">
+        <v>111</v>
+      </c>
+      <c r="D537" s="4">
+        <v>40.961701388661403</v>
+      </c>
+      <c r="E537" s="6">
+        <v>20</v>
+      </c>
+      <c r="F537" s="3">
+        <f t="shared" ref="F537:F549" si="14">D537-(D537*E537)/100</f>
+        <v>32.769361110929125</v>
+      </c>
+      <c r="G537" s="1"/>
+      <c r="H537" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8">
+      <c r="A538" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B538" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C538" s="9">
+        <v>118</v>
+      </c>
+      <c r="D538" s="4">
+        <v>61.584973333333302</v>
+      </c>
+      <c r="E538" s="6">
+        <v>20</v>
+      </c>
+      <c r="F538" s="3">
+        <f t="shared" si="14"/>
+        <v>49.267978666666643</v>
+      </c>
+      <c r="G538" s="1"/>
+      <c r="H538" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8">
+      <c r="A539" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B539" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C539" s="9">
+        <v>142</v>
+      </c>
+      <c r="D539" s="4">
+        <v>61.584973333333302</v>
+      </c>
+      <c r="E539" s="6">
+        <v>20</v>
+      </c>
+      <c r="F539" s="3">
+        <f t="shared" si="14"/>
+        <v>49.267978666666643</v>
+      </c>
+      <c r="G539" s="1"/>
+      <c r="H539" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8">
+      <c r="A540" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B540" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C540" s="9">
+        <v>168</v>
+      </c>
+      <c r="D540" s="4">
+        <v>36.438440426168903</v>
+      </c>
+      <c r="E540" s="6">
+        <v>20</v>
+      </c>
+      <c r="F540" s="3">
+        <f t="shared" si="14"/>
+        <v>29.150752340935121</v>
+      </c>
+      <c r="G540" s="1"/>
+      <c r="H540" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8">
+      <c r="A541" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B541" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C541" s="9">
+        <v>36</v>
+      </c>
+      <c r="D541" s="4">
+        <v>67.290670911775607</v>
+      </c>
+      <c r="E541" s="6">
+        <v>20</v>
+      </c>
+      <c r="F541" s="3">
+        <f t="shared" si="14"/>
+        <v>53.832536729420482</v>
+      </c>
+      <c r="G541" s="1"/>
+      <c r="H541" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8">
+      <c r="A542" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B542" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C542" s="9">
+        <v>8</v>
+      </c>
+      <c r="D542" s="4">
+        <v>96.034423295454602</v>
+      </c>
+      <c r="E542" s="6">
+        <v>20</v>
+      </c>
+      <c r="F542" s="3">
+        <f t="shared" si="14"/>
+        <v>76.827538636363684</v>
+      </c>
+      <c r="G542" s="1"/>
+      <c r="H542" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8">
+      <c r="A543" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B543" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C543" s="9">
+        <v>160</v>
+      </c>
+      <c r="D543" s="4">
+        <v>38.779223021596501</v>
+      </c>
+      <c r="E543" s="6">
+        <v>20</v>
+      </c>
+      <c r="F543" s="3">
+        <f t="shared" si="14"/>
+        <v>31.0233784172772</v>
+      </c>
+      <c r="G543" s="1"/>
+      <c r="H543" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8">
+      <c r="A544" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B544" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C544" s="9">
+        <v>134</v>
+      </c>
+      <c r="D544" s="4">
+        <v>84.694827430344404</v>
+      </c>
+      <c r="E544" s="6">
+        <v>20</v>
+      </c>
+      <c r="F544" s="3">
+        <f t="shared" si="14"/>
+        <v>67.755861944275523</v>
+      </c>
+      <c r="G544" s="1"/>
+      <c r="H544" s="8"/>
+    </row>
+    <row r="545" spans="1:8">
+      <c r="A545" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B545" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C545" s="9">
+        <v>135</v>
+      </c>
+      <c r="D545" s="4">
+        <v>40.363893521960598</v>
+      </c>
+      <c r="E545" s="6">
+        <v>20</v>
+      </c>
+      <c r="F545" s="3">
+        <f t="shared" si="14"/>
+        <v>32.291114817568477</v>
+      </c>
+      <c r="G545" s="1"/>
+      <c r="H545" s="8"/>
+    </row>
+    <row r="546" spans="1:8">
+      <c r="A546" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B546" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C546" s="9">
+        <v>136</v>
+      </c>
+      <c r="D546" s="4">
+        <v>56.487683815992497</v>
+      </c>
+      <c r="E546" s="6">
+        <v>20</v>
+      </c>
+      <c r="F546" s="3">
+        <f t="shared" si="14"/>
+        <v>45.190147052793996</v>
+      </c>
+      <c r="G546" s="1"/>
+      <c r="H546" s="8"/>
+    </row>
+    <row r="547" spans="1:8">
+      <c r="A547" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B547" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C547" s="9">
+        <v>136</v>
+      </c>
+      <c r="D547" s="4">
+        <v>36.173856615965498</v>
+      </c>
+      <c r="E547" s="6">
+        <v>20</v>
+      </c>
+      <c r="F547" s="3">
+        <f t="shared" si="14"/>
+        <v>28.939085292772397</v>
+      </c>
+      <c r="G547" s="1"/>
+      <c r="H547" s="8"/>
+    </row>
+    <row r="548" spans="1:8">
+      <c r="A548" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B548" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C548" s="9">
+        <v>104</v>
+      </c>
+      <c r="D548" s="4">
+        <v>67.305037539466895</v>
+      </c>
+      <c r="E548" s="6">
+        <v>20</v>
+      </c>
+      <c r="F548" s="3">
+        <f t="shared" si="14"/>
+        <v>53.844030031573517</v>
+      </c>
+      <c r="G548" s="1"/>
+      <c r="H548" s="8"/>
+    </row>
+    <row r="549" spans="1:8">
+      <c r="A549" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B549" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C549" s="9">
+        <v>136</v>
+      </c>
+      <c r="D549" s="4">
+        <v>45.386746522257503</v>
+      </c>
+      <c r="E549" s="6">
+        <v>20</v>
+      </c>
+      <c r="F549" s="3">
+        <f t="shared" si="14"/>
+        <v>36.309397217806001</v>
+      </c>
+      <c r="G549" s="1"/>
+      <c r="H549" s="8"/>
+    </row>
+    <row r="550" spans="1:8">
+      <c r="A550" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B550" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C550" s="9">
+        <v>166</v>
+      </c>
+      <c r="D550" s="4">
+        <v>58.702747191011198</v>
+      </c>
+      <c r="E550" s="6">
+        <v>20</v>
+      </c>
+      <c r="F550" s="3">
+        <f t="shared" ref="F550:F551" si="15">D550-(D550*E550)/100</f>
+        <v>46.962197752808962</v>
+      </c>
+      <c r="G550" s="1"/>
+      <c r="H550" s="8"/>
+    </row>
+    <row r="551" spans="1:8">
+      <c r="A551" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B551" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C551" s="9">
+        <v>16</v>
+      </c>
+      <c r="D551" s="4">
+        <v>96.034423295454602</v>
+      </c>
+      <c r="E551" s="6">
+        <v>20</v>
+      </c>
+      <c r="F551" s="3">
+        <f t="shared" si="15"/>
+        <v>76.827538636363684</v>
+      </c>
+      <c r="G551" s="1"/>
+      <c r="H551" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G480"/>
+  <autoFilter ref="A1:G551"/>
   <hyperlinks>
     <hyperlink ref="G74" r:id="rId1"/>
     <hyperlink ref="H74" r:id="rId2"/>
@@ -13289,6 +15039,67 @@
     <hyperlink ref="H473" r:id="rId438"/>
     <hyperlink ref="H474" r:id="rId439"/>
     <hyperlink ref="H439" r:id="rId440" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="G481" r:id="rId441"/>
+    <hyperlink ref="H481" r:id="rId442"/>
+    <hyperlink ref="H482" r:id="rId443"/>
+    <hyperlink ref="H484" r:id="rId444"/>
+    <hyperlink ref="H485" r:id="rId445"/>
+    <hyperlink ref="H486" r:id="rId446"/>
+    <hyperlink ref="H487" r:id="rId447"/>
+    <hyperlink ref="H488" r:id="rId448"/>
+    <hyperlink ref="H490" r:id="rId449"/>
+    <hyperlink ref="H491" r:id="rId450"/>
+    <hyperlink ref="H492" r:id="rId451"/>
+    <hyperlink ref="H493" r:id="rId452"/>
+    <hyperlink ref="H494" r:id="rId453"/>
+    <hyperlink ref="H496" r:id="rId454"/>
+    <hyperlink ref="H497" r:id="rId455"/>
+    <hyperlink ref="H498" r:id="rId456"/>
+    <hyperlink ref="H499" r:id="rId457"/>
+    <hyperlink ref="H500" r:id="rId458"/>
+    <hyperlink ref="H501" r:id="rId459"/>
+    <hyperlink ref="H502" r:id="rId460"/>
+    <hyperlink ref="H503" r:id="rId461"/>
+    <hyperlink ref="H504" r:id="rId462"/>
+    <hyperlink ref="H505" r:id="rId463"/>
+    <hyperlink ref="H506" r:id="rId464"/>
+    <hyperlink ref="H507" r:id="rId465"/>
+    <hyperlink ref="H509" r:id="rId466"/>
+    <hyperlink ref="H510" r:id="rId467"/>
+    <hyperlink ref="H511" r:id="rId468"/>
+    <hyperlink ref="H512" r:id="rId469"/>
+    <hyperlink ref="H513" r:id="rId470"/>
+    <hyperlink ref="H514" r:id="rId471"/>
+    <hyperlink ref="H515" r:id="rId472"/>
+    <hyperlink ref="H516" r:id="rId473"/>
+    <hyperlink ref="H517" r:id="rId474"/>
+    <hyperlink ref="H518" r:id="rId475"/>
+    <hyperlink ref="H519" r:id="rId476"/>
+    <hyperlink ref="H520" r:id="rId477"/>
+    <hyperlink ref="H521" r:id="rId478"/>
+    <hyperlink ref="H522" r:id="rId479"/>
+    <hyperlink ref="H523" r:id="rId480"/>
+    <hyperlink ref="H524" r:id="rId481"/>
+    <hyperlink ref="H525" r:id="rId482"/>
+    <hyperlink ref="H526" r:id="rId483"/>
+    <hyperlink ref="H527" r:id="rId484"/>
+    <hyperlink ref="H528" r:id="rId485"/>
+    <hyperlink ref="H529" r:id="rId486"/>
+    <hyperlink ref="H530" r:id="rId487"/>
+    <hyperlink ref="H531" r:id="rId488"/>
+    <hyperlink ref="H532" r:id="rId489"/>
+    <hyperlink ref="H533" r:id="rId490"/>
+    <hyperlink ref="H534" r:id="rId491"/>
+    <hyperlink ref="H535" r:id="rId492"/>
+    <hyperlink ref="H536" r:id="rId493"/>
+    <hyperlink ref="H537" r:id="rId494"/>
+    <hyperlink ref="H538" r:id="rId495"/>
+    <hyperlink ref="H539" r:id="rId496"/>
+    <hyperlink ref="H540" r:id="rId497"/>
+    <hyperlink ref="H541" r:id="rId498"/>
+    <hyperlink ref="H542" r:id="rId499"/>
+    <hyperlink ref="H543" r:id="rId500"/>
+    <hyperlink ref="H508" r:id="rId501" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -12,14 +12,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$551</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$J$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="160">
   <si>
     <t>Tecnico</t>
   </si>
@@ -642,7 +642,15 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -12844,20 +12852,20 @@
         <v>4</v>
       </c>
       <c r="B481" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C481" s="9">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D481" s="12">
-        <v>31.369738297872299</v>
+        <v>31.758050607287402</v>
       </c>
       <c r="E481" s="13">
         <v>20</v>
       </c>
       <c r="F481" s="14">
         <f t="shared" si="12"/>
-        <v>25.095790638297839</v>
+        <v>25.406440485829922</v>
       </c>
       <c r="G481" s="15" t="s">
         <v>67</v>
@@ -12871,20 +12879,20 @@
         <v>5</v>
       </c>
       <c r="B482" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C482" s="9">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D482" s="4">
-        <v>68.427141715896894</v>
+        <v>67.292444272445806</v>
       </c>
       <c r="E482" s="6">
         <v>20</v>
       </c>
       <c r="F482" s="3">
         <f t="shared" si="12"/>
-        <v>54.741713372717513</v>
+        <v>53.833955417956645</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>67</v>
@@ -12898,20 +12906,20 @@
         <v>139</v>
       </c>
       <c r="B483" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C483" s="9">
         <v>48</v>
       </c>
       <c r="D483" s="4">
-        <v>62.524824470029202</v>
+        <v>76.095521987417996</v>
       </c>
       <c r="E483" s="6">
         <v>20</v>
       </c>
       <c r="F483" s="3">
         <f t="shared" si="12"/>
-        <v>50.019859576023364</v>
+        <v>60.876417589934398</v>
       </c>
       <c r="G483" s="1"/>
       <c r="H483" s="8"/>
@@ -12921,20 +12929,20 @@
         <v>6</v>
       </c>
       <c r="B484" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C484" s="9">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D484" s="4">
-        <v>27.291165827366999</v>
+        <v>23.688493921286501</v>
       </c>
       <c r="E484" s="6">
         <v>20</v>
       </c>
       <c r="F484" s="3">
         <f t="shared" si="12"/>
-        <v>21.832932661893601</v>
+        <v>18.9507951370292</v>
       </c>
       <c r="G484" s="1"/>
       <c r="H484" s="8" t="s">
@@ -12946,20 +12954,20 @@
         <v>7</v>
       </c>
       <c r="B485" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C485" s="9">
         <v>128</v>
       </c>
       <c r="D485" s="4">
-        <v>55.180107829944198</v>
+        <v>78.8174726001794</v>
       </c>
       <c r="E485" s="6">
         <v>20</v>
       </c>
       <c r="F485" s="3">
         <f t="shared" si="12"/>
-        <v>44.144086263955359</v>
+        <v>63.053978080143523</v>
       </c>
       <c r="G485" s="1"/>
       <c r="H485" s="8" t="s">
@@ -12971,20 +12979,20 @@
         <v>8</v>
       </c>
       <c r="B486" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C486" s="9">
         <v>144</v>
       </c>
       <c r="D486" s="4">
-        <v>27.698004984567898</v>
+        <v>37.8087600755361</v>
       </c>
       <c r="E486" s="6">
         <v>20</v>
       </c>
       <c r="F486" s="3">
         <f t="shared" si="12"/>
-        <v>22.158403987654317</v>
+        <v>30.247008060428879</v>
       </c>
       <c r="G486" s="1"/>
       <c r="H486" s="8" t="s">
@@ -12996,20 +13004,20 @@
         <v>9</v>
       </c>
       <c r="B487" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C487" s="9">
         <v>120</v>
       </c>
       <c r="D487" s="4">
-        <v>37.553407178451202</v>
+        <v>44.681566228458301</v>
       </c>
       <c r="E487" s="6">
         <v>20</v>
       </c>
       <c r="F487" s="3">
         <f t="shared" si="12"/>
-        <v>30.042725742760961</v>
+        <v>35.745252982766644</v>
       </c>
       <c r="G487" s="1"/>
       <c r="H487" s="8" t="s">
@@ -13021,20 +13029,20 @@
         <v>10</v>
       </c>
       <c r="B488" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C488" s="9">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D488" s="4">
-        <v>32.971718333333399</v>
+        <v>39.5605422469636</v>
       </c>
       <c r="E488" s="6">
         <v>20</v>
       </c>
       <c r="F488" s="3">
         <f t="shared" si="12"/>
-        <v>26.377374666666718</v>
+        <v>31.648433797570881</v>
       </c>
       <c r="G488" s="1"/>
       <c r="H488" s="8" t="s">
@@ -13046,20 +13054,20 @@
         <v>157</v>
       </c>
       <c r="B489" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C489" s="9">
         <v>160</v>
       </c>
       <c r="D489" s="4">
-        <v>27.7307202238174</v>
+        <v>30.4661878232207</v>
       </c>
       <c r="E489" s="6">
         <v>20</v>
       </c>
       <c r="F489" s="3">
         <f t="shared" si="12"/>
-        <v>22.18457617905392</v>
+        <v>24.372950258576559</v>
       </c>
       <c r="G489" s="1"/>
       <c r="H489" s="8"/>
@@ -13069,20 +13077,20 @@
         <v>11</v>
       </c>
       <c r="B490" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C490" s="9">
         <v>128</v>
       </c>
       <c r="D490" s="4">
-        <v>36.1157055555556</v>
+        <v>44.245408333333302</v>
       </c>
       <c r="E490" s="6">
         <v>20</v>
       </c>
       <c r="F490" s="3">
         <f t="shared" si="12"/>
-        <v>28.892564444444481</v>
+        <v>35.396326666666639</v>
       </c>
       <c r="G490" s="1"/>
       <c r="H490" s="8" t="s">
@@ -13094,20 +13102,20 @@
         <v>12</v>
       </c>
       <c r="B491" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C491" s="9">
         <v>112</v>
       </c>
       <c r="D491" s="4">
-        <v>90.0277420183983</v>
+        <v>100.50772067099599</v>
       </c>
       <c r="E491" s="6">
         <v>20</v>
       </c>
       <c r="F491" s="3">
         <f t="shared" si="12"/>
-        <v>72.022193614718645</v>
+        <v>80.406176536796792</v>
       </c>
       <c r="G491" s="1"/>
       <c r="H491" s="8" t="s">
@@ -13119,20 +13127,20 @@
         <v>13</v>
       </c>
       <c r="B492" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C492" s="9">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D492" s="4">
-        <v>85.482263166956599</v>
+        <v>97.567440024682895</v>
       </c>
       <c r="E492" s="6">
         <v>20</v>
       </c>
       <c r="F492" s="3">
         <f t="shared" si="12"/>
-        <v>68.385810533565277</v>
+        <v>78.053952019746319</v>
       </c>
       <c r="G492" s="1"/>
       <c r="H492" s="8" t="s">
@@ -13144,20 +13152,20 @@
         <v>14</v>
       </c>
       <c r="B493" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C493" s="9">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D493" s="4">
-        <v>41.0361639829488</v>
+        <v>40.460687330920202</v>
       </c>
       <c r="E493" s="6">
         <v>20</v>
       </c>
       <c r="F493" s="3">
         <f t="shared" si="12"/>
-        <v>32.828931186359043</v>
+        <v>32.36854986473616</v>
       </c>
       <c r="G493" s="1"/>
       <c r="H493" s="8" t="s">
@@ -13169,20 +13177,20 @@
         <v>16</v>
       </c>
       <c r="B494" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C494" s="9">
         <v>140</v>
       </c>
       <c r="D494" s="4">
-        <v>27.8431319126984</v>
+        <v>37.912744291979998</v>
       </c>
       <c r="E494" s="6">
         <v>20</v>
       </c>
       <c r="F494" s="3">
         <f t="shared" si="12"/>
-        <v>22.27450553015872</v>
+        <v>30.330195433583999</v>
       </c>
       <c r="G494" s="1"/>
       <c r="H494" s="8" t="s">
@@ -13194,20 +13202,20 @@
         <v>154</v>
       </c>
       <c r="B495" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C495" s="9">
         <v>144</v>
       </c>
       <c r="D495" s="4">
-        <v>54.1322669989367</v>
+        <v>76.787972066269603</v>
       </c>
       <c r="E495" s="6">
         <v>20</v>
       </c>
       <c r="F495" s="3">
         <f t="shared" si="12"/>
-        <v>43.30581359914936</v>
+        <v>61.430377653015682</v>
       </c>
       <c r="G495" s="1"/>
       <c r="H495" s="8"/>
@@ -13217,7 +13225,7 @@
         <v>17</v>
       </c>
       <c r="B496" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C496" s="9">
         <v>152</v>
@@ -13242,20 +13250,20 @@
         <v>18</v>
       </c>
       <c r="B497" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C497" s="9">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D497" s="4">
-        <v>31.924892655502401</v>
+        <v>35.773359665551801</v>
       </c>
       <c r="E497" s="6">
         <v>20</v>
       </c>
       <c r="F497" s="3">
         <f t="shared" si="12"/>
-        <v>25.539914124401921</v>
+        <v>28.61868773244144</v>
       </c>
       <c r="G497" s="1"/>
       <c r="H497" s="8" t="s">
@@ -13267,20 +13275,20 @@
         <v>20</v>
       </c>
       <c r="B498" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C498" s="9">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D498" s="4">
-        <v>31.369738297872299</v>
+        <v>31.758050607287402</v>
       </c>
       <c r="E498" s="6">
         <v>20</v>
       </c>
       <c r="F498" s="3">
         <f t="shared" si="12"/>
-        <v>25.095790638297839</v>
+        <v>25.406440485829922</v>
       </c>
       <c r="G498" s="1"/>
       <c r="H498" s="8" t="s">
@@ -13292,20 +13300,20 @@
         <v>21</v>
       </c>
       <c r="B499" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C499" s="9">
         <v>168</v>
       </c>
       <c r="D499" s="4">
-        <v>34.4356642342984</v>
+        <v>36.226309910409803</v>
       </c>
       <c r="E499" s="6">
         <v>20</v>
       </c>
       <c r="F499" s="3">
         <f t="shared" si="12"/>
-        <v>27.548531387438722</v>
+        <v>28.981047928327843</v>
       </c>
       <c r="G499" s="1"/>
       <c r="H499" s="8" t="s">
@@ -13317,20 +13325,20 @@
         <v>22</v>
       </c>
       <c r="B500" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C500" s="9">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D500" s="4">
-        <v>58.702747191011198</v>
+        <v>59.139026881720397</v>
       </c>
       <c r="E500" s="6">
         <v>20</v>
       </c>
       <c r="F500" s="3">
         <f t="shared" si="12"/>
-        <v>46.962197752808962</v>
+        <v>47.311221505376317</v>
       </c>
       <c r="G500" s="1"/>
       <c r="H500" s="8" t="s">
@@ -13342,20 +13350,20 @@
         <v>23</v>
       </c>
       <c r="B501" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C501" s="9">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D501" s="4">
-        <v>40.473494282834103</v>
+        <v>39.89</v>
       </c>
       <c r="E501" s="6">
         <v>20</v>
       </c>
       <c r="F501" s="3">
         <f t="shared" si="12"/>
-        <v>32.378795426267281</v>
+        <v>31.911999999999999</v>
       </c>
       <c r="G501" s="1"/>
       <c r="H501" s="8" t="s">
@@ -13367,20 +13375,20 @@
         <v>25</v>
       </c>
       <c r="B502" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C502" s="9">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D502" s="4">
-        <v>33.5808769455844</v>
+        <v>32.487203262540099</v>
       </c>
       <c r="E502" s="6">
         <v>20</v>
       </c>
       <c r="F502" s="3">
         <f t="shared" si="12"/>
-        <v>26.864701556467519</v>
+        <v>25.989762610032081</v>
       </c>
       <c r="G502" s="1"/>
       <c r="H502" s="8" t="s">
@@ -13392,20 +13400,20 @@
         <v>26</v>
       </c>
       <c r="B503" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C503" s="9">
         <v>160</v>
       </c>
       <c r="D503" s="4">
-        <v>33.605256443048901</v>
+        <v>40.252999215878198</v>
       </c>
       <c r="E503" s="6">
         <v>20</v>
       </c>
       <c r="F503" s="3">
         <f t="shared" si="12"/>
-        <v>26.884205154439123</v>
+        <v>32.202399372702558</v>
       </c>
       <c r="G503" s="1"/>
       <c r="H503" s="8" t="s">
@@ -13417,20 +13425,20 @@
         <v>27</v>
       </c>
       <c r="B504" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C504" s="9">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D504" s="4">
-        <v>44.996793451486703</v>
+        <v>45.979327838890001</v>
       </c>
       <c r="E504" s="6">
         <v>20</v>
       </c>
       <c r="F504" s="3">
         <f t="shared" si="12"/>
-        <v>35.997434761189361</v>
+        <v>36.783462271112001</v>
       </c>
       <c r="G504" s="1"/>
       <c r="H504" s="8" t="s">
@@ -13442,20 +13450,20 @@
         <v>28</v>
       </c>
       <c r="B505" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C505" s="9">
         <v>128</v>
       </c>
       <c r="D505" s="4">
-        <v>93.406500236742403</v>
+        <v>105.95314185606099</v>
       </c>
       <c r="E505" s="6">
         <v>20</v>
       </c>
       <c r="F505" s="3">
         <f t="shared" si="12"/>
-        <v>74.725200189393917</v>
+        <v>84.762513484848796</v>
       </c>
       <c r="G505" s="1"/>
       <c r="H505" s="8" t="s">
@@ -13467,20 +13475,20 @@
         <v>29</v>
       </c>
       <c r="B506" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C506" s="9">
         <v>88</v>
       </c>
       <c r="D506" s="4">
-        <v>35.171477272727302</v>
+        <v>43.912687499999997</v>
       </c>
       <c r="E506" s="6">
         <v>20</v>
       </c>
       <c r="F506" s="3">
         <f t="shared" si="12"/>
-        <v>28.13718181818184</v>
+        <v>35.13015</v>
       </c>
       <c r="G506" s="1"/>
       <c r="H506" s="8" t="s">
@@ -13492,20 +13500,20 @@
         <v>30</v>
       </c>
       <c r="B507" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C507" s="9">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D507" s="4">
-        <v>25.610488888888899</v>
+        <v>20.955948320413398</v>
       </c>
       <c r="E507" s="6">
         <v>20</v>
       </c>
       <c r="F507" s="3">
         <f t="shared" si="12"/>
-        <v>20.48839111111112</v>
+        <v>16.76475865633072</v>
       </c>
       <c r="G507" s="1"/>
       <c r="H507" s="8" t="s">
@@ -13517,20 +13525,20 @@
         <v>137</v>
       </c>
       <c r="B508" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C508" s="9">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D508" s="4">
-        <v>31.418000797993599</v>
+        <v>29.536541442465602</v>
       </c>
       <c r="E508" s="6">
         <v>20</v>
       </c>
       <c r="F508" s="3">
         <f t="shared" si="12"/>
-        <v>25.134400638394879</v>
+        <v>23.629233153972482</v>
       </c>
       <c r="G508" s="1"/>
       <c r="H508" s="8" t="s">
@@ -13542,20 +13550,20 @@
         <v>31</v>
       </c>
       <c r="B509" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C509" s="9">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D509" s="4">
-        <v>40.823227272727301</v>
+        <v>42.069800884955697</v>
       </c>
       <c r="E509" s="6">
         <v>20</v>
       </c>
       <c r="F509" s="3">
         <f t="shared" si="12"/>
-        <v>32.658581818181844</v>
+        <v>33.655840707964558</v>
       </c>
       <c r="G509" s="1"/>
       <c r="H509" s="8" t="s">
@@ -13567,20 +13575,20 @@
         <v>32</v>
       </c>
       <c r="B510" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C510" s="9">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D510" s="4">
-        <v>45.039889158163298</v>
+        <v>206.99323991935501</v>
       </c>
       <c r="E510" s="6">
         <v>20</v>
       </c>
       <c r="F510" s="3">
         <f t="shared" si="12"/>
-        <v>36.03191132653064</v>
+        <v>165.594591935484</v>
       </c>
       <c r="G510" s="1"/>
       <c r="H510" s="8" t="s">
@@ -13592,20 +13600,20 @@
         <v>33</v>
       </c>
       <c r="B511" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C511" s="9">
         <v>160</v>
       </c>
       <c r="D511" s="4">
-        <v>37.453238338870399</v>
+        <v>39.706873977358804</v>
       </c>
       <c r="E511" s="6">
         <v>20</v>
       </c>
       <c r="F511" s="3">
         <f t="shared" si="12"/>
-        <v>29.962590671096319</v>
+        <v>31.765499181887044</v>
       </c>
       <c r="G511" s="1"/>
       <c r="H511" s="8" t="s">
@@ -13617,20 +13625,20 @@
         <v>34</v>
       </c>
       <c r="B512" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C512" s="9">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D512" s="4">
-        <v>34.756645348837203</v>
+        <v>32.524718832891203</v>
       </c>
       <c r="E512" s="6">
         <v>20</v>
       </c>
       <c r="F512" s="3">
         <f t="shared" si="12"/>
-        <v>27.805316279069764</v>
+        <v>26.019775066312963</v>
       </c>
       <c r="G512" s="1"/>
       <c r="H512" s="8" t="s">
@@ -13642,20 +13650,20 @@
         <v>35</v>
       </c>
       <c r="B513" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C513" s="9">
         <v>136</v>
       </c>
       <c r="D513" s="4">
-        <v>56.388075359016803</v>
+        <v>62.9656072217619</v>
       </c>
       <c r="E513" s="6">
         <v>20</v>
       </c>
       <c r="F513" s="3">
         <f t="shared" si="12"/>
-        <v>45.110460287213442</v>
+        <v>50.372485777409523</v>
       </c>
       <c r="G513" s="1"/>
       <c r="H513" s="8" t="s">
@@ -13667,20 +13675,20 @@
         <v>36</v>
       </c>
       <c r="B514" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C514" s="9">
         <v>168</v>
       </c>
       <c r="D514" s="4">
-        <v>25.395943537415</v>
+        <v>30.7104456946625</v>
       </c>
       <c r="E514" s="6">
         <v>20</v>
       </c>
       <c r="F514" s="3">
         <f t="shared" si="12"/>
-        <v>20.316754829932002</v>
+        <v>24.568356555729999</v>
       </c>
       <c r="G514" s="1"/>
       <c r="H514" s="8" t="s">
@@ -13692,20 +13700,20 @@
         <v>37</v>
       </c>
       <c r="B515" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C515" s="9">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D515" s="4">
-        <v>45.133217675061402</v>
+        <v>45.684566746969402</v>
       </c>
       <c r="E515" s="6">
         <v>20</v>
       </c>
       <c r="F515" s="3">
         <f t="shared" si="12"/>
-        <v>36.106574140049119</v>
+        <v>36.547653397575523</v>
       </c>
       <c r="G515" s="1"/>
       <c r="H515" s="8" t="s">
@@ -13717,20 +13725,20 @@
         <v>38</v>
       </c>
       <c r="B516" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C516" s="9">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D516" s="4">
-        <v>43.885611309523803</v>
+        <v>46.516124596774198</v>
       </c>
       <c r="E516" s="6">
         <v>20</v>
       </c>
       <c r="F516" s="3">
         <f t="shared" si="12"/>
-        <v>35.108489047619045</v>
+        <v>37.212899677419358</v>
       </c>
       <c r="G516" s="1"/>
       <c r="H516" s="8" t="s">
@@ -13742,20 +13750,20 @@
         <v>39</v>
       </c>
       <c r="B517" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C517" s="9">
         <v>120</v>
       </c>
       <c r="D517" s="4">
-        <v>93.932084848484905</v>
+        <v>106.800207373737</v>
       </c>
       <c r="E517" s="6">
         <v>20</v>
       </c>
       <c r="F517" s="3">
         <f t="shared" si="12"/>
-        <v>75.145667878787918</v>
+        <v>85.440165898989591</v>
       </c>
       <c r="G517" s="1"/>
       <c r="H517" s="8" t="s">
@@ -13767,20 +13775,20 @@
         <v>40</v>
       </c>
       <c r="B518" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C518" s="9">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D518" s="4">
-        <v>26.5068125816993</v>
+        <v>22.737825428396601</v>
       </c>
       <c r="E518" s="6">
         <v>20</v>
       </c>
       <c r="F518" s="3">
         <f t="shared" si="12"/>
-        <v>21.20545006535944</v>
+        <v>18.190260342717281</v>
       </c>
       <c r="G518" s="1"/>
       <c r="H518" s="8" t="s">
@@ -13792,20 +13800,20 @@
         <v>41</v>
       </c>
       <c r="B519" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C519" s="9">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D519" s="4">
-        <v>40.364205663083901</v>
+        <v>41.651433670587402</v>
       </c>
       <c r="E519" s="6">
         <v>20</v>
       </c>
       <c r="F519" s="3">
         <f t="shared" si="12"/>
-        <v>32.291364530467121</v>
+        <v>33.321146936469923</v>
       </c>
       <c r="G519" s="1"/>
       <c r="H519" s="8" t="s">
@@ -13817,20 +13825,20 @@
         <v>42</v>
       </c>
       <c r="B520" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C520" s="9">
         <v>160</v>
       </c>
       <c r="D520" s="4">
-        <v>36.1998541424419</v>
+        <v>39.402819691644602</v>
       </c>
       <c r="E520" s="6">
         <v>20</v>
       </c>
       <c r="F520" s="3">
         <f t="shared" si="12"/>
-        <v>28.959883313953519</v>
+        <v>31.522255753315683</v>
       </c>
       <c r="G520" s="1"/>
       <c r="H520" s="8" t="s">
@@ -13842,20 +13850,20 @@
         <v>43</v>
       </c>
       <c r="B521" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C521" s="9">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D521" s="4">
-        <v>40.717765624999998</v>
+        <v>40.648450757575802</v>
       </c>
       <c r="E521" s="6">
         <v>20</v>
       </c>
       <c r="F521" s="3">
         <f t="shared" si="12"/>
-        <v>32.574212500000002</v>
+        <v>32.518760606060638</v>
       </c>
       <c r="G521" s="1"/>
       <c r="H521" s="8" t="s">
@@ -13867,20 +13875,20 @@
         <v>44</v>
       </c>
       <c r="B522" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C522" s="9">
         <v>40</v>
       </c>
       <c r="D522" s="4">
-        <v>73.754156030701793</v>
+        <v>90.038993051568298</v>
       </c>
       <c r="E522" s="6">
         <v>20</v>
       </c>
       <c r="F522" s="3">
         <f t="shared" si="12"/>
-        <v>59.003324824561432</v>
+        <v>72.031194441254641</v>
       </c>
       <c r="G522" s="1"/>
       <c r="H522" s="8" t="s">
@@ -13892,20 +13900,20 @@
         <v>45</v>
       </c>
       <c r="B523" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C523" s="9">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D523" s="4">
-        <v>31.569829822864701</v>
+        <v>32.365782451923103</v>
       </c>
       <c r="E523" s="6">
         <v>20</v>
       </c>
       <c r="F523" s="3">
         <f t="shared" si="12"/>
-        <v>25.255863858291761</v>
+        <v>25.892625961538482</v>
       </c>
       <c r="G523" s="1"/>
       <c r="H523" s="8" t="s">
@@ -13917,20 +13925,20 @@
         <v>46</v>
       </c>
       <c r="B524" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C524" s="9">
         <v>120</v>
       </c>
       <c r="D524" s="4">
-        <v>65.886603448275807</v>
+        <v>70.907206896551699</v>
       </c>
       <c r="E524" s="6">
         <v>20</v>
       </c>
       <c r="F524" s="3">
         <f t="shared" si="12"/>
-        <v>52.709282758620645</v>
+        <v>56.725765517241356</v>
       </c>
       <c r="G524" s="1"/>
       <c r="H524" s="8" t="s">
@@ -13942,20 +13950,20 @@
         <v>47</v>
       </c>
       <c r="B525" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C525" s="9">
         <v>88</v>
       </c>
       <c r="D525" s="4">
-        <v>57.412687526675199</v>
+        <v>67.577964041826704</v>
       </c>
       <c r="E525" s="6">
         <v>20</v>
       </c>
       <c r="F525" s="3">
         <f t="shared" si="12"/>
-        <v>45.930150021340161</v>
+        <v>54.062371233461363</v>
       </c>
       <c r="G525" s="1"/>
       <c r="H525" s="8" t="s">
@@ -13967,20 +13975,20 @@
         <v>48</v>
       </c>
       <c r="B526" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C526" s="9">
         <v>128</v>
       </c>
       <c r="D526" s="4">
-        <v>56.505478836560997</v>
+        <v>63.494106440727698</v>
       </c>
       <c r="E526" s="6">
         <v>20</v>
       </c>
       <c r="F526" s="3">
         <f t="shared" si="12"/>
-        <v>45.204383069248799</v>
+        <v>50.79528515258216</v>
       </c>
       <c r="G526" s="1"/>
       <c r="H526" s="8" t="s">
@@ -13992,20 +14000,20 @@
         <v>49</v>
       </c>
       <c r="B527" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C527" s="9">
         <v>144</v>
       </c>
       <c r="D527" s="4">
-        <v>39.297410062406101</v>
+        <v>44.458025678021698</v>
       </c>
       <c r="E527" s="6">
         <v>20</v>
       </c>
       <c r="F527" s="3">
         <f t="shared" si="12"/>
-        <v>31.437928049924881</v>
+        <v>35.566420542417362</v>
       </c>
       <c r="G527" s="1"/>
       <c r="H527" s="8" t="s">
@@ -14017,20 +14025,20 @@
         <v>50</v>
       </c>
       <c r="B528" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C528" s="9">
         <v>152</v>
       </c>
       <c r="D528" s="4">
-        <v>27.168310810810802</v>
+        <v>33.285641891891899</v>
       </c>
       <c r="E528" s="6">
         <v>20</v>
       </c>
       <c r="F528" s="3">
         <f t="shared" si="12"/>
-        <v>21.734648648648641</v>
+        <v>26.628513513513518</v>
       </c>
       <c r="G528" s="1"/>
       <c r="H528" s="8" t="s">
@@ -14042,20 +14050,20 @@
         <v>51</v>
       </c>
       <c r="B529" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C529" s="9">
         <v>160</v>
       </c>
       <c r="D529" s="4">
-        <v>38.808745310991803</v>
+        <v>44.196049847671297</v>
       </c>
       <c r="E529" s="6">
         <v>20</v>
       </c>
       <c r="F529" s="3">
         <f t="shared" si="12"/>
-        <v>31.046996248793441</v>
+        <v>35.356839878137038</v>
       </c>
       <c r="G529" s="1"/>
       <c r="H529" s="8" t="s">
@@ -14067,20 +14075,20 @@
         <v>52</v>
       </c>
       <c r="B530" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C530" s="9">
         <v>152</v>
       </c>
       <c r="D530" s="4">
-        <v>32.504854196301601</v>
+        <v>39.587576458036999</v>
       </c>
       <c r="E530" s="6">
         <v>20</v>
       </c>
       <c r="F530" s="3">
         <f t="shared" si="12"/>
-        <v>26.003883357041282</v>
+        <v>31.670061166429598</v>
       </c>
       <c r="G530" s="1"/>
       <c r="H530" s="8" t="s">
@@ -14092,20 +14100,20 @@
         <v>53</v>
       </c>
       <c r="B531" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C531" s="9">
         <v>160</v>
       </c>
       <c r="D531" s="4">
-        <v>33.8817909610705</v>
+        <v>37.007300588709697</v>
       </c>
       <c r="E531" s="6">
         <v>20</v>
       </c>
       <c r="F531" s="3">
         <f t="shared" si="12"/>
-        <v>27.105432768856399</v>
+        <v>29.605840470967756</v>
       </c>
       <c r="G531" s="1"/>
       <c r="H531" s="8" t="s">
@@ -14117,20 +14125,20 @@
         <v>54</v>
       </c>
       <c r="B532" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C532" s="9">
         <v>120</v>
       </c>
       <c r="D532" s="4">
-        <v>36.205773563218401</v>
+        <v>43.229188793103397</v>
       </c>
       <c r="E532" s="6">
         <v>20</v>
       </c>
       <c r="F532" s="3">
         <f t="shared" si="12"/>
-        <v>28.96461885057472</v>
+        <v>34.583351034482718</v>
       </c>
       <c r="G532" s="1"/>
       <c r="H532" s="8" t="s">
@@ -14142,20 +14150,20 @@
         <v>55</v>
       </c>
       <c r="B533" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C533" s="9">
         <v>160</v>
       </c>
       <c r="D533" s="4">
-        <v>35.133196965479499</v>
+        <v>36.348020198538897</v>
       </c>
       <c r="E533" s="6">
         <v>20</v>
       </c>
       <c r="F533" s="3">
         <f t="shared" si="12"/>
-        <v>28.106557572383601</v>
+        <v>29.078416158831118</v>
       </c>
       <c r="G533" s="1"/>
       <c r="H533" s="8" t="s">
@@ -14167,20 +14175,20 @@
         <v>56</v>
       </c>
       <c r="B534" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C534" s="9">
         <v>112</v>
       </c>
       <c r="D534" s="4">
-        <v>34.085714285714303</v>
+        <v>41.252187499999998</v>
       </c>
       <c r="E534" s="6">
         <v>20</v>
       </c>
       <c r="F534" s="3">
         <f t="shared" si="12"/>
-        <v>27.268571428571441</v>
+        <v>33.001750000000001</v>
       </c>
       <c r="G534" s="1"/>
       <c r="H534" s="8" t="s">
@@ -14192,20 +14200,20 @@
         <v>57</v>
       </c>
       <c r="B535" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C535" s="9">
         <v>136</v>
       </c>
       <c r="D535" s="4">
-        <v>34.841180916969101</v>
+        <v>40.496842633928601</v>
       </c>
       <c r="E535" s="6">
         <v>20</v>
       </c>
       <c r="F535" s="3">
         <f t="shared" si="12"/>
-        <v>27.872944733575281</v>
+        <v>32.397474107142884</v>
       </c>
       <c r="G535" s="1"/>
       <c r="H535" s="8" t="s">
@@ -14217,20 +14225,20 @@
         <v>58</v>
       </c>
       <c r="B536" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C536" s="9">
         <v>80</v>
       </c>
       <c r="D536" s="4">
-        <v>461.84753124999997</v>
+        <v>274.81869999999998</v>
       </c>
       <c r="E536" s="6">
         <v>20</v>
       </c>
       <c r="F536" s="3">
         <f t="shared" si="12"/>
-        <v>369.478025</v>
+        <v>219.85495999999998</v>
       </c>
       <c r="G536" s="1"/>
       <c r="H536" s="8" t="s">
@@ -14242,20 +14250,20 @@
         <v>59</v>
       </c>
       <c r="B537" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C537" s="9">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D537" s="4">
-        <v>40.961701388661403</v>
+        <v>40.413917862124798</v>
       </c>
       <c r="E537" s="6">
         <v>20</v>
       </c>
       <c r="F537" s="3">
         <f t="shared" ref="F537:F549" si="14">D537-(D537*E537)/100</f>
-        <v>32.769361110929125</v>
+        <v>32.33113428969984</v>
       </c>
       <c r="G537" s="1"/>
       <c r="H537" s="8" t="s">
@@ -14267,20 +14275,20 @@
         <v>60</v>
       </c>
       <c r="B538" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C538" s="9">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D538" s="4">
-        <v>61.584973333333302</v>
+        <v>61.886292763157897</v>
       </c>
       <c r="E538" s="6">
         <v>20</v>
       </c>
       <c r="F538" s="3">
         <f t="shared" si="14"/>
-        <v>49.267978666666643</v>
+        <v>49.509034210526316</v>
       </c>
       <c r="G538" s="1"/>
       <c r="H538" s="8" t="s">
@@ -14292,20 +14300,20 @@
         <v>61</v>
       </c>
       <c r="B539" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C539" s="9">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D539" s="4">
-        <v>61.584973333333302</v>
+        <v>61.886292763157897</v>
       </c>
       <c r="E539" s="6">
         <v>20</v>
       </c>
       <c r="F539" s="3">
         <f t="shared" si="14"/>
-        <v>49.267978666666643</v>
+        <v>49.509034210526316</v>
       </c>
       <c r="G539" s="1"/>
       <c r="H539" s="8" t="s">
@@ -14317,20 +14325,20 @@
         <v>62</v>
       </c>
       <c r="B540" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C540" s="9">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D540" s="4">
-        <v>36.438440426168903</v>
+        <v>40.007166900922599</v>
       </c>
       <c r="E540" s="6">
         <v>20</v>
       </c>
       <c r="F540" s="3">
         <f t="shared" si="14"/>
-        <v>29.150752340935121</v>
+        <v>32.005733520738076</v>
       </c>
       <c r="G540" s="1"/>
       <c r="H540" s="8" t="s">
@@ -14342,20 +14350,20 @@
         <v>63</v>
       </c>
       <c r="B541" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C541" s="9">
         <v>36</v>
       </c>
       <c r="D541" s="4">
-        <v>67.290670911775607</v>
+        <v>62.307746536987899</v>
       </c>
       <c r="E541" s="6">
         <v>20</v>
       </c>
       <c r="F541" s="3">
         <f t="shared" si="14"/>
-        <v>53.832536729420482</v>
+        <v>49.846197229590317</v>
       </c>
       <c r="G541" s="1"/>
       <c r="H541" s="8" t="s">
@@ -14367,20 +14375,20 @@
         <v>64</v>
       </c>
       <c r="B542" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C542" s="9">
         <v>8</v>
       </c>
       <c r="D542" s="4">
-        <v>96.034423295454602</v>
+        <v>110.188469444444</v>
       </c>
       <c r="E542" s="6">
         <v>20</v>
       </c>
       <c r="F542" s="3">
         <f t="shared" si="14"/>
-        <v>76.827538636363684</v>
+        <v>88.1507755555552</v>
       </c>
       <c r="G542" s="1"/>
       <c r="H542" s="8" t="s">
@@ -14392,20 +14400,20 @@
         <v>65</v>
       </c>
       <c r="B543" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C543" s="9">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D543" s="4">
-        <v>38.779223021596501</v>
+        <v>39.574879706933302</v>
       </c>
       <c r="E543" s="6">
         <v>20</v>
       </c>
       <c r="F543" s="3">
         <f t="shared" si="14"/>
-        <v>31.0233784172772</v>
+        <v>31.659903765546641</v>
       </c>
       <c r="G543" s="1"/>
       <c r="H543" s="8" t="s">
@@ -14417,20 +14425,20 @@
         <v>134</v>
       </c>
       <c r="B544" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C544" s="9">
         <v>134</v>
       </c>
       <c r="D544" s="4">
-        <v>84.694827430344404</v>
+        <v>88.967339863582794</v>
       </c>
       <c r="E544" s="6">
         <v>20</v>
       </c>
       <c r="F544" s="3">
         <f t="shared" si="14"/>
-        <v>67.755861944275523</v>
+        <v>71.173871890866238</v>
       </c>
       <c r="G544" s="1"/>
       <c r="H544" s="8"/>
@@ -14440,20 +14448,20 @@
         <v>133</v>
       </c>
       <c r="B545" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C545" s="9">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D545" s="4">
-        <v>40.363893521960598</v>
+        <v>41.590217287528503</v>
       </c>
       <c r="E545" s="6">
         <v>20</v>
       </c>
       <c r="F545" s="3">
         <f t="shared" si="14"/>
-        <v>32.291114817568477</v>
+        <v>33.272173830022801</v>
       </c>
       <c r="G545" s="1"/>
       <c r="H545" s="8"/>
@@ -14463,20 +14471,20 @@
         <v>135</v>
       </c>
       <c r="B546" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C546" s="9">
         <v>136</v>
       </c>
       <c r="D546" s="4">
-        <v>56.487683815992497</v>
+        <v>61.779495130120402</v>
       </c>
       <c r="E546" s="6">
         <v>20</v>
       </c>
       <c r="F546" s="3">
         <f t="shared" si="14"/>
-        <v>45.190147052793996</v>
+        <v>49.423596104096319</v>
       </c>
       <c r="G546" s="1"/>
       <c r="H546" s="8"/>
@@ -14486,20 +14494,20 @@
         <v>136</v>
       </c>
       <c r="B547" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C547" s="9">
         <v>136</v>
       </c>
       <c r="D547" s="4">
-        <v>36.173856615965498</v>
+        <v>38.6160299141997</v>
       </c>
       <c r="E547" s="6">
         <v>20</v>
       </c>
       <c r="F547" s="3">
         <f t="shared" si="14"/>
-        <v>28.939085292772397</v>
+        <v>30.892823931359761</v>
       </c>
       <c r="G547" s="1"/>
       <c r="H547" s="8"/>
@@ -14509,20 +14517,20 @@
         <v>156</v>
       </c>
       <c r="B548" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C548" s="9">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D548" s="4">
-        <v>67.305037539466895</v>
+        <v>68.6313388387928</v>
       </c>
       <c r="E548" s="6">
         <v>20</v>
       </c>
       <c r="F548" s="3">
         <f t="shared" si="14"/>
-        <v>53.844030031573517</v>
+        <v>54.905071071034243</v>
       </c>
       <c r="G548" s="1"/>
       <c r="H548" s="8"/>
@@ -14532,20 +14540,20 @@
         <v>155</v>
       </c>
       <c r="B549" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C549" s="9">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D549" s="4">
-        <v>45.386746522257503</v>
+        <v>45.684566746969402</v>
       </c>
       <c r="E549" s="6">
         <v>20</v>
       </c>
       <c r="F549" s="3">
         <f t="shared" si="14"/>
-        <v>36.309397217806001</v>
+        <v>36.547653397575523</v>
       </c>
       <c r="G549" s="1"/>
       <c r="H549" s="8"/>
@@ -14555,20 +14563,20 @@
         <v>158</v>
       </c>
       <c r="B550" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C550" s="9">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D550" s="4">
-        <v>58.702747191011198</v>
+        <v>59.139026881720397</v>
       </c>
       <c r="E550" s="6">
         <v>20</v>
       </c>
       <c r="F550" s="3">
         <f t="shared" ref="F550:F551" si="15">D550-(D550*E550)/100</f>
-        <v>46.962197752808962</v>
+        <v>47.311221505376317</v>
       </c>
       <c r="G550" s="1"/>
       <c r="H550" s="8"/>
@@ -14578,20 +14586,20 @@
         <v>159</v>
       </c>
       <c r="B551" s="11">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C551" s="9">
         <v>16</v>
       </c>
       <c r="D551" s="4">
-        <v>96.034423295454602</v>
+        <v>110.188469444444</v>
       </c>
       <c r="E551" s="6">
         <v>20</v>
       </c>
       <c r="F551" s="3">
         <f t="shared" si="15"/>
-        <v>76.827538636363684</v>
+        <v>88.1507755555552</v>
       </c>
       <c r="G551" s="1"/>
       <c r="H551" s="8"/>
@@ -15107,7 +15115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
@@ -15116,9 +15124,13 @@
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15137,8 +15149,20 @@
       <c r="F1" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="10" t="s">
         <v>22</v>
       </c>
@@ -15157,8 +15181,20 @@
       <c r="F2" s="3">
         <v>30.545952866098958</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="J2" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L2" s="9">
+        <v>152</v>
+      </c>
+      <c r="M2" s="4">
+        <v>40.648450757575802</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>22</v>
       </c>
@@ -15177,8 +15213,20 @@
       <c r="F3" s="3">
         <v>40.570974664491281</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="J3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L3" s="9">
+        <v>176</v>
+      </c>
+      <c r="M3" s="4">
+        <v>40.007166900922599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -15197,8 +15245,20 @@
       <c r="F4" s="3">
         <v>35.225275679528316</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="J4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L4" s="9">
+        <v>168</v>
+      </c>
+      <c r="M4" s="4">
+        <v>39.89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -15217,8 +15277,20 @@
       <c r="F5" s="3">
         <v>25.791108154037278</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="J5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L5" s="9">
+        <v>160</v>
+      </c>
+      <c r="M5" s="4">
+        <v>39.706873977358804</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
@@ -15237,8 +15309,20 @@
       <c r="F6" s="3">
         <v>36.056159366539838</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="J6" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L6" s="9">
+        <v>168</v>
+      </c>
+      <c r="M6" s="4">
+        <v>39.574879706933302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
@@ -15257,8 +15341,20 @@
       <c r="F7" s="3">
         <v>40.505304989033441</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="J7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L7" s="9">
+        <v>152</v>
+      </c>
+      <c r="M7" s="4">
+        <v>39.5605422469636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
@@ -15277,8 +15373,20 @@
       <c r="F8" s="3">
         <v>39.921053835152875</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="J8" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L8" s="9">
+        <v>160</v>
+      </c>
+      <c r="M8" s="4">
+        <v>39.402819691644602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
@@ -15297,8 +15405,20 @@
       <c r="F9" s="3">
         <v>45.997910566887121</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="J9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L9" s="9">
+        <v>160</v>
+      </c>
+      <c r="M9" s="4">
+        <v>37.007300588709697</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
@@ -15317,8 +15437,20 @@
       <c r="F10" s="3">
         <v>34.137898157804479</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="J10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L10" s="9">
+        <v>160</v>
+      </c>
+      <c r="M10" s="4">
+        <v>36.348020198538897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="10" t="s">
         <v>27</v>
       </c>
@@ -15337,8 +15469,20 @@
       <c r="F11" s="3">
         <v>43.835492660637684</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="J11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L11" s="9">
+        <v>168</v>
+      </c>
+      <c r="M11" s="4">
+        <v>36.226309910409803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
@@ -15357,8 +15501,20 @@
       <c r="F12" s="3">
         <v>39.654763547407363</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="J12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L12" s="9">
+        <v>152</v>
+      </c>
+      <c r="M12" s="4">
+        <v>36.1098</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
@@ -15377,8 +15533,20 @@
       <c r="F13" s="3">
         <v>32.397284576589996</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="J13" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L13" s="9">
+        <v>184</v>
+      </c>
+      <c r="M13" s="4">
+        <v>35.773359665551801</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="10" t="s">
         <v>31</v>
       </c>
@@ -15397,8 +15565,20 @@
       <c r="F14" s="3">
         <v>34.11044738950568</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="J14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L14" s="9">
+        <v>168</v>
+      </c>
+      <c r="M14" s="4">
+        <v>30.7104456946625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="10" t="s">
         <v>31</v>
       </c>
@@ -15417,8 +15597,20 @@
       <c r="F15" s="3">
         <v>44.107063657290638</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="J15" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="K15" s="11">
+        <v>46081</v>
+      </c>
+      <c r="L15" s="9">
+        <v>160</v>
+      </c>
+      <c r="M15" s="4">
+        <v>30.4661878232207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="10" t="s">
         <v>31</v>
       </c>
@@ -15755,11 +15947,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1">
-    <sortState ref="A2:F32">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="J1:M15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -12,14 +12,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$551</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$J$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$O$1:$R$15</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="160">
   <si>
     <t>Tecnico</t>
   </si>
@@ -642,15 +642,7 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -12885,14 +12877,14 @@
         <v>136</v>
       </c>
       <c r="D482" s="4">
-        <v>67.292444272445806</v>
+        <v>67.769929179566603</v>
       </c>
       <c r="E482" s="6">
         <v>20</v>
       </c>
       <c r="F482" s="3">
         <f t="shared" si="12"/>
-        <v>53.833955417956645</v>
+        <v>54.215943343653279</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>67</v>
@@ -12912,14 +12904,14 @@
         <v>48</v>
       </c>
       <c r="D483" s="4">
-        <v>76.095521987417996</v>
+        <v>77.448395890926804</v>
       </c>
       <c r="E483" s="6">
         <v>20</v>
       </c>
       <c r="F483" s="3">
         <f t="shared" si="12"/>
-        <v>60.876417589934398</v>
+        <v>61.958716712741442</v>
       </c>
       <c r="G483" s="1"/>
       <c r="H483" s="8"/>
@@ -12960,14 +12952,14 @@
         <v>128</v>
       </c>
       <c r="D485" s="4">
-        <v>78.8174726001794</v>
+        <v>82.368766596889898</v>
       </c>
       <c r="E485" s="6">
         <v>20</v>
       </c>
       <c r="F485" s="3">
         <f t="shared" si="12"/>
-        <v>63.053978080143523</v>
+        <v>65.895013277511922</v>
       </c>
       <c r="G485" s="1"/>
       <c r="H485" s="8" t="s">
@@ -12985,14 +12977,14 @@
         <v>144</v>
       </c>
       <c r="D486" s="4">
-        <v>37.8087600755361</v>
+        <v>38.227440631091604</v>
       </c>
       <c r="E486" s="6">
         <v>20</v>
       </c>
       <c r="F486" s="3">
         <f t="shared" si="12"/>
-        <v>30.247008060428879</v>
+        <v>30.581952504873282</v>
       </c>
       <c r="G486" s="1"/>
       <c r="H486" s="8" t="s">
@@ -13010,14 +13002,14 @@
         <v>120</v>
       </c>
       <c r="D487" s="4">
-        <v>44.681566228458301</v>
+        <v>44.932774561791597</v>
       </c>
       <c r="E487" s="6">
         <v>20</v>
       </c>
       <c r="F487" s="3">
         <f t="shared" si="12"/>
-        <v>35.745252982766644</v>
+        <v>35.946219649433274</v>
       </c>
       <c r="G487" s="1"/>
       <c r="H487" s="8" t="s">
@@ -13035,14 +13027,14 @@
         <v>152</v>
       </c>
       <c r="D488" s="4">
-        <v>39.5605422469636</v>
+        <v>40.663364801600402</v>
       </c>
       <c r="E488" s="6">
         <v>20</v>
       </c>
       <c r="F488" s="3">
         <f t="shared" si="12"/>
-        <v>31.648433797570881</v>
+        <v>32.530691841280323</v>
       </c>
       <c r="G488" s="1"/>
       <c r="H488" s="8" t="s">
@@ -13060,14 +13052,14 @@
         <v>160</v>
       </c>
       <c r="D489" s="4">
-        <v>30.4661878232207</v>
+        <v>32.761814131069102</v>
       </c>
       <c r="E489" s="6">
         <v>20</v>
       </c>
       <c r="F489" s="3">
         <f t="shared" si="12"/>
-        <v>24.372950258576559</v>
+        <v>26.209451304855282</v>
       </c>
       <c r="G489" s="1"/>
       <c r="H489" s="8"/>
@@ -13133,14 +13125,14 @@
         <v>140</v>
       </c>
       <c r="D492" s="4">
-        <v>97.567440024682895</v>
+        <v>97.799361265284404</v>
       </c>
       <c r="E492" s="6">
         <v>20</v>
       </c>
       <c r="F492" s="3">
         <f t="shared" si="12"/>
-        <v>78.053952019746319</v>
+        <v>78.239489012227523</v>
       </c>
       <c r="G492" s="1"/>
       <c r="H492" s="8" t="s">
@@ -13158,14 +13150,14 @@
         <v>121</v>
       </c>
       <c r="D493" s="4">
-        <v>40.460687330920202</v>
+        <v>40.521285967283802</v>
       </c>
       <c r="E493" s="6">
         <v>20</v>
       </c>
       <c r="F493" s="3">
         <f t="shared" si="12"/>
-        <v>32.36854986473616</v>
+        <v>32.417028773827042</v>
       </c>
       <c r="G493" s="1"/>
       <c r="H493" s="8" t="s">
@@ -13183,14 +13175,14 @@
         <v>140</v>
       </c>
       <c r="D494" s="4">
-        <v>37.912744291979998</v>
+        <v>38.343387149122798</v>
       </c>
       <c r="E494" s="6">
         <v>20</v>
       </c>
       <c r="F494" s="3">
         <f t="shared" si="12"/>
-        <v>30.330195433583999</v>
+        <v>30.674709719298239</v>
       </c>
       <c r="G494" s="1"/>
       <c r="H494" s="8" t="s">
@@ -13208,14 +13200,14 @@
         <v>144</v>
       </c>
       <c r="D495" s="4">
-        <v>76.787972066269603</v>
+        <v>80.170156825041602</v>
       </c>
       <c r="E495" s="6">
         <v>20</v>
       </c>
       <c r="F495" s="3">
         <f t="shared" si="12"/>
-        <v>61.430377653015682</v>
+        <v>64.136125460033284</v>
       </c>
       <c r="G495" s="1"/>
       <c r="H495" s="8"/>
@@ -13231,14 +13223,14 @@
         <v>152</v>
       </c>
       <c r="D496" s="4">
-        <v>36.1098</v>
+        <v>36.625466666666703</v>
       </c>
       <c r="E496" s="6">
         <v>20</v>
       </c>
       <c r="F496" s="3">
         <f t="shared" si="12"/>
-        <v>28.887840000000001</v>
+        <v>29.300373333333361</v>
       </c>
       <c r="G496" s="1"/>
       <c r="H496" s="8" t="s">
@@ -13256,14 +13248,14 @@
         <v>184</v>
       </c>
       <c r="D497" s="4">
-        <v>35.773359665551801</v>
+        <v>36.845269002736401</v>
       </c>
       <c r="E497" s="6">
         <v>20</v>
       </c>
       <c r="F497" s="3">
         <f t="shared" si="12"/>
-        <v>28.61868773244144</v>
+        <v>29.47621520218912</v>
       </c>
       <c r="G497" s="1"/>
       <c r="H497" s="8" t="s">
@@ -13306,14 +13298,14 @@
         <v>168</v>
       </c>
       <c r="D499" s="4">
-        <v>36.226309910409803</v>
+        <v>37.711496758482298</v>
       </c>
       <c r="E499" s="6">
         <v>20</v>
       </c>
       <c r="F499" s="3">
         <f t="shared" si="12"/>
-        <v>28.981047928327843</v>
+        <v>30.169197406785838</v>
       </c>
       <c r="G499" s="1"/>
       <c r="H499" s="8" t="s">
@@ -13356,14 +13348,14 @@
         <v>168</v>
       </c>
       <c r="D501" s="4">
-        <v>39.89</v>
+        <v>40.696204348405999</v>
       </c>
       <c r="E501" s="6">
         <v>20</v>
       </c>
       <c r="F501" s="3">
         <f t="shared" si="12"/>
-        <v>31.911999999999999</v>
+        <v>32.556963478724796</v>
       </c>
       <c r="G501" s="1"/>
       <c r="H501" s="8" t="s">
@@ -13406,14 +13398,14 @@
         <v>160</v>
       </c>
       <c r="D503" s="4">
-        <v>40.252999215878198</v>
+        <v>40.408411395365299</v>
       </c>
       <c r="E503" s="6">
         <v>20</v>
       </c>
       <c r="F503" s="3">
         <f t="shared" si="12"/>
-        <v>32.202399372702558</v>
+        <v>32.326729116292242</v>
       </c>
       <c r="G503" s="1"/>
       <c r="H503" s="8" t="s">
@@ -13606,14 +13598,14 @@
         <v>160</v>
       </c>
       <c r="D511" s="4">
-        <v>39.706873977358804</v>
+        <v>41.528098620215999</v>
       </c>
       <c r="E511" s="6">
         <v>20</v>
       </c>
       <c r="F511" s="3">
         <f t="shared" si="12"/>
-        <v>31.765499181887044</v>
+        <v>33.222478896172802</v>
       </c>
       <c r="G511" s="1"/>
       <c r="H511" s="8" t="s">
@@ -13656,14 +13648,14 @@
         <v>136</v>
       </c>
       <c r="D513" s="4">
-        <v>62.9656072217619</v>
+        <v>69.884268986467802</v>
       </c>
       <c r="E513" s="6">
         <v>20</v>
       </c>
       <c r="F513" s="3">
         <f t="shared" si="12"/>
-        <v>50.372485777409523</v>
+        <v>55.907415189174245</v>
       </c>
       <c r="G513" s="1"/>
       <c r="H513" s="8" t="s">
@@ -13681,14 +13673,14 @@
         <v>168</v>
       </c>
       <c r="D514" s="4">
-        <v>30.7104456946625</v>
+        <v>34.831495886912798</v>
       </c>
       <c r="E514" s="6">
         <v>20</v>
       </c>
       <c r="F514" s="3">
         <f t="shared" si="12"/>
-        <v>24.568356555729999</v>
+        <v>27.865196709530238</v>
       </c>
       <c r="G514" s="1"/>
       <c r="H514" s="8" t="s">
@@ -13831,14 +13823,14 @@
         <v>160</v>
       </c>
       <c r="D520" s="4">
-        <v>39.402819691644602</v>
+        <v>43.671285941644598</v>
       </c>
       <c r="E520" s="6">
         <v>20</v>
       </c>
       <c r="F520" s="3">
         <f t="shared" si="12"/>
-        <v>31.522255753315683</v>
+        <v>34.93702875331568</v>
       </c>
       <c r="G520" s="1"/>
       <c r="H520" s="8" t="s">
@@ -13856,14 +13848,14 @@
         <v>152</v>
       </c>
       <c r="D521" s="4">
-        <v>40.648450757575802</v>
+        <v>43.029939393939401</v>
       </c>
       <c r="E521" s="6">
         <v>20</v>
       </c>
       <c r="F521" s="3">
         <f t="shared" si="12"/>
-        <v>32.518760606060638</v>
+        <v>34.423951515151522</v>
       </c>
       <c r="G521" s="1"/>
       <c r="H521" s="8" t="s">
@@ -13881,14 +13873,14 @@
         <v>40</v>
       </c>
       <c r="D522" s="4">
-        <v>90.038993051568298</v>
+        <v>91.662441735778799</v>
       </c>
       <c r="E522" s="6">
         <v>20</v>
       </c>
       <c r="F522" s="3">
         <f t="shared" si="12"/>
-        <v>72.031194441254641</v>
+        <v>73.329953388623039</v>
       </c>
       <c r="G522" s="1"/>
       <c r="H522" s="8" t="s">
@@ -13956,14 +13948,14 @@
         <v>88</v>
       </c>
       <c r="D525" s="4">
-        <v>67.577964041826704</v>
+        <v>78.270441314554006</v>
       </c>
       <c r="E525" s="6">
         <v>20</v>
       </c>
       <c r="F525" s="3">
         <f t="shared" si="12"/>
-        <v>54.062371233461363</v>
+        <v>62.616353051643202</v>
       </c>
       <c r="G525" s="1"/>
       <c r="H525" s="8" t="s">
@@ -13981,14 +13973,14 @@
         <v>128</v>
       </c>
       <c r="D526" s="4">
-        <v>63.494106440727698</v>
+        <v>70.845184565727706</v>
       </c>
       <c r="E526" s="6">
         <v>20</v>
       </c>
       <c r="F526" s="3">
         <f t="shared" si="12"/>
-        <v>50.79528515258216</v>
+        <v>56.676147652582166</v>
       </c>
       <c r="G526" s="1"/>
       <c r="H526" s="8" t="s">
@@ -14106,14 +14098,14 @@
         <v>160</v>
       </c>
       <c r="D531" s="4">
-        <v>37.007300588709697</v>
+        <v>37.256393326648798</v>
       </c>
       <c r="E531" s="6">
         <v>20</v>
       </c>
       <c r="F531" s="3">
         <f t="shared" si="12"/>
-        <v>29.605840470967756</v>
+        <v>29.805114661319038</v>
       </c>
       <c r="G531" s="1"/>
       <c r="H531" s="8" t="s">
@@ -14153,17 +14145,17 @@
         <v>46081</v>
       </c>
       <c r="C533" s="9">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D533" s="4">
-        <v>36.348020198538897</v>
+        <v>35.995552894314798</v>
       </c>
       <c r="E533" s="6">
         <v>20</v>
       </c>
       <c r="F533" s="3">
         <f t="shared" si="12"/>
-        <v>29.078416158831118</v>
+        <v>28.796442315451838</v>
       </c>
       <c r="G533" s="1"/>
       <c r="H533" s="8" t="s">
@@ -14256,14 +14248,14 @@
         <v>123</v>
       </c>
       <c r="D537" s="4">
-        <v>40.413917862124798</v>
+        <v>40.474735463750797</v>
       </c>
       <c r="E537" s="6">
         <v>20</v>
       </c>
       <c r="F537" s="3">
         <f t="shared" ref="F537:F549" si="14">D537-(D537*E537)/100</f>
-        <v>32.33113428969984</v>
+        <v>32.379788371000636</v>
       </c>
       <c r="G537" s="1"/>
       <c r="H537" s="8" t="s">
@@ -14281,14 +14273,14 @@
         <v>120</v>
       </c>
       <c r="D538" s="4">
-        <v>61.886292763157897</v>
+        <v>65.654417763157895</v>
       </c>
       <c r="E538" s="6">
         <v>20</v>
       </c>
       <c r="F538" s="3">
         <f t="shared" si="14"/>
-        <v>49.509034210526316</v>
+        <v>52.523534210526314</v>
       </c>
       <c r="G538" s="1"/>
       <c r="H538" s="8" t="s">
@@ -14306,14 +14298,14 @@
         <v>144</v>
       </c>
       <c r="D539" s="4">
-        <v>61.886292763157897</v>
+        <v>65.654417763157895</v>
       </c>
       <c r="E539" s="6">
         <v>20</v>
       </c>
       <c r="F539" s="3">
         <f t="shared" si="14"/>
-        <v>49.509034210526316</v>
+        <v>52.523534210526314</v>
       </c>
       <c r="G539" s="1"/>
       <c r="H539" s="8" t="s">
@@ -14331,14 +14323,14 @@
         <v>176</v>
       </c>
       <c r="D540" s="4">
-        <v>40.007166900922599</v>
+        <v>40.169399737639203</v>
       </c>
       <c r="E540" s="6">
         <v>20</v>
       </c>
       <c r="F540" s="3">
         <f t="shared" si="14"/>
-        <v>32.005733520738076</v>
+        <v>32.13551979011136</v>
       </c>
       <c r="G540" s="1"/>
       <c r="H540" s="8" t="s">
@@ -14406,14 +14398,14 @@
         <v>168</v>
       </c>
       <c r="D543" s="4">
-        <v>39.574879706933302</v>
+        <v>43.6260912268948</v>
       </c>
       <c r="E543" s="6">
         <v>20</v>
       </c>
       <c r="F543" s="3">
         <f t="shared" si="14"/>
-        <v>31.659903765546641</v>
+        <v>34.900872981515839</v>
       </c>
       <c r="G543" s="1"/>
       <c r="H543" s="8" t="s">
@@ -14454,14 +14446,14 @@
         <v>149</v>
       </c>
       <c r="D545" s="4">
-        <v>41.590217287528503</v>
+        <v>41.718082449212503</v>
       </c>
       <c r="E545" s="6">
         <v>20</v>
       </c>
       <c r="F545" s="3">
         <f t="shared" si="14"/>
-        <v>33.272173830022801</v>
+        <v>33.374465959369999</v>
       </c>
       <c r="G545" s="1"/>
       <c r="H545" s="8"/>
@@ -14500,14 +14492,14 @@
         <v>136</v>
       </c>
       <c r="D547" s="4">
-        <v>38.6160299141997</v>
+        <v>38.043402102429503</v>
       </c>
       <c r="E547" s="6">
         <v>20</v>
       </c>
       <c r="F547" s="3">
         <f t="shared" si="14"/>
-        <v>30.892823931359761</v>
+        <v>30.434721681943603</v>
       </c>
       <c r="G547" s="1"/>
       <c r="H547" s="8"/>
@@ -14523,14 +14515,14 @@
         <v>128</v>
       </c>
       <c r="D548" s="4">
-        <v>68.6313388387928</v>
+        <v>69.138666552608598</v>
       </c>
       <c r="E548" s="6">
         <v>20</v>
       </c>
       <c r="F548" s="3">
         <f t="shared" si="14"/>
-        <v>54.905071071034243</v>
+        <v>55.310933242086875</v>
       </c>
       <c r="G548" s="1"/>
       <c r="H548" s="8"/>
@@ -15115,7 +15107,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M32"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
@@ -15128,9 +15121,13 @@
     <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15161,8 +15158,20 @@
       <c r="M1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" hidden="1">
       <c r="A2" s="10" t="s">
         <v>22</v>
       </c>
@@ -15193,8 +15202,20 @@
       <c r="M2" s="4">
         <v>40.648450757575802</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="O2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>160</v>
+      </c>
+      <c r="R2" s="4">
+        <v>43.671285941644598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" hidden="1">
       <c r="A3" s="10" t="s">
         <v>22</v>
       </c>
@@ -15225,8 +15246,20 @@
       <c r="M3" s="4">
         <v>40.007166900922599</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="O3" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>168</v>
+      </c>
+      <c r="R3" s="4">
+        <v>43.6260912268948</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" hidden="1">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -15257,8 +15290,20 @@
       <c r="M4" s="4">
         <v>39.89</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="O4" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>152</v>
+      </c>
+      <c r="R4" s="4">
+        <v>43.029939393939401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" hidden="1">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -15289,8 +15334,20 @@
       <c r="M5" s="4">
         <v>39.706873977358804</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="O5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>160</v>
+      </c>
+      <c r="R5" s="4">
+        <v>41.528098620215999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" hidden="1">
       <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
@@ -15321,8 +15378,20 @@
       <c r="M6" s="4">
         <v>39.574879706933302</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="O6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>168</v>
+      </c>
+      <c r="R6" s="4">
+        <v>40.696204348405999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" hidden="1">
       <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
@@ -15353,8 +15422,20 @@
       <c r="M7" s="4">
         <v>39.5605422469636</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="O7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>152</v>
+      </c>
+      <c r="R7" s="4">
+        <v>40.663364801600402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" hidden="1">
       <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
@@ -15385,8 +15466,20 @@
       <c r="M8" s="4">
         <v>39.402819691644602</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="O8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>176</v>
+      </c>
+      <c r="R8" s="4">
+        <v>40.169399737639203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
@@ -15417,8 +15510,20 @@
       <c r="M9" s="4">
         <v>37.007300588709697</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="O9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>168</v>
+      </c>
+      <c r="R9" s="4">
+        <v>37.711496758482298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
@@ -15449,8 +15554,20 @@
       <c r="M10" s="4">
         <v>36.348020198538897</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="O10" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>160</v>
+      </c>
+      <c r="R10" s="4">
+        <v>37.256393326648798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="10" t="s">
         <v>27</v>
       </c>
@@ -15481,8 +15598,20 @@
       <c r="M11" s="4">
         <v>36.226309910409803</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="O11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>184</v>
+      </c>
+      <c r="R11" s="4">
+        <v>36.845269002736401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
@@ -15513,8 +15642,20 @@
       <c r="M12" s="4">
         <v>36.1098</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="O12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>152</v>
+      </c>
+      <c r="R12" s="4">
+        <v>36.625466666666703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
@@ -15545,8 +15686,20 @@
       <c r="M13" s="4">
         <v>35.773359665551801</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="O13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="P13" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>168</v>
+      </c>
+      <c r="R13" s="4">
+        <v>35.995552894314798</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="10" t="s">
         <v>31</v>
       </c>
@@ -15577,8 +15730,20 @@
       <c r="M14" s="4">
         <v>30.7104456946625</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="O14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>168</v>
+      </c>
+      <c r="R14" s="4">
+        <v>34.831495886912798</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="10" t="s">
         <v>31</v>
       </c>
@@ -15609,8 +15774,20 @@
       <c r="M15" s="4">
         <v>30.4661878232207</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="O15" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="P15" s="11">
+        <v>46081</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>160</v>
+      </c>
+      <c r="R15" s="4">
+        <v>32.761814131069102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="10" t="s">
         <v>31</v>
       </c>
@@ -15947,7 +16124,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="J1:M15"/>
+  <autoFilter ref="O1:R15">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="lessThan" val="38"/>
+      </customFilters>
+    </filterColumn>
+    <sortState ref="O2:R15">
+      <sortCondition descending="1" ref="R1:R15"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -12850,14 +12850,14 @@
         <v>167</v>
       </c>
       <c r="D481" s="12">
-        <v>31.758050607287402</v>
+        <v>31.3491842105263</v>
       </c>
       <c r="E481" s="13">
         <v>20</v>
       </c>
       <c r="F481" s="14">
         <f t="shared" si="12"/>
-        <v>25.406440485829922</v>
+        <v>25.07934736842104</v>
       </c>
       <c r="G481" s="15" t="s">
         <v>67</v>
@@ -12877,14 +12877,14 @@
         <v>136</v>
       </c>
       <c r="D482" s="4">
-        <v>67.769929179566603</v>
+        <v>71.954269076670897</v>
       </c>
       <c r="E482" s="6">
         <v>20</v>
       </c>
       <c r="F482" s="3">
         <f t="shared" si="12"/>
-        <v>54.215943343653279</v>
+        <v>57.563415261336715</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>67</v>
@@ -12904,14 +12904,14 @@
         <v>48</v>
       </c>
       <c r="D483" s="4">
-        <v>77.448395890926804</v>
+        <v>80.216951470848898</v>
       </c>
       <c r="E483" s="6">
         <v>20</v>
       </c>
       <c r="F483" s="3">
         <f t="shared" si="12"/>
-        <v>61.958716712741442</v>
+        <v>64.173561176679115</v>
       </c>
       <c r="G483" s="1"/>
       <c r="H483" s="8"/>
@@ -12927,14 +12927,14 @@
         <v>160</v>
       </c>
       <c r="D484" s="4">
-        <v>23.688493921286501</v>
+        <v>23.6477270862697</v>
       </c>
       <c r="E484" s="6">
         <v>20</v>
       </c>
       <c r="F484" s="3">
         <f t="shared" si="12"/>
-        <v>18.9507951370292</v>
+        <v>18.918181669015759</v>
       </c>
       <c r="G484" s="1"/>
       <c r="H484" s="8" t="s">
@@ -12952,14 +12952,14 @@
         <v>128</v>
       </c>
       <c r="D485" s="4">
-        <v>82.368766596889898</v>
+        <v>90.256759195574205</v>
       </c>
       <c r="E485" s="6">
         <v>20</v>
       </c>
       <c r="F485" s="3">
         <f t="shared" si="12"/>
-        <v>65.895013277511922</v>
+        <v>72.205407356459361</v>
       </c>
       <c r="G485" s="1"/>
       <c r="H485" s="8" t="s">
@@ -12977,14 +12977,14 @@
         <v>144</v>
       </c>
       <c r="D486" s="4">
-        <v>38.227440631091604</v>
+        <v>39.772975581749499</v>
       </c>
       <c r="E486" s="6">
         <v>20</v>
       </c>
       <c r="F486" s="3">
         <f t="shared" si="12"/>
-        <v>30.581952504873282</v>
+        <v>31.818380465399599</v>
       </c>
       <c r="G486" s="1"/>
       <c r="H486" s="8" t="s">
@@ -13002,14 +13002,14 @@
         <v>120</v>
       </c>
       <c r="D487" s="4">
-        <v>44.932774561791597</v>
+        <v>45.051787719686402</v>
       </c>
       <c r="E487" s="6">
         <v>20</v>
       </c>
       <c r="F487" s="3">
         <f t="shared" si="12"/>
-        <v>35.946219649433274</v>
+        <v>36.04143017574912</v>
       </c>
       <c r="G487" s="1"/>
       <c r="H487" s="8" t="s">
@@ -13100,14 +13100,14 @@
         <v>112</v>
       </c>
       <c r="D491" s="4">
-        <v>100.50772067099599</v>
+        <v>99.899850432900394</v>
       </c>
       <c r="E491" s="6">
         <v>20</v>
       </c>
       <c r="F491" s="3">
         <f t="shared" si="12"/>
-        <v>80.406176536796792</v>
+        <v>79.919880346320312</v>
       </c>
       <c r="G491" s="1"/>
       <c r="H491" s="8" t="s">
@@ -13125,14 +13125,14 @@
         <v>140</v>
       </c>
       <c r="D492" s="4">
-        <v>97.799361265284404</v>
+        <v>97.666100555175802</v>
       </c>
       <c r="E492" s="6">
         <v>20</v>
       </c>
       <c r="F492" s="3">
         <f t="shared" si="12"/>
-        <v>78.239489012227523</v>
+        <v>78.132880444140639</v>
       </c>
       <c r="G492" s="1"/>
       <c r="H492" s="8" t="s">
@@ -13150,14 +13150,14 @@
         <v>121</v>
       </c>
       <c r="D493" s="4">
-        <v>40.521285967283802</v>
+        <v>40.427509842398599</v>
       </c>
       <c r="E493" s="6">
         <v>20</v>
       </c>
       <c r="F493" s="3">
         <f t="shared" si="12"/>
-        <v>32.417028773827042</v>
+        <v>32.342007873918881</v>
       </c>
       <c r="G493" s="1"/>
       <c r="H493" s="8" t="s">
@@ -13175,14 +13175,14 @@
         <v>140</v>
       </c>
       <c r="D494" s="4">
-        <v>38.343387149122798</v>
+        <v>39.886891223370903</v>
       </c>
       <c r="E494" s="6">
         <v>20</v>
       </c>
       <c r="F494" s="3">
         <f t="shared" si="12"/>
-        <v>30.674709719298239</v>
+        <v>31.909512978696721</v>
       </c>
       <c r="G494" s="1"/>
       <c r="H494" s="8" t="s">
@@ -13200,14 +13200,14 @@
         <v>144</v>
       </c>
       <c r="D495" s="4">
-        <v>80.170156825041602</v>
+        <v>87.682530728550404</v>
       </c>
       <c r="E495" s="6">
         <v>20</v>
       </c>
       <c r="F495" s="3">
         <f t="shared" si="12"/>
-        <v>64.136125460033284</v>
+        <v>70.146024582840326</v>
       </c>
       <c r="G495" s="1"/>
       <c r="H495" s="8"/>
@@ -13248,14 +13248,14 @@
         <v>184</v>
       </c>
       <c r="D497" s="4">
-        <v>36.845269002736401</v>
+        <v>36.887702113104297</v>
       </c>
       <c r="E497" s="6">
         <v>20</v>
       </c>
       <c r="F497" s="3">
         <f t="shared" si="12"/>
-        <v>29.47621520218912</v>
+        <v>29.510161690483436</v>
       </c>
       <c r="G497" s="1"/>
       <c r="H497" s="8" t="s">
@@ -13273,14 +13273,14 @@
         <v>167</v>
       </c>
       <c r="D498" s="4">
-        <v>31.758050607287402</v>
+        <v>31.3491842105263</v>
       </c>
       <c r="E498" s="6">
         <v>20</v>
       </c>
       <c r="F498" s="3">
         <f t="shared" si="12"/>
-        <v>25.406440485829922</v>
+        <v>25.07934736842104</v>
       </c>
       <c r="G498" s="1"/>
       <c r="H498" s="8" t="s">
@@ -13298,14 +13298,14 @@
         <v>168</v>
       </c>
       <c r="D499" s="4">
-        <v>37.711496758482298</v>
+        <v>37.678140057711801</v>
       </c>
       <c r="E499" s="6">
         <v>20</v>
       </c>
       <c r="F499" s="3">
         <f t="shared" si="12"/>
-        <v>30.169197406785838</v>
+        <v>30.14251204616944</v>
       </c>
       <c r="G499" s="1"/>
       <c r="H499" s="8" t="s">
@@ -13373,14 +13373,14 @@
         <v>149</v>
       </c>
       <c r="D502" s="4">
-        <v>32.487203262540099</v>
+        <v>31.9747637453343</v>
       </c>
       <c r="E502" s="6">
         <v>20</v>
       </c>
       <c r="F502" s="3">
         <f t="shared" si="12"/>
-        <v>25.989762610032081</v>
+        <v>25.57981099626744</v>
       </c>
       <c r="G502" s="1"/>
       <c r="H502" s="8" t="s">
@@ -13395,17 +13395,17 @@
         <v>46081</v>
       </c>
       <c r="C503" s="9">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D503" s="4">
-        <v>40.408411395365299</v>
+        <v>40.028527809117101</v>
       </c>
       <c r="E503" s="6">
         <v>20</v>
       </c>
       <c r="F503" s="3">
         <f t="shared" si="12"/>
-        <v>32.326729116292242</v>
+        <v>32.022822247293682</v>
       </c>
       <c r="G503" s="1"/>
       <c r="H503" s="8" t="s">
@@ -13448,14 +13448,14 @@
         <v>128</v>
       </c>
       <c r="D505" s="4">
-        <v>105.95314185606099</v>
+        <v>104.889368939394</v>
       </c>
       <c r="E505" s="6">
         <v>20</v>
       </c>
       <c r="F505" s="3">
         <f t="shared" si="12"/>
-        <v>84.762513484848796</v>
+        <v>83.911495151515197</v>
       </c>
       <c r="G505" s="1"/>
       <c r="H505" s="8" t="s">
@@ -13470,17 +13470,17 @@
         <v>46081</v>
       </c>
       <c r="C506" s="9">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D506" s="4">
-        <v>43.912687499999997</v>
+        <v>32.4255541666667</v>
       </c>
       <c r="E506" s="6">
         <v>20</v>
       </c>
       <c r="F506" s="3">
         <f t="shared" si="12"/>
-        <v>35.13015</v>
+        <v>25.940443333333359</v>
       </c>
       <c r="G506" s="1"/>
       <c r="H506" s="8" t="s">
@@ -13523,14 +13523,14 @@
         <v>70</v>
       </c>
       <c r="D508" s="4">
-        <v>29.536541442465602</v>
+        <v>28.916106808134401</v>
       </c>
       <c r="E508" s="6">
         <v>20</v>
       </c>
       <c r="F508" s="3">
         <f t="shared" si="12"/>
-        <v>23.629233153972482</v>
+        <v>23.132885446507522</v>
       </c>
       <c r="G508" s="1"/>
       <c r="H508" s="8" t="s">
@@ -13573,14 +13573,14 @@
         <v>120</v>
       </c>
       <c r="D510" s="4">
-        <v>206.99323991935501</v>
+        <v>207.46527619386501</v>
       </c>
       <c r="E510" s="6">
         <v>20</v>
       </c>
       <c r="F510" s="3">
         <f t="shared" si="12"/>
-        <v>165.594591935484</v>
+        <v>165.97222095509201</v>
       </c>
       <c r="G510" s="1"/>
       <c r="H510" s="8" t="s">
@@ -13598,14 +13598,14 @@
         <v>160</v>
       </c>
       <c r="D511" s="4">
-        <v>41.528098620215999</v>
+        <v>41.493074084406999</v>
       </c>
       <c r="E511" s="6">
         <v>20</v>
       </c>
       <c r="F511" s="3">
         <f t="shared" si="12"/>
-        <v>33.222478896172802</v>
+        <v>33.194459267525602</v>
       </c>
       <c r="G511" s="1"/>
       <c r="H511" s="8" t="s">
@@ -13623,14 +13623,14 @@
         <v>178</v>
       </c>
       <c r="D512" s="4">
-        <v>32.524718832891203</v>
+        <v>31.824228116710898</v>
       </c>
       <c r="E512" s="6">
         <v>20</v>
       </c>
       <c r="F512" s="3">
         <f t="shared" si="12"/>
-        <v>26.019775066312963</v>
+        <v>25.459382493368718</v>
       </c>
       <c r="G512" s="1"/>
       <c r="H512" s="8" t="s">
@@ -13648,14 +13648,14 @@
         <v>136</v>
       </c>
       <c r="D513" s="4">
-        <v>69.884268986467802</v>
+        <v>69.665418496271698</v>
       </c>
       <c r="E513" s="6">
         <v>20</v>
       </c>
       <c r="F513" s="3">
         <f t="shared" si="12"/>
-        <v>55.907415189174245</v>
+        <v>55.732334797017359</v>
       </c>
       <c r="G513" s="1"/>
       <c r="H513" s="8" t="s">
@@ -13673,14 +13673,14 @@
         <v>168</v>
       </c>
       <c r="D514" s="4">
-        <v>34.831495886912798</v>
+        <v>34.338768184720799</v>
       </c>
       <c r="E514" s="6">
         <v>20</v>
       </c>
       <c r="F514" s="3">
         <f t="shared" si="12"/>
-        <v>27.865196709530238</v>
+        <v>27.47101454777664</v>
       </c>
       <c r="G514" s="1"/>
       <c r="H514" s="8" t="s">
@@ -13723,14 +13723,14 @@
         <v>160</v>
       </c>
       <c r="D516" s="4">
-        <v>46.516124596774198</v>
+        <v>46.870151802656601</v>
       </c>
       <c r="E516" s="6">
         <v>20</v>
       </c>
       <c r="F516" s="3">
         <f t="shared" si="12"/>
-        <v>37.212899677419358</v>
+        <v>37.496121442125279</v>
       </c>
       <c r="G516" s="1"/>
       <c r="H516" s="8" t="s">
@@ -13748,14 +13748,14 @@
         <v>120</v>
       </c>
       <c r="D517" s="4">
-        <v>106.800207373737</v>
+        <v>105.665516262626</v>
       </c>
       <c r="E517" s="6">
         <v>20</v>
       </c>
       <c r="F517" s="3">
         <f t="shared" si="12"/>
-        <v>85.440165898989591</v>
+        <v>84.532413010100797</v>
       </c>
       <c r="G517" s="1"/>
       <c r="H517" s="8" t="s">
@@ -13798,14 +13798,14 @@
         <v>152</v>
       </c>
       <c r="D519" s="4">
-        <v>41.651433670587402</v>
+        <v>40.868096342952597</v>
       </c>
       <c r="E519" s="6">
         <v>20</v>
       </c>
       <c r="F519" s="3">
         <f t="shared" si="12"/>
-        <v>33.321146936469923</v>
+        <v>32.694477074362077</v>
       </c>
       <c r="G519" s="1"/>
       <c r="H519" s="8" t="s">
@@ -13823,14 +13823,14 @@
         <v>160</v>
       </c>
       <c r="D520" s="4">
-        <v>43.671285941644598</v>
+        <v>43.636261405835597</v>
       </c>
       <c r="E520" s="6">
         <v>20</v>
       </c>
       <c r="F520" s="3">
         <f t="shared" si="12"/>
-        <v>34.93702875331568</v>
+        <v>34.909009124668479</v>
       </c>
       <c r="G520" s="1"/>
       <c r="H520" s="8" t="s">
@@ -13873,14 +13873,14 @@
         <v>40</v>
       </c>
       <c r="D522" s="4">
-        <v>91.662441735778799</v>
+        <v>94.984708431685306</v>
       </c>
       <c r="E522" s="6">
         <v>20</v>
       </c>
       <c r="F522" s="3">
         <f t="shared" si="12"/>
-        <v>73.329953388623039</v>
+        <v>75.987766745348239</v>
       </c>
       <c r="G522" s="1"/>
       <c r="H522" s="8" t="s">
@@ -13898,14 +13898,14 @@
         <v>160</v>
       </c>
       <c r="D523" s="4">
-        <v>32.365782451923103</v>
+        <v>31.4030027083333</v>
       </c>
       <c r="E523" s="6">
         <v>20</v>
       </c>
       <c r="F523" s="3">
         <f t="shared" si="12"/>
-        <v>25.892625961538482</v>
+        <v>25.122402166666639</v>
       </c>
       <c r="G523" s="1"/>
       <c r="H523" s="8" t="s">
@@ -13920,17 +13920,17 @@
         <v>46081</v>
       </c>
       <c r="C524" s="9">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D524" s="4">
-        <v>70.907206896551699</v>
+        <v>66.332548387096693</v>
       </c>
       <c r="E524" s="6">
         <v>20</v>
       </c>
       <c r="F524" s="3">
         <f t="shared" si="12"/>
-        <v>56.725765517241356</v>
+        <v>53.066038709677358</v>
       </c>
       <c r="G524" s="1"/>
       <c r="H524" s="8" t="s">
@@ -13948,14 +13948,14 @@
         <v>88</v>
       </c>
       <c r="D525" s="4">
-        <v>78.270441314554006</v>
+        <v>77.932217829705493</v>
       </c>
       <c r="E525" s="6">
         <v>20</v>
       </c>
       <c r="F525" s="3">
         <f t="shared" si="12"/>
-        <v>62.616353051643202</v>
+        <v>62.345774263764397</v>
       </c>
       <c r="G525" s="1"/>
       <c r="H525" s="8" t="s">
@@ -13973,14 +13973,14 @@
         <v>128</v>
       </c>
       <c r="D526" s="4">
-        <v>70.845184565727706</v>
+        <v>70.612655919894394</v>
       </c>
       <c r="E526" s="6">
         <v>20</v>
       </c>
       <c r="F526" s="3">
         <f t="shared" si="12"/>
-        <v>56.676147652582166</v>
+        <v>56.490124735915515</v>
       </c>
       <c r="G526" s="1"/>
       <c r="H526" s="8" t="s">
@@ -13995,17 +13995,17 @@
         <v>46081</v>
       </c>
       <c r="C527" s="9">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D527" s="4">
-        <v>44.458025678021698</v>
+        <v>36.323564242534303</v>
       </c>
       <c r="E527" s="6">
         <v>20</v>
       </c>
       <c r="F527" s="3">
         <f t="shared" si="12"/>
-        <v>35.566420542417362</v>
+        <v>29.058851394027442</v>
       </c>
       <c r="G527" s="1"/>
       <c r="H527" s="8" t="s">
@@ -14020,17 +14020,17 @@
         <v>46081</v>
       </c>
       <c r="C528" s="9">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D528" s="4">
-        <v>33.285641891891899</v>
+        <v>30.628343023255798</v>
       </c>
       <c r="E528" s="6">
         <v>20</v>
       </c>
       <c r="F528" s="3">
         <f t="shared" si="12"/>
-        <v>26.628513513513518</v>
+        <v>24.502674418604638</v>
       </c>
       <c r="G528" s="1"/>
       <c r="H528" s="8" t="s">
@@ -14045,17 +14045,17 @@
         <v>46081</v>
       </c>
       <c r="C529" s="9">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D529" s="4">
-        <v>44.196049847671297</v>
+        <v>36.230015976961802</v>
       </c>
       <c r="E529" s="6">
         <v>20</v>
       </c>
       <c r="F529" s="3">
         <f t="shared" si="12"/>
-        <v>35.356839878137038</v>
+        <v>28.98401278156944</v>
       </c>
       <c r="G529" s="1"/>
       <c r="H529" s="8" t="s">
@@ -14070,17 +14070,17 @@
         <v>46081</v>
       </c>
       <c r="C530" s="9">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D530" s="4">
-        <v>39.587576458036999</v>
+        <v>34.4800436046512</v>
       </c>
       <c r="E530" s="6">
         <v>20</v>
       </c>
       <c r="F530" s="3">
         <f t="shared" si="12"/>
-        <v>31.670061166429598</v>
+        <v>27.58403488372096</v>
       </c>
       <c r="G530" s="1"/>
       <c r="H530" s="8" t="s">
@@ -14098,14 +14098,14 @@
         <v>160</v>
       </c>
       <c r="D531" s="4">
-        <v>37.256393326648798</v>
+        <v>37.286601659982203</v>
       </c>
       <c r="E531" s="6">
         <v>20</v>
       </c>
       <c r="F531" s="3">
         <f t="shared" si="12"/>
-        <v>29.805114661319038</v>
+        <v>29.829281327985761</v>
       </c>
       <c r="G531" s="1"/>
       <c r="H531" s="8" t="s">
@@ -14120,17 +14120,17 @@
         <v>46081</v>
       </c>
       <c r="C532" s="9">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D532" s="4">
-        <v>43.229188793103397</v>
+        <v>36.0253846326165</v>
       </c>
       <c r="E532" s="6">
         <v>20</v>
       </c>
       <c r="F532" s="3">
         <f t="shared" si="12"/>
-        <v>34.583351034482718</v>
+        <v>28.8203077060932</v>
       </c>
       <c r="G532" s="1"/>
       <c r="H532" s="8" t="s">
@@ -14145,17 +14145,17 @@
         <v>46081</v>
       </c>
       <c r="C533" s="9">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D533" s="4">
-        <v>35.995552894314798</v>
+        <v>36.020594779071999</v>
       </c>
       <c r="E533" s="6">
         <v>20</v>
       </c>
       <c r="F533" s="3">
         <f t="shared" si="12"/>
-        <v>28.796442315451838</v>
+        <v>28.816475823257598</v>
       </c>
       <c r="G533" s="1"/>
       <c r="H533" s="8" t="s">
@@ -14170,17 +14170,17 @@
         <v>46081</v>
       </c>
       <c r="C534" s="9">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D534" s="4">
-        <v>41.252187499999998</v>
+        <v>34.242610294117597</v>
       </c>
       <c r="E534" s="6">
         <v>20</v>
       </c>
       <c r="F534" s="3">
         <f t="shared" si="12"/>
-        <v>33.001750000000001</v>
+        <v>27.394088235294078</v>
       </c>
       <c r="G534" s="1"/>
       <c r="H534" s="8" t="s">
@@ -14195,17 +14195,17 @@
         <v>46081</v>
       </c>
       <c r="C535" s="9">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="D535" s="4">
-        <v>40.496842633928601</v>
+        <v>33.050941807209</v>
       </c>
       <c r="E535" s="6">
         <v>20</v>
       </c>
       <c r="F535" s="3">
         <f t="shared" si="12"/>
-        <v>32.397474107142884</v>
+        <v>26.4407534457672</v>
       </c>
       <c r="G535" s="1"/>
       <c r="H535" s="8" t="s">
@@ -14223,14 +14223,14 @@
         <v>80</v>
       </c>
       <c r="D536" s="4">
-        <v>274.81869999999998</v>
+        <v>276.27365406249999</v>
       </c>
       <c r="E536" s="6">
         <v>20</v>
       </c>
       <c r="F536" s="3">
         <f t="shared" si="12"/>
-        <v>219.85495999999998</v>
+        <v>221.01892325</v>
       </c>
       <c r="G536" s="1"/>
       <c r="H536" s="8" t="s">
@@ -14248,14 +14248,14 @@
         <v>123</v>
       </c>
       <c r="D537" s="4">
-        <v>40.474735463750797</v>
+        <v>40.382484153904301</v>
       </c>
       <c r="E537" s="6">
         <v>20</v>
       </c>
       <c r="F537" s="3">
         <f t="shared" ref="F537:F549" si="14">D537-(D537*E537)/100</f>
-        <v>32.379788371000636</v>
+        <v>32.305987323123439</v>
       </c>
       <c r="G537" s="1"/>
       <c r="H537" s="8" t="s">
@@ -14273,14 +14273,14 @@
         <v>120</v>
       </c>
       <c r="D538" s="4">
-        <v>65.654417763157895</v>
+        <v>67.439615131579004</v>
       </c>
       <c r="E538" s="6">
         <v>20</v>
       </c>
       <c r="F538" s="3">
         <f t="shared" si="14"/>
-        <v>52.523534210526314</v>
+        <v>53.951692105263206</v>
       </c>
       <c r="G538" s="1"/>
       <c r="H538" s="8" t="s">
@@ -14298,14 +14298,14 @@
         <v>144</v>
       </c>
       <c r="D539" s="4">
-        <v>65.654417763157895</v>
+        <v>67.439615131579004</v>
       </c>
       <c r="E539" s="6">
         <v>20</v>
       </c>
       <c r="F539" s="3">
         <f t="shared" si="14"/>
-        <v>52.523534210526314</v>
+        <v>53.951692105263206</v>
       </c>
       <c r="G539" s="1"/>
       <c r="H539" s="8" t="s">
@@ -14323,14 +14323,14 @@
         <v>176</v>
       </c>
       <c r="D540" s="4">
-        <v>40.169399737639203</v>
+        <v>40.0486134254284</v>
       </c>
       <c r="E540" s="6">
         <v>20</v>
       </c>
       <c r="F540" s="3">
         <f t="shared" si="14"/>
-        <v>32.13551979011136</v>
+        <v>32.038890740342723</v>
       </c>
       <c r="G540" s="1"/>
       <c r="H540" s="8" t="s">
@@ -14348,14 +14348,14 @@
         <v>36</v>
       </c>
       <c r="D541" s="4">
-        <v>62.307746536987899</v>
+        <v>65.376822731922104</v>
       </c>
       <c r="E541" s="6">
         <v>20</v>
       </c>
       <c r="F541" s="3">
         <f t="shared" si="14"/>
-        <v>49.846197229590317</v>
+        <v>52.301458185537683</v>
       </c>
       <c r="G541" s="1"/>
       <c r="H541" s="8" t="s">
@@ -14373,14 +14373,14 @@
         <v>8</v>
       </c>
       <c r="D542" s="4">
-        <v>110.188469444444</v>
+        <v>108.770105555556</v>
       </c>
       <c r="E542" s="6">
         <v>20</v>
       </c>
       <c r="F542" s="3">
         <f t="shared" si="14"/>
-        <v>88.1507755555552</v>
+        <v>87.0160844444448</v>
       </c>
       <c r="G542" s="1"/>
       <c r="H542" s="8" t="s">
@@ -14446,14 +14446,14 @@
         <v>149</v>
       </c>
       <c r="D545" s="4">
-        <v>41.718082449212503</v>
+        <v>40.979165871381603</v>
       </c>
       <c r="E545" s="6">
         <v>20</v>
       </c>
       <c r="F545" s="3">
         <f t="shared" si="14"/>
-        <v>33.374465959369999</v>
+        <v>32.78333269710528</v>
       </c>
       <c r="G545" s="1"/>
       <c r="H545" s="8"/>
@@ -14466,17 +14466,17 @@
         <v>46081</v>
       </c>
       <c r="C546" s="9">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D546" s="4">
-        <v>61.779495130120402</v>
+        <v>56.556982198955701</v>
       </c>
       <c r="E546" s="6">
         <v>20</v>
       </c>
       <c r="F546" s="3">
         <f t="shared" si="14"/>
-        <v>49.423596104096319</v>
+        <v>45.245585759164562</v>
       </c>
       <c r="G546" s="1"/>
       <c r="H546" s="8"/>
@@ -14489,17 +14489,17 @@
         <v>46081</v>
       </c>
       <c r="C547" s="9">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D547" s="4">
-        <v>38.043402102429503</v>
+        <v>36.750679158383001</v>
       </c>
       <c r="E547" s="6">
         <v>20</v>
       </c>
       <c r="F547" s="3">
         <f t="shared" si="14"/>
-        <v>30.434721681943603</v>
+        <v>29.400543326706401</v>
       </c>
       <c r="G547" s="1"/>
       <c r="H547" s="8"/>
@@ -14515,14 +14515,14 @@
         <v>128</v>
       </c>
       <c r="D548" s="4">
-        <v>69.138666552608598</v>
+        <v>72.673905528778505</v>
       </c>
       <c r="E548" s="6">
         <v>20</v>
       </c>
       <c r="F548" s="3">
         <f t="shared" si="14"/>
-        <v>55.310933242086875</v>
+        <v>58.139124423022807</v>
       </c>
       <c r="G548" s="1"/>
       <c r="H548" s="8"/>
@@ -14584,20 +14584,22 @@
         <v>16</v>
       </c>
       <c r="D551" s="4">
-        <v>110.188469444444</v>
+        <v>108.770105555556</v>
       </c>
       <c r="E551" s="6">
         <v>20</v>
       </c>
       <c r="F551" s="3">
         <f t="shared" si="15"/>
-        <v>88.1507755555552</v>
+        <v>87.0160844444448</v>
       </c>
       <c r="G551" s="1"/>
       <c r="H551" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G551"/>
+  <autoFilter ref="A1:G551">
+    <filterColumn colId="0"/>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="G74" r:id="rId1"/>
     <hyperlink ref="H74" r:id="rId2"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -9,17 +9,18 @@
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
+    <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$213</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Foglio2!$J$35:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Foglio3!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="142">
   <si>
     <t>Tecnico</t>
   </si>
@@ -424,30 +425,6 @@
   </si>
   <si>
     <t>IRTE0000005 - ALFONSO ROBERTO</t>
-  </si>
-  <si>
-    <t>Luglio</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Settembre</t>
-  </si>
-  <si>
-    <t>Ottobre</t>
-  </si>
-  <si>
-    <t>Produzione Reale</t>
-  </si>
-  <si>
-    <t>Sconto %</t>
-  </si>
-  <si>
-    <t>Avanzamento scontato</t>
-  </si>
-  <si>
-    <t>Mese</t>
   </si>
   <si>
     <t>IRTE0000026 - FISICHELLA CRISTIANO</t>
@@ -506,6 +483,7 @@
       <sz val="8.25"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -585,7 +563,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -593,7 +571,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
@@ -607,6 +584,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -616,7 +599,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6DDE8"/>
+          <fgColor rgb="FF92D050"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -911,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -948,29 +931,29 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>46053</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>120</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>34.926737804878101</v>
       </c>
-      <c r="E2" s="13">
-        <v>20</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="E2" s="12">
+        <v>20</v>
+      </c>
+      <c r="F2" s="13">
         <f t="shared" ref="F2:F62" si="0">D2-(D2*E2)/100</f>
         <v>27.941390243902482</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>90</v>
       </c>
     </row>
@@ -978,10 +961,10 @@
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>46053</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>87.5</v>
       </c>
       <c r="D3" s="4">
@@ -997,7 +980,7 @@
       <c r="G3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1005,10 +988,10 @@
       <c r="A4" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <v>46053</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>16</v>
       </c>
       <c r="D4" s="4">
@@ -1022,16 +1005,16 @@
         <v>34.66928771428568</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="8"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>46053</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>100</v>
       </c>
       <c r="D5" s="4">
@@ -1045,7 +1028,7 @@
         <v>18.029397030303038</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1053,10 +1036,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>46053</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>128</v>
       </c>
       <c r="D6" s="4">
@@ -1070,7 +1053,7 @@
         <v>54.250221646341437</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1078,10 +1061,10 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>46053</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>136</v>
       </c>
       <c r="D7" s="4">
@@ -1095,7 +1078,7 @@
         <v>20.636931111111117</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1103,10 +1086,10 @@
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>46053</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>109</v>
       </c>
       <c r="D8" s="4">
@@ -1120,18 +1103,18 @@
         <v>27.60334596107424</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>46053</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>160</v>
       </c>
       <c r="D9" s="4">
@@ -1145,7 +1128,7 @@
         <v>31.434164102564079</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1153,10 +1136,10 @@
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>46053</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>96</v>
       </c>
       <c r="D10" s="4">
@@ -1170,7 +1153,7 @@
         <v>28.612349999999999</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1178,10 +1161,10 @@
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>46053</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>104</v>
       </c>
       <c r="D11" s="4">
@@ -1195,7 +1178,7 @@
         <v>69.666304878048805</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1203,10 +1186,10 @@
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>46053</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>112</v>
       </c>
       <c r="D12" s="4">
@@ -1220,7 +1203,7 @@
         <v>78.151304268292719</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1228,10 +1211,10 @@
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>46053</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>126</v>
       </c>
       <c r="D13" s="4">
@@ -1245,7 +1228,7 @@
         <v>25.790538288648797</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1253,10 +1236,10 @@
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>46053</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>144</v>
       </c>
       <c r="D14" s="4">
@@ -1270,18 +1253,18 @@
         <v>20.636931111111117</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="11">
+        <v>135</v>
+      </c>
+      <c r="B15" s="10">
         <v>46053</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>112</v>
       </c>
       <c r="D15" s="4">
@@ -1295,16 +1278,16 @@
         <v>46.845031881533117</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>46053</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>136</v>
       </c>
       <c r="D16" s="4">
@@ -1318,18 +1301,18 @@
         <v>31.527523529411759</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>46053</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <v>152</v>
       </c>
       <c r="D17" s="4">
@@ -1343,7 +1326,7 @@
         <v>27.628707014309999</v>
       </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1351,10 +1334,10 @@
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>46053</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>120</v>
       </c>
       <c r="D18" s="4">
@@ -1368,18 +1351,18 @@
         <v>27.941390243902482</v>
       </c>
       <c r="G18" s="1"/>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>46053</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <v>160</v>
       </c>
       <c r="D19" s="4">
@@ -1393,18 +1376,18 @@
         <v>27.577174725806479</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="11">
+      <c r="A20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="10">
         <v>46053</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>152</v>
       </c>
       <c r="D20" s="4">
@@ -1418,18 +1401,18 @@
         <v>38.59292961514376</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>46053</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <v>144</v>
       </c>
       <c r="D21" s="4">
@@ -1443,18 +1426,18 @@
         <v>30.015444496065118</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>46053</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>135.5</v>
       </c>
       <c r="D22" s="4">
@@ -1468,7 +1451,7 @@
         <v>40.288149525054806</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1476,10 +1459,10 @@
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>46053</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <v>96</v>
       </c>
       <c r="D23" s="4">
@@ -1493,7 +1476,7 @@
         <v>28.60417487373736</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1501,10 +1484,10 @@
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>46053</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>109</v>
       </c>
       <c r="D24" s="4">
@@ -1518,18 +1501,18 @@
         <v>26.550464932078558</v>
       </c>
       <c r="G24" s="1"/>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>46053</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="8">
         <v>135</v>
       </c>
       <c r="D25" s="4">
@@ -1543,7 +1526,7 @@
         <v>44.629187257414323</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1551,10 +1534,10 @@
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>46053</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>96</v>
       </c>
       <c r="D26" s="4">
@@ -1568,18 +1551,18 @@
         <v>67.124386585365841</v>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>46053</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="8">
         <v>64</v>
       </c>
       <c r="D27" s="4">
@@ -1593,7 +1576,7 @@
         <v>42.688437499999999</v>
       </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1601,10 +1584,10 @@
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>46053</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>72</v>
       </c>
       <c r="D28" s="4">
@@ -1618,7 +1601,7 @@
         <v>17.894725000000001</v>
       </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1626,10 +1609,10 @@
       <c r="A29" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>46053</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>48</v>
       </c>
       <c r="D29" s="4">
@@ -1643,18 +1626,18 @@
         <v>36.139657575757596</v>
       </c>
       <c r="G29" s="1"/>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>46053</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>143</v>
       </c>
       <c r="D30" s="4">
@@ -1668,7 +1651,7 @@
         <v>44.683424399062957</v>
       </c>
       <c r="G30" s="1"/>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1676,10 +1659,10 @@
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>46053</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="8">
         <v>128</v>
       </c>
       <c r="D31" s="4">
@@ -1693,18 +1676,18 @@
         <v>42.648151110627204</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>46053</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>160</v>
       </c>
       <c r="D32" s="4">
@@ -1718,7 +1701,7 @@
         <v>27.6997775</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1726,10 +1709,10 @@
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>46053</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="8">
         <v>136</v>
       </c>
       <c r="D33" s="4">
@@ -1743,7 +1726,7 @@
         <v>35.448285561497357</v>
       </c>
       <c r="G33" s="1"/>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1751,10 +1734,10 @@
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>46053</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <v>128</v>
       </c>
       <c r="D34" s="4">
@@ -1768,18 +1751,18 @@
         <v>50.2044485947712</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>46053</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="8">
         <v>168</v>
       </c>
       <c r="D35" s="4">
@@ -1793,18 +1776,18 @@
         <v>22.139505714285761</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>46053</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>150</v>
       </c>
       <c r="D36" s="4">
@@ -1818,7 +1801,7 @@
         <v>44.659020926398725</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1826,10 +1809,10 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>46053</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="8">
         <v>128</v>
       </c>
       <c r="D37" s="4">
@@ -1843,7 +1826,7 @@
         <v>42.648151110627204</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1851,10 +1834,10 @@
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>46053</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="8">
         <v>112</v>
       </c>
       <c r="D38" s="4">
@@ -1868,7 +1851,7 @@
         <v>68.348273170731687</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="7" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1876,10 +1859,10 @@
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>46053</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="8">
         <v>108</v>
       </c>
       <c r="D39" s="4">
@@ -1893,7 +1876,7 @@
         <v>19.187217171717201</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1901,10 +1884,10 @@
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>46053</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <v>146</v>
       </c>
       <c r="D40" s="4">
@@ -1918,18 +1901,18 @@
         <v>24.386333333333361</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>46053</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="8">
         <v>156</v>
       </c>
       <c r="D41" s="4">
@@ -1943,18 +1926,18 @@
         <v>30.946064362859357</v>
       </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>46053</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <v>184</v>
       </c>
       <c r="D42" s="4">
@@ -1968,7 +1951,7 @@
         <v>30.804919002835522</v>
       </c>
       <c r="G42" s="1"/>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="7" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1976,10 +1959,10 @@
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>46053</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="8">
         <v>8</v>
       </c>
       <c r="D43" s="4">
@@ -1993,7 +1976,7 @@
         <v>22.848359663865519</v>
       </c>
       <c r="G43" s="1"/>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2001,10 +1984,10 @@
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>46053</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>104</v>
       </c>
       <c r="D44" s="4">
@@ -2018,18 +2001,18 @@
         <v>27.9653251766916</v>
       </c>
       <c r="G44" s="1"/>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>46053</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="8">
         <v>112</v>
       </c>
       <c r="D45" s="4">
@@ -2043,18 +2026,18 @@
         <v>27.767057142857119</v>
       </c>
       <c r="G45" s="1"/>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>46053</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>90</v>
       </c>
       <c r="D46" s="4">
@@ -2068,18 +2051,18 @@
         <v>54.856512941176483</v>
       </c>
       <c r="G46" s="1"/>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>46053</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="8">
         <v>130</v>
       </c>
       <c r="D47" s="4">
@@ -2093,18 +2076,18 @@
         <v>50.276018815485124</v>
       </c>
       <c r="G47" s="1"/>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>46053</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>112</v>
       </c>
       <c r="D48" s="4">
@@ -2118,18 +2101,18 @@
         <v>39.39060428571424</v>
       </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>46053</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>104</v>
       </c>
       <c r="D49" s="4">
@@ -2143,18 +2126,18 @@
         <v>29.845194493223921</v>
       </c>
       <c r="G49" s="1"/>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>46053</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>96</v>
       </c>
       <c r="D50" s="4">
@@ -2168,18 +2151,18 @@
         <v>41.828229807692324</v>
       </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>46053</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>112</v>
       </c>
       <c r="D51" s="4">
@@ -2193,18 +2176,18 @@
         <v>30.810339285714321</v>
       </c>
       <c r="G51" s="1"/>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>46053</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>176</v>
       </c>
       <c r="D52" s="4">
@@ -2218,18 +2201,18 @@
         <v>23.52151422890752</v>
       </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>46053</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="8">
         <v>64</v>
       </c>
       <c r="D53" s="4">
@@ -2243,18 +2226,18 @@
         <v>41.999125639850881</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="10">
         <v>46053</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="8">
         <v>152</v>
       </c>
       <c r="D54" s="4">
@@ -2268,18 +2251,18 @@
         <v>29.581480186095042</v>
       </c>
       <c r="G54" s="1"/>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>46053</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="8">
         <v>96</v>
       </c>
       <c r="D55" s="4">
@@ -2293,18 +2276,18 @@
         <v>34.443560000000005</v>
       </c>
       <c r="G55" s="1"/>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <v>46053</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>80</v>
       </c>
       <c r="D56" s="4">
@@ -2318,7 +2301,7 @@
         <v>40.32859321428576</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2326,10 +2309,10 @@
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>46053</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="8">
         <v>111.5</v>
       </c>
       <c r="D57" s="4">
@@ -2343,7 +2326,7 @@
         <v>25.249410491021681</v>
       </c>
       <c r="G57" s="1"/>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2351,10 +2334,10 @@
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="10">
         <v>46053</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="8">
         <v>128</v>
       </c>
       <c r="D58" s="4">
@@ -2368,7 +2351,7 @@
         <v>23.053807976628161</v>
       </c>
       <c r="G58" s="1"/>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2376,10 +2359,10 @@
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="10">
         <v>46053</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>128</v>
       </c>
       <c r="D59" s="4">
@@ -2393,7 +2376,7 @@
         <v>34.789034375</v>
       </c>
       <c r="G59" s="1"/>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2401,10 +2384,10 @@
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="10">
         <v>46053</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>128</v>
       </c>
       <c r="D60" s="4">
@@ -2418,18 +2401,18 @@
         <v>34.789034375</v>
       </c>
       <c r="G60" s="1"/>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>46053</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="8">
         <v>176</v>
       </c>
       <c r="D61" s="4">
@@ -2443,7 +2426,7 @@
         <v>30.008334452214477</v>
       </c>
       <c r="G61" s="1"/>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="7" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2451,10 +2434,10 @@
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="10">
         <v>46053</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="8">
         <v>64</v>
       </c>
       <c r="D62" s="4">
@@ -2468,7 +2451,7 @@
         <v>34.411233714285679</v>
       </c>
       <c r="G62" s="1"/>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="7" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2476,10 +2459,10 @@
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="10">
         <v>46053</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="8">
         <v>32</v>
       </c>
       <c r="D63" s="4">
@@ -2493,18 +2476,18 @@
         <v>57.585238086698077</v>
       </c>
       <c r="G63" s="1"/>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="10">
         <v>46053</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="8">
         <v>176</v>
       </c>
       <c r="D64" s="4">
@@ -2518,18 +2501,18 @@
         <v>31.762361343873522</v>
       </c>
       <c r="G64" s="1"/>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>46053</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="8">
         <v>144</v>
       </c>
       <c r="D65" s="4">
@@ -2543,16 +2526,16 @@
         <v>56.872957671109283</v>
       </c>
       <c r="G65" s="1"/>
-      <c r="H65" s="8"/>
+      <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="10">
         <v>46053</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="8">
         <v>146</v>
       </c>
       <c r="D66" s="4">
@@ -2566,16 +2549,16 @@
         <v>24.386333333333361</v>
       </c>
       <c r="G66" s="1"/>
-      <c r="H66" s="8"/>
+      <c r="H66" s="7"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>46053</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="8">
         <v>104</v>
       </c>
       <c r="D67" s="4">
@@ -2589,16 +2572,16 @@
         <v>27.767057142857119</v>
       </c>
       <c r="G67" s="1"/>
-      <c r="H67" s="8"/>
+      <c r="H67" s="7"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="10">
         <v>46053</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>96</v>
       </c>
       <c r="D68" s="4">
@@ -2612,16 +2595,16 @@
         <v>35.556906445791519</v>
       </c>
       <c r="G68" s="1"/>
-      <c r="H68" s="8"/>
+      <c r="H68" s="7"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="11">
+        <v>137</v>
+      </c>
+      <c r="B69" s="10">
         <v>46053</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="8">
         <v>32</v>
       </c>
       <c r="D69" s="4">
@@ -2635,16 +2618,16 @@
         <v>70.796046341463438</v>
       </c>
       <c r="G69" s="1"/>
-      <c r="H69" s="8"/>
+      <c r="H69" s="7"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="11">
+        <v>136</v>
+      </c>
+      <c r="B70" s="10">
         <v>46053</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="8">
         <v>134</v>
       </c>
       <c r="D70" s="4">
@@ -2658,32 +2641,32 @@
         <v>45.636617278167357</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="8"/>
+      <c r="H70" s="7"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="10">
         <v>46081</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="8">
         <v>167</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="11">
         <v>31.3491842105263</v>
       </c>
-      <c r="E71" s="13">
-        <v>20</v>
-      </c>
-      <c r="F71" s="14">
+      <c r="E71" s="12">
+        <v>20</v>
+      </c>
+      <c r="F71" s="13">
         <f t="shared" si="1"/>
         <v>25.07934736842104</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="G71" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="15" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2691,10 +2674,10 @@
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="10">
         <v>46081</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="8">
         <v>136</v>
       </c>
       <c r="D72" s="4">
@@ -2710,7 +2693,7 @@
       <c r="G72" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="7" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2718,10 +2701,10 @@
       <c r="A73" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="10">
         <v>46081</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C73" s="8">
         <v>48</v>
       </c>
       <c r="D73" s="4">
@@ -2735,16 +2718,16 @@
         <v>64.173561176679115</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="8"/>
+      <c r="H73" s="7"/>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="10">
         <v>46081</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="8">
         <v>160</v>
       </c>
       <c r="D74" s="4">
@@ -2758,7 +2741,7 @@
         <v>18.918181669015759</v>
       </c>
       <c r="G74" s="1"/>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2766,10 +2749,10 @@
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="10">
         <v>46081</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="8">
         <v>128</v>
       </c>
       <c r="D75" s="4">
@@ -2783,7 +2766,7 @@
         <v>72.205407356459361</v>
       </c>
       <c r="G75" s="1"/>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2791,10 +2774,10 @@
       <c r="A76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="10">
         <v>46081</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="8">
         <v>144</v>
       </c>
       <c r="D76" s="4">
@@ -2808,7 +2791,7 @@
         <v>31.818380465399599</v>
       </c>
       <c r="G76" s="1"/>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2816,10 +2799,10 @@
       <c r="A77" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="10">
         <v>46081</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="8">
         <v>120</v>
       </c>
       <c r="D77" s="4">
@@ -2833,18 +2816,18 @@
         <v>36.04143017574912</v>
       </c>
       <c r="G77" s="1"/>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="10">
         <v>46081</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="8">
         <v>152</v>
       </c>
       <c r="D78" s="4">
@@ -2858,18 +2841,18 @@
         <v>32.530691841280323</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B79" s="11">
+      <c r="A79" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B79" s="10">
         <v>46081</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="8">
         <v>160</v>
       </c>
       <c r="D79" s="4">
@@ -2883,16 +2866,16 @@
         <v>26.209451304855282</v>
       </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="8"/>
+      <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="10">
         <v>46081</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <v>128</v>
       </c>
       <c r="D80" s="4">
@@ -2906,7 +2889,7 @@
         <v>35.396326666666639</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2914,10 +2897,10 @@
       <c r="A81" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>46081</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="8">
         <v>112</v>
       </c>
       <c r="D81" s="4">
@@ -2931,7 +2914,7 @@
         <v>79.919880346320312</v>
       </c>
       <c r="G81" s="1"/>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2939,10 +2922,10 @@
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="10">
         <v>46081</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>140</v>
       </c>
       <c r="D82" s="4">
@@ -2956,7 +2939,7 @@
         <v>78.132880444140639</v>
       </c>
       <c r="G82" s="1"/>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2964,10 +2947,10 @@
       <c r="A83" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="10">
         <v>46081</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="8">
         <v>121</v>
       </c>
       <c r="D83" s="4">
@@ -2981,7 +2964,7 @@
         <v>32.342007873918881</v>
       </c>
       <c r="G83" s="1"/>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="7" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2989,10 +2972,10 @@
       <c r="A84" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="10">
         <v>46081</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="8">
         <v>140</v>
       </c>
       <c r="D84" s="4">
@@ -3006,18 +2989,18 @@
         <v>31.909512978696721</v>
       </c>
       <c r="G84" s="1"/>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="11">
+        <v>135</v>
+      </c>
+      <c r="B85" s="10">
         <v>46081</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="8">
         <v>144</v>
       </c>
       <c r="D85" s="4">
@@ -3031,16 +3014,16 @@
         <v>70.146024582840326</v>
       </c>
       <c r="G85" s="1"/>
-      <c r="H85" s="8"/>
+      <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="17" t="s">
+      <c r="A86" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="10">
         <v>46081</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="8">
         <v>152</v>
       </c>
       <c r="D86" s="4">
@@ -3054,18 +3037,18 @@
         <v>29.300373333333361</v>
       </c>
       <c r="G86" s="1"/>
-      <c r="H86" s="8" t="s">
+      <c r="H86" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="10">
         <v>46081</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="8">
         <v>184</v>
       </c>
       <c r="D87" s="4">
@@ -3079,7 +3062,7 @@
         <v>29.510161690483436</v>
       </c>
       <c r="G87" s="1"/>
-      <c r="H87" s="8" t="s">
+      <c r="H87" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3087,10 +3070,10 @@
       <c r="A88" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="10">
         <v>46081</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <v>167</v>
       </c>
       <c r="D88" s="4">
@@ -3104,18 +3087,18 @@
         <v>25.07934736842104</v>
       </c>
       <c r="G88" s="1"/>
-      <c r="H88" s="8" t="s">
+      <c r="H88" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="10">
         <v>46081</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="8">
         <v>168</v>
       </c>
       <c r="D89" s="4">
@@ -3129,18 +3112,18 @@
         <v>30.14251204616944</v>
       </c>
       <c r="G89" s="1"/>
-      <c r="H89" s="8" t="s">
+      <c r="H89" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B90" s="11">
+      <c r="A90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="10">
         <v>46081</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <v>166</v>
       </c>
       <c r="D90" s="4">
@@ -3154,18 +3137,18 @@
         <v>47.311221505376317</v>
       </c>
       <c r="G90" s="1"/>
-      <c r="H90" s="8" t="s">
+      <c r="H90" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="10">
         <v>46081</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="8">
         <v>168</v>
       </c>
       <c r="D91" s="4">
@@ -3179,7 +3162,7 @@
         <v>32.556963478724796</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="7" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3187,10 +3170,10 @@
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B92" s="11">
+      <c r="B92" s="10">
         <v>46081</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="8">
         <v>149</v>
       </c>
       <c r="D92" s="4">
@@ -3204,7 +3187,7 @@
         <v>25.57981099626744</v>
       </c>
       <c r="G92" s="1"/>
-      <c r="H92" s="8" t="s">
+      <c r="H92" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3212,10 +3195,10 @@
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>46081</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="8">
         <v>168</v>
       </c>
       <c r="D93" s="4">
@@ -3229,18 +3212,18 @@
         <v>32.022822247293682</v>
       </c>
       <c r="G93" s="1"/>
-      <c r="H93" s="8" t="s">
+      <c r="H93" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="10">
         <v>46081</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="8">
         <v>149</v>
       </c>
       <c r="D94" s="4">
@@ -3254,7 +3237,7 @@
         <v>36.783462271112001</v>
       </c>
       <c r="G94" s="1"/>
-      <c r="H94" s="8" t="s">
+      <c r="H94" s="7" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3262,10 +3245,10 @@
       <c r="A95" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>46081</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="8">
         <v>128</v>
       </c>
       <c r="D95" s="4">
@@ -3279,18 +3262,18 @@
         <v>83.911495151515197</v>
       </c>
       <c r="G95" s="1"/>
-      <c r="H95" s="8" t="s">
+      <c r="H95" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="18" t="s">
+      <c r="A96" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B96" s="11">
+      <c r="B96" s="10">
         <v>46081</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="8">
         <v>120</v>
       </c>
       <c r="D96" s="4">
@@ -3304,7 +3287,7 @@
         <v>25.940443333333359</v>
       </c>
       <c r="G96" s="1"/>
-      <c r="H96" s="8" t="s">
+      <c r="H96" s="7" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3312,10 +3295,10 @@
       <c r="A97" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>46081</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="8">
         <v>119</v>
       </c>
       <c r="D97" s="4">
@@ -3329,7 +3312,7 @@
         <v>16.76475865633072</v>
       </c>
       <c r="G97" s="1"/>
-      <c r="H97" s="8" t="s">
+      <c r="H97" s="7" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3337,10 +3320,10 @@
       <c r="A98" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="10">
         <v>46081</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="8">
         <v>70</v>
       </c>
       <c r="D98" s="4">
@@ -3354,18 +3337,18 @@
         <v>23.132885446507522</v>
       </c>
       <c r="G98" s="1"/>
-      <c r="H98" s="8" t="s">
+      <c r="H98" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="10">
         <v>46081</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="8">
         <v>143</v>
       </c>
       <c r="D99" s="4">
@@ -3379,7 +3362,7 @@
         <v>33.655840707964558</v>
       </c>
       <c r="G99" s="1"/>
-      <c r="H99" s="8" t="s">
+      <c r="H99" s="7" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3387,10 +3370,10 @@
       <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="10">
         <v>46081</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="8">
         <v>120</v>
       </c>
       <c r="D100" s="4">
@@ -3404,18 +3387,18 @@
         <v>165.97222095509201</v>
       </c>
       <c r="G100" s="1"/>
-      <c r="H100" s="8" t="s">
+      <c r="H100" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="10">
         <v>46081</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="8">
         <v>160</v>
       </c>
       <c r="D101" s="4">
@@ -3429,7 +3412,7 @@
         <v>33.194459267525602</v>
       </c>
       <c r="G101" s="1"/>
-      <c r="H101" s="8" t="s">
+      <c r="H101" s="7" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3437,10 +3420,10 @@
       <c r="A102" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B102" s="11">
+      <c r="B102" s="10">
         <v>46081</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="8">
         <v>178</v>
       </c>
       <c r="D102" s="4">
@@ -3454,7 +3437,7 @@
         <v>25.459382493368718</v>
       </c>
       <c r="G102" s="1"/>
-      <c r="H102" s="8" t="s">
+      <c r="H102" s="7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3462,10 +3445,10 @@
       <c r="A103" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>46081</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="8">
         <v>136</v>
       </c>
       <c r="D103" s="4">
@@ -3479,18 +3462,18 @@
         <v>55.732334797017359</v>
       </c>
       <c r="G103" s="1"/>
-      <c r="H103" s="8" t="s">
+      <c r="H103" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="11">
+      <c r="B104" s="10">
         <v>46081</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <v>168</v>
       </c>
       <c r="D104" s="4">
@@ -3504,18 +3487,18 @@
         <v>27.47101454777664</v>
       </c>
       <c r="G104" s="1"/>
-      <c r="H104" s="8" t="s">
+      <c r="H104" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>46081</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="8">
         <v>152</v>
       </c>
       <c r="D105" s="4">
@@ -3529,7 +3512,7 @@
         <v>36.547653397575523</v>
       </c>
       <c r="G105" s="1"/>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="7" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3537,10 +3520,10 @@
       <c r="A106" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="11">
+      <c r="B106" s="10">
         <v>46081</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <v>160</v>
       </c>
       <c r="D106" s="4">
@@ -3554,7 +3537,7 @@
         <v>37.496121442125279</v>
       </c>
       <c r="G106" s="1"/>
-      <c r="H106" s="8" t="s">
+      <c r="H106" s="7" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3562,10 +3545,10 @@
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>46081</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107" s="8">
         <v>120</v>
       </c>
       <c r="D107" s="4">
@@ -3579,7 +3562,7 @@
         <v>84.532413010100797</v>
       </c>
       <c r="G107" s="1"/>
-      <c r="H107" s="8" t="s">
+      <c r="H107" s="7" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3587,10 +3570,10 @@
       <c r="A108" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B108" s="11">
+      <c r="B108" s="10">
         <v>46081</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <v>152</v>
       </c>
       <c r="D108" s="4">
@@ -3604,7 +3587,7 @@
         <v>18.190260342717281</v>
       </c>
       <c r="G108" s="1"/>
-      <c r="H108" s="8" t="s">
+      <c r="H108" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3612,10 +3595,10 @@
       <c r="A109" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="10">
         <v>46081</v>
       </c>
-      <c r="C109" s="9">
+      <c r="C109" s="8">
         <v>152</v>
       </c>
       <c r="D109" s="4">
@@ -3629,18 +3612,18 @@
         <v>32.694477074362077</v>
       </c>
       <c r="G109" s="1"/>
-      <c r="H109" s="8" t="s">
+      <c r="H109" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B110" s="11">
+      <c r="B110" s="10">
         <v>46081</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="8">
         <v>160</v>
       </c>
       <c r="D110" s="4">
@@ -3654,18 +3637,18 @@
         <v>34.909009124668479</v>
       </c>
       <c r="G110" s="1"/>
-      <c r="H110" s="8" t="s">
+      <c r="H110" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="17" t="s">
+      <c r="A111" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="10">
         <v>46081</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C111" s="8">
         <v>152</v>
       </c>
       <c r="D111" s="4">
@@ -3679,7 +3662,7 @@
         <v>34.423951515151522</v>
       </c>
       <c r="G111" s="1"/>
-      <c r="H111" s="8" t="s">
+      <c r="H111" s="7" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3687,10 +3670,10 @@
       <c r="A112" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B112" s="11">
+      <c r="B112" s="10">
         <v>46081</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="8">
         <v>40</v>
       </c>
       <c r="D112" s="4">
@@ -3704,7 +3687,7 @@
         <v>75.987766745348239</v>
       </c>
       <c r="G112" s="1"/>
-      <c r="H112" s="8" t="s">
+      <c r="H112" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3712,10 +3695,10 @@
       <c r="A113" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="10">
         <v>46081</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C113" s="8">
         <v>160</v>
       </c>
       <c r="D113" s="4">
@@ -3729,18 +3712,18 @@
         <v>25.122402166666639</v>
       </c>
       <c r="G113" s="1"/>
-      <c r="H113" s="8" t="s">
+      <c r="H113" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="18" t="s">
+      <c r="A114" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B114" s="11">
+      <c r="B114" s="10">
         <v>46081</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="8">
         <v>128</v>
       </c>
       <c r="D114" s="4">
@@ -3754,18 +3737,18 @@
         <v>53.066038709677358</v>
       </c>
       <c r="G114" s="1"/>
-      <c r="H114" s="8" t="s">
+      <c r="H114" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="10">
         <v>46081</v>
       </c>
-      <c r="C115" s="9">
+      <c r="C115" s="8">
         <v>88</v>
       </c>
       <c r="D115" s="4">
@@ -3779,18 +3762,18 @@
         <v>62.345774263764397</v>
       </c>
       <c r="G115" s="1"/>
-      <c r="H115" s="8" t="s">
+      <c r="H115" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="10">
         <v>46081</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="8">
         <v>128</v>
       </c>
       <c r="D116" s="4">
@@ -3804,18 +3787,18 @@
         <v>56.490124735915515</v>
       </c>
       <c r="G116" s="1"/>
-      <c r="H116" s="8" t="s">
+      <c r="H116" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="18" t="s">
+      <c r="A117" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="10">
         <v>46081</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C117" s="8">
         <v>176</v>
       </c>
       <c r="D117" s="4">
@@ -3829,18 +3812,18 @@
         <v>29.058851394027442</v>
       </c>
       <c r="G117" s="1"/>
-      <c r="H117" s="8" t="s">
+      <c r="H117" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="18" t="s">
+      <c r="A118" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B118" s="11">
+      <c r="B118" s="10">
         <v>46081</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="8">
         <v>184</v>
       </c>
       <c r="D118" s="4">
@@ -3854,18 +3837,18 @@
         <v>24.502674418604638</v>
       </c>
       <c r="G118" s="1"/>
-      <c r="H118" s="8" t="s">
+      <c r="H118" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="18" t="s">
+      <c r="A119" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="10">
         <v>46081</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C119" s="8">
         <v>184</v>
       </c>
       <c r="D119" s="4">
@@ -3879,18 +3862,18 @@
         <v>28.98401278156944</v>
       </c>
       <c r="G119" s="1"/>
-      <c r="H119" s="8" t="s">
+      <c r="H119" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B120" s="11">
+      <c r="B120" s="10">
         <v>46081</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="8">
         <v>176</v>
       </c>
       <c r="D120" s="4">
@@ -3904,18 +3887,18 @@
         <v>27.58403488372096</v>
       </c>
       <c r="G120" s="1"/>
-      <c r="H120" s="8" t="s">
+      <c r="H120" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="17" t="s">
+      <c r="A121" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="10">
         <v>46081</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C121" s="8">
         <v>160</v>
       </c>
       <c r="D121" s="4">
@@ -3929,18 +3912,18 @@
         <v>29.829281327985761</v>
       </c>
       <c r="G121" s="1"/>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="18" t="s">
+      <c r="A122" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B122" s="10">
         <v>46081</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="8">
         <v>144</v>
       </c>
       <c r="D122" s="4">
@@ -3954,18 +3937,18 @@
         <v>28.8203077060932</v>
       </c>
       <c r="G122" s="1"/>
-      <c r="H122" s="8" t="s">
+      <c r="H122" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="17" t="s">
+      <c r="A123" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="10">
         <v>46081</v>
       </c>
-      <c r="C123" s="9">
+      <c r="C123" s="8">
         <v>176</v>
       </c>
       <c r="D123" s="4">
@@ -3979,18 +3962,18 @@
         <v>28.816475823257598</v>
       </c>
       <c r="G123" s="1"/>
-      <c r="H123" s="8" t="s">
+      <c r="H123" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="18" t="s">
+      <c r="A124" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B124" s="11">
+      <c r="B124" s="10">
         <v>46081</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="8">
         <v>136</v>
       </c>
       <c r="D124" s="4">
@@ -4004,18 +3987,18 @@
         <v>27.394088235294078</v>
       </c>
       <c r="G124" s="1"/>
-      <c r="H124" s="8" t="s">
+      <c r="H124" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="10">
         <v>46081</v>
       </c>
-      <c r="C125" s="9">
+      <c r="C125" s="8">
         <v>168</v>
       </c>
       <c r="D125" s="4">
@@ -4029,7 +4012,7 @@
         <v>26.4407534457672</v>
       </c>
       <c r="G125" s="1"/>
-      <c r="H125" s="8" t="s">
+      <c r="H125" s="7" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4037,10 +4020,10 @@
       <c r="A126" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B126" s="11">
+      <c r="B126" s="10">
         <v>46081</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="8">
         <v>80</v>
       </c>
       <c r="D126" s="4">
@@ -4054,7 +4037,7 @@
         <v>221.01892325</v>
       </c>
       <c r="G126" s="1"/>
-      <c r="H126" s="8" t="s">
+      <c r="H126" s="7" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4062,10 +4045,10 @@
       <c r="A127" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="10">
         <v>46081</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C127" s="8">
         <v>123</v>
       </c>
       <c r="D127" s="4">
@@ -4079,7 +4062,7 @@
         <v>32.305987323123439</v>
       </c>
       <c r="G127" s="1"/>
-      <c r="H127" s="8" t="s">
+      <c r="H127" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4087,10 +4070,10 @@
       <c r="A128" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B128" s="11">
+      <c r="B128" s="10">
         <v>46081</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="8">
         <v>120</v>
       </c>
       <c r="D128" s="4">
@@ -4104,7 +4087,7 @@
         <v>53.951692105263206</v>
       </c>
       <c r="G128" s="1"/>
-      <c r="H128" s="8" t="s">
+      <c r="H128" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4112,10 +4095,10 @@
       <c r="A129" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="10">
         <v>46081</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C129" s="8">
         <v>144</v>
       </c>
       <c r="D129" s="4">
@@ -4129,18 +4112,18 @@
         <v>53.951692105263206</v>
       </c>
       <c r="G129" s="1"/>
-      <c r="H129" s="8" t="s">
+      <c r="H129" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="17" t="s">
+      <c r="A130" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B130" s="11">
+      <c r="B130" s="10">
         <v>46081</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="8">
         <v>176</v>
       </c>
       <c r="D130" s="4">
@@ -4154,7 +4137,7 @@
         <v>32.038890740342723</v>
       </c>
       <c r="G130" s="1"/>
-      <c r="H130" s="8" t="s">
+      <c r="H130" s="7" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4162,10 +4145,10 @@
       <c r="A131" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B131" s="11">
+      <c r="B131" s="10">
         <v>46081</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C131" s="8">
         <v>36</v>
       </c>
       <c r="D131" s="4">
@@ -4179,7 +4162,7 @@
         <v>52.301458185537683</v>
       </c>
       <c r="G131" s="1"/>
-      <c r="H131" s="8" t="s">
+      <c r="H131" s="7" t="s">
         <v>125</v>
       </c>
     </row>
@@ -4187,10 +4170,10 @@
       <c r="A132" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B132" s="11">
+      <c r="B132" s="10">
         <v>46081</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="8">
         <v>8</v>
       </c>
       <c r="D132" s="4">
@@ -4204,18 +4187,18 @@
         <v>87.0160844444448</v>
       </c>
       <c r="G132" s="1"/>
-      <c r="H132" s="8" t="s">
+      <c r="H132" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="17" t="s">
+      <c r="A133" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="10">
         <v>46081</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C133" s="8">
         <v>168</v>
       </c>
       <c r="D133" s="4">
@@ -4229,18 +4212,18 @@
         <v>34.900872981515839</v>
       </c>
       <c r="G133" s="1"/>
-      <c r="H133" s="8" t="s">
+      <c r="H133" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B134" s="11">
+      <c r="B134" s="10">
         <v>46081</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="8">
         <v>134</v>
       </c>
       <c r="D134" s="4">
@@ -4254,16 +4237,16 @@
         <v>71.173871890866238</v>
       </c>
       <c r="G134" s="1"/>
-      <c r="H134" s="8"/>
+      <c r="H134" s="7"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="10">
         <v>46081</v>
       </c>
-      <c r="C135" s="9">
+      <c r="C135" s="8">
         <v>149</v>
       </c>
       <c r="D135" s="4">
@@ -4277,16 +4260,16 @@
         <v>32.78333269710528</v>
       </c>
       <c r="G135" s="1"/>
-      <c r="H135" s="8"/>
+      <c r="H135" s="7"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="18" t="s">
+      <c r="A136" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="B136" s="11">
+      <c r="B136" s="10">
         <v>46081</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="8">
         <v>152</v>
       </c>
       <c r="D136" s="4">
@@ -4300,16 +4283,16 @@
         <v>45.245585759164562</v>
       </c>
       <c r="G136" s="1"/>
-      <c r="H136" s="8"/>
+      <c r="H136" s="7"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="18" t="s">
+      <c r="A137" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="10">
         <v>46081</v>
       </c>
-      <c r="C137" s="9">
+      <c r="C137" s="8">
         <v>144</v>
       </c>
       <c r="D137" s="4">
@@ -4323,16 +4306,16 @@
         <v>29.400543326706401</v>
       </c>
       <c r="G137" s="1"/>
-      <c r="H137" s="8"/>
+      <c r="H137" s="7"/>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B138" s="11">
+        <v>137</v>
+      </c>
+      <c r="B138" s="10">
         <v>46081</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="8">
         <v>128</v>
       </c>
       <c r="D138" s="4">
@@ -4346,16 +4329,16 @@
         <v>58.139124423022807</v>
       </c>
       <c r="G138" s="1"/>
-      <c r="H138" s="8"/>
+      <c r="H138" s="7"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" s="11">
+        <v>136</v>
+      </c>
+      <c r="B139" s="10">
         <v>46081</v>
       </c>
-      <c r="C139" s="9">
+      <c r="C139" s="8">
         <v>152</v>
       </c>
       <c r="D139" s="4">
@@ -4369,16 +4352,16 @@
         <v>36.547653397575523</v>
       </c>
       <c r="G139" s="1"/>
-      <c r="H139" s="8"/>
+      <c r="H139" s="7"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B140" s="11">
+        <v>139</v>
+      </c>
+      <c r="B140" s="10">
         <v>46081</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="8">
         <v>174</v>
       </c>
       <c r="D140" s="4">
@@ -4392,16 +4375,16 @@
         <v>47.311221505376317</v>
       </c>
       <c r="G140" s="1"/>
-      <c r="H140" s="8"/>
+      <c r="H140" s="7"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B141" s="11">
+        <v>140</v>
+      </c>
+      <c r="B141" s="10">
         <v>46081</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C141" s="8">
         <v>16</v>
       </c>
       <c r="D141" s="4">
@@ -4415,32 +4398,32 @@
         <v>87.0160844444448</v>
       </c>
       <c r="G141" s="1"/>
-      <c r="H141" s="8"/>
+      <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="10" t="s">
+      <c r="A142" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B142" s="11">
+      <c r="B142" s="10">
         <v>46112</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="8">
         <v>175</v>
       </c>
-      <c r="D142" s="12">
+      <c r="D142" s="11">
         <v>32.9559038588799</v>
       </c>
-      <c r="E142" s="13">
-        <v>20</v>
-      </c>
-      <c r="F142" s="14">
+      <c r="E142" s="12">
+        <v>20</v>
+      </c>
+      <c r="F142" s="13">
         <f t="shared" si="4"/>
         <v>26.364723087103918</v>
       </c>
-      <c r="G142" s="15" t="s">
+      <c r="G142" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H142" s="16" t="s">
+      <c r="H142" s="15" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4448,10 +4431,10 @@
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="10">
         <v>46112</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="8">
         <v>32</v>
       </c>
       <c r="D143" s="4">
@@ -4467,7 +4450,7 @@
       <c r="G143" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H143" s="8" t="s">
+      <c r="H143" s="7" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4475,10 +4458,10 @@
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B144" s="11">
+      <c r="B144" s="10">
         <v>46112</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>88</v>
       </c>
       <c r="D144" s="4">
@@ -4492,16 +4475,16 @@
         <v>58.314067867744484</v>
       </c>
       <c r="G144" s="1"/>
-      <c r="H144" s="8"/>
+      <c r="H144" s="7"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="10">
         <v>46112</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145" s="8">
         <v>152</v>
       </c>
       <c r="D145" s="4">
@@ -4515,7 +4498,7 @@
         <v>17.307133333333361</v>
       </c>
       <c r="G145" s="1"/>
-      <c r="H145" s="8" t="s">
+      <c r="H145" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4523,10 +4506,10 @@
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B146" s="11">
+      <c r="B146" s="10">
         <v>46112</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="8">
         <v>80</v>
       </c>
       <c r="D146" s="4">
@@ -4540,7 +4523,7 @@
         <v>84.121485014244797</v>
       </c>
       <c r="G146" s="1"/>
-      <c r="H146" s="8" t="s">
+      <c r="H146" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4548,10 +4531,10 @@
       <c r="A147" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="10">
         <v>46112</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147" s="8">
         <v>152</v>
       </c>
       <c r="D147" s="4">
@@ -4565,7 +4548,7 @@
         <v>26.789674509803923</v>
       </c>
       <c r="G147" s="1"/>
-      <c r="H147" s="8" t="s">
+      <c r="H147" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4573,10 +4556,10 @@
       <c r="A148" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="10">
         <v>46112</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="8">
         <v>136</v>
       </c>
       <c r="D148" s="4">
@@ -4590,18 +4573,18 @@
         <v>30.881691565083202</v>
       </c>
       <c r="G148" s="1"/>
-      <c r="H148" s="8" t="s">
+      <c r="H148" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="17" t="s">
+      <c r="A149" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="10">
         <v>46112</v>
       </c>
-      <c r="C149" s="9">
+      <c r="C149" s="8">
         <v>172</v>
       </c>
       <c r="D149" s="4">
@@ -4615,18 +4598,18 @@
         <v>28.752989610389601</v>
       </c>
       <c r="G149" s="1"/>
-      <c r="H149" s="8" t="s">
+      <c r="H149" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B150" s="11">
+      <c r="A150" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B150" s="10">
         <v>46112</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="8">
         <v>168</v>
       </c>
       <c r="D150" s="4">
@@ -4640,16 +4623,16 @@
         <v>26.416474074074081</v>
       </c>
       <c r="G150" s="1"/>
-      <c r="H150" s="8"/>
+      <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="10">
         <v>46112</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C151" s="8">
         <v>160</v>
       </c>
       <c r="D151" s="4">
@@ -4663,7 +4646,7 @@
         <v>30.506154435820001</v>
       </c>
       <c r="G151" s="1"/>
-      <c r="H151" s="8" t="s">
+      <c r="H151" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4671,10 +4654,10 @@
       <c r="A152" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B152" s="11">
+      <c r="B152" s="10">
         <v>46112</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="8">
         <v>144</v>
       </c>
       <c r="D152" s="4">
@@ -4688,7 +4671,7 @@
         <v>145.597996296296</v>
       </c>
       <c r="G152" s="1"/>
-      <c r="H152" s="8" t="s">
+      <c r="H152" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4696,10 +4679,10 @@
       <c r="A153" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="10">
         <v>46112</v>
       </c>
-      <c r="C153" s="9">
+      <c r="C153" s="8">
         <v>144</v>
       </c>
       <c r="D153" s="4">
@@ -4713,7 +4696,7 @@
         <v>145.597996296296</v>
       </c>
       <c r="G153" s="1"/>
-      <c r="H153" s="8" t="s">
+      <c r="H153" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4721,10 +4704,10 @@
       <c r="A154" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B154" s="11">
+      <c r="B154" s="10">
         <v>46112</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="8">
         <v>168</v>
       </c>
       <c r="D154" s="4">
@@ -4738,7 +4721,7 @@
         <v>29.563991604009999</v>
       </c>
       <c r="G154" s="1"/>
-      <c r="H154" s="8" t="s">
+      <c r="H154" s="7" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4746,10 +4729,10 @@
       <c r="A155" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="10">
         <v>46112</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C155" s="8">
         <v>160</v>
       </c>
       <c r="D155" s="4">
@@ -4763,18 +4746,18 @@
         <v>27.027939938832638</v>
       </c>
       <c r="G155" s="1"/>
-      <c r="H155" s="8" t="s">
+      <c r="H155" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B156" s="11">
+        <v>135</v>
+      </c>
+      <c r="B156" s="10">
         <v>46112</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="8">
         <v>98</v>
       </c>
       <c r="D156" s="4">
@@ -4788,16 +4771,16 @@
         <v>91.552355504012809</v>
       </c>
       <c r="G156" s="1"/>
-      <c r="H156" s="8"/>
+      <c r="H156" s="7"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="17" t="s">
+      <c r="A157" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="10">
         <v>46112</v>
       </c>
-      <c r="C157" s="9">
+      <c r="C157" s="8">
         <v>152</v>
       </c>
       <c r="D157" s="4">
@@ -4811,18 +4794,18 @@
         <v>32.795740540540478</v>
       </c>
       <c r="G157" s="1"/>
-      <c r="H157" s="8" t="s">
+      <c r="H157" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="17" t="s">
+      <c r="A158" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B158" s="11">
+      <c r="B158" s="10">
         <v>46112</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="8">
         <v>176</v>
       </c>
       <c r="D158" s="4">
@@ -4836,7 +4819,7 @@
         <v>31.388353846153841</v>
       </c>
       <c r="G158" s="1"/>
-      <c r="H158" s="8" t="s">
+      <c r="H158" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4844,10 +4827,10 @@
       <c r="A159" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="10">
         <v>46112</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C159" s="8">
         <v>143</v>
       </c>
       <c r="D159" s="4">
@@ -4861,18 +4844,18 @@
         <v>26.635869179305281</v>
       </c>
       <c r="G159" s="1"/>
-      <c r="H159" s="8" t="s">
+      <c r="H159" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="17" t="s">
+      <c r="A160" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B160" s="11">
+      <c r="B160" s="10">
         <v>46112</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="8">
         <v>192</v>
       </c>
       <c r="D160" s="4">
@@ -4886,18 +4869,18 @@
         <v>31.030134877725839</v>
       </c>
       <c r="G160" s="1"/>
-      <c r="H160" s="8" t="s">
+      <c r="H160" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B161" s="11">
+      <c r="A161" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B161" s="10">
         <v>46112</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161" s="8">
         <v>145</v>
       </c>
       <c r="D161" s="4">
@@ -4911,18 +4894,18 @@
         <v>39.044921436282877</v>
       </c>
       <c r="G161" s="1"/>
-      <c r="H161" s="8" t="s">
+      <c r="H161" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="17" t="s">
+      <c r="A162" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B162" s="11">
+      <c r="B162" s="10">
         <v>46112</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="8">
         <v>192</v>
       </c>
       <c r="D162" s="4">
@@ -4936,7 +4919,7 @@
         <v>29.931657392351678</v>
       </c>
       <c r="G162" s="1"/>
-      <c r="H162" s="8" t="s">
+      <c r="H162" s="7" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4944,10 +4927,10 @@
       <c r="A163" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B163" s="11">
+      <c r="B163" s="10">
         <v>46112</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163" s="8">
         <v>152</v>
       </c>
       <c r="D163" s="4">
@@ -4961,7 +4944,7 @@
         <v>34.273747399572237</v>
       </c>
       <c r="G163" s="1"/>
-      <c r="H163" s="8" t="s">
+      <c r="H163" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4969,10 +4952,10 @@
       <c r="A164" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B164" s="11">
+      <c r="B164" s="10">
         <v>46112</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="8">
         <v>148</v>
       </c>
       <c r="D164" s="4">
@@ -4986,18 +4969,18 @@
         <v>30.734897405337041</v>
       </c>
       <c r="G164" s="1"/>
-      <c r="H164" s="8" t="s">
+      <c r="H164" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="10" t="s">
+      <c r="A165" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="10">
         <v>46112</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165" s="8">
         <v>164</v>
       </c>
       <c r="D165" s="4">
@@ -5011,7 +4994,7 @@
         <v>35.750638472433522</v>
       </c>
       <c r="G165" s="1"/>
-      <c r="H165" s="8" t="s">
+      <c r="H165" s="7" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5019,10 +5002,10 @@
       <c r="A166" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B166" s="11">
+      <c r="B166" s="10">
         <v>46112</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="8">
         <v>112</v>
       </c>
       <c r="D166" s="4">
@@ -5036,18 +5019,18 @@
         <v>91.6325801244856</v>
       </c>
       <c r="G166" s="1"/>
-      <c r="H166" s="8" t="s">
+      <c r="H166" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="18" t="s">
+      <c r="A167" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="10">
         <v>46112</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C167" s="8">
         <v>136</v>
       </c>
       <c r="D167" s="4">
@@ -5061,7 +5044,7 @@
         <v>27.704000000000001</v>
       </c>
       <c r="G167" s="1"/>
-      <c r="H167" s="8" t="s">
+      <c r="H167" s="7" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5069,10 +5052,10 @@
       <c r="A168" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B168" s="11">
+      <c r="B168" s="10">
         <v>46112</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="8">
         <v>168</v>
       </c>
       <c r="D168" s="4">
@@ -5086,7 +5069,7 @@
         <v>17.98560236938312</v>
       </c>
       <c r="G168" s="1"/>
-      <c r="H168" s="8" t="s">
+      <c r="H168" s="7" t="s">
         <v>95</v>
       </c>
     </row>
@@ -5094,10 +5077,10 @@
       <c r="A169" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B169" s="11">
+      <c r="B169" s="10">
         <v>46112</v>
       </c>
-      <c r="C169" s="9">
+      <c r="C169" s="8">
         <v>32</v>
       </c>
       <c r="D169" s="4">
@@ -5111,18 +5094,18 @@
         <v>73.943243243243202</v>
       </c>
       <c r="G169" s="1"/>
-      <c r="H169" s="8" t="s">
+      <c r="H169" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="10" t="s">
+      <c r="A170" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B170" s="11">
+      <c r="B170" s="10">
         <v>46112</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="8">
         <v>156</v>
       </c>
       <c r="D170" s="4">
@@ -5136,7 +5119,7 @@
         <v>35.146393199526642</v>
       </c>
       <c r="G170" s="1"/>
-      <c r="H170" s="8" t="s">
+      <c r="H170" s="7" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5144,10 +5127,10 @@
       <c r="A171" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="10">
         <v>46112</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C171" s="8">
         <v>85</v>
       </c>
       <c r="D171" s="4">
@@ -5161,18 +5144,18 @@
         <v>46.41844847696656</v>
       </c>
       <c r="G171" s="1"/>
-      <c r="H171" s="8" t="s">
+      <c r="H171" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="17" t="s">
+      <c r="A172" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B172" s="11">
+      <c r="B172" s="10">
         <v>46112</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="8">
         <v>176</v>
       </c>
       <c r="D172" s="4">
@@ -5186,7 +5169,7 @@
         <v>31.20583255813952</v>
       </c>
       <c r="G172" s="1"/>
-      <c r="H172" s="8" t="s">
+      <c r="H172" s="7" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5194,10 +5177,10 @@
       <c r="A173" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="10">
         <v>46112</v>
       </c>
-      <c r="C173" s="9">
+      <c r="C173" s="8">
         <v>168</v>
       </c>
       <c r="D173" s="4">
@@ -5211,7 +5194,7 @@
         <v>34.277199798695037</v>
       </c>
       <c r="G173" s="1"/>
-      <c r="H173" s="8" t="s">
+      <c r="H173" s="7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5219,10 +5202,10 @@
       <c r="A174" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B174" s="11">
+      <c r="B174" s="10">
         <v>46112</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="8">
         <v>144</v>
       </c>
       <c r="D174" s="4">
@@ -5236,18 +5219,18 @@
         <v>48.48845998517568</v>
       </c>
       <c r="G174" s="1"/>
-      <c r="H174" s="8" t="s">
+      <c r="H174" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="17" t="s">
+      <c r="A175" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="10">
         <v>46112</v>
       </c>
-      <c r="C175" s="9">
+      <c r="C175" s="8">
         <v>200</v>
       </c>
       <c r="D175" s="4">
@@ -5261,18 +5244,18 @@
         <v>27.363842962962963</v>
       </c>
       <c r="G175" s="1"/>
-      <c r="H175" s="8" t="s">
+      <c r="H175" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B176" s="11">
+      <c r="B176" s="10">
         <v>46112</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="8">
         <v>178</v>
       </c>
       <c r="D176" s="4">
@@ -5286,7 +5269,7 @@
         <v>37.241296576371838</v>
       </c>
       <c r="G176" s="1"/>
-      <c r="H176" s="8" t="s">
+      <c r="H176" s="7" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5294,10 +5277,10 @@
       <c r="A177" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="10">
         <v>46112</v>
       </c>
-      <c r="C177" s="9">
+      <c r="C177" s="8">
         <v>117</v>
       </c>
       <c r="D177" s="4">
@@ -5311,7 +5294,7 @@
         <v>51.510988749479601</v>
       </c>
       <c r="G177" s="1"/>
-      <c r="H177" s="8" t="s">
+      <c r="H177" s="7" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5319,10 +5302,10 @@
       <c r="A178" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B178" s="11">
+      <c r="B178" s="10">
         <v>46112</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178" s="8">
         <v>101</v>
       </c>
       <c r="D178" s="4">
@@ -5336,7 +5319,7 @@
         <v>99.240670241657597</v>
       </c>
       <c r="G178" s="1"/>
-      <c r="H178" s="8" t="s">
+      <c r="H178" s="7" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5344,10 +5327,10 @@
       <c r="A179" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="10">
         <v>46112</v>
       </c>
-      <c r="C179" s="9">
+      <c r="C179" s="8">
         <v>160</v>
       </c>
       <c r="D179" s="4">
@@ -5361,7 +5344,7 @@
         <v>18.157276546184722</v>
       </c>
       <c r="G179" s="1"/>
-      <c r="H179" s="8" t="s">
+      <c r="H179" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5369,10 +5352,10 @@
       <c r="A180" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B180" s="11">
+      <c r="B180" s="10">
         <v>46112</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180" s="8">
         <v>120</v>
       </c>
       <c r="D180" s="4">
@@ -5386,18 +5369,18 @@
         <v>36.257265625000002</v>
       </c>
       <c r="G180" s="1"/>
-      <c r="H180" s="8" t="s">
+      <c r="H180" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="17" t="s">
+      <c r="A181" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="10">
         <v>46112</v>
       </c>
-      <c r="C181" s="9">
+      <c r="C181" s="8">
         <v>176</v>
       </c>
       <c r="D181" s="4">
@@ -5411,18 +5394,18 @@
         <v>31.839228678349759</v>
       </c>
       <c r="G181" s="1"/>
-      <c r="H181" s="8" t="s">
+      <c r="H181" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="17" t="s">
+      <c r="A182" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B182" s="11">
+      <c r="B182" s="10">
         <v>46112</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182" s="8">
         <v>160</v>
       </c>
       <c r="D182" s="4">
@@ -5436,7 +5419,7 @@
         <v>38.786934210526319</v>
       </c>
       <c r="G182" s="1"/>
-      <c r="H182" s="8" t="s">
+      <c r="H182" s="7" t="s">
         <v>109</v>
       </c>
     </row>
@@ -5444,10 +5427,10 @@
       <c r="A183" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="10">
         <v>46112</v>
       </c>
-      <c r="C183" s="9">
+      <c r="C183" s="8">
         <v>80</v>
       </c>
       <c r="D183" s="4">
@@ -5461,7 +5444,7 @@
         <v>58.18664365451896</v>
       </c>
       <c r="G183" s="1"/>
-      <c r="H183" s="8" t="s">
+      <c r="H183" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5469,10 +5452,10 @@
       <c r="A184" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B184" s="11">
+      <c r="B184" s="10">
         <v>46112</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184" s="8">
         <v>151</v>
       </c>
       <c r="D184" s="4">
@@ -5486,18 +5469,18 @@
         <v>26.325087813864162</v>
       </c>
       <c r="G184" s="1"/>
-      <c r="H184" s="8" t="s">
+      <c r="H184" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="18" t="s">
+      <c r="A185" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="10">
         <v>46112</v>
       </c>
-      <c r="C185" s="9">
+      <c r="C185" s="8">
         <v>168</v>
       </c>
       <c r="D185" s="4">
@@ -5511,18 +5494,18 @@
         <v>41.44</v>
       </c>
       <c r="G185" s="1"/>
-      <c r="H185" s="8" t="s">
+      <c r="H185" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="10" t="s">
+      <c r="A186" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B186" s="11">
+      <c r="B186" s="10">
         <v>46112</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186" s="8">
         <v>152</v>
       </c>
       <c r="D186" s="4">
@@ -5536,18 +5519,18 @@
         <v>45.282240121587357</v>
       </c>
       <c r="G186" s="1"/>
-      <c r="H186" s="8" t="s">
+      <c r="H186" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="10">
         <v>46112</v>
       </c>
-      <c r="C187" s="9">
+      <c r="C187" s="8">
         <v>144</v>
       </c>
       <c r="D187" s="4">
@@ -5561,18 +5544,18 @@
         <v>48.537965707070718</v>
       </c>
       <c r="G187" s="1"/>
-      <c r="H187" s="8" t="s">
+      <c r="H187" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="18" t="s">
+      <c r="A188" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B188" s="11">
+      <c r="B188" s="10">
         <v>46112</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188" s="8">
         <v>184</v>
       </c>
       <c r="D188" s="4">
@@ -5586,18 +5569,18 @@
         <v>28.28</v>
       </c>
       <c r="G188" s="1"/>
-      <c r="H188" s="8" t="s">
+      <c r="H188" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="18" t="s">
+      <c r="A189" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="10">
         <v>46112</v>
       </c>
-      <c r="C189" s="9">
+      <c r="C189" s="8">
         <v>168</v>
       </c>
       <c r="D189" s="4">
@@ -5611,18 +5594,18 @@
         <v>26.463999999999999</v>
       </c>
       <c r="G189" s="1"/>
-      <c r="H189" s="8" t="s">
+      <c r="H189" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="18" t="s">
+      <c r="A190" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B190" s="11">
+      <c r="B190" s="10">
         <v>46112</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C190" s="8">
         <v>157</v>
       </c>
       <c r="D190" s="4">
@@ -5636,18 +5619,18 @@
         <v>29.104000000000003</v>
       </c>
       <c r="G190" s="1"/>
-      <c r="H190" s="8" t="s">
+      <c r="H190" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="18" t="s">
+      <c r="A191" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B191" s="11">
+      <c r="B191" s="10">
         <v>46112</v>
       </c>
-      <c r="C191" s="9">
+      <c r="C191" s="8">
         <v>176</v>
       </c>
       <c r="D191" s="4">
@@ -5661,18 +5644,18 @@
         <v>32.472000000000001</v>
       </c>
       <c r="G191" s="1"/>
-      <c r="H191" s="8" t="s">
+      <c r="H191" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="17" t="s">
+      <c r="A192" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B192" s="11">
+      <c r="B192" s="10">
         <v>46112</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C192" s="8">
         <v>184</v>
       </c>
       <c r="D192" s="4">
@@ -5686,18 +5669,18 @@
         <v>30.973545641977278</v>
       </c>
       <c r="G192" s="1"/>
-      <c r="H192" s="8" t="s">
+      <c r="H192" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="18" t="s">
+      <c r="A193" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B193" s="11">
+      <c r="B193" s="10">
         <v>46112</v>
       </c>
-      <c r="C193" s="9">
+      <c r="C193" s="8">
         <v>168</v>
       </c>
       <c r="D193" s="4">
@@ -5711,18 +5694,18 @@
         <v>26.576000000000001</v>
       </c>
       <c r="G193" s="1"/>
-      <c r="H193" s="8" t="s">
+      <c r="H193" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="17" t="s">
+      <c r="A194" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B194" s="11">
+      <c r="B194" s="10">
         <v>46112</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194" s="8">
         <v>184</v>
       </c>
       <c r="D194" s="4">
@@ -5736,18 +5719,18 @@
         <v>33.3767936417184</v>
       </c>
       <c r="G194" s="1"/>
-      <c r="H194" s="8" t="s">
+      <c r="H194" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="18" t="s">
+      <c r="A195" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B195" s="11">
+      <c r="B195" s="10">
         <v>46112</v>
       </c>
-      <c r="C195" s="9">
+      <c r="C195" s="8">
         <v>176</v>
       </c>
       <c r="D195" s="4">
@@ -5761,18 +5744,18 @@
         <v>26.136000000000003</v>
       </c>
       <c r="G195" s="1"/>
-      <c r="H195" s="8" t="s">
+      <c r="H195" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="18" t="s">
+      <c r="A196" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B196" s="11">
+      <c r="B196" s="10">
         <v>46112</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C196" s="8">
         <v>160</v>
       </c>
       <c r="D196" s="4">
@@ -5786,7 +5769,7 @@
         <v>27.983999999999998</v>
       </c>
       <c r="G196" s="1"/>
-      <c r="H196" s="8" t="s">
+      <c r="H196" s="7" t="s">
         <v>115</v>
       </c>
     </row>
@@ -5794,10 +5777,10 @@
       <c r="A197" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="10">
         <v>46112</v>
       </c>
-      <c r="C197" s="9"/>
+      <c r="C197" s="8"/>
       <c r="D197" s="4"/>
       <c r="E197" s="6">
         <v>20</v>
@@ -5807,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="G197" s="1"/>
-      <c r="H197" s="8" t="s">
+      <c r="H197" s="7" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5815,10 +5798,10 @@
       <c r="A198" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B198" s="11">
+      <c r="B198" s="10">
         <v>46112</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198" s="8">
         <v>168</v>
       </c>
       <c r="D198" s="4">
@@ -5832,7 +5815,7 @@
         <v>29.563991604009999</v>
       </c>
       <c r="G198" s="1"/>
-      <c r="H198" s="8" t="s">
+      <c r="H198" s="7" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5840,10 +5823,10 @@
       <c r="A199" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="10">
         <v>46112</v>
       </c>
-      <c r="C199" s="9">
+      <c r="C199" s="8">
         <v>168</v>
       </c>
       <c r="D199" s="4">
@@ -5857,7 +5840,7 @@
         <v>41.97598809523808</v>
       </c>
       <c r="G199" s="1"/>
-      <c r="H199" s="8" t="s">
+      <c r="H199" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -5865,10 +5848,10 @@
       <c r="A200" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B200" s="11">
+      <c r="B200" s="10">
         <v>46112</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C200" s="8">
         <v>168</v>
       </c>
       <c r="D200" s="4">
@@ -5882,18 +5865,18 @@
         <v>41.97598809523808</v>
       </c>
       <c r="G200" s="1"/>
-      <c r="H200" s="8" t="s">
+      <c r="H200" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="17" t="s">
+      <c r="A201" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B201" s="11">
+      <c r="B201" s="10">
         <v>46112</v>
       </c>
-      <c r="C201" s="9">
+      <c r="C201" s="8">
         <v>192</v>
       </c>
       <c r="D201" s="4">
@@ -5907,7 +5890,7 @@
         <v>30.414991483285281</v>
       </c>
       <c r="G201" s="1"/>
-      <c r="H201" s="8" t="s">
+      <c r="H201" s="7" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5915,10 +5898,10 @@
       <c r="A202" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B202" s="11">
+      <c r="B202" s="10">
         <v>46112</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C202" s="8">
         <v>40</v>
       </c>
       <c r="D202" s="4">
@@ -5932,7 +5915,7 @@
         <v>54.138369230688397</v>
       </c>
       <c r="G202" s="1"/>
-      <c r="H202" s="8" t="s">
+      <c r="H202" s="7" t="s">
         <v>125</v>
       </c>
     </row>
@@ -5940,10 +5923,10 @@
       <c r="A203" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B203" s="11">
+      <c r="B203" s="10">
         <v>46112</v>
       </c>
-      <c r="C203" s="9">
+      <c r="C203" s="8">
         <v>50</v>
       </c>
       <c r="D203" s="4">
@@ -5957,18 +5940,18 @@
         <v>127.10180083344881</v>
       </c>
       <c r="G203" s="1"/>
-      <c r="H203" s="8" t="s">
+      <c r="H203" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="17" t="s">
+      <c r="A204" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B204" s="11">
+      <c r="B204" s="10">
         <v>46112</v>
       </c>
-      <c r="C204" s="9">
+      <c r="C204" s="8">
         <v>192</v>
       </c>
       <c r="D204" s="4">
@@ -5978,22 +5961,22 @@
         <v>20</v>
       </c>
       <c r="F204" s="3">
-        <f t="shared" ref="F204:F213" si="5">D204-(D204*E204)/100</f>
+        <f t="shared" ref="F204:F267" si="5">D204-(D204*E204)/100</f>
         <v>37.184640517570315</v>
       </c>
       <c r="G204" s="1"/>
-      <c r="H204" s="8" t="s">
+      <c r="H204" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="10" t="s">
+      <c r="A205" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B205" s="11">
+      <c r="B205" s="10">
         <v>46112</v>
       </c>
-      <c r="C205" s="9">
+      <c r="C205" s="8">
         <v>144</v>
       </c>
       <c r="D205" s="4">
@@ -6007,16 +5990,16 @@
         <v>71.178771521206002</v>
       </c>
       <c r="G205" s="1"/>
-      <c r="H205" s="8"/>
+      <c r="H205" s="7"/>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B206" s="11">
+      <c r="B206" s="10">
         <v>46112</v>
       </c>
-      <c r="C206" s="9">
+      <c r="C206" s="8">
         <v>120</v>
       </c>
       <c r="D206" s="4">
@@ -6030,16 +6013,16 @@
         <v>36.257265625000002</v>
       </c>
       <c r="G206" s="1"/>
-      <c r="H206" s="8"/>
+      <c r="H206" s="7"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="18" t="s">
+      <c r="A207" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="B207" s="11">
+      <c r="B207" s="10">
         <v>46112</v>
       </c>
-      <c r="C207" s="9">
+      <c r="C207" s="8">
         <v>168</v>
       </c>
       <c r="D207" s="4">
@@ -6053,16 +6036,16 @@
         <v>39.480000000000004</v>
       </c>
       <c r="G207" s="1"/>
-      <c r="H207" s="8"/>
+      <c r="H207" s="7"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="18" t="s">
+      <c r="A208" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B208" s="11">
+      <c r="B208" s="10">
         <v>46112</v>
       </c>
-      <c r="C208" s="9">
+      <c r="C208" s="8">
         <v>192</v>
       </c>
       <c r="D208" s="4">
@@ -6076,16 +6059,16 @@
         <v>32.007999999999996</v>
       </c>
       <c r="G208" s="1"/>
-      <c r="H208" s="8"/>
+      <c r="H208" s="7"/>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B209" s="11">
+        <v>137</v>
+      </c>
+      <c r="B209" s="10">
         <v>46112</v>
       </c>
-      <c r="C209" s="9">
+      <c r="C209" s="8">
         <v>96</v>
       </c>
       <c r="D209" s="4">
@@ -6099,16 +6082,16 @@
         <v>53.311397747747762</v>
       </c>
       <c r="G209" s="1"/>
-      <c r="H209" s="8"/>
+      <c r="H209" s="7"/>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B210" s="11">
+        <v>136</v>
+      </c>
+      <c r="B210" s="10">
         <v>46112</v>
       </c>
-      <c r="C210" s="9">
+      <c r="C210" s="8">
         <v>171</v>
       </c>
       <c r="D210" s="4">
@@ -6122,16 +6105,16 @@
         <v>37.250649721667919</v>
       </c>
       <c r="G210" s="1"/>
-      <c r="H210" s="8"/>
+      <c r="H210" s="7"/>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B211" s="11">
+        <v>139</v>
+      </c>
+      <c r="B211" s="10">
         <v>46112</v>
       </c>
-      <c r="C211" s="9">
+      <c r="C211" s="8">
         <v>179</v>
       </c>
       <c r="D211" s="4">
@@ -6145,16 +6128,16 @@
         <v>41.129951133704239</v>
       </c>
       <c r="G211" s="1"/>
-      <c r="H211" s="8"/>
+      <c r="H211" s="7"/>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B212" s="11">
+        <v>140</v>
+      </c>
+      <c r="B212" s="10">
         <v>46112</v>
       </c>
-      <c r="C212" s="9">
+      <c r="C212" s="8">
         <v>80</v>
       </c>
       <c r="D212" s="4">
@@ -6168,16 +6151,16 @@
         <v>102.6051444644648</v>
       </c>
       <c r="G212" s="1"/>
-      <c r="H212" s="8"/>
+      <c r="H212" s="7"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B213" s="11">
+      <c r="A213" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B213" s="10">
         <v>46112</v>
       </c>
-      <c r="C213" s="9">
+      <c r="C213" s="8">
         <v>144</v>
       </c>
       <c r="D213" s="4">
@@ -6191,10 +6174,1786 @@
         <v>27.78819074074072</v>
       </c>
       <c r="G213" s="1"/>
-      <c r="H213" s="8"/>
+      <c r="H213" s="7"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B214" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C214" s="8">
+        <v>119</v>
+      </c>
+      <c r="D214" s="11">
+        <v>57.895782398246901</v>
+      </c>
+      <c r="E214" s="12">
+        <v>20</v>
+      </c>
+      <c r="F214" s="13">
+        <f t="shared" si="5"/>
+        <v>46.316625918597524</v>
+      </c>
+      <c r="G214" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H214" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C215" s="8">
+        <v>72</v>
+      </c>
+      <c r="D215" s="4">
+        <v>79.053075102880598</v>
+      </c>
+      <c r="E215" s="6">
+        <v>20</v>
+      </c>
+      <c r="F215" s="3">
+        <f t="shared" si="5"/>
+        <v>63.242460082304476</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H215" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B216" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C216" s="8">
+        <v>32</v>
+      </c>
+      <c r="D216" s="4">
+        <v>68.099632335105895</v>
+      </c>
+      <c r="E216" s="6">
+        <v>20</v>
+      </c>
+      <c r="F216" s="3">
+        <f t="shared" si="5"/>
+        <v>54.479705868084714</v>
+      </c>
+      <c r="G216" s="1"/>
+      <c r="H216" s="7"/>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B217" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C217" s="8">
+        <v>157</v>
+      </c>
+      <c r="D217" s="4">
+        <v>27.506303393213599</v>
+      </c>
+      <c r="E217" s="6">
+        <v>20</v>
+      </c>
+      <c r="F217" s="3">
+        <f t="shared" si="5"/>
+        <v>22.00504271457088</v>
+      </c>
+      <c r="G217" s="1"/>
+      <c r="H217" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B218" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C218" s="8">
+        <v>96</v>
+      </c>
+      <c r="D218" s="4">
+        <v>87.062514790714303</v>
+      </c>
+      <c r="E218" s="6">
+        <v>20</v>
+      </c>
+      <c r="F218" s="3">
+        <f t="shared" si="5"/>
+        <v>69.650011832571437</v>
+      </c>
+      <c r="G218" s="1"/>
+      <c r="H218" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B219" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C219" s="8">
+        <v>168</v>
+      </c>
+      <c r="D219" s="4">
+        <v>42.614125818889697</v>
+      </c>
+      <c r="E219" s="6">
+        <v>20</v>
+      </c>
+      <c r="F219" s="3">
+        <f t="shared" si="5"/>
+        <v>34.091300655111759</v>
+      </c>
+      <c r="G219" s="1"/>
+      <c r="H219" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C220" s="8">
+        <v>160</v>
+      </c>
+      <c r="D220" s="4">
+        <v>46.4649604116332</v>
+      </c>
+      <c r="E220" s="6">
+        <v>20</v>
+      </c>
+      <c r="F220" s="3">
+        <f t="shared" si="5"/>
+        <v>37.171968329306559</v>
+      </c>
+      <c r="G220" s="1"/>
+      <c r="H220" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B221" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C221" s="8">
+        <v>168</v>
+      </c>
+      <c r="D221" s="4">
+        <v>37.598206081081102</v>
+      </c>
+      <c r="E221" s="6">
+        <v>20</v>
+      </c>
+      <c r="F221" s="3">
+        <f t="shared" si="5"/>
+        <v>30.07856486486488</v>
+      </c>
+      <c r="G221" s="1"/>
+      <c r="H221" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B222" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C222" s="8">
+        <v>176</v>
+      </c>
+      <c r="D222" s="4">
+        <v>31.106949346212499</v>
+      </c>
+      <c r="E222" s="6">
+        <v>20</v>
+      </c>
+      <c r="F222" s="3">
+        <f t="shared" si="5"/>
+        <v>24.885559476969998</v>
+      </c>
+      <c r="G222" s="1"/>
+      <c r="H222" s="7"/>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C223" s="8">
+        <v>136</v>
+      </c>
+      <c r="D223" s="4">
+        <v>45.0348347102613</v>
+      </c>
+      <c r="E223" s="6">
+        <v>20</v>
+      </c>
+      <c r="F223" s="3">
+        <f t="shared" si="5"/>
+        <v>36.027867768209042</v>
+      </c>
+      <c r="G223" s="1"/>
+      <c r="H223" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C224" s="8">
+        <v>152</v>
+      </c>
+      <c r="D224" s="4">
+        <v>89.986523929471005</v>
+      </c>
+      <c r="E224" s="6">
+        <v>20</v>
+      </c>
+      <c r="F224" s="3">
+        <f t="shared" si="5"/>
+        <v>71.989219143576804</v>
+      </c>
+      <c r="G224" s="1"/>
+      <c r="H224" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B225" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C225" s="8">
+        <v>160</v>
+      </c>
+      <c r="D225" s="4">
+        <v>89.986523929471005</v>
+      </c>
+      <c r="E225" s="6">
+        <v>20</v>
+      </c>
+      <c r="F225" s="3">
+        <f t="shared" si="5"/>
+        <v>71.989219143576804</v>
+      </c>
+      <c r="G225" s="1"/>
+      <c r="H225" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C226" s="8">
+        <v>116</v>
+      </c>
+      <c r="D226" s="4">
+        <v>40.948176724137902</v>
+      </c>
+      <c r="E226" s="6">
+        <v>20</v>
+      </c>
+      <c r="F226" s="3">
+        <f t="shared" si="5"/>
+        <v>32.758541379310323</v>
+      </c>
+      <c r="G226" s="1"/>
+      <c r="H226" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B227" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C227" s="8">
+        <v>168</v>
+      </c>
+      <c r="D227" s="4">
+        <v>43.118544441749499</v>
+      </c>
+      <c r="E227" s="6">
+        <v>20</v>
+      </c>
+      <c r="F227" s="3">
+        <f t="shared" si="5"/>
+        <v>34.494835553399597</v>
+      </c>
+      <c r="G227" s="1"/>
+      <c r="H227" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B228" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C228" s="8">
+        <v>120</v>
+      </c>
+      <c r="D228" s="4">
+        <v>87.342072326398593</v>
+      </c>
+      <c r="E228" s="6">
+        <v>20</v>
+      </c>
+      <c r="F228" s="3">
+        <f t="shared" si="5"/>
+        <v>69.873657861118872</v>
+      </c>
+      <c r="G228" s="1"/>
+      <c r="H228" s="7"/>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C229" s="8">
+        <v>160</v>
+      </c>
+      <c r="D229" s="4">
+        <v>42.479528125000002</v>
+      </c>
+      <c r="E229" s="6">
+        <v>20</v>
+      </c>
+      <c r="F229" s="3">
+        <f t="shared" si="5"/>
+        <v>33.983622500000003</v>
+      </c>
+      <c r="G229" s="1"/>
+      <c r="H229" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B230" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C230" s="8">
+        <v>166</v>
+      </c>
+      <c r="D230" s="4">
+        <v>32.183252734025302</v>
+      </c>
+      <c r="E230" s="6">
+        <v>20</v>
+      </c>
+      <c r="F230" s="3">
+        <f t="shared" si="5"/>
+        <v>25.74660218722024</v>
+      </c>
+      <c r="G230" s="1"/>
+      <c r="H230" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B231" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C231" s="8">
+        <v>138</v>
+      </c>
+      <c r="D231" s="4">
+        <v>56.936981765649499</v>
+      </c>
+      <c r="E231" s="6">
+        <v>20</v>
+      </c>
+      <c r="F231" s="3">
+        <f t="shared" si="5"/>
+        <v>45.549585412519598</v>
+      </c>
+      <c r="G231" s="1"/>
+      <c r="H231" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B232" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C232" s="8">
+        <v>182</v>
+      </c>
+      <c r="D232" s="4">
+        <v>42.335981090293998</v>
+      </c>
+      <c r="E232" s="6">
+        <v>20</v>
+      </c>
+      <c r="F232" s="3">
+        <f t="shared" si="5"/>
+        <v>33.868784872235196</v>
+      </c>
+      <c r="G232" s="1"/>
+      <c r="H232" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B233" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C233" s="8">
+        <v>151</v>
+      </c>
+      <c r="D233" s="4">
+        <v>57.761796774193598</v>
+      </c>
+      <c r="E233" s="6">
+        <v>20</v>
+      </c>
+      <c r="F233" s="3">
+        <f t="shared" si="5"/>
+        <v>46.209437419354877</v>
+      </c>
+      <c r="G233" s="1"/>
+      <c r="H233" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B234" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C234" s="8">
+        <v>136</v>
+      </c>
+      <c r="D234" s="4">
+        <v>30.212524501078299</v>
+      </c>
+      <c r="E234" s="6">
+        <v>20</v>
+      </c>
+      <c r="F234" s="3">
+        <f t="shared" si="5"/>
+        <v>24.170019600862638</v>
+      </c>
+      <c r="G234" s="1"/>
+      <c r="H234" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B235" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C235" s="8">
+        <v>144</v>
+      </c>
+      <c r="D235" s="4">
+        <v>39.417273809523799</v>
+      </c>
+      <c r="E235" s="6">
+        <v>20</v>
+      </c>
+      <c r="F235" s="3">
+        <f t="shared" si="5"/>
+        <v>31.533819047619041</v>
+      </c>
+      <c r="G235" s="1"/>
+      <c r="H235" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B236" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C236" s="8">
+        <v>152</v>
+      </c>
+      <c r="D236" s="4">
+        <v>42.463784231380203</v>
+      </c>
+      <c r="E236" s="6">
+        <v>20</v>
+      </c>
+      <c r="F236" s="3">
+        <f t="shared" si="5"/>
+        <v>33.971027385104165</v>
+      </c>
+      <c r="G236" s="1"/>
+      <c r="H236" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B237" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C237" s="8">
+        <v>166</v>
+      </c>
+      <c r="D237" s="4">
+        <v>45.615204420515198</v>
+      </c>
+      <c r="E237" s="6">
+        <v>20</v>
+      </c>
+      <c r="F237" s="3">
+        <f t="shared" si="5"/>
+        <v>36.492163536412157</v>
+      </c>
+      <c r="G237" s="1"/>
+      <c r="H237" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B238" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C238" s="8">
+        <v>90</v>
+      </c>
+      <c r="D238" s="4">
+        <v>92.099738683127597</v>
+      </c>
+      <c r="E238" s="6">
+        <v>20</v>
+      </c>
+      <c r="F238" s="3">
+        <f t="shared" si="5"/>
+        <v>73.679790946502081</v>
+      </c>
+      <c r="G238" s="1"/>
+      <c r="H238" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B239" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C239" s="8">
+        <v>24</v>
+      </c>
+      <c r="D239" s="4">
+        <v>17.9812986111111</v>
+      </c>
+      <c r="E239" s="6">
+        <v>20</v>
+      </c>
+      <c r="F239" s="3">
+        <f t="shared" si="5"/>
+        <v>14.38503888888888</v>
+      </c>
+      <c r="G239" s="1"/>
+      <c r="H239" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B240" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C240" s="8">
+        <v>160</v>
+      </c>
+      <c r="D240" s="4">
+        <v>27.506303393213599</v>
+      </c>
+      <c r="E240" s="6">
+        <v>20</v>
+      </c>
+      <c r="F240" s="3">
+        <f t="shared" si="5"/>
+        <v>22.00504271457088</v>
+      </c>
+      <c r="G240" s="1"/>
+      <c r="H240" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B241" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C241" s="8"/>
+      <c r="D241" s="4"/>
+      <c r="E241" s="6">
+        <v>20</v>
+      </c>
+      <c r="F241" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G241" s="1"/>
+      <c r="H241" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B242" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C242" s="8">
+        <v>173</v>
+      </c>
+      <c r="D242" s="4">
+        <v>45.780756692200697</v>
+      </c>
+      <c r="E242" s="6">
+        <v>20</v>
+      </c>
+      <c r="F242" s="3">
+        <f t="shared" si="5"/>
+        <v>36.624605353760558</v>
+      </c>
+      <c r="G242" s="1"/>
+      <c r="H242" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B243" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C243" s="8">
+        <v>128</v>
+      </c>
+      <c r="D243" s="4">
+        <v>90.135102430555605</v>
+      </c>
+      <c r="E243" s="6">
+        <v>20</v>
+      </c>
+      <c r="F243" s="3">
+        <f t="shared" si="5"/>
+        <v>72.108081944444478</v>
+      </c>
+      <c r="G243" s="1"/>
+      <c r="H243" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B244" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C244" s="8">
+        <v>176</v>
+      </c>
+      <c r="D244" s="4">
+        <v>44.902997023809498</v>
+      </c>
+      <c r="E244" s="6">
+        <v>20</v>
+      </c>
+      <c r="F244" s="3">
+        <f t="shared" si="5"/>
+        <v>35.922397619047601</v>
+      </c>
+      <c r="G244" s="1"/>
+      <c r="H244" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B245" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C245" s="8">
+        <v>168</v>
+      </c>
+      <c r="D245" s="4">
+        <v>39.417273809523799</v>
+      </c>
+      <c r="E245" s="6">
+        <v>20</v>
+      </c>
+      <c r="F245" s="3">
+        <f t="shared" si="5"/>
+        <v>31.533819047619041</v>
+      </c>
+      <c r="G245" s="1"/>
+      <c r="H245" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B246" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C246" s="8">
+        <v>144</v>
+      </c>
+      <c r="D246" s="4">
+        <v>66.040613671944897</v>
+      </c>
+      <c r="E246" s="6">
+        <v>20</v>
+      </c>
+      <c r="F246" s="3">
+        <f t="shared" si="5"/>
+        <v>52.832490937555917</v>
+      </c>
+      <c r="G246" s="1"/>
+      <c r="H246" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B247" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C247" s="8">
+        <v>168</v>
+      </c>
+      <c r="D247" s="4">
+        <v>35.147493750000002</v>
+      </c>
+      <c r="E247" s="6">
+        <v>20</v>
+      </c>
+      <c r="F247" s="3">
+        <f t="shared" si="5"/>
+        <v>28.117995000000001</v>
+      </c>
+      <c r="G247" s="1"/>
+      <c r="H247" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B248" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C248" s="8">
+        <v>159</v>
+      </c>
+      <c r="D248" s="4">
+        <v>44.738621807461598</v>
+      </c>
+      <c r="E248" s="6">
+        <v>20</v>
+      </c>
+      <c r="F248" s="3">
+        <f t="shared" si="5"/>
+        <v>35.790897445969279</v>
+      </c>
+      <c r="G248" s="1"/>
+      <c r="H248" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B249" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C249" s="8">
+        <v>136</v>
+      </c>
+      <c r="D249" s="4">
+        <v>90.054265522875795</v>
+      </c>
+      <c r="E249" s="6">
+        <v>20</v>
+      </c>
+      <c r="F249" s="3">
+        <f t="shared" si="5"/>
+        <v>72.043412418300633</v>
+      </c>
+      <c r="G249" s="1"/>
+      <c r="H249" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B250" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C250" s="8">
+        <v>72</v>
+      </c>
+      <c r="D250" s="4">
+        <v>92.425481481481498</v>
+      </c>
+      <c r="E250" s="6">
+        <v>20</v>
+      </c>
+      <c r="F250" s="3">
+        <f t="shared" si="5"/>
+        <v>73.940385185185193</v>
+      </c>
+      <c r="G250" s="1"/>
+      <c r="H250" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B251" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C251" s="8">
+        <v>160</v>
+      </c>
+      <c r="D251" s="4">
+        <v>28.101851914029101</v>
+      </c>
+      <c r="E251" s="6">
+        <v>20</v>
+      </c>
+      <c r="F251" s="3">
+        <f t="shared" si="5"/>
+        <v>22.481481531223281</v>
+      </c>
+      <c r="G251" s="1"/>
+      <c r="H251" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B252" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C252" s="8">
+        <v>154</v>
+      </c>
+      <c r="D252" s="4">
+        <v>41.581935064935102</v>
+      </c>
+      <c r="E252" s="6">
+        <v>20</v>
+      </c>
+      <c r="F252" s="3">
+        <f t="shared" si="5"/>
+        <v>33.26554805194808</v>
+      </c>
+      <c r="G252" s="1"/>
+      <c r="H252" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B253" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C253" s="8">
+        <v>160</v>
+      </c>
+      <c r="D253" s="4">
+        <v>33.4537949404762</v>
+      </c>
+      <c r="E253" s="6">
+        <v>20</v>
+      </c>
+      <c r="F253" s="3">
+        <f t="shared" si="5"/>
+        <v>26.76303595238096</v>
+      </c>
+      <c r="G253" s="1"/>
+      <c r="H253" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B254" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C254" s="8">
+        <v>168</v>
+      </c>
+      <c r="D254" s="4">
+        <v>46.194493749999999</v>
+      </c>
+      <c r="E254" s="6">
+        <v>20</v>
+      </c>
+      <c r="F254" s="3">
+        <f t="shared" si="5"/>
+        <v>36.955595000000002</v>
+      </c>
+      <c r="G254" s="1"/>
+      <c r="H254" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B255" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C255" s="8">
+        <v>37</v>
+      </c>
+      <c r="D255" s="4">
+        <v>90.513866102878694</v>
+      </c>
+      <c r="E255" s="6">
+        <v>20</v>
+      </c>
+      <c r="F255" s="3">
+        <f t="shared" si="5"/>
+        <v>72.411092882302952</v>
+      </c>
+      <c r="G255" s="1"/>
+      <c r="H255" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B256" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C256" s="8">
+        <v>136</v>
+      </c>
+      <c r="D256" s="4">
+        <v>52.548104071482101</v>
+      </c>
+      <c r="E256" s="6">
+        <v>20</v>
+      </c>
+      <c r="F256" s="3">
+        <f t="shared" si="5"/>
+        <v>42.038483257185682</v>
+      </c>
+      <c r="G256" s="1"/>
+      <c r="H256" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B257" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C257" s="8">
+        <v>160</v>
+      </c>
+      <c r="D257" s="4">
+        <v>34.924801758489203</v>
+      </c>
+      <c r="E257" s="6">
+        <v>20</v>
+      </c>
+      <c r="F257" s="3">
+        <f t="shared" si="5"/>
+        <v>27.939841406791363</v>
+      </c>
+      <c r="G257" s="1"/>
+      <c r="H257" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B258" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C258" s="8">
+        <v>144</v>
+      </c>
+      <c r="D258" s="4">
+        <v>68.780731481481496</v>
+      </c>
+      <c r="E258" s="6">
+        <v>20</v>
+      </c>
+      <c r="F258" s="3">
+        <f t="shared" si="5"/>
+        <v>55.024585185185195</v>
+      </c>
+      <c r="G258" s="1"/>
+      <c r="H258" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B259" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C259" s="8">
+        <v>152</v>
+      </c>
+      <c r="D259" s="4">
+        <v>72.186617300194897</v>
+      </c>
+      <c r="E259" s="6">
+        <v>20</v>
+      </c>
+      <c r="F259" s="3">
+        <f t="shared" si="5"/>
+        <v>57.749293840155914</v>
+      </c>
+      <c r="G259" s="1"/>
+      <c r="H259" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B260" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C260" s="8">
+        <v>176</v>
+      </c>
+      <c r="D260" s="4">
+        <v>24.612914772727301</v>
+      </c>
+      <c r="E260" s="6">
+        <v>20</v>
+      </c>
+      <c r="F260" s="3">
+        <f t="shared" si="5"/>
+        <v>19.690331818181839</v>
+      </c>
+      <c r="G260" s="1"/>
+      <c r="H260" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B261" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C261" s="8">
+        <v>168</v>
+      </c>
+      <c r="D261" s="4">
+        <v>27.2189743589744</v>
+      </c>
+      <c r="E261" s="6">
+        <v>20</v>
+      </c>
+      <c r="F261" s="3">
+        <f t="shared" si="5"/>
+        <v>21.775179487179521</v>
+      </c>
+      <c r="G261" s="1"/>
+      <c r="H261" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B262" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C262" s="8">
+        <v>160</v>
+      </c>
+      <c r="D262" s="4">
+        <v>24.743217752039602</v>
+      </c>
+      <c r="E262" s="6">
+        <v>20</v>
+      </c>
+      <c r="F262" s="3">
+        <f t="shared" si="5"/>
+        <v>19.794574201631683</v>
+      </c>
+      <c r="G262" s="1"/>
+      <c r="H262" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B263" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C263" s="8">
+        <v>168</v>
+      </c>
+      <c r="D263" s="4">
+        <v>32.8333992986543</v>
+      </c>
+      <c r="E263" s="6">
+        <v>20</v>
+      </c>
+      <c r="F263" s="3">
+        <f t="shared" si="5"/>
+        <v>26.266719438923438</v>
+      </c>
+      <c r="G263" s="1"/>
+      <c r="H263" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B264" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C264" s="8">
+        <v>176</v>
+      </c>
+      <c r="D264" s="4">
+        <v>32.186248637203597</v>
+      </c>
+      <c r="E264" s="6">
+        <v>20</v>
+      </c>
+      <c r="F264" s="3">
+        <f t="shared" si="5"/>
+        <v>25.748998909762879</v>
+      </c>
+      <c r="G264" s="1"/>
+      <c r="H264" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B265" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C265" s="8">
+        <v>160</v>
+      </c>
+      <c r="D265" s="4">
+        <v>25.544377833850898</v>
+      </c>
+      <c r="E265" s="6">
+        <v>20</v>
+      </c>
+      <c r="F265" s="3">
+        <f t="shared" si="5"/>
+        <v>20.435502267080718</v>
+      </c>
+      <c r="G265" s="1"/>
+      <c r="H265" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B266" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C266" s="8">
+        <v>168</v>
+      </c>
+      <c r="D266" s="4">
+        <v>39.814689156314699</v>
+      </c>
+      <c r="E266" s="6">
+        <v>20</v>
+      </c>
+      <c r="F266" s="3">
+        <f t="shared" si="5"/>
+        <v>31.851751325051758</v>
+      </c>
+      <c r="G266" s="1"/>
+      <c r="H266" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B267" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C267" s="8">
+        <v>144</v>
+      </c>
+      <c r="D267" s="4">
+        <v>24.154722222222201</v>
+      </c>
+      <c r="E267" s="6">
+        <v>20</v>
+      </c>
+      <c r="F267" s="3">
+        <f t="shared" si="5"/>
+        <v>19.32377777777776</v>
+      </c>
+      <c r="G267" s="1"/>
+      <c r="H267" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B268" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C268" s="8">
+        <v>152</v>
+      </c>
+      <c r="D268" s="4">
+        <v>25.026456962719301</v>
+      </c>
+      <c r="E268" s="6">
+        <v>20</v>
+      </c>
+      <c r="F268" s="3">
+        <f t="shared" ref="F268:F285" si="6">D268-(D268*E268)/100</f>
+        <v>20.021165570175441</v>
+      </c>
+      <c r="G268" s="1"/>
+      <c r="H268" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B269" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C269" s="8">
+        <v>64</v>
+      </c>
+      <c r="D269" s="4">
+        <v>46.829870288624797</v>
+      </c>
+      <c r="E269" s="6">
+        <v>20</v>
+      </c>
+      <c r="F269" s="3">
+        <f t="shared" si="6"/>
+        <v>37.463896230899834</v>
+      </c>
+      <c r="G269" s="1"/>
+      <c r="H269" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B270" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C270" s="8">
+        <v>140</v>
+      </c>
+      <c r="D270" s="4">
+        <v>38.643855581693799</v>
+      </c>
+      <c r="E270" s="6">
+        <v>20</v>
+      </c>
+      <c r="F270" s="3">
+        <f t="shared" si="6"/>
+        <v>30.91508446535504</v>
+      </c>
+      <c r="G270" s="1"/>
+      <c r="H270" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B271" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C271" s="8">
+        <v>120</v>
+      </c>
+      <c r="D271" s="4">
+        <v>64.815526315789498</v>
+      </c>
+      <c r="E271" s="6">
+        <v>20</v>
+      </c>
+      <c r="F271" s="3">
+        <f t="shared" si="6"/>
+        <v>51.852421052631598</v>
+      </c>
+      <c r="G271" s="1"/>
+      <c r="H271" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B272" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C272" s="8">
+        <v>152</v>
+      </c>
+      <c r="D272" s="4">
+        <v>64.815526315789498</v>
+      </c>
+      <c r="E272" s="6">
+        <v>20</v>
+      </c>
+      <c r="F272" s="3">
+        <f t="shared" si="6"/>
+        <v>51.852421052631598</v>
+      </c>
+      <c r="G272" s="1"/>
+      <c r="H272" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B273" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C273" s="8">
+        <v>144</v>
+      </c>
+      <c r="D273" s="4">
+        <v>39.1587380818318</v>
+      </c>
+      <c r="E273" s="6">
+        <v>20</v>
+      </c>
+      <c r="F273" s="3">
+        <f t="shared" si="6"/>
+        <v>31.326990465465439</v>
+      </c>
+      <c r="G273" s="1"/>
+      <c r="H273" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B274" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C274" s="8">
+        <v>40</v>
+      </c>
+      <c r="D274" s="4">
+        <v>86.500167592592604</v>
+      </c>
+      <c r="E274" s="6">
+        <v>20</v>
+      </c>
+      <c r="F274" s="3">
+        <f t="shared" si="6"/>
+        <v>69.200134074074086</v>
+      </c>
+      <c r="G274" s="1"/>
+      <c r="H274" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B275" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C275" s="8">
+        <v>16</v>
+      </c>
+      <c r="D275" s="4">
+        <v>92.425481481481498</v>
+      </c>
+      <c r="E275" s="6">
+        <v>20</v>
+      </c>
+      <c r="F275" s="3">
+        <f t="shared" si="6"/>
+        <v>73.940385185185193</v>
+      </c>
+      <c r="G275" s="1"/>
+      <c r="H275" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B276" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C276" s="8">
+        <v>176</v>
+      </c>
+      <c r="D276" s="4">
+        <v>44.903615728305802</v>
+      </c>
+      <c r="E276" s="6">
+        <v>20</v>
+      </c>
+      <c r="F276" s="3">
+        <f t="shared" si="6"/>
+        <v>35.922892582644643</v>
+      </c>
+      <c r="G276" s="1"/>
+      <c r="H276" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B277" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C277" s="8">
+        <v>128</v>
+      </c>
+      <c r="D277" s="4">
+        <v>84.958689120370394</v>
+      </c>
+      <c r="E277" s="6">
+        <v>20</v>
+      </c>
+      <c r="F277" s="3">
+        <f t="shared" si="6"/>
+        <v>67.966951296296315</v>
+      </c>
+      <c r="G277" s="1"/>
+      <c r="H277" s="7"/>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B278" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C278" s="8">
+        <v>154</v>
+      </c>
+      <c r="D278" s="4">
+        <v>41.581935064935102</v>
+      </c>
+      <c r="E278" s="6">
+        <v>20</v>
+      </c>
+      <c r="F278" s="3">
+        <f t="shared" si="6"/>
+        <v>33.26554805194808</v>
+      </c>
+      <c r="G278" s="1"/>
+      <c r="H278" s="7"/>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B279" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C279" s="8">
+        <v>152</v>
+      </c>
+      <c r="D279" s="4">
+        <v>34.176445812588902</v>
+      </c>
+      <c r="E279" s="6">
+        <v>20</v>
+      </c>
+      <c r="F279" s="3">
+        <f t="shared" si="6"/>
+        <v>27.34115665007112</v>
+      </c>
+      <c r="G279" s="1"/>
+      <c r="H279" s="7"/>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B280" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C280" s="8">
+        <v>144</v>
+      </c>
+      <c r="D280" s="4">
+        <v>28.5937359041422</v>
+      </c>
+      <c r="E280" s="6">
+        <v>20</v>
+      </c>
+      <c r="F280" s="3">
+        <f t="shared" si="6"/>
+        <v>22.874988723313759</v>
+      </c>
+      <c r="G280" s="1"/>
+      <c r="H280" s="7"/>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B281" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C281" s="8">
+        <v>56</v>
+      </c>
+      <c r="D281" s="4">
+        <v>72.440430555555594</v>
+      </c>
+      <c r="E281" s="6">
+        <v>20</v>
+      </c>
+      <c r="F281" s="3">
+        <f t="shared" si="6"/>
+        <v>57.952344444444478</v>
+      </c>
+      <c r="G281" s="1"/>
+      <c r="H281" s="7"/>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B282" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C282" s="8">
+        <v>173</v>
+      </c>
+      <c r="D282" s="4">
+        <v>44.207474234800998</v>
+      </c>
+      <c r="E282" s="6">
+        <v>20</v>
+      </c>
+      <c r="F282" s="3">
+        <f t="shared" si="6"/>
+        <v>35.365979387840795</v>
+      </c>
+      <c r="G282" s="1"/>
+      <c r="H282" s="7"/>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B283" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C283" s="8">
+        <v>175</v>
+      </c>
+      <c r="D283" s="4">
+        <v>57.2577432684717</v>
+      </c>
+      <c r="E283" s="6">
+        <v>20</v>
+      </c>
+      <c r="F283" s="3">
+        <f t="shared" si="6"/>
+        <v>45.806194614777361</v>
+      </c>
+      <c r="G283" s="1"/>
+      <c r="H283" s="7"/>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B284" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C284" s="8">
+        <v>80</v>
+      </c>
+      <c r="D284" s="4">
+        <v>92.181585726280403</v>
+      </c>
+      <c r="E284" s="6">
+        <v>20</v>
+      </c>
+      <c r="F284" s="3">
+        <f t="shared" si="6"/>
+        <v>73.74526858102432</v>
+      </c>
+      <c r="G284" s="1"/>
+      <c r="H284" s="7"/>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B285" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C285" s="8">
+        <v>168</v>
+      </c>
+      <c r="D285" s="4">
+        <v>35.5917846645753</v>
+      </c>
+      <c r="E285" s="6">
+        <v>20</v>
+      </c>
+      <c r="F285" s="3">
+        <f t="shared" si="6"/>
+        <v>28.473427731660241</v>
+      </c>
+      <c r="G285" s="1"/>
+      <c r="H285" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G213">
+  <autoFilter ref="A1:G285">
     <filterColumn colId="0"/>
     <filterColumn colId="1"/>
   </autoFilter>
@@ -6383,6 +8142,67 @@
     <hyperlink ref="H203" r:id="rId182"/>
     <hyperlink ref="H204" r:id="rId183"/>
     <hyperlink ref="H169" r:id="rId184" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="G214" r:id="rId185"/>
+    <hyperlink ref="H214" r:id="rId186"/>
+    <hyperlink ref="H215" r:id="rId187"/>
+    <hyperlink ref="H217" r:id="rId188"/>
+    <hyperlink ref="H218" r:id="rId189"/>
+    <hyperlink ref="H219" r:id="rId190"/>
+    <hyperlink ref="H220" r:id="rId191"/>
+    <hyperlink ref="H221" r:id="rId192"/>
+    <hyperlink ref="H223" r:id="rId193"/>
+    <hyperlink ref="H224" r:id="rId194"/>
+    <hyperlink ref="H225" r:id="rId195"/>
+    <hyperlink ref="H226" r:id="rId196"/>
+    <hyperlink ref="H227" r:id="rId197"/>
+    <hyperlink ref="H229" r:id="rId198"/>
+    <hyperlink ref="H230" r:id="rId199"/>
+    <hyperlink ref="H231" r:id="rId200"/>
+    <hyperlink ref="H232" r:id="rId201"/>
+    <hyperlink ref="H233" r:id="rId202"/>
+    <hyperlink ref="H234" r:id="rId203"/>
+    <hyperlink ref="H235" r:id="rId204"/>
+    <hyperlink ref="H236" r:id="rId205"/>
+    <hyperlink ref="H237" r:id="rId206"/>
+    <hyperlink ref="H238" r:id="rId207"/>
+    <hyperlink ref="H239" r:id="rId208"/>
+    <hyperlink ref="H240" r:id="rId209"/>
+    <hyperlink ref="H242" r:id="rId210"/>
+    <hyperlink ref="H243" r:id="rId211"/>
+    <hyperlink ref="H244" r:id="rId212"/>
+    <hyperlink ref="H245" r:id="rId213"/>
+    <hyperlink ref="H246" r:id="rId214"/>
+    <hyperlink ref="H247" r:id="rId215"/>
+    <hyperlink ref="H248" r:id="rId216"/>
+    <hyperlink ref="H249" r:id="rId217"/>
+    <hyperlink ref="H250" r:id="rId218"/>
+    <hyperlink ref="H251" r:id="rId219"/>
+    <hyperlink ref="H252" r:id="rId220"/>
+    <hyperlink ref="H253" r:id="rId221"/>
+    <hyperlink ref="H254" r:id="rId222"/>
+    <hyperlink ref="H255" r:id="rId223"/>
+    <hyperlink ref="H256" r:id="rId224"/>
+    <hyperlink ref="H257" r:id="rId225"/>
+    <hyperlink ref="H258" r:id="rId226"/>
+    <hyperlink ref="H259" r:id="rId227"/>
+    <hyperlink ref="H260" r:id="rId228"/>
+    <hyperlink ref="H261" r:id="rId229"/>
+    <hyperlink ref="H262" r:id="rId230"/>
+    <hyperlink ref="H263" r:id="rId231"/>
+    <hyperlink ref="H264" r:id="rId232"/>
+    <hyperlink ref="H265" r:id="rId233"/>
+    <hyperlink ref="H266" r:id="rId234"/>
+    <hyperlink ref="H267" r:id="rId235"/>
+    <hyperlink ref="H268" r:id="rId236"/>
+    <hyperlink ref="H269" r:id="rId237"/>
+    <hyperlink ref="H270" r:id="rId238"/>
+    <hyperlink ref="H271" r:id="rId239"/>
+    <hyperlink ref="H272" r:id="rId240"/>
+    <hyperlink ref="H273" r:id="rId241"/>
+    <hyperlink ref="H274" r:id="rId242"/>
+    <hyperlink ref="H275" r:id="rId243"/>
+    <hyperlink ref="H276" r:id="rId244"/>
+    <hyperlink ref="H241" r:id="rId245" display="mailto:cyborg.3@hotmail.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6390,1401 +8210,1699 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R42"/>
+  <dimension ref="D1:L87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:12">
+      <c r="D1" s="18">
+        <v>46023</v>
+      </c>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="4:12">
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="4:12">
+      <c r="D3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F3" s="8">
+        <v>176</v>
+      </c>
+      <c r="G3" s="4">
+        <v>39.702951679841902</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K3" s="8">
+        <v>144</v>
+      </c>
+      <c r="L3" s="4">
+        <v>37.519305620081397</v>
+      </c>
+    </row>
+    <row r="4" spans="4:12">
+      <c r="D4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F4" s="8">
+        <v>136</v>
+      </c>
+      <c r="G4" s="4">
+        <v>39.409404411764697</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K4" s="8">
+        <v>176</v>
+      </c>
+      <c r="L4" s="4">
+        <v>37.510418065268098</v>
+      </c>
+    </row>
+    <row r="5" spans="4:12">
+      <c r="D5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F5" s="8">
+        <v>160</v>
+      </c>
+      <c r="G5" s="4">
+        <v>39.2927051282051</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K5" s="8">
+        <v>152</v>
+      </c>
+      <c r="L5" s="4">
+        <v>36.976850232618801</v>
+      </c>
+    </row>
+    <row r="6" spans="4:12">
+      <c r="D6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F6" s="8">
+        <v>156</v>
+      </c>
+      <c r="G6" s="4">
+        <v>38.682580453574197</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K6" s="8">
+        <v>160</v>
+      </c>
+      <c r="L6" s="4">
+        <v>34.624721874999999</v>
+      </c>
+    </row>
+    <row r="7" spans="4:12">
+      <c r="D7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F7" s="8">
+        <v>184</v>
+      </c>
+      <c r="G7" s="4">
+        <v>38.506148753544402</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K7" s="8">
+        <v>152</v>
+      </c>
+      <c r="L7" s="4">
+        <v>34.535883767887498</v>
+      </c>
+    </row>
+    <row r="8" spans="4:12">
+      <c r="I8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K8" s="8">
+        <v>160</v>
+      </c>
+      <c r="L8" s="4">
+        <v>34.471468407258101</v>
+      </c>
+    </row>
+    <row r="9" spans="4:12">
+      <c r="I9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K9" s="8">
+        <v>176</v>
+      </c>
+      <c r="L9" s="4">
+        <v>29.4018927861344</v>
+      </c>
+    </row>
+    <row r="10" spans="4:12">
+      <c r="I10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K10" s="8">
+        <v>168</v>
+      </c>
+      <c r="L10" s="4">
+        <v>27.674382142857201</v>
+      </c>
+    </row>
+    <row r="13" spans="4:12">
+      <c r="D13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="4:12">
+      <c r="D14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F14" s="8">
+        <v>64</v>
+      </c>
+      <c r="G14" s="4">
+        <v>53.360546874999997</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K14" s="8">
+        <v>104</v>
+      </c>
+      <c r="L14" s="4">
+        <v>37.3064931165299</v>
+      </c>
+    </row>
+    <row r="15" spans="4:12">
+      <c r="D15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F15" s="8">
+        <v>64</v>
+      </c>
+      <c r="G15" s="4">
+        <v>52.498907049813603</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K15" s="8">
+        <v>112</v>
+      </c>
+      <c r="L15" s="4">
+        <v>34.708821428571397</v>
+      </c>
+    </row>
+    <row r="16" spans="4:12">
+      <c r="D16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F16" s="8">
+        <v>96</v>
+      </c>
+      <c r="G16" s="4">
+        <v>52.285287259615401</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="10">
+        <v>46053</v>
+      </c>
+      <c r="K16" s="8">
+        <v>104</v>
+      </c>
+      <c r="L16" s="4">
+        <v>34.708821428571397</v>
+      </c>
+    </row>
+    <row r="17" spans="4:12">
+      <c r="D17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F17" s="8">
+        <v>80</v>
+      </c>
+      <c r="G17" s="4">
+        <v>50.410741517857197</v>
+      </c>
+    </row>
+    <row r="18" spans="4:12">
+      <c r="D18" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F18" s="8">
+        <v>112</v>
+      </c>
+      <c r="G18" s="4">
+        <v>49.238255357142798</v>
+      </c>
+    </row>
+    <row r="19" spans="4:12">
+      <c r="D19" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F19" s="8">
+        <v>96</v>
+      </c>
+      <c r="G19" s="4">
+        <v>44.4461330572394</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12">
+      <c r="D20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F20" s="8">
+        <v>96</v>
+      </c>
+      <c r="G20" s="4">
+        <v>43.054450000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12">
+      <c r="D21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="10">
+        <v>46053</v>
+      </c>
+      <c r="F21" s="8">
+        <v>112</v>
+      </c>
+      <c r="G21" s="4">
+        <v>38.512924107142901</v>
+      </c>
+    </row>
+    <row r="25" spans="4:12">
+      <c r="D25" s="18">
+        <v>46054</v>
+      </c>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="4:12">
+      <c r="D26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="4:12">
+      <c r="D27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F27" s="8">
+        <v>160</v>
+      </c>
+      <c r="G27" s="4">
+        <v>43.671285941644598</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K27" s="8">
+        <v>168</v>
+      </c>
+      <c r="L27" s="4">
+        <v>37.711496758482298</v>
+      </c>
+    </row>
+    <row r="28" spans="4:12">
+      <c r="D28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F28" s="8">
+        <v>168</v>
+      </c>
+      <c r="G28" s="4">
+        <v>43.6260912268948</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K28" s="8">
+        <v>160</v>
+      </c>
+      <c r="L28" s="4">
+        <v>37.256393326648798</v>
+      </c>
+    </row>
+    <row r="29" spans="4:12">
+      <c r="D29" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F29" s="8">
+        <v>152</v>
+      </c>
+      <c r="G29" s="4">
+        <v>43.029939393939401</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K29" s="8">
+        <v>184</v>
+      </c>
+      <c r="L29" s="4">
+        <v>36.845269002736401</v>
+      </c>
+    </row>
+    <row r="30" spans="4:12">
+      <c r="D30" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F30" s="8">
+        <v>160</v>
+      </c>
+      <c r="G30" s="4">
+        <v>41.528098620215999</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K30" s="8">
+        <v>152</v>
+      </c>
+      <c r="L30" s="4">
+        <v>36.625466666666703</v>
+      </c>
+    </row>
+    <row r="31" spans="4:12">
+      <c r="D31" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F31" s="8">
+        <v>168</v>
+      </c>
+      <c r="G31" s="4">
+        <v>40.696204348405999</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J31" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K31" s="8">
+        <v>168</v>
+      </c>
+      <c r="L31" s="4">
+        <v>35.995552894314798</v>
+      </c>
+    </row>
+    <row r="32" spans="4:12">
+      <c r="D32" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F32" s="8">
+        <v>152</v>
+      </c>
+      <c r="G32" s="4">
+        <v>40.663364801600402</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K32" s="8">
+        <v>168</v>
+      </c>
+      <c r="L32" s="4">
+        <v>34.831495886912798</v>
+      </c>
+    </row>
+    <row r="33" spans="4:12">
+      <c r="D33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F33" s="8">
+        <v>176</v>
+      </c>
+      <c r="G33" s="4">
+        <v>40.169399737639203</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K33" s="8">
+        <v>160</v>
+      </c>
+      <c r="L33" s="4">
+        <v>32.761814131069102</v>
+      </c>
+    </row>
+    <row r="37" spans="4:12">
+      <c r="D37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="4:12">
+      <c r="D38" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F38" s="8">
+        <v>128</v>
+      </c>
+      <c r="G38" s="4">
+        <v>66.332548387096693</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J38" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K38" s="8">
+        <v>144</v>
+      </c>
+      <c r="L38" s="4">
+        <v>36.750679158383001</v>
+      </c>
+    </row>
+    <row r="39" spans="4:12">
+      <c r="D39" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="10">
+        <v>46081</v>
+      </c>
+      <c r="F39" s="8">
+        <v>152</v>
+      </c>
+      <c r="G39" s="4">
+        <v>56.556982198955701</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K39" s="8">
+        <v>176</v>
+      </c>
+      <c r="L39" s="4">
+        <v>36.323564242534303</v>
+      </c>
+    </row>
+    <row r="40" spans="4:12">
+      <c r="I40" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K40" s="8">
+        <v>184</v>
+      </c>
+      <c r="L40" s="4">
+        <v>36.230015976961802</v>
+      </c>
+    </row>
+    <row r="41" spans="4:12">
+      <c r="I41" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K41" s="8">
+        <v>144</v>
+      </c>
+      <c r="L41" s="4">
+        <v>36.0253846326165</v>
+      </c>
+    </row>
+    <row r="42" spans="4:12">
+      <c r="I42" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K42" s="8">
+        <v>176</v>
+      </c>
+      <c r="L42" s="4">
+        <v>34.4800436046512</v>
+      </c>
+    </row>
+    <row r="43" spans="4:12">
+      <c r="I43" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J43" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K43" s="8">
+        <v>136</v>
+      </c>
+      <c r="L43" s="4">
+        <v>34.242610294117597</v>
+      </c>
+    </row>
+    <row r="44" spans="4:12">
+      <c r="I44" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K44" s="8">
+        <v>168</v>
+      </c>
+      <c r="L44" s="4">
+        <v>33.050941807209</v>
+      </c>
+    </row>
+    <row r="45" spans="4:12">
+      <c r="I45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K45" s="8">
+        <v>120</v>
+      </c>
+      <c r="L45" s="4">
+        <v>32.4255541666667</v>
+      </c>
+    </row>
+    <row r="46" spans="4:12">
+      <c r="I46" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J46" s="10">
+        <v>46081</v>
+      </c>
+      <c r="K46" s="8">
+        <v>184</v>
+      </c>
+      <c r="L46" s="4">
+        <v>30.628343023255798</v>
+      </c>
+    </row>
+    <row r="50" spans="4:12">
+      <c r="D50" s="18">
+        <v>46082</v>
+      </c>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+    </row>
+    <row r="51" spans="4:12">
+      <c r="D51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="4:12">
+      <c r="D52" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F52" s="8">
+        <v>160</v>
+      </c>
+      <c r="G52" s="4">
+        <v>48.483667763157897</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J52" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K52" s="8">
+        <v>176</v>
+      </c>
+      <c r="L52" s="4">
+        <v>39.799035847937198</v>
+      </c>
+    </row>
+    <row r="53" spans="4:12">
+      <c r="D53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F53" s="8">
+        <v>192</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46.480800646962898</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K53" s="8">
+        <v>176</v>
+      </c>
+      <c r="L53" s="4">
+        <v>39.235442307692303</v>
+      </c>
+    </row>
+    <row r="54" spans="4:12">
+      <c r="D54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F54" s="8">
+        <v>184</v>
+      </c>
+      <c r="G54" s="4">
+        <v>41.720992052147999</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K54" s="8">
+        <v>176</v>
+      </c>
+      <c r="L54" s="4">
+        <v>39.007290697674399</v>
+      </c>
+    </row>
+    <row r="55" spans="4:12">
+      <c r="D55" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F55" s="8">
+        <v>152</v>
+      </c>
+      <c r="G55" s="4">
+        <v>40.994675675675602</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K55" s="8">
+        <v>192</v>
+      </c>
+      <c r="L55" s="4">
+        <v>38.7876685971573</v>
+      </c>
+    </row>
+    <row r="56" spans="4:12">
+      <c r="I56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J56" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K56" s="8">
+        <v>184</v>
+      </c>
+      <c r="L56" s="4">
+        <v>38.716932052471599</v>
+      </c>
+    </row>
+    <row r="57" spans="4:12">
+      <c r="I57" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J57" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K57" s="8">
+        <v>192</v>
+      </c>
+      <c r="L57" s="4">
+        <v>38.0187393541066</v>
+      </c>
+    </row>
+    <row r="58" spans="4:12">
+      <c r="I58" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K58" s="8">
+        <v>192</v>
+      </c>
+      <c r="L58" s="4">
+        <v>37.414571740439598</v>
+      </c>
+    </row>
+    <row r="59" spans="4:12">
+      <c r="I59" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K59" s="8">
+        <v>172</v>
+      </c>
+      <c r="L59" s="4">
+        <v>35.941237012987003</v>
+      </c>
+    </row>
+    <row r="60" spans="4:12">
+      <c r="I60" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J60" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K60" s="8">
+        <v>144</v>
+      </c>
+      <c r="L60" s="4">
+        <v>34.7352384259259</v>
+      </c>
+    </row>
+    <row r="61" spans="4:12">
+      <c r="I61" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J61" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K61" s="8">
+        <v>200</v>
+      </c>
+      <c r="L61" s="4">
+        <v>34.204803703703703</v>
+      </c>
+    </row>
+    <row r="62" spans="4:12">
+      <c r="I62" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J62" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K62" s="8">
+        <v>168</v>
+      </c>
+      <c r="L62" s="4">
+        <v>33.0205925925926</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12">
+      <c r="D65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12">
+      <c r="D66" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E66" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F66" s="8">
+        <v>168</v>
+      </c>
+      <c r="G66" s="4">
+        <v>51.8</v>
+      </c>
+      <c r="I66" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K66" s="8">
+        <v>157</v>
+      </c>
+      <c r="L66" s="4">
+        <v>36.380000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12">
+      <c r="D67" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E67" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F67" s="8">
+        <v>168</v>
+      </c>
+      <c r="G67" s="4">
+        <v>49.35</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J67" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K67" s="8">
+        <v>184</v>
+      </c>
+      <c r="L67" s="4">
+        <v>35.35</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12">
+      <c r="D68" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F68" s="8">
+        <v>176</v>
+      </c>
+      <c r="G68" s="4">
+        <v>40.590000000000003</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J68" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K68" s="8">
+        <v>160</v>
+      </c>
+      <c r="L68" s="4">
+        <v>34.979999999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="4:12">
+      <c r="D69" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="10">
+        <v>46112</v>
+      </c>
+      <c r="F69" s="8">
+        <v>192</v>
+      </c>
+      <c r="G69" s="4">
+        <v>40.01</v>
+      </c>
+      <c r="I69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K69" s="8">
+        <v>136</v>
+      </c>
+      <c r="L69" s="4">
+        <v>34.630000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="4:12">
+      <c r="I70" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J70" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K70" s="8">
+        <v>168</v>
+      </c>
+      <c r="L70" s="4">
+        <v>33.22</v>
+      </c>
+    </row>
+    <row r="71" spans="4:12">
+      <c r="I71" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K71" s="8">
+        <v>168</v>
+      </c>
+      <c r="L71" s="4">
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="72" spans="4:12">
+      <c r="I72" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J72" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K72" s="8">
+        <v>176</v>
+      </c>
+      <c r="L72" s="4">
+        <v>32.67</v>
+      </c>
+    </row>
+    <row r="78" spans="4:12">
+      <c r="D78" s="18">
+        <v>46113</v>
+      </c>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
+      <c r="K78" s="19"/>
+      <c r="L78" s="19"/>
+    </row>
+    <row r="79" spans="4:12">
+      <c r="D79" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="4:12">
+      <c r="D80" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="8">
+        <v>168</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46.194493749999999</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J80" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K80" s="8">
+        <v>168</v>
+      </c>
+      <c r="L80" s="4">
+        <v>37.598206081081102</v>
+      </c>
+    </row>
+    <row r="81" spans="4:12">
+      <c r="D81" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E81" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F81" s="8">
+        <v>176</v>
+      </c>
+      <c r="G81" s="4">
+        <v>44.903615728305802</v>
+      </c>
+      <c r="I81" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J81" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K81" s="8">
+        <v>168</v>
+      </c>
+      <c r="L81" s="4">
+        <v>35.5917846645753</v>
+      </c>
+    </row>
+    <row r="82" spans="4:12">
+      <c r="D82" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F82" s="8">
+        <v>176</v>
+      </c>
+      <c r="G82" s="4">
+        <v>44.902997023809498</v>
+      </c>
+      <c r="I82" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J82" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K82" s="8">
+        <v>168</v>
+      </c>
+      <c r="L82" s="4">
+        <v>35.147493750000002</v>
+      </c>
+    </row>
+    <row r="83" spans="4:12">
+      <c r="D83" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F83" s="8">
+        <v>160</v>
+      </c>
+      <c r="G83" s="4">
+        <v>42.479528125000002</v>
+      </c>
+      <c r="I83" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J83" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K83" s="8">
+        <v>160</v>
+      </c>
+      <c r="L83" s="4">
+        <v>33.4537949404762</v>
+      </c>
+    </row>
+    <row r="84" spans="4:12">
+      <c r="D84" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F84" s="8">
+        <v>182</v>
+      </c>
+      <c r="G84" s="4">
+        <v>42.335981090293998</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J84" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K84" s="8">
+        <v>176</v>
+      </c>
+      <c r="L84" s="4">
+        <v>32.186248637203597</v>
+      </c>
+    </row>
+    <row r="85" spans="4:12">
+      <c r="D85" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F85" s="8">
+        <v>168</v>
+      </c>
+      <c r="G85" s="4">
+        <v>39.814689156314699</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K85" s="8">
+        <v>166</v>
+      </c>
+      <c r="L85" s="4">
+        <v>32.183252734025302</v>
+      </c>
+    </row>
+    <row r="86" spans="4:12">
+      <c r="D86" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E86" s="10">
+        <v>46142</v>
+      </c>
+      <c r="F86" s="8">
+        <v>144</v>
+      </c>
+      <c r="G86" s="4">
+        <v>39.1587380818318</v>
+      </c>
+      <c r="I86" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J86" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K86" s="8">
+        <v>176</v>
+      </c>
+      <c r="L86" s="4">
+        <v>31.106949346212499</v>
+      </c>
+    </row>
+    <row r="87" spans="4:12">
+      <c r="I87" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="10">
+        <v>46142</v>
+      </c>
+      <c r="K87" s="8">
+        <v>136</v>
+      </c>
+      <c r="L87" s="4">
+        <v>30.212524501078299</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="D78:L78"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C2" s="8">
+        <v>168</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46.194493749999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C3" s="8">
+        <v>176</v>
+      </c>
+      <c r="D3" s="4">
+        <v>44.903615728305802</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C4" s="8">
+        <v>176</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44.902997023809498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C5" s="8">
+        <v>160</v>
+      </c>
+      <c r="D5" s="4">
+        <v>42.479528125000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C6" s="8">
+        <v>182</v>
+      </c>
+      <c r="D6" s="4">
+        <v>42.335981090293998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C7" s="8">
+        <v>168</v>
+      </c>
+      <c r="D7" s="4">
+        <v>39.814689156314699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C8" s="8">
+        <v>144</v>
+      </c>
+      <c r="D8" s="4">
+        <v>39.1587380818318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C9" s="8">
+        <v>168</v>
+      </c>
+      <c r="D9" s="4">
+        <v>37.598206081081102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="9">
+      <c r="B10" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C10" s="8">
+        <v>168</v>
+      </c>
+      <c r="D10" s="4">
+        <v>35.5917846645753</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C11" s="8">
+        <v>168</v>
+      </c>
+      <c r="D11" s="4">
+        <v>35.147493750000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C12" s="8">
         <v>160</v>
       </c>
-      <c r="D2" s="4">
-        <v>38.182441082623697</v>
-      </c>
-      <c r="E2" s="6">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3">
-        <v>30.545952866098958</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L2" s="9">
-        <v>152</v>
-      </c>
-      <c r="M2" s="4">
-        <v>40.648450757575802</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q2" s="9">
-        <v>160</v>
-      </c>
-      <c r="R2" s="4">
-        <v>43.671285941644598</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="D12" s="4">
+        <v>33.4537949404762</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C13" s="8">
+        <v>176</v>
+      </c>
+      <c r="D13" s="4">
+        <v>32.186248637203597</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C14" s="8">
+        <v>166</v>
+      </c>
+      <c r="D14" s="4">
+        <v>32.183252734025302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C15" s="8">
+        <v>176</v>
+      </c>
+      <c r="D15" s="4">
+        <v>31.106949346212499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C16" s="8">
         <v>136</v>
       </c>
-      <c r="C3" s="9">
-        <v>80</v>
-      </c>
-      <c r="D3" s="4">
-        <v>50.7137183306141</v>
-      </c>
-      <c r="E3" s="6">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3">
-        <v>40.570974664491281</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L3" s="9">
-        <v>176</v>
-      </c>
-      <c r="M3" s="4">
-        <v>40.007166900922599</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>168</v>
-      </c>
-      <c r="R3" s="4">
-        <v>43.6260912268948</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="9">
-        <v>175</v>
-      </c>
-      <c r="D4" s="4">
-        <v>44.031594599410397</v>
-      </c>
-      <c r="E4" s="6">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3">
-        <v>35.225275679528316</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L4" s="9">
-        <v>168</v>
-      </c>
-      <c r="M4" s="4">
-        <v>39.89</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>152</v>
-      </c>
-      <c r="R4" s="4">
-        <v>43.029939393939401</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="9">
-        <v>100</v>
-      </c>
-      <c r="D5" s="4">
-        <v>32.238885192546597</v>
-      </c>
-      <c r="E5" s="6">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3">
-        <v>25.791108154037278</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L5" s="9">
-        <v>160</v>
-      </c>
-      <c r="M5" s="4">
-        <v>39.706873977358804</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>160</v>
-      </c>
-      <c r="R5" s="4">
-        <v>41.528098620215999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="9">
-        <v>186</v>
-      </c>
-      <c r="D6" s="4">
-        <v>45.070199208174799</v>
-      </c>
-      <c r="E6" s="6">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3">
-        <v>36.056159366539838</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L6" s="9">
-        <v>168</v>
-      </c>
-      <c r="M6" s="4">
-        <v>39.574879706933302</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>168</v>
-      </c>
-      <c r="R6" s="4">
-        <v>40.696204348405999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="9">
-        <v>88</v>
-      </c>
-      <c r="D7" s="4">
-        <v>50.631631236291803</v>
-      </c>
-      <c r="E7" s="6">
-        <v>20</v>
-      </c>
-      <c r="F7" s="3">
-        <v>40.505304989033441</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L7" s="9">
-        <v>152</v>
-      </c>
-      <c r="M7" s="4">
-        <v>39.5605422469636</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="P7" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>152</v>
-      </c>
-      <c r="R7" s="4">
-        <v>40.663364801600402</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="9">
-        <v>144</v>
-      </c>
-      <c r="D8" s="4">
-        <v>49.901317293941098</v>
-      </c>
-      <c r="E8" s="6">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3">
-        <v>39.921053835152875</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L8" s="9">
-        <v>160</v>
-      </c>
-      <c r="M8" s="4">
-        <v>39.402819691644602</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>176</v>
-      </c>
-      <c r="R8" s="4">
-        <v>40.169399737639203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="9">
-        <v>129</v>
-      </c>
-      <c r="D9" s="4">
-        <v>57.497388208608903</v>
-      </c>
-      <c r="E9" s="6">
-        <v>20</v>
-      </c>
-      <c r="F9" s="3">
-        <v>45.997910566887121</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L9" s="9">
-        <v>160</v>
-      </c>
-      <c r="M9" s="4">
-        <v>37.007300588709697</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>168</v>
-      </c>
-      <c r="R9" s="4">
-        <v>37.711496758482298</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="9">
-        <v>168</v>
-      </c>
-      <c r="D10" s="4">
-        <v>42.672372697255597</v>
-      </c>
-      <c r="E10" s="6">
-        <v>20</v>
-      </c>
-      <c r="F10" s="3">
-        <v>34.137898157804479</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L10" s="9">
-        <v>160</v>
-      </c>
-      <c r="M10" s="4">
-        <v>36.348020198538897</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>160</v>
-      </c>
-      <c r="R10" s="4">
-        <v>37.256393326648798</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="9">
-        <v>128</v>
-      </c>
-      <c r="D11" s="4">
-        <v>54.794365825797101</v>
-      </c>
-      <c r="E11" s="6">
-        <v>20</v>
-      </c>
-      <c r="F11" s="3">
-        <v>43.835492660637684</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L11" s="9">
-        <v>168</v>
-      </c>
-      <c r="M11" s="4">
-        <v>36.226309910409803</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>184</v>
-      </c>
-      <c r="R11" s="4">
-        <v>36.845269002736401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="9">
-        <v>132</v>
-      </c>
-      <c r="D12" s="4">
-        <v>49.568454434259202</v>
-      </c>
-      <c r="E12" s="6">
-        <v>20</v>
-      </c>
-      <c r="F12" s="3">
-        <v>39.654763547407363</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L12" s="9">
-        <v>152</v>
-      </c>
-      <c r="M12" s="4">
-        <v>36.1098</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="P12" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>152</v>
-      </c>
-      <c r="R12" s="4">
-        <v>36.625466666666703</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="9">
-        <v>135</v>
-      </c>
-      <c r="D13" s="4">
-        <v>40.496605720737499</v>
-      </c>
-      <c r="E13" s="6">
-        <v>20</v>
-      </c>
-      <c r="F13" s="3">
-        <v>32.397284576589996</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L13" s="9">
-        <v>184</v>
-      </c>
-      <c r="M13" s="4">
-        <v>35.773359665551801</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="P13" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>168</v>
-      </c>
-      <c r="R13" s="4">
-        <v>35.995552894314798</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="9">
-        <v>166</v>
-      </c>
-      <c r="D14" s="4">
-        <v>42.6380592368821</v>
-      </c>
-      <c r="E14" s="6">
-        <v>20</v>
-      </c>
-      <c r="F14" s="3">
-        <v>34.11044738950568</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L14" s="9">
-        <v>168</v>
-      </c>
-      <c r="M14" s="4">
-        <v>30.7104456946625</v>
-      </c>
-      <c r="O14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P14" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>168</v>
-      </c>
-      <c r="R14" s="4">
-        <v>34.831495886912798</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="9">
-        <v>120</v>
-      </c>
-      <c r="D15" s="4">
-        <v>55.133829571613298</v>
-      </c>
-      <c r="E15" s="6">
-        <v>20</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44.107063657290638</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="K15" s="11">
-        <v>46081</v>
-      </c>
-      <c r="L15" s="9">
-        <v>160</v>
-      </c>
-      <c r="M15" s="4">
-        <v>30.4661878232207</v>
-      </c>
-      <c r="O15" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="P15" s="11">
-        <v>46081</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>160</v>
-      </c>
-      <c r="R15" s="4">
-        <v>32.761814131069102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="9">
-        <v>140</v>
-      </c>
       <c r="D16" s="4">
-        <v>47.438137801035097</v>
-      </c>
-      <c r="E16" s="6">
-        <v>20</v>
-      </c>
-      <c r="F16" s="3">
-        <v>37.950510240828081</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="9">
-        <v>133</v>
-      </c>
-      <c r="D17" s="4">
-        <v>40.924182463762797</v>
-      </c>
-      <c r="E17" s="6">
-        <v>20</v>
-      </c>
-      <c r="F17" s="3">
-        <v>32.739345971010238</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="9">
-        <v>186</v>
-      </c>
-      <c r="D18" s="4">
-        <v>45.070199208174799</v>
-      </c>
-      <c r="E18" s="6">
-        <v>20</v>
-      </c>
-      <c r="F18" s="3">
-        <v>36.056159366539838</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="9">
-        <v>80</v>
-      </c>
-      <c r="D19" s="4">
-        <v>49.989056165476498</v>
-      </c>
-      <c r="E19" s="6">
-        <v>20</v>
-      </c>
-      <c r="F19" s="3">
-        <v>39.9912449323812</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="9">
-        <v>172</v>
-      </c>
-      <c r="D20" s="4">
-        <v>50.760818994742202</v>
-      </c>
-      <c r="E20" s="6">
-        <v>20</v>
-      </c>
-      <c r="F20" s="3">
-        <v>40.608655195793759</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="9">
-        <v>132</v>
-      </c>
-      <c r="D21" s="4">
-        <v>60.166545304890803</v>
-      </c>
-      <c r="E21" s="6">
-        <v>20</v>
-      </c>
-      <c r="F21" s="3">
-        <v>48.133236243912641</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="9">
-        <v>162</v>
-      </c>
-      <c r="D22" s="4">
-        <v>49.543563829787203</v>
-      </c>
-      <c r="E22" s="6">
-        <v>20</v>
-      </c>
-      <c r="F22" s="3">
-        <v>39.634851063829764</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K22" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L22" s="9">
-        <v>160</v>
-      </c>
-      <c r="M22" s="4">
-        <v>48.483667763157897</v>
-      </c>
-      <c r="O22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>192</v>
-      </c>
-      <c r="R22" s="4">
-        <v>37.414571740439598</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="9">
-        <v>152</v>
-      </c>
-      <c r="D23" s="4">
-        <v>49.269868126838801</v>
-      </c>
-      <c r="E23" s="6">
-        <v>20</v>
-      </c>
-      <c r="F23" s="3">
-        <v>39.415894501471044</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K23" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L23" s="9">
-        <v>192</v>
-      </c>
-      <c r="M23" s="4">
-        <v>46.480800646962898</v>
-      </c>
-      <c r="O23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="P23" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>172</v>
-      </c>
-      <c r="R23" s="4">
-        <v>35.941237012987003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="9">
-        <v>176</v>
-      </c>
-      <c r="D24" s="4">
-        <v>81.029703389830502</v>
-      </c>
-      <c r="E24" s="6">
-        <v>20</v>
-      </c>
-      <c r="F24" s="3">
-        <v>64.823762711864404</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K24" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L24" s="9">
-        <v>184</v>
-      </c>
-      <c r="M24" s="4">
-        <v>41.720992052147999</v>
-      </c>
-      <c r="O24" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="P24" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>144</v>
-      </c>
-      <c r="R24" s="4">
-        <v>34.7352384259259</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="9">
-        <v>112</v>
-      </c>
-      <c r="D25" s="4">
-        <v>86.741216864001004</v>
-      </c>
-      <c r="E25" s="6">
-        <v>20</v>
-      </c>
-      <c r="F25" s="3">
-        <v>69.392973491200806</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K25" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L25" s="9">
-        <v>152</v>
-      </c>
-      <c r="M25" s="4">
-        <v>40.994675675675602</v>
-      </c>
-      <c r="O25" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P25" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>200</v>
-      </c>
-      <c r="R25" s="4">
-        <v>34.204803703703703</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="9">
-        <v>154</v>
-      </c>
-      <c r="D26" s="4">
-        <v>49.543563829787203</v>
-      </c>
-      <c r="E26" s="6">
-        <v>20</v>
-      </c>
-      <c r="F26" s="3">
-        <v>39.634851063829764</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K26" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L26" s="9">
-        <v>176</v>
-      </c>
-      <c r="M26" s="4">
-        <v>39.799035847937198</v>
-      </c>
-      <c r="O26" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="P26" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q26" s="9">
-        <v>168</v>
-      </c>
-      <c r="R26" s="4">
-        <v>33.0205925925926</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="9">
-        <v>152</v>
-      </c>
-      <c r="D27" s="4">
-        <v>49.269868126838801</v>
-      </c>
-      <c r="E27" s="6">
-        <v>20</v>
-      </c>
-      <c r="F27" s="3">
-        <v>39.415894501471044</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L27" s="9">
-        <v>176</v>
-      </c>
-      <c r="M27" s="4">
-        <v>39.235442307692303</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="9">
-        <v>104</v>
-      </c>
-      <c r="D28" s="4">
-        <v>81.029703389830502</v>
-      </c>
-      <c r="E28" s="6">
-        <v>20</v>
-      </c>
-      <c r="F28" s="3">
-        <v>64.823762711864404</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L28" s="9">
-        <v>176</v>
-      </c>
-      <c r="M28" s="4">
-        <v>39.007290697674399</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="9">
-        <v>114</v>
-      </c>
-      <c r="D29" s="4">
-        <v>83.828793746109397</v>
-      </c>
-      <c r="E29" s="6">
-        <v>20</v>
-      </c>
-      <c r="F29" s="3">
-        <v>67.063034996887524</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L29" s="9">
-        <v>192</v>
-      </c>
-      <c r="M29" s="4">
-        <v>38.7876685971573</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K30" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L30" s="9">
-        <v>184</v>
-      </c>
-      <c r="M30" s="4">
-        <v>38.716932052471599</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="9">
-        <v>184</v>
-      </c>
-      <c r="D31" s="4">
-        <v>101.082867346939</v>
-      </c>
-      <c r="E31" s="6">
-        <v>20</v>
-      </c>
-      <c r="F31" s="3">
-        <v>80.8662938775512</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="K31" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L31" s="9">
-        <v>192</v>
-      </c>
-      <c r="M31" s="4">
-        <v>38.0187393541066</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="9">
-        <v>132</v>
-      </c>
-      <c r="D32" s="4">
-        <v>108.266729710902</v>
-      </c>
-      <c r="E32" s="6">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3">
-        <v>86.613383768721604</v>
-      </c>
-    </row>
-    <row r="35" spans="10:18">
-      <c r="J35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="10:18">
-      <c r="J36" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K36" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L36" s="9">
-        <v>168</v>
-      </c>
-      <c r="M36" s="4">
-        <v>51.8</v>
-      </c>
-      <c r="O36" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="P36" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q36" s="9">
-        <v>157</v>
-      </c>
-      <c r="R36" s="4">
-        <v>36.380000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="10:18">
-      <c r="J37" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="K37" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L37" s="9">
-        <v>168</v>
-      </c>
-      <c r="M37" s="4">
-        <v>49.35</v>
-      </c>
-      <c r="O37" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="P37" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>184</v>
-      </c>
-      <c r="R37" s="4">
-        <v>35.35</v>
-      </c>
-    </row>
-    <row r="38" spans="10:18">
-      <c r="J38" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="K38" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L38" s="9">
-        <v>176</v>
-      </c>
-      <c r="M38" s="4">
-        <v>40.590000000000003</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="P38" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q38" s="9">
-        <v>160</v>
-      </c>
-      <c r="R38" s="4">
-        <v>34.979999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="10:18">
-      <c r="J39" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="K39" s="11">
-        <v>46112</v>
-      </c>
-      <c r="L39" s="9">
-        <v>192</v>
-      </c>
-      <c r="M39" s="4">
-        <v>40.01</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="P39" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>136</v>
-      </c>
-      <c r="R39" s="4">
-        <v>34.630000000000003</v>
-      </c>
-    </row>
-    <row r="40" spans="10:18">
-      <c r="O40" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="P40" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>168</v>
-      </c>
-      <c r="R40" s="4">
-        <v>33.22</v>
-      </c>
-    </row>
-    <row r="41" spans="10:18">
-      <c r="O41" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="P41" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>168</v>
-      </c>
-      <c r="R41" s="4">
-        <v>33.08</v>
-      </c>
-    </row>
-    <row r="42" spans="10:18">
-      <c r="O42" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="P42" s="11">
-        <v>46112</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>176</v>
-      </c>
-      <c r="R42" s="4">
-        <v>32.67</v>
+        <v>30.212524501078299</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="J35:M46">
-    <sortState ref="J36:M46">
-      <sortCondition descending="1" ref="M35:M46"/>
+  <autoFilter ref="A1:D16">
+    <sortState ref="A2:D16">
+      <sortCondition descending="1" ref="D1:D16"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="28695" windowHeight="12540"/>
+    <workbookView xWindow="120" yWindow="45" windowWidth="28695" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$357</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Foglio3!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="144">
   <si>
     <t>Tecnico</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>IRTE0000121 - CANNARELLA VINCENZO</t>
+  </si>
+  <si>
+    <t>IRTE0000123 - ALFONSO SIMONE</t>
+  </si>
+  <si>
+    <t>IRTE0000122 - AMENTA SONNY</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -555,6 +561,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA9A9A9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -563,7 +595,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -584,6 +616,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -894,7 +939,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H285"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -930,7 +976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -957,7 +1003,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" hidden="1">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -984,7 +1030,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" s="1" t="s">
         <v>134</v>
       </c>
@@ -1007,7 +1053,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1032,7 +1078,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,7 +1103,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1082,7 +1128,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1107,7 +1153,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
@@ -1132,7 +1178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,7 +1203,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1182,7 +1228,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1207,7 +1253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1232,7 +1278,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1257,7 +1303,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" s="1" t="s">
         <v>135</v>
       </c>
@@ -1280,7 +1326,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" s="16" t="s">
         <v>16</v>
       </c>
@@ -1305,7 +1351,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" hidden="1">
       <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
@@ -1330,7 +1376,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" hidden="1">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1355,7 +1401,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" s="16" t="s">
         <v>19</v>
       </c>
@@ -1380,7 +1426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" hidden="1">
       <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
@@ -1405,7 +1451,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" hidden="1">
       <c r="A21" s="16" t="s">
         <v>21</v>
       </c>
@@ -1430,7 +1476,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
@@ -1455,7 +1501,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" hidden="1">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1480,7 +1526,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" hidden="1">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -1505,7 +1551,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -1530,7 +1576,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" hidden="1">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -1555,7 +1601,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" hidden="1">
       <c r="A27" s="17" t="s">
         <v>27</v>
       </c>
@@ -1580,7 +1626,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" hidden="1">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -1605,7 +1651,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" hidden="1">
       <c r="A29" s="1" t="s">
         <v>132</v>
       </c>
@@ -1630,7 +1676,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" s="9" t="s">
         <v>29</v>
       </c>
@@ -1655,7 +1701,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1680,7 +1726,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" s="16" t="s">
         <v>31</v>
       </c>
@@ -1705,7 +1751,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" hidden="1">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1730,7 +1776,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" hidden="1">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1755,7 +1801,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" hidden="1">
       <c r="A35" s="16" t="s">
         <v>34</v>
       </c>
@@ -1780,7 +1826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" hidden="1">
       <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
@@ -1805,7 +1851,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" hidden="1">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1830,7 +1876,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" hidden="1">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1855,7 +1901,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" hidden="1">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1880,7 +1926,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" hidden="1">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1905,7 +1951,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" hidden="1">
       <c r="A41" s="16" t="s">
         <v>40</v>
       </c>
@@ -1930,7 +1976,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" hidden="1">
       <c r="A42" s="16" t="s">
         <v>41</v>
       </c>
@@ -1955,7 +2001,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" hidden="1">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -1980,7 +2026,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" hidden="1">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -2005,7 +2051,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" hidden="1">
       <c r="A45" s="17" t="s">
         <v>44</v>
       </c>
@@ -2030,7 +2076,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" hidden="1">
       <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
@@ -2055,7 +2101,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" hidden="1">
       <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
@@ -2080,7 +2126,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" hidden="1">
       <c r="A48" s="17" t="s">
         <v>47</v>
       </c>
@@ -2105,7 +2151,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" hidden="1">
       <c r="A49" s="17" t="s">
         <v>48</v>
       </c>
@@ -2130,7 +2176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" hidden="1">
       <c r="A50" s="17" t="s">
         <v>49</v>
       </c>
@@ -2155,7 +2201,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" hidden="1">
       <c r="A51" s="17" t="s">
         <v>50</v>
       </c>
@@ -2180,7 +2226,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" hidden="1">
       <c r="A52" s="16" t="s">
         <v>51</v>
       </c>
@@ -2205,7 +2251,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" hidden="1">
       <c r="A53" s="17" t="s">
         <v>52</v>
       </c>
@@ -2230,7 +2276,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" hidden="1">
       <c r="A54" s="16" t="s">
         <v>53</v>
       </c>
@@ -2255,7 +2301,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" hidden="1">
       <c r="A55" s="17" t="s">
         <v>54</v>
       </c>
@@ -2280,7 +2326,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" hidden="1">
       <c r="A56" s="17" t="s">
         <v>55</v>
       </c>
@@ -2305,7 +2351,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" hidden="1">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
@@ -2330,7 +2376,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" hidden="1">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -2355,7 +2401,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" hidden="1">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
@@ -2380,7 +2426,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" hidden="1">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
@@ -2405,7 +2451,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" hidden="1">
       <c r="A61" s="16" t="s">
         <v>60</v>
       </c>
@@ -2430,7 +2476,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" hidden="1">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
@@ -2455,7 +2501,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" hidden="1">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
@@ -2480,7 +2526,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" hidden="1">
       <c r="A64" s="16" t="s">
         <v>63</v>
       </c>
@@ -2505,7 +2551,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" hidden="1">
       <c r="A65" s="9" t="s">
         <v>129</v>
       </c>
@@ -2528,7 +2574,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" hidden="1">
       <c r="A66" s="1" t="s">
         <v>128</v>
       </c>
@@ -2551,7 +2597,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" hidden="1">
       <c r="A67" s="17" t="s">
         <v>130</v>
       </c>
@@ -2574,7 +2620,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" hidden="1">
       <c r="A68" s="17" t="s">
         <v>131</v>
       </c>
@@ -2597,7 +2643,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" hidden="1">
       <c r="A69" s="1" t="s">
         <v>137</v>
       </c>
@@ -2620,7 +2666,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" hidden="1">
       <c r="A70" s="1" t="s">
         <v>136</v>
       </c>
@@ -2643,7 +2689,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" hidden="1">
       <c r="A71" s="14" t="s">
         <v>4</v>
       </c>
@@ -2670,7 +2716,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" hidden="1">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -2697,7 +2743,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" hidden="1">
       <c r="A73" s="1" t="s">
         <v>134</v>
       </c>
@@ -2720,7 +2766,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" hidden="1">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -2745,7 +2791,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" hidden="1">
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
@@ -2770,7 +2816,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" hidden="1">
       <c r="A76" s="1" t="s">
         <v>8</v>
       </c>
@@ -2795,7 +2841,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" hidden="1">
       <c r="A77" s="1" t="s">
         <v>9</v>
       </c>
@@ -2820,7 +2866,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" hidden="1">
       <c r="A78" s="16" t="s">
         <v>10</v>
       </c>
@@ -2845,7 +2891,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" hidden="1">
       <c r="A79" s="16" t="s">
         <v>138</v>
       </c>
@@ -2868,7 +2914,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" hidden="1">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -2893,7 +2939,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" hidden="1">
       <c r="A81" s="1" t="s">
         <v>12</v>
       </c>
@@ -2918,7 +2964,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" hidden="1">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
@@ -2943,7 +2989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" hidden="1">
       <c r="A83" s="1" t="s">
         <v>14</v>
       </c>
@@ -2968,7 +3014,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" hidden="1">
       <c r="A84" s="1" t="s">
         <v>15</v>
       </c>
@@ -2993,7 +3039,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" hidden="1">
       <c r="A85" s="1" t="s">
         <v>135</v>
       </c>
@@ -3016,7 +3062,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" hidden="1">
       <c r="A86" s="16" t="s">
         <v>16</v>
       </c>
@@ -3041,7 +3087,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" hidden="1">
       <c r="A87" s="16" t="s">
         <v>17</v>
       </c>
@@ -3066,7 +3112,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" hidden="1">
       <c r="A88" s="1" t="s">
         <v>18</v>
       </c>
@@ -3091,7 +3137,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" hidden="1">
       <c r="A89" s="16" t="s">
         <v>19</v>
       </c>
@@ -3116,7 +3162,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" hidden="1">
       <c r="A90" s="9" t="s">
         <v>20</v>
       </c>
@@ -3141,7 +3187,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" hidden="1">
       <c r="A91" s="16" t="s">
         <v>21</v>
       </c>
@@ -3166,7 +3212,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" hidden="1">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -3191,7 +3237,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" hidden="1">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -3216,7 +3262,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" hidden="1">
       <c r="A94" s="9" t="s">
         <v>25</v>
       </c>
@@ -3241,7 +3287,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" hidden="1">
       <c r="A95" s="1" t="s">
         <v>26</v>
       </c>
@@ -3266,7 +3312,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" hidden="1">
       <c r="A96" s="17" t="s">
         <v>27</v>
       </c>
@@ -3291,7 +3337,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" hidden="1">
       <c r="A97" s="1" t="s">
         <v>28</v>
       </c>
@@ -3316,7 +3362,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" hidden="1">
       <c r="A98" s="1" t="s">
         <v>132</v>
       </c>
@@ -3341,7 +3387,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" hidden="1">
       <c r="A99" s="9" t="s">
         <v>29</v>
       </c>
@@ -3366,7 +3412,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" hidden="1">
       <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
@@ -3391,7 +3437,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" hidden="1">
       <c r="A101" s="16" t="s">
         <v>31</v>
       </c>
@@ -3416,7 +3462,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" hidden="1">
       <c r="A102" s="1" t="s">
         <v>32</v>
       </c>
@@ -3441,7 +3487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" hidden="1">
       <c r="A103" s="1" t="s">
         <v>33</v>
       </c>
@@ -3466,7 +3512,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" hidden="1">
       <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
@@ -3491,7 +3537,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" hidden="1">
       <c r="A105" s="9" t="s">
         <v>35</v>
       </c>
@@ -3516,7 +3562,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" hidden="1">
       <c r="A106" s="1" t="s">
         <v>36</v>
       </c>
@@ -3541,7 +3587,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" hidden="1">
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
@@ -3566,7 +3612,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" hidden="1">
       <c r="A108" s="1" t="s">
         <v>38</v>
       </c>
@@ -3591,7 +3637,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" hidden="1">
       <c r="A109" s="1" t="s">
         <v>39</v>
       </c>
@@ -3616,7 +3662,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" hidden="1">
       <c r="A110" s="16" t="s">
         <v>40</v>
       </c>
@@ -3641,7 +3687,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" hidden="1">
       <c r="A111" s="16" t="s">
         <v>41</v>
       </c>
@@ -3666,7 +3712,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" hidden="1">
       <c r="A112" s="1" t="s">
         <v>42</v>
       </c>
@@ -3691,7 +3737,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" hidden="1">
       <c r="A113" s="1" t="s">
         <v>43</v>
       </c>
@@ -3716,7 +3762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" hidden="1">
       <c r="A114" s="17" t="s">
         <v>44</v>
       </c>
@@ -3741,7 +3787,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" hidden="1">
       <c r="A115" s="9" t="s">
         <v>45</v>
       </c>
@@ -3766,7 +3812,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" hidden="1">
       <c r="A116" s="9" t="s">
         <v>46</v>
       </c>
@@ -3791,7 +3837,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" hidden="1">
       <c r="A117" s="17" t="s">
         <v>47</v>
       </c>
@@ -3816,7 +3862,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" hidden="1">
       <c r="A118" s="17" t="s">
         <v>48</v>
       </c>
@@ -3841,7 +3887,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" hidden="1">
       <c r="A119" s="17" t="s">
         <v>49</v>
       </c>
@@ -3866,7 +3912,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" hidden="1">
       <c r="A120" s="17" t="s">
         <v>50</v>
       </c>
@@ -3891,7 +3937,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" hidden="1">
       <c r="A121" s="16" t="s">
         <v>51</v>
       </c>
@@ -3916,7 +3962,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" hidden="1">
       <c r="A122" s="17" t="s">
         <v>52</v>
       </c>
@@ -3941,7 +3987,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" hidden="1">
       <c r="A123" s="16" t="s">
         <v>53</v>
       </c>
@@ -3966,7 +4012,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" hidden="1">
       <c r="A124" s="17" t="s">
         <v>54</v>
       </c>
@@ -3991,7 +4037,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" hidden="1">
       <c r="A125" s="17" t="s">
         <v>55</v>
       </c>
@@ -4016,7 +4062,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" hidden="1">
       <c r="A126" s="1" t="s">
         <v>56</v>
       </c>
@@ -4041,7 +4087,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" hidden="1">
       <c r="A127" s="1" t="s">
         <v>57</v>
       </c>
@@ -4066,7 +4112,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" hidden="1">
       <c r="A128" s="1" t="s">
         <v>58</v>
       </c>
@@ -4091,7 +4137,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" hidden="1">
       <c r="A129" s="1" t="s">
         <v>59</v>
       </c>
@@ -4116,7 +4162,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" hidden="1">
       <c r="A130" s="16" t="s">
         <v>60</v>
       </c>
@@ -4141,7 +4187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" hidden="1">
       <c r="A131" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,7 +4212,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" hidden="1">
       <c r="A132" s="1" t="s">
         <v>62</v>
       </c>
@@ -4191,7 +4237,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" hidden="1">
       <c r="A133" s="16" t="s">
         <v>63</v>
       </c>
@@ -4216,7 +4262,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" hidden="1">
       <c r="A134" s="9" t="s">
         <v>129</v>
       </c>
@@ -4239,7 +4285,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" hidden="1">
       <c r="A135" s="1" t="s">
         <v>128</v>
       </c>
@@ -4262,7 +4308,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" hidden="1">
       <c r="A136" s="17" t="s">
         <v>130</v>
       </c>
@@ -4285,7 +4331,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" hidden="1">
       <c r="A137" s="17" t="s">
         <v>131</v>
       </c>
@@ -4308,7 +4354,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" hidden="1">
       <c r="A138" s="1" t="s">
         <v>137</v>
       </c>
@@ -4331,7 +4377,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" hidden="1">
       <c r="A139" s="1" t="s">
         <v>136</v>
       </c>
@@ -4354,7 +4400,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" hidden="1">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
@@ -4377,7 +4423,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" hidden="1">
       <c r="A141" s="1" t="s">
         <v>140</v>
       </c>
@@ -4400,7 +4446,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" hidden="1">
       <c r="A142" s="14" t="s">
         <v>4</v>
       </c>
@@ -4427,7 +4473,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" hidden="1">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -4454,7 +4500,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" hidden="1">
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
@@ -4477,7 +4523,7 @@
       <c r="G144" s="1"/>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" hidden="1">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -4502,7 +4548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" hidden="1">
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
@@ -4527,7 +4573,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" hidden="1">
       <c r="A147" s="1" t="s">
         <v>8</v>
       </c>
@@ -4552,7 +4598,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" hidden="1">
       <c r="A148" s="1" t="s">
         <v>9</v>
       </c>
@@ -4577,7 +4623,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" hidden="1">
       <c r="A149" s="16" t="s">
         <v>10</v>
       </c>
@@ -4602,7 +4648,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" hidden="1">
       <c r="A150" s="16" t="s">
         <v>138</v>
       </c>
@@ -4625,7 +4671,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" hidden="1">
       <c r="A151" s="1" t="s">
         <v>11</v>
       </c>
@@ -4650,7 +4696,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" hidden="1">
       <c r="A152" s="1" t="s">
         <v>12</v>
       </c>
@@ -4675,7 +4721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" hidden="1">
       <c r="A153" s="1" t="s">
         <v>13</v>
       </c>
@@ -4700,7 +4746,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" hidden="1">
       <c r="A154" s="1" t="s">
         <v>14</v>
       </c>
@@ -4725,7 +4771,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" hidden="1">
       <c r="A155" s="1" t="s">
         <v>15</v>
       </c>
@@ -4750,7 +4796,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" hidden="1">
       <c r="A156" s="1" t="s">
         <v>135</v>
       </c>
@@ -4773,7 +4819,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" hidden="1">
       <c r="A157" s="16" t="s">
         <v>16</v>
       </c>
@@ -4798,7 +4844,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" hidden="1">
       <c r="A158" s="16" t="s">
         <v>17</v>
       </c>
@@ -4823,7 +4869,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" hidden="1">
       <c r="A159" s="1" t="s">
         <v>18</v>
       </c>
@@ -4848,7 +4894,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" hidden="1">
       <c r="A160" s="16" t="s">
         <v>19</v>
       </c>
@@ -4873,7 +4919,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" hidden="1">
       <c r="A161" s="9" t="s">
         <v>20</v>
       </c>
@@ -4898,7 +4944,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" hidden="1">
       <c r="A162" s="16" t="s">
         <v>21</v>
       </c>
@@ -4923,7 +4969,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" hidden="1">
       <c r="A163" s="1" t="s">
         <v>23</v>
       </c>
@@ -4948,7 +4994,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" hidden="1">
       <c r="A164" s="1" t="s">
         <v>24</v>
       </c>
@@ -4973,7 +5019,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" hidden="1">
       <c r="A165" s="9" t="s">
         <v>25</v>
       </c>
@@ -4998,7 +5044,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" hidden="1">
       <c r="A166" s="1" t="s">
         <v>26</v>
       </c>
@@ -5023,7 +5069,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" hidden="1">
       <c r="A167" s="17" t="s">
         <v>27</v>
       </c>
@@ -5048,7 +5094,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" hidden="1">
       <c r="A168" s="1" t="s">
         <v>28</v>
       </c>
@@ -5073,7 +5119,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" hidden="1">
       <c r="A169" s="1" t="s">
         <v>132</v>
       </c>
@@ -5098,7 +5144,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" hidden="1">
       <c r="A170" s="9" t="s">
         <v>29</v>
       </c>
@@ -5123,7 +5169,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" hidden="1">
       <c r="A171" s="1" t="s">
         <v>30</v>
       </c>
@@ -5148,7 +5194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" hidden="1">
       <c r="A172" s="16" t="s">
         <v>31</v>
       </c>
@@ -5173,7 +5219,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" hidden="1">
       <c r="A173" s="1" t="s">
         <v>32</v>
       </c>
@@ -5198,7 +5244,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" hidden="1">
       <c r="A174" s="1" t="s">
         <v>33</v>
       </c>
@@ -5223,7 +5269,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" hidden="1">
       <c r="A175" s="16" t="s">
         <v>34</v>
       </c>
@@ -5248,7 +5294,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" hidden="1">
       <c r="A176" s="9" t="s">
         <v>35</v>
       </c>
@@ -5273,7 +5319,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" hidden="1">
       <c r="A177" s="1" t="s">
         <v>36</v>
       </c>
@@ -5298,7 +5344,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" hidden="1">
       <c r="A178" s="1" t="s">
         <v>37</v>
       </c>
@@ -5323,7 +5369,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" hidden="1">
       <c r="A179" s="1" t="s">
         <v>38</v>
       </c>
@@ -5348,7 +5394,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" hidden="1">
       <c r="A180" s="1" t="s">
         <v>39</v>
       </c>
@@ -5373,7 +5419,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" hidden="1">
       <c r="A181" s="16" t="s">
         <v>40</v>
       </c>
@@ -5398,7 +5444,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" hidden="1">
       <c r="A182" s="16" t="s">
         <v>41</v>
       </c>
@@ -5423,7 +5469,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" hidden="1">
       <c r="A183" s="1" t="s">
         <v>42</v>
       </c>
@@ -5448,7 +5494,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" hidden="1">
       <c r="A184" s="1" t="s">
         <v>43</v>
       </c>
@@ -5473,7 +5519,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" hidden="1">
       <c r="A185" s="17" t="s">
         <v>44</v>
       </c>
@@ -5498,7 +5544,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" hidden="1">
       <c r="A186" s="9" t="s">
         <v>45</v>
       </c>
@@ -5523,7 +5569,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" hidden="1">
       <c r="A187" s="9" t="s">
         <v>46</v>
       </c>
@@ -5548,7 +5594,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" hidden="1">
       <c r="A188" s="17" t="s">
         <v>47</v>
       </c>
@@ -5573,7 +5619,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" hidden="1">
       <c r="A189" s="17" t="s">
         <v>48</v>
       </c>
@@ -5598,7 +5644,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" hidden="1">
       <c r="A190" s="17" t="s">
         <v>49</v>
       </c>
@@ -5623,7 +5669,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" hidden="1">
       <c r="A191" s="17" t="s">
         <v>50</v>
       </c>
@@ -5648,7 +5694,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" hidden="1">
       <c r="A192" s="16" t="s">
         <v>51</v>
       </c>
@@ -5673,7 +5719,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" hidden="1">
       <c r="A193" s="17" t="s">
         <v>52</v>
       </c>
@@ -5698,7 +5744,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" hidden="1">
       <c r="A194" s="16" t="s">
         <v>53</v>
       </c>
@@ -5723,7 +5769,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" hidden="1">
       <c r="A195" s="17" t="s">
         <v>54</v>
       </c>
@@ -5748,7 +5794,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" hidden="1">
       <c r="A196" s="17" t="s">
         <v>55</v>
       </c>
@@ -5773,7 +5819,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" hidden="1">
       <c r="A197" s="1" t="s">
         <v>56</v>
       </c>
@@ -5794,7 +5840,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" hidden="1">
       <c r="A198" s="1" t="s">
         <v>57</v>
       </c>
@@ -5819,7 +5865,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" hidden="1">
       <c r="A199" s="1" t="s">
         <v>58</v>
       </c>
@@ -5844,7 +5890,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" hidden="1">
       <c r="A200" s="1" t="s">
         <v>59</v>
       </c>
@@ -5869,7 +5915,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" hidden="1">
       <c r="A201" s="16" t="s">
         <v>60</v>
       </c>
@@ -5894,7 +5940,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" hidden="1">
       <c r="A202" s="1" t="s">
         <v>61</v>
       </c>
@@ -5919,7 +5965,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" hidden="1">
       <c r="A203" s="1" t="s">
         <v>62</v>
       </c>
@@ -5944,7 +5990,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" hidden="1">
       <c r="A204" s="16" t="s">
         <v>63</v>
       </c>
@@ -5969,7 +6015,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" hidden="1">
       <c r="A205" s="9" t="s">
         <v>129</v>
       </c>
@@ -5992,7 +6038,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" hidden="1">
       <c r="A206" s="1" t="s">
         <v>128</v>
       </c>
@@ -6015,7 +6061,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" hidden="1">
       <c r="A207" s="17" t="s">
         <v>130</v>
       </c>
@@ -6038,7 +6084,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" hidden="1">
       <c r="A208" s="17" t="s">
         <v>131</v>
       </c>
@@ -6061,7 +6107,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" hidden="1">
       <c r="A209" s="1" t="s">
         <v>137</v>
       </c>
@@ -6084,7 +6130,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" hidden="1">
       <c r="A210" s="1" t="s">
         <v>136</v>
       </c>
@@ -6107,7 +6153,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" hidden="1">
       <c r="A211" s="1" t="s">
         <v>139</v>
       </c>
@@ -6130,7 +6176,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" hidden="1">
       <c r="A212" s="1" t="s">
         <v>140</v>
       </c>
@@ -6153,7 +6199,7 @@
       <c r="G212" s="1"/>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" hidden="1">
       <c r="A213" s="16" t="s">
         <v>141</v>
       </c>
@@ -6176,7 +6222,7 @@
       <c r="G213" s="1"/>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" hidden="1">
       <c r="A214" s="14" t="s">
         <v>4</v>
       </c>
@@ -6203,7 +6249,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" hidden="1">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -6230,7 +6276,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" hidden="1">
       <c r="A216" s="1" t="s">
         <v>134</v>
       </c>
@@ -6253,7 +6299,7 @@
       <c r="G216" s="1"/>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" hidden="1">
       <c r="A217" s="1" t="s">
         <v>6</v>
       </c>
@@ -6278,7 +6324,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" hidden="1">
       <c r="A218" s="1" t="s">
         <v>7</v>
       </c>
@@ -6303,7 +6349,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" hidden="1">
       <c r="A219" s="1" t="s">
         <v>8</v>
       </c>
@@ -6328,7 +6374,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" hidden="1">
       <c r="A220" s="1" t="s">
         <v>9</v>
       </c>
@@ -6353,7 +6399,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" hidden="1">
       <c r="A221" s="16" t="s">
         <v>10</v>
       </c>
@@ -6378,7 +6424,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" hidden="1">
       <c r="A222" s="16" t="s">
         <v>138</v>
       </c>
@@ -6401,7 +6447,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" hidden="1">
       <c r="A223" s="1" t="s">
         <v>11</v>
       </c>
@@ -6426,7 +6472,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" hidden="1">
       <c r="A224" s="1" t="s">
         <v>12</v>
       </c>
@@ -6451,7 +6497,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" hidden="1">
       <c r="A225" s="1" t="s">
         <v>13</v>
       </c>
@@ -6476,7 +6522,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" hidden="1">
       <c r="A226" s="1" t="s">
         <v>14</v>
       </c>
@@ -6501,7 +6547,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" hidden="1">
       <c r="A227" s="1" t="s">
         <v>15</v>
       </c>
@@ -6526,7 +6572,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" hidden="1">
       <c r="A228" s="1" t="s">
         <v>135</v>
       </c>
@@ -6549,7 +6595,7 @@
       <c r="G228" s="1"/>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" hidden="1">
       <c r="A229" s="16" t="s">
         <v>16</v>
       </c>
@@ -6574,7 +6620,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" hidden="1">
       <c r="A230" s="16" t="s">
         <v>17</v>
       </c>
@@ -6599,7 +6645,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" hidden="1">
       <c r="A231" s="1" t="s">
         <v>18</v>
       </c>
@@ -6624,7 +6670,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" hidden="1">
       <c r="A232" s="16" t="s">
         <v>19</v>
       </c>
@@ -6649,7 +6695,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" hidden="1">
       <c r="A233" s="9" t="s">
         <v>20</v>
       </c>
@@ -6674,7 +6720,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" hidden="1">
       <c r="A234" s="16" t="s">
         <v>21</v>
       </c>
@@ -6699,7 +6745,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" hidden="1">
       <c r="A235" s="1" t="s">
         <v>23</v>
       </c>
@@ -6724,7 +6770,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" hidden="1">
       <c r="A236" s="1" t="s">
         <v>24</v>
       </c>
@@ -6749,7 +6795,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" hidden="1">
       <c r="A237" s="9" t="s">
         <v>25</v>
       </c>
@@ -6774,7 +6820,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" hidden="1">
       <c r="A238" s="1" t="s">
         <v>26</v>
       </c>
@@ -6799,7 +6845,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" hidden="1">
       <c r="A239" s="17" t="s">
         <v>27</v>
       </c>
@@ -6824,7 +6870,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" hidden="1">
       <c r="A240" s="1" t="s">
         <v>28</v>
       </c>
@@ -6849,7 +6895,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" hidden="1">
       <c r="A241" s="1" t="s">
         <v>132</v>
       </c>
@@ -6870,7 +6916,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" hidden="1">
       <c r="A242" s="9" t="s">
         <v>29</v>
       </c>
@@ -6895,7 +6941,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" hidden="1">
       <c r="A243" s="1" t="s">
         <v>30</v>
       </c>
@@ -6920,7 +6966,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" hidden="1">
       <c r="A244" s="16" t="s">
         <v>31</v>
       </c>
@@ -6945,7 +6991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" hidden="1">
       <c r="A245" s="1" t="s">
         <v>32</v>
       </c>
@@ -6970,7 +7016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" hidden="1">
       <c r="A246" s="1" t="s">
         <v>33</v>
       </c>
@@ -6995,7 +7041,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" hidden="1">
       <c r="A247" s="16" t="s">
         <v>34</v>
       </c>
@@ -7020,7 +7066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" hidden="1">
       <c r="A248" s="9" t="s">
         <v>35</v>
       </c>
@@ -7045,7 +7091,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" hidden="1">
       <c r="A249" s="1" t="s">
         <v>36</v>
       </c>
@@ -7070,7 +7116,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" hidden="1">
       <c r="A250" s="1" t="s">
         <v>37</v>
       </c>
@@ -7095,7 +7141,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" hidden="1">
       <c r="A251" s="1" t="s">
         <v>38</v>
       </c>
@@ -7120,7 +7166,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" hidden="1">
       <c r="A252" s="1" t="s">
         <v>39</v>
       </c>
@@ -7145,7 +7191,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" hidden="1">
       <c r="A253" s="16" t="s">
         <v>40</v>
       </c>
@@ -7170,7 +7216,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" hidden="1">
       <c r="A254" s="16" t="s">
         <v>41</v>
       </c>
@@ -7195,7 +7241,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" hidden="1">
       <c r="A255" s="1" t="s">
         <v>42</v>
       </c>
@@ -7220,7 +7266,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" hidden="1">
       <c r="A256" s="1" t="s">
         <v>43</v>
       </c>
@@ -7245,7 +7291,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" hidden="1">
       <c r="A257" s="17" t="s">
         <v>44</v>
       </c>
@@ -7270,7 +7316,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" hidden="1">
       <c r="A258" s="9" t="s">
         <v>45</v>
       </c>
@@ -7295,7 +7341,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" hidden="1">
       <c r="A259" s="9" t="s">
         <v>46</v>
       </c>
@@ -7320,7 +7366,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" hidden="1">
       <c r="A260" s="17" t="s">
         <v>47</v>
       </c>
@@ -7345,7 +7391,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" hidden="1">
       <c r="A261" s="17" t="s">
         <v>48</v>
       </c>
@@ -7370,7 +7416,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" hidden="1">
       <c r="A262" s="17" t="s">
         <v>49</v>
       </c>
@@ -7395,7 +7441,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" hidden="1">
       <c r="A263" s="17" t="s">
         <v>50</v>
       </c>
@@ -7420,7 +7466,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" hidden="1">
       <c r="A264" s="16" t="s">
         <v>51</v>
       </c>
@@ -7445,7 +7491,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" hidden="1">
       <c r="A265" s="17" t="s">
         <v>52</v>
       </c>
@@ -7470,7 +7516,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" hidden="1">
       <c r="A266" s="16" t="s">
         <v>53</v>
       </c>
@@ -7495,7 +7541,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" hidden="1">
       <c r="A267" s="17" t="s">
         <v>54</v>
       </c>
@@ -7520,7 +7566,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" hidden="1">
       <c r="A268" s="17" t="s">
         <v>55</v>
       </c>
@@ -7537,7 +7583,7 @@
         <v>20</v>
       </c>
       <c r="F268" s="3">
-        <f t="shared" ref="F268:F285" si="6">D268-(D268*E268)/100</f>
+        <f t="shared" ref="F268:F330" si="6">D268-(D268*E268)/100</f>
         <v>20.021165570175441</v>
       </c>
       <c r="G268" s="1"/>
@@ -7545,7 +7591,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" hidden="1">
       <c r="A269" s="1" t="s">
         <v>56</v>
       </c>
@@ -7570,7 +7616,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" hidden="1">
       <c r="A270" s="1" t="s">
         <v>57</v>
       </c>
@@ -7595,7 +7641,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" hidden="1">
       <c r="A271" s="1" t="s">
         <v>58</v>
       </c>
@@ -7620,7 +7666,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" hidden="1">
       <c r="A272" s="1" t="s">
         <v>59</v>
       </c>
@@ -7645,7 +7691,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" hidden="1">
       <c r="A273" s="16" t="s">
         <v>60</v>
       </c>
@@ -7670,7 +7716,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" hidden="1">
       <c r="A274" s="1" t="s">
         <v>61</v>
       </c>
@@ -7695,7 +7741,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" hidden="1">
       <c r="A275" s="1" t="s">
         <v>62</v>
       </c>
@@ -7720,7 +7766,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" hidden="1">
       <c r="A276" s="16" t="s">
         <v>63</v>
       </c>
@@ -7745,7 +7791,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" hidden="1">
       <c r="A277" s="9" t="s">
         <v>129</v>
       </c>
@@ -7768,7 +7814,7 @@
       <c r="G277" s="1"/>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" hidden="1">
       <c r="A278" s="1" t="s">
         <v>128</v>
       </c>
@@ -7791,7 +7837,7 @@
       <c r="G278" s="1"/>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" hidden="1">
       <c r="A279" s="17" t="s">
         <v>130</v>
       </c>
@@ -7814,7 +7860,7 @@
       <c r="G279" s="1"/>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" hidden="1">
       <c r="A280" s="17" t="s">
         <v>131</v>
       </c>
@@ -7837,7 +7883,7 @@
       <c r="G280" s="1"/>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" hidden="1">
       <c r="A281" s="1" t="s">
         <v>137</v>
       </c>
@@ -7860,7 +7906,7 @@
       <c r="G281" s="1"/>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" hidden="1">
       <c r="A282" s="1" t="s">
         <v>136</v>
       </c>
@@ -7883,7 +7929,7 @@
       <c r="G282" s="1"/>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" hidden="1">
       <c r="A283" s="1" t="s">
         <v>139</v>
       </c>
@@ -7906,7 +7952,7 @@
       <c r="G283" s="1"/>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" hidden="1">
       <c r="A284" s="1" t="s">
         <v>140</v>
       </c>
@@ -7929,7 +7975,7 @@
       <c r="G284" s="1"/>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" hidden="1">
       <c r="A285" s="16" t="s">
         <v>141</v>
       </c>
@@ -7952,10 +7998,1792 @@
       <c r="G285" s="1"/>
       <c r="H285" s="7"/>
     </row>
+    <row r="286" spans="1:8" hidden="1">
+      <c r="A286" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B286" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C286" s="8">
+        <v>178</v>
+      </c>
+      <c r="D286" s="11">
+        <v>36.873445235286198</v>
+      </c>
+      <c r="E286" s="12">
+        <v>20</v>
+      </c>
+      <c r="F286" s="13">
+        <f t="shared" si="6"/>
+        <v>29.49875618822896</v>
+      </c>
+      <c r="G286" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H286" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" hidden="1">
+      <c r="A287" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B287" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C287" s="8">
+        <v>112</v>
+      </c>
+      <c r="D287" s="4">
+        <v>51.437316453495498</v>
+      </c>
+      <c r="E287" s="6">
+        <v>20</v>
+      </c>
+      <c r="F287" s="3">
+        <f t="shared" si="6"/>
+        <v>41.149853162796397</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H287" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" hidden="1">
+      <c r="A288" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B288" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C288" s="8">
+        <v>4</v>
+      </c>
+      <c r="D288" s="4">
+        <v>34.765338028168998</v>
+      </c>
+      <c r="E288" s="6">
+        <v>20</v>
+      </c>
+      <c r="F288" s="3">
+        <f t="shared" si="6"/>
+        <v>27.8122704225352</v>
+      </c>
+      <c r="G288" s="1"/>
+      <c r="H288" s="7"/>
+    </row>
+    <row r="289" spans="1:8" hidden="1">
+      <c r="A289" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B289" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C289" s="8">
+        <v>151</v>
+      </c>
+      <c r="D289" s="4">
+        <v>21.1199807081511</v>
+      </c>
+      <c r="E289" s="6">
+        <v>20</v>
+      </c>
+      <c r="F289" s="3">
+        <f t="shared" si="6"/>
+        <v>16.89598456652088</v>
+      </c>
+      <c r="G289" s="1"/>
+      <c r="H289" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" hidden="1">
+      <c r="A290" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B290" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C290" s="8">
+        <v>136</v>
+      </c>
+      <c r="D290" s="4">
+        <v>79.443899130700103</v>
+      </c>
+      <c r="E290" s="6">
+        <v>20</v>
+      </c>
+      <c r="F290" s="3">
+        <f t="shared" si="6"/>
+        <v>63.55511930456008</v>
+      </c>
+      <c r="G290" s="1"/>
+      <c r="H290" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" hidden="1">
+      <c r="A291" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B291" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C291" s="8">
+        <v>165</v>
+      </c>
+      <c r="D291" s="4">
+        <v>36.5645112911212</v>
+      </c>
+      <c r="E291" s="6">
+        <v>20</v>
+      </c>
+      <c r="F291" s="3">
+        <f t="shared" si="6"/>
+        <v>29.251609032896958</v>
+      </c>
+      <c r="G291" s="1"/>
+      <c r="H291" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" hidden="1">
+      <c r="A292" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C292" s="8">
+        <v>150</v>
+      </c>
+      <c r="D292" s="4">
+        <v>26.652654623306201</v>
+      </c>
+      <c r="E292" s="6">
+        <v>20</v>
+      </c>
+      <c r="F292" s="3">
+        <f t="shared" si="6"/>
+        <v>21.322123698644962</v>
+      </c>
+      <c r="G292" s="1"/>
+      <c r="H292" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B293" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C293" s="8">
+        <v>176</v>
+      </c>
+      <c r="D293" s="4">
+        <v>38.983727564102601</v>
+      </c>
+      <c r="E293" s="6">
+        <v>20</v>
+      </c>
+      <c r="F293" s="3">
+        <f t="shared" si="6"/>
+        <v>31.186982051282079</v>
+      </c>
+      <c r="G293" s="1"/>
+      <c r="H293" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B294" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C294" s="8">
+        <v>152</v>
+      </c>
+      <c r="D294" s="4">
+        <v>29.369150000000001</v>
+      </c>
+      <c r="E294" s="6">
+        <v>20</v>
+      </c>
+      <c r="F294" s="3">
+        <f t="shared" si="6"/>
+        <v>23.49532</v>
+      </c>
+      <c r="G294" s="1"/>
+      <c r="H294" s="7"/>
+    </row>
+    <row r="295" spans="1:8" hidden="1">
+      <c r="A295" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B295" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C295" s="8">
+        <v>144</v>
+      </c>
+      <c r="D295" s="4">
+        <v>25.9015791666667</v>
+      </c>
+      <c r="E295" s="6">
+        <v>20</v>
+      </c>
+      <c r="F295" s="3">
+        <f t="shared" si="6"/>
+        <v>20.721263333333361</v>
+      </c>
+      <c r="G295" s="1"/>
+      <c r="H295" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" hidden="1">
+      <c r="A296" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C296" s="8">
+        <v>152</v>
+      </c>
+      <c r="D296" s="4">
+        <v>51.8131396791036</v>
+      </c>
+      <c r="E296" s="6">
+        <v>20</v>
+      </c>
+      <c r="F296" s="3">
+        <f t="shared" si="6"/>
+        <v>41.450511743282881</v>
+      </c>
+      <c r="G296" s="1"/>
+      <c r="H296" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" hidden="1">
+      <c r="A297" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B297" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C297" s="8">
+        <v>160</v>
+      </c>
+      <c r="D297" s="4">
+        <v>51.689584941242103</v>
+      </c>
+      <c r="E297" s="6">
+        <v>20</v>
+      </c>
+      <c r="F297" s="3">
+        <f t="shared" si="6"/>
+        <v>41.351667952993679</v>
+      </c>
+      <c r="G297" s="1"/>
+      <c r="H297" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" hidden="1">
+      <c r="A298" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B298" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C298" s="8">
+        <v>140</v>
+      </c>
+      <c r="D298" s="4">
+        <v>33.752337015425901</v>
+      </c>
+      <c r="E298" s="6">
+        <v>20</v>
+      </c>
+      <c r="F298" s="3">
+        <f t="shared" si="6"/>
+        <v>27.00186961234072</v>
+      </c>
+      <c r="G298" s="1"/>
+      <c r="H298" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" hidden="1">
+      <c r="A299" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B299" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C299" s="8">
+        <v>152</v>
+      </c>
+      <c r="D299" s="4">
+        <v>36.639637711864403</v>
+      </c>
+      <c r="E299" s="6">
+        <v>20</v>
+      </c>
+      <c r="F299" s="3">
+        <f t="shared" si="6"/>
+        <v>29.311710169491523</v>
+      </c>
+      <c r="G299" s="1"/>
+      <c r="H299" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" hidden="1">
+      <c r="A300" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B300" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C300" s="8">
+        <v>120</v>
+      </c>
+      <c r="D300" s="4">
+        <v>82.710917210477902</v>
+      </c>
+      <c r="E300" s="6">
+        <v>20</v>
+      </c>
+      <c r="F300" s="3">
+        <f t="shared" si="6"/>
+        <v>66.168733768382324</v>
+      </c>
+      <c r="G300" s="1"/>
+      <c r="H300" s="7"/>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B301" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C301" s="8">
+        <v>152</v>
+      </c>
+      <c r="D301" s="4">
+        <v>41.237774305555597</v>
+      </c>
+      <c r="E301" s="6">
+        <v>20</v>
+      </c>
+      <c r="F301" s="3">
+        <f t="shared" si="6"/>
+        <v>32.990219444444477</v>
+      </c>
+      <c r="G301" s="1"/>
+      <c r="H301" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B302" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C302" s="8">
+        <v>176</v>
+      </c>
+      <c r="D302" s="4">
+        <v>35.776740853658502</v>
+      </c>
+      <c r="E302" s="6">
+        <v>20</v>
+      </c>
+      <c r="F302" s="3">
+        <f t="shared" si="6"/>
+        <v>28.621392682926803</v>
+      </c>
+      <c r="G302" s="1"/>
+      <c r="H302" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" hidden="1">
+      <c r="A303" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B303" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C303" s="8">
+        <v>155</v>
+      </c>
+      <c r="D303" s="4">
+        <v>34.409324694867799</v>
+      </c>
+      <c r="E303" s="6">
+        <v>20</v>
+      </c>
+      <c r="F303" s="3">
+        <f t="shared" si="6"/>
+        <v>27.527459755894238</v>
+      </c>
+      <c r="G303" s="1"/>
+      <c r="H303" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B304" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C304" s="8">
+        <v>160</v>
+      </c>
+      <c r="D304" s="4">
+        <v>39.613659736257702</v>
+      </c>
+      <c r="E304" s="6">
+        <v>20</v>
+      </c>
+      <c r="F304" s="3">
+        <f t="shared" si="6"/>
+        <v>31.69092778900616</v>
+      </c>
+      <c r="G304" s="1"/>
+      <c r="H304" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" hidden="1">
+      <c r="A305" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B305" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C305" s="8">
+        <v>149</v>
+      </c>
+      <c r="D305" s="4">
+        <v>48.518500000000003</v>
+      </c>
+      <c r="E305" s="6">
+        <v>20</v>
+      </c>
+      <c r="F305" s="3">
+        <f t="shared" si="6"/>
+        <v>38.814800000000005</v>
+      </c>
+      <c r="G305" s="1"/>
+      <c r="H305" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C306" s="8">
+        <v>136</v>
+      </c>
+      <c r="D306" s="4">
+        <v>38.165462682006002</v>
+      </c>
+      <c r="E306" s="6">
+        <v>20</v>
+      </c>
+      <c r="F306" s="3">
+        <f t="shared" si="6"/>
+        <v>30.532370145604801</v>
+      </c>
+      <c r="G306" s="1"/>
+      <c r="H306" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" hidden="1">
+      <c r="A307" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B307" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C307" s="8">
+        <v>116</v>
+      </c>
+      <c r="D307" s="4">
+        <v>45.3100733333333</v>
+      </c>
+      <c r="E307" s="6">
+        <v>20</v>
+      </c>
+      <c r="F307" s="3">
+        <f t="shared" si="6"/>
+        <v>36.248058666666637</v>
+      </c>
+      <c r="G307" s="1"/>
+      <c r="H307" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" hidden="1">
+      <c r="A308" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B308" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C308" s="8">
+        <v>160</v>
+      </c>
+      <c r="D308" s="4">
+        <v>29.939920560611199</v>
+      </c>
+      <c r="E308" s="6">
+        <v>20</v>
+      </c>
+      <c r="F308" s="3">
+        <f t="shared" si="6"/>
+        <v>23.951936448488958</v>
+      </c>
+      <c r="G308" s="1"/>
+      <c r="H308" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" hidden="1">
+      <c r="A309" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B309" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C309" s="8">
+        <v>166</v>
+      </c>
+      <c r="D309" s="4">
+        <v>42.274472239994097</v>
+      </c>
+      <c r="E309" s="6">
+        <v>20</v>
+      </c>
+      <c r="F309" s="3">
+        <f t="shared" si="6"/>
+        <v>33.819577791995279</v>
+      </c>
+      <c r="G309" s="1"/>
+      <c r="H309" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" hidden="1">
+      <c r="A310" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B310" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C310" s="8">
+        <v>72</v>
+      </c>
+      <c r="D310" s="4">
+        <v>56.807669735863101</v>
+      </c>
+      <c r="E310" s="6">
+        <v>20</v>
+      </c>
+      <c r="F310" s="3">
+        <f t="shared" si="6"/>
+        <v>45.446135788690484</v>
+      </c>
+      <c r="G310" s="1"/>
+      <c r="H310" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" hidden="1">
+      <c r="A311" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B311" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C311" s="8">
+        <v>144</v>
+      </c>
+      <c r="D311" s="4">
+        <v>32.576381578947398</v>
+      </c>
+      <c r="E311" s="6">
+        <v>20</v>
+      </c>
+      <c r="F311" s="3">
+        <f t="shared" si="6"/>
+        <v>26.06110526315792</v>
+      </c>
+      <c r="G311" s="1"/>
+      <c r="H311" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" hidden="1">
+      <c r="A312" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B312" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C312" s="8">
+        <v>144</v>
+      </c>
+      <c r="D312" s="4">
+        <v>20.854525842696599</v>
+      </c>
+      <c r="E312" s="6">
+        <v>20</v>
+      </c>
+      <c r="F312" s="3">
+        <f t="shared" si="6"/>
+        <v>16.683620674157279</v>
+      </c>
+      <c r="G312" s="1"/>
+      <c r="H312" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" hidden="1">
+      <c r="A313" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B313" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C313" s="8">
+        <v>149</v>
+      </c>
+      <c r="D313" s="4">
+        <v>41.7979743687415</v>
+      </c>
+      <c r="E313" s="6">
+        <v>20</v>
+      </c>
+      <c r="F313" s="3">
+        <f t="shared" si="6"/>
+        <v>33.4383794949932</v>
+      </c>
+      <c r="G313" s="1"/>
+      <c r="H313" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" hidden="1">
+      <c r="A314" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B314" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C314" s="8">
+        <v>88</v>
+      </c>
+      <c r="D314" s="4">
+        <v>46.328410714285702</v>
+      </c>
+      <c r="E314" s="6">
+        <v>20</v>
+      </c>
+      <c r="F314" s="3">
+        <f t="shared" si="6"/>
+        <v>37.062728571428565</v>
+      </c>
+      <c r="G314" s="1"/>
+      <c r="H314" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B315" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C315" s="8">
+        <v>168</v>
+      </c>
+      <c r="D315" s="4">
+        <v>41.891496794871799</v>
+      </c>
+      <c r="E315" s="6">
+        <v>20</v>
+      </c>
+      <c r="F315" s="3">
+        <f t="shared" si="6"/>
+        <v>33.513197435897439</v>
+      </c>
+      <c r="G315" s="1"/>
+      <c r="H315" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" hidden="1">
+      <c r="A316" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B316" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C316" s="8">
+        <v>152</v>
+      </c>
+      <c r="D316" s="4">
+        <v>45.171326816160096</v>
+      </c>
+      <c r="E316" s="6">
+        <v>20</v>
+      </c>
+      <c r="F316" s="3">
+        <f t="shared" si="6"/>
+        <v>36.13706145292808</v>
+      </c>
+      <c r="G316" s="1"/>
+      <c r="H316" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" hidden="1">
+      <c r="A317" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B317" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C317" s="8">
+        <v>160</v>
+      </c>
+      <c r="D317" s="4">
+        <v>46.961879458762901</v>
+      </c>
+      <c r="E317" s="6">
+        <v>20</v>
+      </c>
+      <c r="F317" s="3">
+        <f t="shared" si="6"/>
+        <v>37.569503567010322</v>
+      </c>
+      <c r="G317" s="1"/>
+      <c r="H317" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B318" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C318" s="8">
+        <v>176</v>
+      </c>
+      <c r="D318" s="4">
+        <v>33.3504886363636</v>
+      </c>
+      <c r="E318" s="6">
+        <v>20</v>
+      </c>
+      <c r="F318" s="3">
+        <f t="shared" si="6"/>
+        <v>26.680390909090882</v>
+      </c>
+      <c r="G318" s="1"/>
+      <c r="H318" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" hidden="1">
+      <c r="A319" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B319" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C319" s="8">
+        <v>155</v>
+      </c>
+      <c r="D319" s="4">
+        <v>43.916780777949199</v>
+      </c>
+      <c r="E319" s="6">
+        <v>20</v>
+      </c>
+      <c r="F319" s="3">
+        <f t="shared" si="6"/>
+        <v>35.133424622359357</v>
+      </c>
+      <c r="G319" s="1"/>
+      <c r="H319" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" hidden="1">
+      <c r="A320" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B320" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C320" s="8">
+        <v>152</v>
+      </c>
+      <c r="D320" s="4">
+        <v>50.409042016806701</v>
+      </c>
+      <c r="E320" s="6">
+        <v>20</v>
+      </c>
+      <c r="F320" s="3">
+        <f t="shared" si="6"/>
+        <v>40.327233613445358</v>
+      </c>
+      <c r="G320" s="1"/>
+      <c r="H320" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" hidden="1">
+      <c r="A321" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B321" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C321" s="8">
+        <v>64</v>
+      </c>
+      <c r="D321" s="4">
+        <v>59.140677490234403</v>
+      </c>
+      <c r="E321" s="6">
+        <v>20</v>
+      </c>
+      <c r="F321" s="3">
+        <f t="shared" si="6"/>
+        <v>47.312541992187519</v>
+      </c>
+      <c r="G321" s="1"/>
+      <c r="H321" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" hidden="1">
+      <c r="A322" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B322" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C322" s="8">
+        <v>153</v>
+      </c>
+      <c r="D322" s="4">
+        <v>21.378495577123001</v>
+      </c>
+      <c r="E322" s="6">
+        <v>20</v>
+      </c>
+      <c r="F322" s="3">
+        <f t="shared" si="6"/>
+        <v>17.1027964616984</v>
+      </c>
+      <c r="G322" s="1"/>
+      <c r="H322" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" hidden="1">
+      <c r="A323" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B323" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C323" s="8">
+        <v>148</v>
+      </c>
+      <c r="D323" s="4">
+        <v>31.354510135135101</v>
+      </c>
+      <c r="E323" s="6">
+        <v>20</v>
+      </c>
+      <c r="F323" s="3">
+        <f t="shared" si="6"/>
+        <v>25.083608108108081</v>
+      </c>
+      <c r="G323" s="1"/>
+      <c r="H323" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B324" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C324" s="8">
+        <v>172</v>
+      </c>
+      <c r="D324" s="4">
+        <v>29.8711051162791</v>
+      </c>
+      <c r="E324" s="6">
+        <v>20</v>
+      </c>
+      <c r="F324" s="3">
+        <f t="shared" si="6"/>
+        <v>23.896884093023282</v>
+      </c>
+      <c r="G324" s="1"/>
+      <c r="H324" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B325" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C325" s="8">
+        <v>160</v>
+      </c>
+      <c r="D325" s="4">
+        <v>42.7987368421052</v>
+      </c>
+      <c r="E325" s="6">
+        <v>20</v>
+      </c>
+      <c r="F325" s="3">
+        <f t="shared" si="6"/>
+        <v>34.238989473684157</v>
+      </c>
+      <c r="G325" s="1"/>
+      <c r="H325" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" hidden="1">
+      <c r="A326" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B326" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C326" s="8">
+        <v>96</v>
+      </c>
+      <c r="D326" s="4">
+        <v>54.521819316198801</v>
+      </c>
+      <c r="E326" s="6">
+        <v>20</v>
+      </c>
+      <c r="F326" s="3">
+        <f t="shared" si="6"/>
+        <v>43.617455452959042</v>
+      </c>
+      <c r="G326" s="1"/>
+      <c r="H326" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" hidden="1">
+      <c r="A327" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B327" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C327" s="8">
+        <v>165</v>
+      </c>
+      <c r="D327" s="4">
+        <v>33.390634494379299</v>
+      </c>
+      <c r="E327" s="6">
+        <v>20</v>
+      </c>
+      <c r="F327" s="3">
+        <f t="shared" si="6"/>
+        <v>26.712507595503439</v>
+      </c>
+      <c r="G327" s="1"/>
+      <c r="H327" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" hidden="1">
+      <c r="A328" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B328" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C328" s="8">
+        <v>88</v>
+      </c>
+      <c r="D328" s="4">
+        <v>33.220852272727299</v>
+      </c>
+      <c r="E328" s="6">
+        <v>20</v>
+      </c>
+      <c r="F328" s="3">
+        <f t="shared" si="6"/>
+        <v>26.576681818181839</v>
+      </c>
+      <c r="G328" s="1"/>
+      <c r="H328" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" hidden="1">
+      <c r="A329" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B329" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C329" s="8">
+        <v>152</v>
+      </c>
+      <c r="D329" s="4">
+        <v>44.647664948453603</v>
+      </c>
+      <c r="E329" s="6">
+        <v>20</v>
+      </c>
+      <c r="F329" s="3">
+        <f t="shared" si="6"/>
+        <v>35.718131958762882</v>
+      </c>
+      <c r="G329" s="1"/>
+      <c r="H329" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" hidden="1">
+      <c r="A330" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B330" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C330" s="8">
+        <v>160</v>
+      </c>
+      <c r="D330" s="4">
+        <v>45.611230451030899</v>
+      </c>
+      <c r="E330" s="6">
+        <v>20</v>
+      </c>
+      <c r="F330" s="3">
+        <f t="shared" si="6"/>
+        <v>36.488984360824716</v>
+      </c>
+      <c r="G330" s="1"/>
+      <c r="H330" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" hidden="1">
+      <c r="A331" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B331" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C331" s="8">
+        <v>176</v>
+      </c>
+      <c r="D331" s="4">
+        <v>27.792088996674099</v>
+      </c>
+      <c r="E331" s="6">
+        <v>20</v>
+      </c>
+      <c r="F331" s="3">
+        <f t="shared" ref="F331:F357" si="7">D331-(D331*E331)/100</f>
+        <v>22.23367119733928</v>
+      </c>
+      <c r="G331" s="1"/>
+      <c r="H331" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" hidden="1">
+      <c r="A332" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B332" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C332" s="8">
+        <v>128</v>
+      </c>
+      <c r="D332" s="4">
+        <v>40.237050000000004</v>
+      </c>
+      <c r="E332" s="6">
+        <v>20</v>
+      </c>
+      <c r="F332" s="3">
+        <f t="shared" si="7"/>
+        <v>32.189640000000004</v>
+      </c>
+      <c r="G332" s="1"/>
+      <c r="H332" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" hidden="1">
+      <c r="A333" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B333" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C333" s="8">
+        <v>104</v>
+      </c>
+      <c r="D333" s="4">
+        <v>30.264486611156599</v>
+      </c>
+      <c r="E333" s="6">
+        <v>20</v>
+      </c>
+      <c r="F333" s="3">
+        <f t="shared" si="7"/>
+        <v>24.211589288925278</v>
+      </c>
+      <c r="G333" s="1"/>
+      <c r="H333" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" hidden="1">
+      <c r="A334" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B334" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C334" s="8">
+        <v>184</v>
+      </c>
+      <c r="D334" s="4">
+        <v>31.831795681804</v>
+      </c>
+      <c r="E334" s="6">
+        <v>20</v>
+      </c>
+      <c r="F334" s="3">
+        <f t="shared" si="7"/>
+        <v>25.4654365454432</v>
+      </c>
+      <c r="G334" s="1"/>
+      <c r="H334" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B335" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C335" s="8">
+        <v>176</v>
+      </c>
+      <c r="D335" s="4">
+        <v>35.322577318067601</v>
+      </c>
+      <c r="E335" s="6">
+        <v>20</v>
+      </c>
+      <c r="F335" s="3">
+        <f t="shared" si="7"/>
+        <v>28.25806185445408</v>
+      </c>
+      <c r="G335" s="1"/>
+      <c r="H335" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" hidden="1">
+      <c r="A336" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B336" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C336" s="8">
+        <v>144</v>
+      </c>
+      <c r="D336" s="4">
+        <v>29.558134722222199</v>
+      </c>
+      <c r="E336" s="6">
+        <v>20</v>
+      </c>
+      <c r="F336" s="3">
+        <f t="shared" si="7"/>
+        <v>23.64650777777776</v>
+      </c>
+      <c r="G336" s="1"/>
+      <c r="H336" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B337" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C337" s="8">
+        <v>176</v>
+      </c>
+      <c r="D337" s="4">
+        <v>39.6423555494639</v>
+      </c>
+      <c r="E337" s="6">
+        <v>20</v>
+      </c>
+      <c r="F337" s="3">
+        <f t="shared" si="7"/>
+        <v>31.713884439571121</v>
+      </c>
+      <c r="G337" s="1"/>
+      <c r="H337" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" hidden="1">
+      <c r="A338" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B338" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C338" s="8">
+        <v>152</v>
+      </c>
+      <c r="D338" s="4">
+        <v>27.077690273477799</v>
+      </c>
+      <c r="E338" s="6">
+        <v>20</v>
+      </c>
+      <c r="F338" s="3">
+        <f t="shared" si="7"/>
+        <v>21.662152218782239</v>
+      </c>
+      <c r="G338" s="1"/>
+      <c r="H338" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" hidden="1">
+      <c r="A339" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B339" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C339" s="8">
+        <v>136</v>
+      </c>
+      <c r="D339" s="4">
+        <v>32.911100855168797</v>
+      </c>
+      <c r="E339" s="6">
+        <v>20</v>
+      </c>
+      <c r="F339" s="3">
+        <f t="shared" si="7"/>
+        <v>26.328880684135036</v>
+      </c>
+      <c r="G339" s="1"/>
+      <c r="H339" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" hidden="1">
+      <c r="A340" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B340" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C340" s="8">
+        <v>116</v>
+      </c>
+      <c r="D340" s="4">
+        <v>46.215099605473</v>
+      </c>
+      <c r="E340" s="6">
+        <v>20</v>
+      </c>
+      <c r="F340" s="3">
+        <f t="shared" si="7"/>
+        <v>36.9720796843784</v>
+      </c>
+      <c r="G340" s="1"/>
+      <c r="H340" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" hidden="1">
+      <c r="A341" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B341" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C341" s="8">
+        <v>160</v>
+      </c>
+      <c r="D341" s="4">
+        <v>33.435774198943697</v>
+      </c>
+      <c r="E341" s="6">
+        <v>20</v>
+      </c>
+      <c r="F341" s="3">
+        <f t="shared" si="7"/>
+        <v>26.748619359154958</v>
+      </c>
+      <c r="G341" s="1"/>
+      <c r="H341" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" hidden="1">
+      <c r="A342" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B342" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C342" s="8">
+        <v>144</v>
+      </c>
+      <c r="D342" s="4">
+        <v>42.045465399363998</v>
+      </c>
+      <c r="E342" s="6">
+        <v>20</v>
+      </c>
+      <c r="F342" s="3">
+        <f t="shared" si="7"/>
+        <v>33.636372319491201</v>
+      </c>
+      <c r="G342" s="1"/>
+      <c r="H342" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" hidden="1">
+      <c r="A343" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B343" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C343" s="8">
+        <v>160</v>
+      </c>
+      <c r="D343" s="4">
+        <v>41.8760733039434</v>
+      </c>
+      <c r="E343" s="6">
+        <v>20</v>
+      </c>
+      <c r="F343" s="3">
+        <f t="shared" si="7"/>
+        <v>33.500858643154722</v>
+      </c>
+      <c r="G343" s="1"/>
+      <c r="H343" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B344" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C344" s="8">
+        <v>184</v>
+      </c>
+      <c r="D344" s="4">
+        <v>38.6545889975392</v>
+      </c>
+      <c r="E344" s="6">
+        <v>20</v>
+      </c>
+      <c r="F344" s="3">
+        <f t="shared" si="7"/>
+        <v>30.923671198031361</v>
+      </c>
+      <c r="G344" s="1"/>
+      <c r="H344" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" hidden="1">
+      <c r="A345" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B345" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C345" s="8">
+        <v>48</v>
+      </c>
+      <c r="D345" s="4">
+        <v>49.342044921875001</v>
+      </c>
+      <c r="E345" s="6">
+        <v>20</v>
+      </c>
+      <c r="F345" s="3">
+        <f t="shared" si="7"/>
+        <v>39.473635937499999</v>
+      </c>
+      <c r="G345" s="1"/>
+      <c r="H345" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B346" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C346" s="8">
+        <v>176</v>
+      </c>
+      <c r="D346" s="4">
+        <v>41.570884657429602</v>
+      </c>
+      <c r="E346" s="6">
+        <v>20</v>
+      </c>
+      <c r="F346" s="3">
+        <f t="shared" si="7"/>
+        <v>33.256707725943684</v>
+      </c>
+      <c r="G346" s="1"/>
+      <c r="H346" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" hidden="1">
+      <c r="A347" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B347" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C347" s="8">
+        <v>160</v>
+      </c>
+      <c r="D347" s="4">
+        <v>46.574795953608202</v>
+      </c>
+      <c r="E347" s="6">
+        <v>20</v>
+      </c>
+      <c r="F347" s="3">
+        <f t="shared" si="7"/>
+        <v>37.259836762886565</v>
+      </c>
+      <c r="G347" s="1"/>
+      <c r="H347" s="7"/>
+    </row>
+    <row r="348" spans="1:8" hidden="1">
+      <c r="A348" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B348" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C348" s="8">
+        <v>148</v>
+      </c>
+      <c r="D348" s="4">
+        <v>31.354510135135101</v>
+      </c>
+      <c r="E348" s="6">
+        <v>20</v>
+      </c>
+      <c r="F348" s="3">
+        <f t="shared" si="7"/>
+        <v>25.083608108108081</v>
+      </c>
+      <c r="G348" s="1"/>
+      <c r="H348" s="7"/>
+    </row>
+    <row r="349" spans="1:8" hidden="1">
+      <c r="A349" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B349" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C349" s="8">
+        <v>136</v>
+      </c>
+      <c r="D349" s="4">
+        <v>32.7995926077487</v>
+      </c>
+      <c r="E349" s="6">
+        <v>20</v>
+      </c>
+      <c r="F349" s="3">
+        <f t="shared" si="7"/>
+        <v>26.23967408619896</v>
+      </c>
+      <c r="G349" s="1"/>
+      <c r="H349" s="7"/>
+    </row>
+    <row r="350" spans="1:8" hidden="1">
+      <c r="A350" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B350" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C350" s="8">
+        <v>160</v>
+      </c>
+      <c r="D350" s="4">
+        <v>31.4801130013233</v>
+      </c>
+      <c r="E350" s="6">
+        <v>20</v>
+      </c>
+      <c r="F350" s="3">
+        <f t="shared" si="7"/>
+        <v>25.18409040105864</v>
+      </c>
+      <c r="G350" s="1"/>
+      <c r="H350" s="7"/>
+    </row>
+    <row r="351" spans="1:8" hidden="1">
+      <c r="A351" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B351" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C351" s="8">
+        <v>48</v>
+      </c>
+      <c r="D351" s="4">
+        <v>49.342044921875001</v>
+      </c>
+      <c r="E351" s="6">
+        <v>20</v>
+      </c>
+      <c r="F351" s="3">
+        <f t="shared" si="7"/>
+        <v>39.473635937499999</v>
+      </c>
+      <c r="G351" s="1"/>
+      <c r="H351" s="7"/>
+    </row>
+    <row r="352" spans="1:8" hidden="1">
+      <c r="A352" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B352" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C352" s="8">
+        <v>152</v>
+      </c>
+      <c r="D352" s="4">
+        <v>43.748869493379999</v>
+      </c>
+      <c r="E352" s="6">
+        <v>20</v>
+      </c>
+      <c r="F352" s="3">
+        <f t="shared" si="7"/>
+        <v>34.999095594704002</v>
+      </c>
+      <c r="G352" s="1"/>
+      <c r="H352" s="7"/>
+    </row>
+    <row r="353" spans="1:8" hidden="1">
+      <c r="A353" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B353" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C353" s="8">
+        <v>144</v>
+      </c>
+      <c r="D353" s="4">
+        <v>48.518500000000003</v>
+      </c>
+      <c r="E353" s="6">
+        <v>20</v>
+      </c>
+      <c r="F353" s="3">
+        <f t="shared" si="7"/>
+        <v>38.814800000000005</v>
+      </c>
+      <c r="G353" s="1"/>
+      <c r="H353" s="7"/>
+    </row>
+    <row r="354" spans="1:8" hidden="1">
+      <c r="A354" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B354" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C354" s="8">
+        <v>56</v>
+      </c>
+      <c r="D354" s="4">
+        <v>48.227740542061902</v>
+      </c>
+      <c r="E354" s="6">
+        <v>20</v>
+      </c>
+      <c r="F354" s="3">
+        <f t="shared" si="7"/>
+        <v>38.582192433649524</v>
+      </c>
+      <c r="G354" s="1"/>
+      <c r="H354" s="7"/>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B355" s="19">
+        <v>46173</v>
+      </c>
+      <c r="C355" s="20">
+        <v>176</v>
+      </c>
+      <c r="D355" s="21">
+        <v>33.3504886363636</v>
+      </c>
+      <c r="E355" s="22">
+        <v>20</v>
+      </c>
+      <c r="F355" s="23">
+        <f t="shared" si="7"/>
+        <v>26.680390909090882</v>
+      </c>
+      <c r="G355" s="24"/>
+      <c r="H355" s="25"/>
+    </row>
+    <row r="356" spans="1:8" hidden="1">
+      <c r="A356" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B356" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C356" s="26">
+        <v>104</v>
+      </c>
+      <c r="D356" s="4">
+        <v>36.3766542165462</v>
+      </c>
+      <c r="E356" s="6">
+        <v>20</v>
+      </c>
+      <c r="F356" s="3">
+        <f t="shared" si="7"/>
+        <v>29.101323373236959</v>
+      </c>
+      <c r="G356" s="1"/>
+      <c r="H356" s="1"/>
+    </row>
+    <row r="357" spans="1:8" hidden="1">
+      <c r="A357" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B357" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C357" s="26">
+        <v>24</v>
+      </c>
+      <c r="D357" s="4">
+        <v>33.060749496904002</v>
+      </c>
+      <c r="E357" s="6">
+        <v>20</v>
+      </c>
+      <c r="F357" s="3">
+        <f t="shared" si="7"/>
+        <v>26.448599597523202</v>
+      </c>
+      <c r="G357" s="1"/>
+      <c r="H357" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G285">
-    <filterColumn colId="0"/>
-    <filterColumn colId="1"/>
+  <autoFilter ref="A1:G357">
+    <filterColumn colId="0">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
@@ -8203,6 +10031,65 @@
     <hyperlink ref="H275" r:id="rId243"/>
     <hyperlink ref="H276" r:id="rId244"/>
     <hyperlink ref="H241" r:id="rId245" display="mailto:cyborg.3@hotmail.it"/>
+    <hyperlink ref="G286" r:id="rId246"/>
+    <hyperlink ref="H286" r:id="rId247"/>
+    <hyperlink ref="H287" r:id="rId248"/>
+    <hyperlink ref="H289" r:id="rId249"/>
+    <hyperlink ref="H290" r:id="rId250"/>
+    <hyperlink ref="H291" r:id="rId251"/>
+    <hyperlink ref="H292" r:id="rId252"/>
+    <hyperlink ref="H293" r:id="rId253"/>
+    <hyperlink ref="H295" r:id="rId254"/>
+    <hyperlink ref="H296" r:id="rId255"/>
+    <hyperlink ref="H297" r:id="rId256"/>
+    <hyperlink ref="H298" r:id="rId257"/>
+    <hyperlink ref="H299" r:id="rId258"/>
+    <hyperlink ref="H301" r:id="rId259"/>
+    <hyperlink ref="H302" r:id="rId260"/>
+    <hyperlink ref="H303" r:id="rId261"/>
+    <hyperlink ref="H304" r:id="rId262"/>
+    <hyperlink ref="H305" r:id="rId263"/>
+    <hyperlink ref="H306" r:id="rId264"/>
+    <hyperlink ref="H307" r:id="rId265"/>
+    <hyperlink ref="H308" r:id="rId266"/>
+    <hyperlink ref="H309" r:id="rId267"/>
+    <hyperlink ref="H310" r:id="rId268"/>
+    <hyperlink ref="H311" r:id="rId269"/>
+    <hyperlink ref="H312" r:id="rId270"/>
+    <hyperlink ref="H313" r:id="rId271"/>
+    <hyperlink ref="H314" r:id="rId272"/>
+    <hyperlink ref="H315" r:id="rId273"/>
+    <hyperlink ref="H316" r:id="rId274"/>
+    <hyperlink ref="H317" r:id="rId275"/>
+    <hyperlink ref="H318" r:id="rId276"/>
+    <hyperlink ref="H319" r:id="rId277"/>
+    <hyperlink ref="H320" r:id="rId278"/>
+    <hyperlink ref="H321" r:id="rId279"/>
+    <hyperlink ref="H322" r:id="rId280"/>
+    <hyperlink ref="H323" r:id="rId281"/>
+    <hyperlink ref="H324" r:id="rId282"/>
+    <hyperlink ref="H325" r:id="rId283"/>
+    <hyperlink ref="H326" r:id="rId284"/>
+    <hyperlink ref="H327" r:id="rId285"/>
+    <hyperlink ref="H328" r:id="rId286"/>
+    <hyperlink ref="H329" r:id="rId287"/>
+    <hyperlink ref="H330" r:id="rId288"/>
+    <hyperlink ref="H331" r:id="rId289"/>
+    <hyperlink ref="H332" r:id="rId290"/>
+    <hyperlink ref="H333" r:id="rId291"/>
+    <hyperlink ref="H334" r:id="rId292"/>
+    <hyperlink ref="H335" r:id="rId293"/>
+    <hyperlink ref="H336" r:id="rId294"/>
+    <hyperlink ref="H337" r:id="rId295"/>
+    <hyperlink ref="H338" r:id="rId296"/>
+    <hyperlink ref="H339" r:id="rId297"/>
+    <hyperlink ref="H340" r:id="rId298"/>
+    <hyperlink ref="H341" r:id="rId299"/>
+    <hyperlink ref="H342" r:id="rId300"/>
+    <hyperlink ref="H343" r:id="rId301"/>
+    <hyperlink ref="H344" r:id="rId302"/>
+    <hyperlink ref="H345" r:id="rId303"/>
+    <hyperlink ref="H346" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8210,7 +10097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D1:L87"/>
+  <dimension ref="D1:L104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -8224,17 +10111,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12">
-      <c r="D1" s="18">
+      <c r="D1" s="27">
         <v>46023</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
     </row>
     <row r="2" spans="4:12">
       <c r="D2" s="1" t="s">
@@ -8609,17 +10496,17 @@
       </c>
     </row>
     <row r="25" spans="4:12">
-      <c r="D25" s="18">
+      <c r="D25" s="27">
         <v>46054</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
     </row>
     <row r="26" spans="4:12">
       <c r="D26" s="1" t="s">
@@ -9006,17 +10893,17 @@
       </c>
     </row>
     <row r="50" spans="4:12">
-      <c r="D50" s="18">
+      <c r="D50" s="27">
         <v>46082</v>
       </c>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
     </row>
     <row r="51" spans="4:12">
       <c r="D51" s="1" t="s">
@@ -9419,17 +11306,17 @@
       </c>
     </row>
     <row r="78" spans="4:12">
-      <c r="D78" s="18">
+      <c r="D78" s="27">
         <v>46113</v>
       </c>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+      <c r="K78" s="28"/>
+      <c r="L78" s="28"/>
     </row>
     <row r="79" spans="4:12">
       <c r="D79" s="1" t="s">
@@ -9653,12 +11540,250 @@
         <v>30.212524501078299</v>
       </c>
     </row>
+    <row r="94" spans="4:12">
+      <c r="D94" s="27">
+        <v>46143</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
+      <c r="J94" s="28"/>
+      <c r="K94" s="28"/>
+      <c r="L94" s="28"/>
+    </row>
+    <row r="95" spans="4:12">
+      <c r="D95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="4:12">
+      <c r="D96" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F96" s="8">
+        <v>160</v>
+      </c>
+      <c r="G96" s="4">
+        <v>42.7987368421052</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="10">
+        <v>46173</v>
+      </c>
+      <c r="K96" s="8">
+        <v>176</v>
+      </c>
+      <c r="L96" s="4">
+        <v>35.776740853658502</v>
+      </c>
+    </row>
+    <row r="97" spans="4:12">
+      <c r="D97" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F97" s="8">
+        <v>168</v>
+      </c>
+      <c r="G97" s="4">
+        <v>41.891496794871799</v>
+      </c>
+      <c r="I97" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J97" s="10">
+        <v>46173</v>
+      </c>
+      <c r="K97" s="8">
+        <v>176</v>
+      </c>
+      <c r="L97" s="4">
+        <v>35.322577318067601</v>
+      </c>
+    </row>
+    <row r="98" spans="4:12">
+      <c r="D98" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E98" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F98" s="8">
+        <v>176</v>
+      </c>
+      <c r="G98" s="4">
+        <v>41.570884657429602</v>
+      </c>
+      <c r="I98" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" s="10">
+        <v>46173</v>
+      </c>
+      <c r="K98" s="8">
+        <v>176</v>
+      </c>
+      <c r="L98" s="4">
+        <v>33.3504886363636</v>
+      </c>
+    </row>
+    <row r="99" spans="4:12">
+      <c r="D99" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F99" s="8">
+        <v>152</v>
+      </c>
+      <c r="G99" s="4">
+        <v>41.237774305555597</v>
+      </c>
+      <c r="I99" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J99" s="10">
+        <v>46173</v>
+      </c>
+      <c r="K99" s="8">
+        <v>176</v>
+      </c>
+      <c r="L99" s="4">
+        <v>33.3504886363636</v>
+      </c>
+    </row>
+    <row r="100" spans="4:12">
+      <c r="D100" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F100" s="8">
+        <v>176</v>
+      </c>
+      <c r="G100" s="4">
+        <v>39.6423555494639</v>
+      </c>
+      <c r="I100" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J100" s="19">
+        <v>46173</v>
+      </c>
+      <c r="K100" s="20">
+        <v>172</v>
+      </c>
+      <c r="L100" s="21">
+        <v>29.8711051162791</v>
+      </c>
+    </row>
+    <row r="101" spans="4:12">
+      <c r="D101" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F101" s="8">
+        <v>160</v>
+      </c>
+      <c r="G101" s="4">
+        <v>39.613659736257702</v>
+      </c>
+      <c r="I101" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J101" s="10">
+        <v>46173</v>
+      </c>
+      <c r="K101" s="26">
+        <v>152</v>
+      </c>
+      <c r="L101" s="4">
+        <v>29.369150000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="4:12">
+      <c r="D102" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F102" s="8">
+        <v>176</v>
+      </c>
+      <c r="G102" s="4">
+        <v>38.983727564102601</v>
+      </c>
+    </row>
+    <row r="103" spans="4:12">
+      <c r="D103" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E103" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F103" s="8">
+        <v>184</v>
+      </c>
+      <c r="G103" s="4">
+        <v>38.6545889975392</v>
+      </c>
+    </row>
+    <row r="104" spans="4:12">
+      <c r="D104" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E104" s="10">
+        <v>46173</v>
+      </c>
+      <c r="F104" s="8">
+        <v>136</v>
+      </c>
+      <c r="G104" s="4">
+        <v>38.165462682006002</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D25:L25"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="D78:L78"/>
+    <mergeCell ref="D94:L94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="28695" windowHeight="12540" activeTab="1"/>
+    <workbookView xWindow="120" yWindow="45" windowWidth="28695" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="145">
   <si>
     <t>Tecnico</t>
   </si>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>IRTE0000122 - AMENTA SONNY</t>
+  </si>
+  <si>
+    <t>IRTE0000127 - DI MAURO FEDERICO</t>
   </si>
 </sst>
 </file>
@@ -640,16 +643,7 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -939,8 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -976,7 +969,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1">
+    <row r="2" spans="1:8">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -1003,7 +996,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1030,7 +1023,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>134</v>
       </c>
@@ -1053,7 +1046,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" hidden="1">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1078,7 +1071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,7 +1096,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1128,7 +1121,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1153,7 +1146,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1">
+    <row r="9" spans="1:8">
       <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
@@ -1178,7 +1171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1203,7 +1196,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1228,7 +1221,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1253,7 +1246,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,7 +1271,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1303,7 +1296,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>135</v>
       </c>
@@ -1326,7 +1319,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" hidden="1">
+    <row r="16" spans="1:8">
       <c r="A16" s="16" t="s">
         <v>16</v>
       </c>
@@ -1351,7 +1344,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1">
+    <row r="17" spans="1:8">
       <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
@@ -1376,7 +1369,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1401,7 +1394,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1">
+    <row r="19" spans="1:8">
       <c r="A19" s="16" t="s">
         <v>19</v>
       </c>
@@ -1426,7 +1419,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1">
+    <row r="20" spans="1:8">
       <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
@@ -1451,7 +1444,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1">
+    <row r="21" spans="1:8">
       <c r="A21" s="16" t="s">
         <v>21</v>
       </c>
@@ -1476,7 +1469,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1">
+    <row r="22" spans="1:8">
       <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
@@ -1501,7 +1494,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,7 +1519,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1">
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,7 +1544,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1">
+    <row r="25" spans="1:8">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -1576,7 +1569,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1">
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -1601,7 +1594,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1">
+    <row r="27" spans="1:8">
       <c r="A27" s="17" t="s">
         <v>27</v>
       </c>
@@ -1626,7 +1619,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1">
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -1651,7 +1644,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>132</v>
       </c>
@@ -1676,7 +1669,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1">
+    <row r="30" spans="1:8">
       <c r="A30" s="9" t="s">
         <v>29</v>
       </c>
@@ -1701,7 +1694,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1">
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1726,7 +1719,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1">
+    <row r="32" spans="1:8">
       <c r="A32" s="16" t="s">
         <v>31</v>
       </c>
@@ -1751,7 +1744,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,7 +1769,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1">
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1801,7 +1794,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1">
+    <row r="35" spans="1:8">
       <c r="A35" s="16" t="s">
         <v>34</v>
       </c>
@@ -1826,7 +1819,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1">
+    <row r="36" spans="1:8">
       <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
@@ -1851,7 +1844,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1">
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1876,7 +1869,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1">
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1901,7 +1894,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1">
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1926,7 +1919,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1">
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1951,7 +1944,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1">
+    <row r="41" spans="1:8">
       <c r="A41" s="16" t="s">
         <v>40</v>
       </c>
@@ -1976,7 +1969,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1">
+    <row r="42" spans="1:8">
       <c r="A42" s="16" t="s">
         <v>41</v>
       </c>
@@ -2001,7 +1994,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1">
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -2026,7 +2019,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1">
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -2051,7 +2044,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1">
+    <row r="45" spans="1:8">
       <c r="A45" s="17" t="s">
         <v>44</v>
       </c>
@@ -2076,7 +2069,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1">
+    <row r="46" spans="1:8">
       <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
@@ -2101,7 +2094,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1">
+    <row r="47" spans="1:8">
       <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
@@ -2126,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1">
+    <row r="48" spans="1:8">
       <c r="A48" s="17" t="s">
         <v>47</v>
       </c>
@@ -2151,7 +2144,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1">
+    <row r="49" spans="1:8">
       <c r="A49" s="17" t="s">
         <v>48</v>
       </c>
@@ -2176,7 +2169,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1">
+    <row r="50" spans="1:8">
       <c r="A50" s="17" t="s">
         <v>49</v>
       </c>
@@ -2201,7 +2194,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1">
+    <row r="51" spans="1:8">
       <c r="A51" s="17" t="s">
         <v>50</v>
       </c>
@@ -2226,7 +2219,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1">
+    <row r="52" spans="1:8">
       <c r="A52" s="16" t="s">
         <v>51</v>
       </c>
@@ -2251,7 +2244,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1">
+    <row r="53" spans="1:8">
       <c r="A53" s="17" t="s">
         <v>52</v>
       </c>
@@ -2276,7 +2269,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1">
+    <row r="54" spans="1:8">
       <c r="A54" s="16" t="s">
         <v>53</v>
       </c>
@@ -2301,7 +2294,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1">
+    <row r="55" spans="1:8">
       <c r="A55" s="17" t="s">
         <v>54</v>
       </c>
@@ -2326,7 +2319,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1">
+    <row r="56" spans="1:8">
       <c r="A56" s="17" t="s">
         <v>55</v>
       </c>
@@ -2351,7 +2344,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1">
+    <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
@@ -2376,7 +2369,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1">
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -2401,7 +2394,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1">
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
@@ -2426,7 +2419,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1">
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
@@ -2451,7 +2444,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1">
+    <row r="61" spans="1:8">
       <c r="A61" s="16" t="s">
         <v>60</v>
       </c>
@@ -2476,7 +2469,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1">
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
@@ -2501,7 +2494,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1">
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
@@ -2526,7 +2519,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1">
+    <row r="64" spans="1:8">
       <c r="A64" s="16" t="s">
         <v>63</v>
       </c>
@@ -2551,7 +2544,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1">
+    <row r="65" spans="1:8">
       <c r="A65" s="9" t="s">
         <v>129</v>
       </c>
@@ -2574,7 +2567,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" hidden="1">
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>128</v>
       </c>
@@ -2597,7 +2590,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" hidden="1">
+    <row r="67" spans="1:8">
       <c r="A67" s="17" t="s">
         <v>130</v>
       </c>
@@ -2620,7 +2613,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" hidden="1">
+    <row r="68" spans="1:8">
       <c r="A68" s="17" t="s">
         <v>131</v>
       </c>
@@ -2643,7 +2636,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" hidden="1">
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>137</v>
       </c>
@@ -2666,7 +2659,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" hidden="1">
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>136</v>
       </c>
@@ -2689,7 +2682,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" hidden="1">
+    <row r="71" spans="1:8">
       <c r="A71" s="14" t="s">
         <v>4</v>
       </c>
@@ -2716,7 +2709,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1">
+    <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -2743,7 +2736,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1">
+    <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
         <v>134</v>
       </c>
@@ -2766,7 +2759,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" hidden="1">
+    <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -2791,7 +2784,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1">
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
@@ -2816,7 +2809,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1">
+    <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
         <v>8</v>
       </c>
@@ -2841,7 +2834,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1">
+    <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
         <v>9</v>
       </c>
@@ -2866,7 +2859,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1">
+    <row r="78" spans="1:8">
       <c r="A78" s="16" t="s">
         <v>10</v>
       </c>
@@ -2891,7 +2884,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1">
+    <row r="79" spans="1:8">
       <c r="A79" s="16" t="s">
         <v>138</v>
       </c>
@@ -2914,7 +2907,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" hidden="1">
+    <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -2939,7 +2932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1">
+    <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
         <v>12</v>
       </c>
@@ -2964,7 +2957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1">
+    <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
@@ -2989,7 +2982,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1">
+    <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
         <v>14</v>
       </c>
@@ -3014,7 +3007,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1">
+    <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
         <v>15</v>
       </c>
@@ -3039,7 +3032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1">
+    <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
         <v>135</v>
       </c>
@@ -3062,7 +3055,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" hidden="1">
+    <row r="86" spans="1:8">
       <c r="A86" s="16" t="s">
         <v>16</v>
       </c>
@@ -3087,7 +3080,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1">
+    <row r="87" spans="1:8">
       <c r="A87" s="16" t="s">
         <v>17</v>
       </c>
@@ -3112,7 +3105,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1">
+    <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
         <v>18</v>
       </c>
@@ -3137,7 +3130,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1">
+    <row r="89" spans="1:8">
       <c r="A89" s="16" t="s">
         <v>19</v>
       </c>
@@ -3162,7 +3155,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1">
+    <row r="90" spans="1:8">
       <c r="A90" s="9" t="s">
         <v>20</v>
       </c>
@@ -3187,7 +3180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1">
+    <row r="91" spans="1:8">
       <c r="A91" s="16" t="s">
         <v>21</v>
       </c>
@@ -3212,7 +3205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1">
+    <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -3237,7 +3230,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1">
+    <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -3262,7 +3255,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1">
+    <row r="94" spans="1:8">
       <c r="A94" s="9" t="s">
         <v>25</v>
       </c>
@@ -3287,7 +3280,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1">
+    <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
         <v>26</v>
       </c>
@@ -3312,7 +3305,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1">
+    <row r="96" spans="1:8">
       <c r="A96" s="17" t="s">
         <v>27</v>
       </c>
@@ -3337,7 +3330,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1">
+    <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
         <v>28</v>
       </c>
@@ -3362,7 +3355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1">
+    <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
         <v>132</v>
       </c>
@@ -3387,7 +3380,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1">
+    <row r="99" spans="1:8">
       <c r="A99" s="9" t="s">
         <v>29</v>
       </c>
@@ -3412,7 +3405,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1">
+    <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
@@ -3437,7 +3430,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1">
+    <row r="101" spans="1:8">
       <c r="A101" s="16" t="s">
         <v>31</v>
       </c>
@@ -3462,7 +3455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1">
+    <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,7 +3480,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1">
+    <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
         <v>33</v>
       </c>
@@ -3512,7 +3505,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1">
+    <row r="104" spans="1:8">
       <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
@@ -3537,7 +3530,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1">
+    <row r="105" spans="1:8">
       <c r="A105" s="9" t="s">
         <v>35</v>
       </c>
@@ -3562,7 +3555,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1">
+    <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
         <v>36</v>
       </c>
@@ -3587,7 +3580,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1">
+    <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
@@ -3612,7 +3605,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1">
+    <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
         <v>38</v>
       </c>
@@ -3637,7 +3630,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1">
+    <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
         <v>39</v>
       </c>
@@ -3662,7 +3655,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1">
+    <row r="110" spans="1:8">
       <c r="A110" s="16" t="s">
         <v>40</v>
       </c>
@@ -3687,7 +3680,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1">
+    <row r="111" spans="1:8">
       <c r="A111" s="16" t="s">
         <v>41</v>
       </c>
@@ -3712,7 +3705,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1">
+    <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
         <v>42</v>
       </c>
@@ -3737,7 +3730,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1">
+    <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
         <v>43</v>
       </c>
@@ -3762,7 +3755,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1">
+    <row r="114" spans="1:8">
       <c r="A114" s="17" t="s">
         <v>44</v>
       </c>
@@ -3787,7 +3780,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1">
+    <row r="115" spans="1:8">
       <c r="A115" s="9" t="s">
         <v>45</v>
       </c>
@@ -3812,7 +3805,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1">
+    <row r="116" spans="1:8">
       <c r="A116" s="9" t="s">
         <v>46</v>
       </c>
@@ -3837,7 +3830,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1">
+    <row r="117" spans="1:8">
       <c r="A117" s="17" t="s">
         <v>47</v>
       </c>
@@ -3862,7 +3855,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1">
+    <row r="118" spans="1:8">
       <c r="A118" s="17" t="s">
         <v>48</v>
       </c>
@@ -3887,7 +3880,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1">
+    <row r="119" spans="1:8">
       <c r="A119" s="17" t="s">
         <v>49</v>
       </c>
@@ -3912,7 +3905,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1">
+    <row r="120" spans="1:8">
       <c r="A120" s="17" t="s">
         <v>50</v>
       </c>
@@ -3937,7 +3930,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1">
+    <row r="121" spans="1:8">
       <c r="A121" s="16" t="s">
         <v>51</v>
       </c>
@@ -3962,7 +3955,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1">
+    <row r="122" spans="1:8">
       <c r="A122" s="17" t="s">
         <v>52</v>
       </c>
@@ -3987,7 +3980,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1">
+    <row r="123" spans="1:8">
       <c r="A123" s="16" t="s">
         <v>53</v>
       </c>
@@ -4012,7 +4005,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1">
+    <row r="124" spans="1:8">
       <c r="A124" s="17" t="s">
         <v>54</v>
       </c>
@@ -4037,7 +4030,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1">
+    <row r="125" spans="1:8">
       <c r="A125" s="17" t="s">
         <v>55</v>
       </c>
@@ -4062,7 +4055,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1">
+    <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
         <v>56</v>
       </c>
@@ -4087,7 +4080,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1">
+    <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,7 +4105,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1">
+    <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
         <v>58</v>
       </c>
@@ -4137,7 +4130,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1">
+    <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
         <v>59</v>
       </c>
@@ -4162,7 +4155,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1">
+    <row r="130" spans="1:8">
       <c r="A130" s="16" t="s">
         <v>60</v>
       </c>
@@ -4187,7 +4180,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1">
+    <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
         <v>61</v>
       </c>
@@ -4212,7 +4205,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1">
+    <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
         <v>62</v>
       </c>
@@ -4237,7 +4230,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1">
+    <row r="133" spans="1:8">
       <c r="A133" s="16" t="s">
         <v>63</v>
       </c>
@@ -4262,7 +4255,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1">
+    <row r="134" spans="1:8">
       <c r="A134" s="9" t="s">
         <v>129</v>
       </c>
@@ -4285,7 +4278,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" hidden="1">
+    <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
         <v>128</v>
       </c>
@@ -4308,7 +4301,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" hidden="1">
+    <row r="136" spans="1:8">
       <c r="A136" s="17" t="s">
         <v>130</v>
       </c>
@@ -4331,7 +4324,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8" hidden="1">
+    <row r="137" spans="1:8">
       <c r="A137" s="17" t="s">
         <v>131</v>
       </c>
@@ -4354,7 +4347,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" hidden="1">
+    <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
         <v>137</v>
       </c>
@@ -4377,7 +4370,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8" hidden="1">
+    <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
         <v>136</v>
       </c>
@@ -4400,7 +4393,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" hidden="1">
+    <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
@@ -4423,7 +4416,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" hidden="1">
+    <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
         <v>140</v>
       </c>
@@ -4446,7 +4439,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" hidden="1">
+    <row r="142" spans="1:8">
       <c r="A142" s="14" t="s">
         <v>4</v>
       </c>
@@ -4473,7 +4466,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1">
+    <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -4500,7 +4493,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1">
+    <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
@@ -4523,7 +4516,7 @@
       <c r="G144" s="1"/>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" hidden="1">
+    <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -4548,7 +4541,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1">
+    <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
@@ -4573,7 +4566,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1">
+    <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
         <v>8</v>
       </c>
@@ -4598,7 +4591,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1">
+    <row r="148" spans="1:8">
       <c r="A148" s="1" t="s">
         <v>9</v>
       </c>
@@ -4623,7 +4616,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1">
+    <row r="149" spans="1:8">
       <c r="A149" s="16" t="s">
         <v>10</v>
       </c>
@@ -4648,7 +4641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1">
+    <row r="150" spans="1:8">
       <c r="A150" s="16" t="s">
         <v>138</v>
       </c>
@@ -4671,7 +4664,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" hidden="1">
+    <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
         <v>11</v>
       </c>
@@ -4696,7 +4689,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1">
+    <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
         <v>12</v>
       </c>
@@ -4721,7 +4714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1">
+    <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
         <v>13</v>
       </c>
@@ -4746,7 +4739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1">
+    <row r="154" spans="1:8">
       <c r="A154" s="1" t="s">
         <v>14</v>
       </c>
@@ -4771,7 +4764,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1">
+    <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
         <v>15</v>
       </c>
@@ -4796,7 +4789,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1">
+    <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
         <v>135</v>
       </c>
@@ -4819,7 +4812,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" hidden="1">
+    <row r="157" spans="1:8">
       <c r="A157" s="16" t="s">
         <v>16</v>
       </c>
@@ -4844,7 +4837,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1">
+    <row r="158" spans="1:8">
       <c r="A158" s="16" t="s">
         <v>17</v>
       </c>
@@ -4869,7 +4862,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1">
+    <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
         <v>18</v>
       </c>
@@ -4894,7 +4887,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1">
+    <row r="160" spans="1:8">
       <c r="A160" s="16" t="s">
         <v>19</v>
       </c>
@@ -4919,7 +4912,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1">
+    <row r="161" spans="1:8">
       <c r="A161" s="9" t="s">
         <v>20</v>
       </c>
@@ -4944,7 +4937,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1">
+    <row r="162" spans="1:8">
       <c r="A162" s="16" t="s">
         <v>21</v>
       </c>
@@ -4969,7 +4962,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1">
+    <row r="163" spans="1:8">
       <c r="A163" s="1" t="s">
         <v>23</v>
       </c>
@@ -4994,7 +4987,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1">
+    <row r="164" spans="1:8">
       <c r="A164" s="1" t="s">
         <v>24</v>
       </c>
@@ -5019,7 +5012,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1">
+    <row r="165" spans="1:8">
       <c r="A165" s="9" t="s">
         <v>25</v>
       </c>
@@ -5044,7 +5037,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1">
+    <row r="166" spans="1:8">
       <c r="A166" s="1" t="s">
         <v>26</v>
       </c>
@@ -5069,7 +5062,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1">
+    <row r="167" spans="1:8">
       <c r="A167" s="17" t="s">
         <v>27</v>
       </c>
@@ -5094,7 +5087,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1">
+    <row r="168" spans="1:8">
       <c r="A168" s="1" t="s">
         <v>28</v>
       </c>
@@ -5119,7 +5112,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1">
+    <row r="169" spans="1:8">
       <c r="A169" s="1" t="s">
         <v>132</v>
       </c>
@@ -5144,7 +5137,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1">
+    <row r="170" spans="1:8">
       <c r="A170" s="9" t="s">
         <v>29</v>
       </c>
@@ -5169,7 +5162,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1">
+    <row r="171" spans="1:8">
       <c r="A171" s="1" t="s">
         <v>30</v>
       </c>
@@ -5194,7 +5187,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1">
+    <row r="172" spans="1:8">
       <c r="A172" s="16" t="s">
         <v>31</v>
       </c>
@@ -5219,7 +5212,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1">
+    <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
         <v>32</v>
       </c>
@@ -5244,7 +5237,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1">
+    <row r="174" spans="1:8">
       <c r="A174" s="1" t="s">
         <v>33</v>
       </c>
@@ -5269,7 +5262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1">
+    <row r="175" spans="1:8">
       <c r="A175" s="16" t="s">
         <v>34</v>
       </c>
@@ -5294,7 +5287,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1">
+    <row r="176" spans="1:8">
       <c r="A176" s="9" t="s">
         <v>35</v>
       </c>
@@ -5319,7 +5312,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1">
+    <row r="177" spans="1:8">
       <c r="A177" s="1" t="s">
         <v>36</v>
       </c>
@@ -5344,7 +5337,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1">
+    <row r="178" spans="1:8">
       <c r="A178" s="1" t="s">
         <v>37</v>
       </c>
@@ -5369,7 +5362,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1">
+    <row r="179" spans="1:8">
       <c r="A179" s="1" t="s">
         <v>38</v>
       </c>
@@ -5394,7 +5387,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1">
+    <row r="180" spans="1:8">
       <c r="A180" s="1" t="s">
         <v>39</v>
       </c>
@@ -5419,7 +5412,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1">
+    <row r="181" spans="1:8">
       <c r="A181" s="16" t="s">
         <v>40</v>
       </c>
@@ -5444,7 +5437,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1">
+    <row r="182" spans="1:8">
       <c r="A182" s="16" t="s">
         <v>41</v>
       </c>
@@ -5469,7 +5462,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1">
+    <row r="183" spans="1:8">
       <c r="A183" s="1" t="s">
         <v>42</v>
       </c>
@@ -5494,7 +5487,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1">
+    <row r="184" spans="1:8">
       <c r="A184" s="1" t="s">
         <v>43</v>
       </c>
@@ -5519,7 +5512,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1">
+    <row r="185" spans="1:8">
       <c r="A185" s="17" t="s">
         <v>44</v>
       </c>
@@ -5544,7 +5537,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1">
+    <row r="186" spans="1:8">
       <c r="A186" s="9" t="s">
         <v>45</v>
       </c>
@@ -5569,7 +5562,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1">
+    <row r="187" spans="1:8">
       <c r="A187" s="9" t="s">
         <v>46</v>
       </c>
@@ -5594,7 +5587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1">
+    <row r="188" spans="1:8">
       <c r="A188" s="17" t="s">
         <v>47</v>
       </c>
@@ -5619,7 +5612,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1">
+    <row r="189" spans="1:8">
       <c r="A189" s="17" t="s">
         <v>48</v>
       </c>
@@ -5644,7 +5637,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1">
+    <row r="190" spans="1:8">
       <c r="A190" s="17" t="s">
         <v>49</v>
       </c>
@@ -5669,7 +5662,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1">
+    <row r="191" spans="1:8">
       <c r="A191" s="17" t="s">
         <v>50</v>
       </c>
@@ -5694,7 +5687,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1">
+    <row r="192" spans="1:8">
       <c r="A192" s="16" t="s">
         <v>51</v>
       </c>
@@ -5719,7 +5712,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1">
+    <row r="193" spans="1:8">
       <c r="A193" s="17" t="s">
         <v>52</v>
       </c>
@@ -5744,7 +5737,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1">
+    <row r="194" spans="1:8">
       <c r="A194" s="16" t="s">
         <v>53</v>
       </c>
@@ -5769,7 +5762,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1">
+    <row r="195" spans="1:8">
       <c r="A195" s="17" t="s">
         <v>54</v>
       </c>
@@ -5794,7 +5787,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1">
+    <row r="196" spans="1:8">
       <c r="A196" s="17" t="s">
         <v>55</v>
       </c>
@@ -5819,7 +5812,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1">
+    <row r="197" spans="1:8">
       <c r="A197" s="1" t="s">
         <v>56</v>
       </c>
@@ -5840,7 +5833,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1">
+    <row r="198" spans="1:8">
       <c r="A198" s="1" t="s">
         <v>57</v>
       </c>
@@ -5865,7 +5858,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1">
+    <row r="199" spans="1:8">
       <c r="A199" s="1" t="s">
         <v>58</v>
       </c>
@@ -5890,7 +5883,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1">
+    <row r="200" spans="1:8">
       <c r="A200" s="1" t="s">
         <v>59</v>
       </c>
@@ -5915,7 +5908,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1">
+    <row r="201" spans="1:8">
       <c r="A201" s="16" t="s">
         <v>60</v>
       </c>
@@ -5940,7 +5933,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1">
+    <row r="202" spans="1:8">
       <c r="A202" s="1" t="s">
         <v>61</v>
       </c>
@@ -5965,7 +5958,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1">
+    <row r="203" spans="1:8">
       <c r="A203" s="1" t="s">
         <v>62</v>
       </c>
@@ -5990,7 +5983,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1">
+    <row r="204" spans="1:8">
       <c r="A204" s="16" t="s">
         <v>63</v>
       </c>
@@ -6015,7 +6008,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1">
+    <row r="205" spans="1:8">
       <c r="A205" s="9" t="s">
         <v>129</v>
       </c>
@@ -6038,7 +6031,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8" hidden="1">
+    <row r="206" spans="1:8">
       <c r="A206" s="1" t="s">
         <v>128</v>
       </c>
@@ -6061,7 +6054,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8" hidden="1">
+    <row r="207" spans="1:8">
       <c r="A207" s="17" t="s">
         <v>130</v>
       </c>
@@ -6084,7 +6077,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8" hidden="1">
+    <row r="208" spans="1:8">
       <c r="A208" s="17" t="s">
         <v>131</v>
       </c>
@@ -6107,7 +6100,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8" hidden="1">
+    <row r="209" spans="1:8">
       <c r="A209" s="1" t="s">
         <v>137</v>
       </c>
@@ -6130,7 +6123,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8" hidden="1">
+    <row r="210" spans="1:8">
       <c r="A210" s="1" t="s">
         <v>136</v>
       </c>
@@ -6153,7 +6146,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" hidden="1">
+    <row r="211" spans="1:8">
       <c r="A211" s="1" t="s">
         <v>139</v>
       </c>
@@ -6176,7 +6169,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" hidden="1">
+    <row r="212" spans="1:8">
       <c r="A212" s="1" t="s">
         <v>140</v>
       </c>
@@ -6199,7 +6192,7 @@
       <c r="G212" s="1"/>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" hidden="1">
+    <row r="213" spans="1:8">
       <c r="A213" s="16" t="s">
         <v>141</v>
       </c>
@@ -6222,7 +6215,7 @@
       <c r="G213" s="1"/>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" hidden="1">
+    <row r="214" spans="1:8">
       <c r="A214" s="14" t="s">
         <v>4</v>
       </c>
@@ -6249,7 +6242,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1">
+    <row r="215" spans="1:8">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -6276,7 +6269,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1">
+    <row r="216" spans="1:8">
       <c r="A216" s="1" t="s">
         <v>134</v>
       </c>
@@ -6299,7 +6292,7 @@
       <c r="G216" s="1"/>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" hidden="1">
+    <row r="217" spans="1:8">
       <c r="A217" s="1" t="s">
         <v>6</v>
       </c>
@@ -6324,7 +6317,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1">
+    <row r="218" spans="1:8">
       <c r="A218" s="1" t="s">
         <v>7</v>
       </c>
@@ -6349,7 +6342,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1">
+    <row r="219" spans="1:8">
       <c r="A219" s="1" t="s">
         <v>8</v>
       </c>
@@ -6374,7 +6367,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1">
+    <row r="220" spans="1:8">
       <c r="A220" s="1" t="s">
         <v>9</v>
       </c>
@@ -6399,7 +6392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1">
+    <row r="221" spans="1:8">
       <c r="A221" s="16" t="s">
         <v>10</v>
       </c>
@@ -6424,7 +6417,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1">
+    <row r="222" spans="1:8">
       <c r="A222" s="16" t="s">
         <v>138</v>
       </c>
@@ -6447,7 +6440,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" hidden="1">
+    <row r="223" spans="1:8">
       <c r="A223" s="1" t="s">
         <v>11</v>
       </c>
@@ -6472,7 +6465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1">
+    <row r="224" spans="1:8">
       <c r="A224" s="1" t="s">
         <v>12</v>
       </c>
@@ -6497,7 +6490,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1">
+    <row r="225" spans="1:8">
       <c r="A225" s="1" t="s">
         <v>13</v>
       </c>
@@ -6522,7 +6515,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1">
+    <row r="226" spans="1:8">
       <c r="A226" s="1" t="s">
         <v>14</v>
       </c>
@@ -6547,7 +6540,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1">
+    <row r="227" spans="1:8">
       <c r="A227" s="1" t="s">
         <v>15</v>
       </c>
@@ -6572,7 +6565,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1">
+    <row r="228" spans="1:8">
       <c r="A228" s="1" t="s">
         <v>135</v>
       </c>
@@ -6595,7 +6588,7 @@
       <c r="G228" s="1"/>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8" hidden="1">
+    <row r="229" spans="1:8">
       <c r="A229" s="16" t="s">
         <v>16</v>
       </c>
@@ -6620,7 +6613,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1">
+    <row r="230" spans="1:8">
       <c r="A230" s="16" t="s">
         <v>17</v>
       </c>
@@ -6645,7 +6638,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1">
+    <row r="231" spans="1:8">
       <c r="A231" s="1" t="s">
         <v>18</v>
       </c>
@@ -6670,7 +6663,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1">
+    <row r="232" spans="1:8">
       <c r="A232" s="16" t="s">
         <v>19</v>
       </c>
@@ -6695,7 +6688,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1">
+    <row r="233" spans="1:8">
       <c r="A233" s="9" t="s">
         <v>20</v>
       </c>
@@ -6720,7 +6713,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1">
+    <row r="234" spans="1:8">
       <c r="A234" s="16" t="s">
         <v>21</v>
       </c>
@@ -6745,7 +6738,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1">
+    <row r="235" spans="1:8">
       <c r="A235" s="1" t="s">
         <v>23</v>
       </c>
@@ -6770,7 +6763,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1">
+    <row r="236" spans="1:8">
       <c r="A236" s="1" t="s">
         <v>24</v>
       </c>
@@ -6795,7 +6788,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1">
+    <row r="237" spans="1:8">
       <c r="A237" s="9" t="s">
         <v>25</v>
       </c>
@@ -6820,7 +6813,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1">
+    <row r="238" spans="1:8">
       <c r="A238" s="1" t="s">
         <v>26</v>
       </c>
@@ -6845,7 +6838,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1">
+    <row r="239" spans="1:8">
       <c r="A239" s="17" t="s">
         <v>27</v>
       </c>
@@ -6870,7 +6863,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1">
+    <row r="240" spans="1:8">
       <c r="A240" s="1" t="s">
         <v>28</v>
       </c>
@@ -6895,7 +6888,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1">
+    <row r="241" spans="1:8">
       <c r="A241" s="1" t="s">
         <v>132</v>
       </c>
@@ -6916,7 +6909,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1">
+    <row r="242" spans="1:8">
       <c r="A242" s="9" t="s">
         <v>29</v>
       </c>
@@ -6941,7 +6934,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1">
+    <row r="243" spans="1:8">
       <c r="A243" s="1" t="s">
         <v>30</v>
       </c>
@@ -6966,7 +6959,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1">
+    <row r="244" spans="1:8">
       <c r="A244" s="16" t="s">
         <v>31</v>
       </c>
@@ -6991,7 +6984,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1">
+    <row r="245" spans="1:8">
       <c r="A245" s="1" t="s">
         <v>32</v>
       </c>
@@ -7016,7 +7009,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1">
+    <row r="246" spans="1:8">
       <c r="A246" s="1" t="s">
         <v>33</v>
       </c>
@@ -7041,7 +7034,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1">
+    <row r="247" spans="1:8">
       <c r="A247" s="16" t="s">
         <v>34</v>
       </c>
@@ -7066,7 +7059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1">
+    <row r="248" spans="1:8">
       <c r="A248" s="9" t="s">
         <v>35</v>
       </c>
@@ -7091,7 +7084,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1">
+    <row r="249" spans="1:8">
       <c r="A249" s="1" t="s">
         <v>36</v>
       </c>
@@ -7116,7 +7109,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1">
+    <row r="250" spans="1:8">
       <c r="A250" s="1" t="s">
         <v>37</v>
       </c>
@@ -7141,7 +7134,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1">
+    <row r="251" spans="1:8">
       <c r="A251" s="1" t="s">
         <v>38</v>
       </c>
@@ -7166,7 +7159,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1">
+    <row r="252" spans="1:8">
       <c r="A252" s="1" t="s">
         <v>39</v>
       </c>
@@ -7191,7 +7184,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1">
+    <row r="253" spans="1:8">
       <c r="A253" s="16" t="s">
         <v>40</v>
       </c>
@@ -7216,7 +7209,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1">
+    <row r="254" spans="1:8">
       <c r="A254" s="16" t="s">
         <v>41</v>
       </c>
@@ -7241,7 +7234,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1">
+    <row r="255" spans="1:8">
       <c r="A255" s="1" t="s">
         <v>42</v>
       </c>
@@ -7266,7 +7259,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1">
+    <row r="256" spans="1:8">
       <c r="A256" s="1" t="s">
         <v>43</v>
       </c>
@@ -7291,7 +7284,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1">
+    <row r="257" spans="1:8">
       <c r="A257" s="17" t="s">
         <v>44</v>
       </c>
@@ -7316,7 +7309,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1">
+    <row r="258" spans="1:8">
       <c r="A258" s="9" t="s">
         <v>45</v>
       </c>
@@ -7341,7 +7334,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1">
+    <row r="259" spans="1:8">
       <c r="A259" s="9" t="s">
         <v>46</v>
       </c>
@@ -7366,7 +7359,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1">
+    <row r="260" spans="1:8">
       <c r="A260" s="17" t="s">
         <v>47</v>
       </c>
@@ -7391,7 +7384,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1">
+    <row r="261" spans="1:8">
       <c r="A261" s="17" t="s">
         <v>48</v>
       </c>
@@ -7416,7 +7409,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1">
+    <row r="262" spans="1:8">
       <c r="A262" s="17" t="s">
         <v>49</v>
       </c>
@@ -7441,7 +7434,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1">
+    <row r="263" spans="1:8">
       <c r="A263" s="17" t="s">
         <v>50</v>
       </c>
@@ -7466,7 +7459,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1">
+    <row r="264" spans="1:8">
       <c r="A264" s="16" t="s">
         <v>51</v>
       </c>
@@ -7491,7 +7484,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1">
+    <row r="265" spans="1:8">
       <c r="A265" s="17" t="s">
         <v>52</v>
       </c>
@@ -7516,7 +7509,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1">
+    <row r="266" spans="1:8">
       <c r="A266" s="16" t="s">
         <v>53</v>
       </c>
@@ -7541,7 +7534,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1">
+    <row r="267" spans="1:8">
       <c r="A267" s="17" t="s">
         <v>54</v>
       </c>
@@ -7566,7 +7559,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1">
+    <row r="268" spans="1:8">
       <c r="A268" s="17" t="s">
         <v>55</v>
       </c>
@@ -7591,7 +7584,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1">
+    <row r="269" spans="1:8">
       <c r="A269" s="1" t="s">
         <v>56</v>
       </c>
@@ -7616,7 +7609,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1">
+    <row r="270" spans="1:8">
       <c r="A270" s="1" t="s">
         <v>57</v>
       </c>
@@ -7641,7 +7634,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1">
+    <row r="271" spans="1:8">
       <c r="A271" s="1" t="s">
         <v>58</v>
       </c>
@@ -7666,7 +7659,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1">
+    <row r="272" spans="1:8">
       <c r="A272" s="1" t="s">
         <v>59</v>
       </c>
@@ -7691,7 +7684,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1">
+    <row r="273" spans="1:8">
       <c r="A273" s="16" t="s">
         <v>60</v>
       </c>
@@ -7716,7 +7709,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1">
+    <row r="274" spans="1:8">
       <c r="A274" s="1" t="s">
         <v>61</v>
       </c>
@@ -7741,7 +7734,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1">
+    <row r="275" spans="1:8">
       <c r="A275" s="1" t="s">
         <v>62</v>
       </c>
@@ -7766,7 +7759,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1">
+    <row r="276" spans="1:8">
       <c r="A276" s="16" t="s">
         <v>63</v>
       </c>
@@ -7791,7 +7784,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1">
+    <row r="277" spans="1:8">
       <c r="A277" s="9" t="s">
         <v>129</v>
       </c>
@@ -7814,7 +7807,7 @@
       <c r="G277" s="1"/>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8" hidden="1">
+    <row r="278" spans="1:8">
       <c r="A278" s="1" t="s">
         <v>128</v>
       </c>
@@ -7837,7 +7830,7 @@
       <c r="G278" s="1"/>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8" hidden="1">
+    <row r="279" spans="1:8">
       <c r="A279" s="17" t="s">
         <v>130</v>
       </c>
@@ -7860,7 +7853,7 @@
       <c r="G279" s="1"/>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8" hidden="1">
+    <row r="280" spans="1:8">
       <c r="A280" s="17" t="s">
         <v>131</v>
       </c>
@@ -7883,7 +7876,7 @@
       <c r="G280" s="1"/>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8" hidden="1">
+    <row r="281" spans="1:8">
       <c r="A281" s="1" t="s">
         <v>137</v>
       </c>
@@ -7906,7 +7899,7 @@
       <c r="G281" s="1"/>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8" hidden="1">
+    <row r="282" spans="1:8">
       <c r="A282" s="1" t="s">
         <v>136</v>
       </c>
@@ -7929,7 +7922,7 @@
       <c r="G282" s="1"/>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8" hidden="1">
+    <row r="283" spans="1:8">
       <c r="A283" s="1" t="s">
         <v>139</v>
       </c>
@@ -7952,7 +7945,7 @@
       <c r="G283" s="1"/>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8" hidden="1">
+    <row r="284" spans="1:8">
       <c r="A284" s="1" t="s">
         <v>140</v>
       </c>
@@ -7975,7 +7968,7 @@
       <c r="G284" s="1"/>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8" hidden="1">
+    <row r="285" spans="1:8">
       <c r="A285" s="16" t="s">
         <v>141</v>
       </c>
@@ -7998,7 +7991,7 @@
       <c r="G285" s="1"/>
       <c r="H285" s="7"/>
     </row>
-    <row r="286" spans="1:8" hidden="1">
+    <row r="286" spans="1:8">
       <c r="A286" s="14" t="s">
         <v>4</v>
       </c>
@@ -8025,7 +8018,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1">
+    <row r="287" spans="1:8">
       <c r="A287" s="1" t="s">
         <v>5</v>
       </c>
@@ -8052,7 +8045,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1">
+    <row r="288" spans="1:8">
       <c r="A288" s="1" t="s">
         <v>134</v>
       </c>
@@ -8075,7 +8068,7 @@
       <c r="G288" s="1"/>
       <c r="H288" s="7"/>
     </row>
-    <row r="289" spans="1:8" hidden="1">
+    <row r="289" spans="1:8">
       <c r="A289" s="1" t="s">
         <v>6</v>
       </c>
@@ -8100,7 +8093,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1">
+    <row r="290" spans="1:8">
       <c r="A290" s="1" t="s">
         <v>7</v>
       </c>
@@ -8125,7 +8118,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1">
+    <row r="291" spans="1:8">
       <c r="A291" s="1" t="s">
         <v>8</v>
       </c>
@@ -8150,7 +8143,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1">
+    <row r="292" spans="1:8">
       <c r="A292" s="1" t="s">
         <v>9</v>
       </c>
@@ -8223,7 +8216,7 @@
       <c r="G294" s="1"/>
       <c r="H294" s="7"/>
     </row>
-    <row r="295" spans="1:8" hidden="1">
+    <row r="295" spans="1:8">
       <c r="A295" s="1" t="s">
         <v>11</v>
       </c>
@@ -8248,7 +8241,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1">
+    <row r="296" spans="1:8">
       <c r="A296" s="1" t="s">
         <v>12</v>
       </c>
@@ -8273,7 +8266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1">
+    <row r="297" spans="1:8">
       <c r="A297" s="1" t="s">
         <v>13</v>
       </c>
@@ -8298,7 +8291,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1">
+    <row r="298" spans="1:8">
       <c r="A298" s="1" t="s">
         <v>14</v>
       </c>
@@ -8323,7 +8316,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1">
+    <row r="299" spans="1:8">
       <c r="A299" s="1" t="s">
         <v>15</v>
       </c>
@@ -8348,7 +8341,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1">
+    <row r="300" spans="1:8">
       <c r="A300" s="1" t="s">
         <v>135</v>
       </c>
@@ -8421,7 +8414,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1">
+    <row r="303" spans="1:8">
       <c r="A303" s="1" t="s">
         <v>18</v>
       </c>
@@ -8471,7 +8464,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1">
+    <row r="305" spans="1:8">
       <c r="A305" s="9" t="s">
         <v>20</v>
       </c>
@@ -8521,7 +8514,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1">
+    <row r="307" spans="1:8">
       <c r="A307" s="1" t="s">
         <v>23</v>
       </c>
@@ -8546,7 +8539,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1">
+    <row r="308" spans="1:8">
       <c r="A308" s="1" t="s">
         <v>24</v>
       </c>
@@ -8571,7 +8564,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1">
+    <row r="309" spans="1:8">
       <c r="A309" s="9" t="s">
         <v>25</v>
       </c>
@@ -8596,7 +8589,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1">
+    <row r="310" spans="1:8">
       <c r="A310" s="1" t="s">
         <v>26</v>
       </c>
@@ -8621,7 +8614,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1">
+    <row r="311" spans="1:8">
       <c r="A311" s="17" t="s">
         <v>27</v>
       </c>
@@ -8646,7 +8639,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1">
+    <row r="312" spans="1:8">
       <c r="A312" s="1" t="s">
         <v>28</v>
       </c>
@@ -8671,7 +8664,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1">
+    <row r="313" spans="1:8">
       <c r="A313" s="9" t="s">
         <v>29</v>
       </c>
@@ -8696,7 +8689,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1">
+    <row r="314" spans="1:8">
       <c r="A314" s="1" t="s">
         <v>30</v>
       </c>
@@ -8746,7 +8739,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1">
+    <row r="316" spans="1:8">
       <c r="A316" s="1" t="s">
         <v>32</v>
       </c>
@@ -8771,7 +8764,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1">
+    <row r="317" spans="1:8">
       <c r="A317" s="1" t="s">
         <v>33</v>
       </c>
@@ -8821,7 +8814,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1">
+    <row r="319" spans="1:8">
       <c r="A319" s="9" t="s">
         <v>35</v>
       </c>
@@ -8846,7 +8839,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1">
+    <row r="320" spans="1:8">
       <c r="A320" s="1" t="s">
         <v>36</v>
       </c>
@@ -8871,7 +8864,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1">
+    <row r="321" spans="1:8">
       <c r="A321" s="1" t="s">
         <v>37</v>
       </c>
@@ -8896,7 +8889,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1">
+    <row r="322" spans="1:8">
       <c r="A322" s="1" t="s">
         <v>38</v>
       </c>
@@ -8921,7 +8914,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1">
+    <row r="323" spans="1:8">
       <c r="A323" s="1" t="s">
         <v>39</v>
       </c>
@@ -8996,7 +8989,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1">
+    <row r="326" spans="1:8">
       <c r="A326" s="1" t="s">
         <v>42</v>
       </c>
@@ -9021,7 +9014,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1">
+    <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
         <v>43</v>
       </c>
@@ -9046,7 +9039,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1">
+    <row r="328" spans="1:8">
       <c r="A328" s="17" t="s">
         <v>44</v>
       </c>
@@ -9071,7 +9064,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1">
+    <row r="329" spans="1:8">
       <c r="A329" s="9" t="s">
         <v>45</v>
       </c>
@@ -9096,7 +9089,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1">
+    <row r="330" spans="1:8">
       <c r="A330" s="9" t="s">
         <v>46</v>
       </c>
@@ -9121,7 +9114,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1">
+    <row r="331" spans="1:8">
       <c r="A331" s="17" t="s">
         <v>47</v>
       </c>
@@ -9138,7 +9131,7 @@
         <v>20</v>
       </c>
       <c r="F331" s="3">
-        <f t="shared" ref="F331:F357" si="7">D331-(D331*E331)/100</f>
+        <f t="shared" ref="F331:F394" si="7">D331-(D331*E331)/100</f>
         <v>22.23367119733928</v>
       </c>
       <c r="G331" s="1"/>
@@ -9146,7 +9139,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1">
+    <row r="332" spans="1:8">
       <c r="A332" s="17" t="s">
         <v>48</v>
       </c>
@@ -9171,7 +9164,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1">
+    <row r="333" spans="1:8">
       <c r="A333" s="17" t="s">
         <v>49</v>
       </c>
@@ -9196,7 +9189,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1">
+    <row r="334" spans="1:8">
       <c r="A334" s="17" t="s">
         <v>50</v>
       </c>
@@ -9246,7 +9239,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1">
+    <row r="336" spans="1:8">
       <c r="A336" s="17" t="s">
         <v>52</v>
       </c>
@@ -9296,7 +9289,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="1">
+    <row r="338" spans="1:8">
       <c r="A338" s="17" t="s">
         <v>54</v>
       </c>
@@ -9321,7 +9314,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="1">
+    <row r="339" spans="1:8">
       <c r="A339" s="17" t="s">
         <v>55</v>
       </c>
@@ -9346,7 +9339,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="1">
+    <row r="340" spans="1:8">
       <c r="A340" s="1" t="s">
         <v>56</v>
       </c>
@@ -9371,7 +9364,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1">
+    <row r="341" spans="1:8">
       <c r="A341" s="1" t="s">
         <v>57</v>
       </c>
@@ -9396,7 +9389,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1">
+    <row r="342" spans="1:8">
       <c r="A342" s="1" t="s">
         <v>58</v>
       </c>
@@ -9421,7 +9414,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="1">
+    <row r="343" spans="1:8">
       <c r="A343" s="1" t="s">
         <v>59</v>
       </c>
@@ -9471,7 +9464,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="1">
+    <row r="345" spans="1:8">
       <c r="A345" s="1" t="s">
         <v>62</v>
       </c>
@@ -9521,7 +9514,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="1">
+    <row r="347" spans="1:8">
       <c r="A347" s="9" t="s">
         <v>129</v>
       </c>
@@ -9544,7 +9537,7 @@
       <c r="G347" s="1"/>
       <c r="H347" s="7"/>
     </row>
-    <row r="348" spans="1:8" hidden="1">
+    <row r="348" spans="1:8">
       <c r="A348" s="1" t="s">
         <v>128</v>
       </c>
@@ -9567,7 +9560,7 @@
       <c r="G348" s="1"/>
       <c r="H348" s="7"/>
     </row>
-    <row r="349" spans="1:8" hidden="1">
+    <row r="349" spans="1:8">
       <c r="A349" s="17" t="s">
         <v>130</v>
       </c>
@@ -9590,7 +9583,7 @@
       <c r="G349" s="1"/>
       <c r="H349" s="7"/>
     </row>
-    <row r="350" spans="1:8" hidden="1">
+    <row r="350" spans="1:8">
       <c r="A350" s="17" t="s">
         <v>131</v>
       </c>
@@ -9613,7 +9606,7 @@
       <c r="G350" s="1"/>
       <c r="H350" s="7"/>
     </row>
-    <row r="351" spans="1:8" hidden="1">
+    <row r="351" spans="1:8">
       <c r="A351" s="1" t="s">
         <v>137</v>
       </c>
@@ -9636,7 +9629,7 @@
       <c r="G351" s="1"/>
       <c r="H351" s="7"/>
     </row>
-    <row r="352" spans="1:8" hidden="1">
+    <row r="352" spans="1:8">
       <c r="A352" s="1" t="s">
         <v>136</v>
       </c>
@@ -9659,7 +9652,7 @@
       <c r="G352" s="1"/>
       <c r="H352" s="7"/>
     </row>
-    <row r="353" spans="1:8" hidden="1">
+    <row r="353" spans="1:8">
       <c r="A353" s="1" t="s">
         <v>139</v>
       </c>
@@ -9682,7 +9675,7 @@
       <c r="G353" s="1"/>
       <c r="H353" s="7"/>
     </row>
-    <row r="354" spans="1:8" hidden="1">
+    <row r="354" spans="1:8">
       <c r="A354" s="1" t="s">
         <v>140</v>
       </c>
@@ -9728,7 +9721,7 @@
       <c r="G355" s="24"/>
       <c r="H355" s="25"/>
     </row>
-    <row r="356" spans="1:8" hidden="1">
+    <row r="356" spans="1:8">
       <c r="A356" s="1" t="s">
         <v>143</v>
       </c>
@@ -9751,7 +9744,7 @@
       <c r="G356" s="1"/>
       <c r="H356" s="1"/>
     </row>
-    <row r="357" spans="1:8" hidden="1">
+    <row r="357" spans="1:8">
       <c r="A357" s="1" t="s">
         <v>142</v>
       </c>
@@ -9774,16 +9767,1793 @@
       <c r="G357" s="1"/>
       <c r="H357" s="1"/>
     </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B358" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C358" s="8">
+        <v>127.5</v>
+      </c>
+      <c r="D358" s="11">
+        <v>39.037488631016899</v>
+      </c>
+      <c r="E358" s="12">
+        <v>20</v>
+      </c>
+      <c r="F358" s="13">
+        <f t="shared" si="7"/>
+        <v>31.229990904813519</v>
+      </c>
+      <c r="G358" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H358" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B359" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C359" s="8">
+        <v>32</v>
+      </c>
+      <c r="D359" s="4">
+        <v>41.328781249999999</v>
+      </c>
+      <c r="E359" s="6">
+        <v>20</v>
+      </c>
+      <c r="F359" s="3">
+        <f t="shared" si="7"/>
+        <v>33.063024999999996</v>
+      </c>
+      <c r="G359" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B360" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C360" s="8"/>
+      <c r="D360" s="4"/>
+      <c r="E360" s="6">
+        <v>20</v>
+      </c>
+      <c r="F360" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G360" s="1"/>
+      <c r="H360" s="7"/>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B361" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C361" s="8">
+        <v>160</v>
+      </c>
+      <c r="D361" s="4">
+        <v>24.623067252345201</v>
+      </c>
+      <c r="E361" s="6">
+        <v>20</v>
+      </c>
+      <c r="F361" s="3">
+        <f t="shared" si="7"/>
+        <v>19.698453801876163</v>
+      </c>
+      <c r="G361" s="1"/>
+      <c r="H361" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B362" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C362" s="8">
+        <v>96</v>
+      </c>
+      <c r="D362" s="4">
+        <v>45.381328947368402</v>
+      </c>
+      <c r="E362" s="6">
+        <v>20</v>
+      </c>
+      <c r="F362" s="3">
+        <f t="shared" si="7"/>
+        <v>36.305063157894722</v>
+      </c>
+      <c r="G362" s="1"/>
+      <c r="H362" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B363" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C363" s="8">
+        <v>160</v>
+      </c>
+      <c r="D363" s="4">
+        <v>19.9667666666667</v>
+      </c>
+      <c r="E363" s="6">
+        <v>20</v>
+      </c>
+      <c r="F363" s="3">
+        <f t="shared" si="7"/>
+        <v>15.97341333333336</v>
+      </c>
+      <c r="G363" s="1"/>
+      <c r="H363" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B364" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C364" s="8">
+        <v>136</v>
+      </c>
+      <c r="D364" s="4">
+        <v>28.510125265971599</v>
+      </c>
+      <c r="E364" s="6">
+        <v>20</v>
+      </c>
+      <c r="F364" s="3">
+        <f t="shared" si="7"/>
+        <v>22.80810021277728</v>
+      </c>
+      <c r="G364" s="1"/>
+      <c r="H364" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B365" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C365" s="8">
+        <v>152</v>
+      </c>
+      <c r="D365" s="4">
+        <v>38.278795454545502</v>
+      </c>
+      <c r="E365" s="6">
+        <v>20</v>
+      </c>
+      <c r="F365" s="3">
+        <f t="shared" si="7"/>
+        <v>30.623036363636402</v>
+      </c>
+      <c r="G365" s="1"/>
+      <c r="H365" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B366" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C366" s="8">
+        <v>93</v>
+      </c>
+      <c r="D366" s="4">
+        <v>31.535950354609898</v>
+      </c>
+      <c r="E366" s="6">
+        <v>20</v>
+      </c>
+      <c r="F366" s="3">
+        <f t="shared" si="7"/>
+        <v>25.228760283687919</v>
+      </c>
+      <c r="G366" s="1"/>
+      <c r="H366" s="7"/>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B367" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C367" s="8">
+        <v>160</v>
+      </c>
+      <c r="D367" s="4">
+        <v>29.782658901267201</v>
+      </c>
+      <c r="E367" s="6">
+        <v>20</v>
+      </c>
+      <c r="F367" s="3">
+        <f t="shared" si="7"/>
+        <v>23.826127121013762</v>
+      </c>
+      <c r="G367" s="1"/>
+      <c r="H367" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B368" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C368" s="8">
+        <v>128</v>
+      </c>
+      <c r="D368" s="4">
+        <v>49.2331863184748</v>
+      </c>
+      <c r="E368" s="6">
+        <v>20</v>
+      </c>
+      <c r="F368" s="3">
+        <f t="shared" si="7"/>
+        <v>39.386549054779842</v>
+      </c>
+      <c r="G368" s="1"/>
+      <c r="H368" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B369" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C369" s="8">
+        <v>128</v>
+      </c>
+      <c r="D369" s="4">
+        <v>49.2331863184748</v>
+      </c>
+      <c r="E369" s="6">
+        <v>20</v>
+      </c>
+      <c r="F369" s="3">
+        <f t="shared" si="7"/>
+        <v>39.386549054779842</v>
+      </c>
+      <c r="G369" s="1"/>
+      <c r="H369" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B370" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C370" s="8">
+        <v>109</v>
+      </c>
+      <c r="D370" s="4">
+        <v>38.966663073138001</v>
+      </c>
+      <c r="E370" s="6">
+        <v>20</v>
+      </c>
+      <c r="F370" s="3">
+        <f t="shared" si="7"/>
+        <v>31.173330458510399</v>
+      </c>
+      <c r="G370" s="1"/>
+      <c r="H370" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B371" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C371" s="8">
+        <v>136</v>
+      </c>
+      <c r="D371" s="4">
+        <v>19.9667666666667</v>
+      </c>
+      <c r="E371" s="6">
+        <v>20</v>
+      </c>
+      <c r="F371" s="3">
+        <f t="shared" si="7"/>
+        <v>15.97341333333336</v>
+      </c>
+      <c r="G371" s="1"/>
+      <c r="H371" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B372" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C372" s="8">
+        <v>128</v>
+      </c>
+      <c r="D372" s="4">
+        <v>45.381328947368402</v>
+      </c>
+      <c r="E372" s="6">
+        <v>20</v>
+      </c>
+      <c r="F372" s="3">
+        <f t="shared" si="7"/>
+        <v>36.305063157894722</v>
+      </c>
+      <c r="G372" s="1"/>
+      <c r="H372" s="7"/>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B373" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C373" s="8">
+        <v>152</v>
+      </c>
+      <c r="D373" s="4">
+        <v>38.420708333333302</v>
+      </c>
+      <c r="E373" s="6">
+        <v>20</v>
+      </c>
+      <c r="F373" s="3">
+        <f t="shared" si="7"/>
+        <v>30.73656666666664</v>
+      </c>
+      <c r="G373" s="1"/>
+      <c r="H373" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B374" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C374" s="8">
+        <v>160</v>
+      </c>
+      <c r="D374" s="4">
+        <v>38.0179628378378</v>
+      </c>
+      <c r="E374" s="6">
+        <v>20</v>
+      </c>
+      <c r="F374" s="3">
+        <f t="shared" si="7"/>
+        <v>30.41437027027024</v>
+      </c>
+      <c r="G374" s="1"/>
+      <c r="H374" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B375" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C375" s="8">
+        <v>123.5</v>
+      </c>
+      <c r="D375" s="4">
+        <v>39.099093036437203</v>
+      </c>
+      <c r="E375" s="6">
+        <v>20</v>
+      </c>
+      <c r="F375" s="3">
+        <f t="shared" si="7"/>
+        <v>31.279274429149762</v>
+      </c>
+      <c r="G375" s="1"/>
+      <c r="H375" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B376" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C376" s="8">
+        <v>168</v>
+      </c>
+      <c r="D376" s="4">
+        <v>38.531518601076797</v>
+      </c>
+      <c r="E376" s="6">
+        <v>20</v>
+      </c>
+      <c r="F376" s="3">
+        <f t="shared" si="7"/>
+        <v>30.825214880861438</v>
+      </c>
+      <c r="G376" s="1"/>
+      <c r="H376" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B377" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C377" s="8">
+        <v>160</v>
+      </c>
+      <c r="D377" s="4">
+        <v>56.065311739751401</v>
+      </c>
+      <c r="E377" s="6">
+        <v>20</v>
+      </c>
+      <c r="F377" s="3">
+        <f t="shared" si="7"/>
+        <v>44.852249391801124</v>
+      </c>
+      <c r="G377" s="1"/>
+      <c r="H377" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B378" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C378" s="8">
+        <v>152</v>
+      </c>
+      <c r="D378" s="4">
+        <v>45.807323229949901</v>
+      </c>
+      <c r="E378" s="6">
+        <v>20</v>
+      </c>
+      <c r="F378" s="3">
+        <f t="shared" si="7"/>
+        <v>36.645858583959921</v>
+      </c>
+      <c r="G378" s="1"/>
+      <c r="H378" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B379" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C379" s="8">
+        <v>155</v>
+      </c>
+      <c r="D379" s="4">
+        <v>40.822944327435799</v>
+      </c>
+      <c r="E379" s="6">
+        <v>20</v>
+      </c>
+      <c r="F379" s="3">
+        <f t="shared" si="7"/>
+        <v>32.658355461948638</v>
+      </c>
+      <c r="G379" s="1"/>
+      <c r="H379" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B380" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C380" s="8">
+        <v>160</v>
+      </c>
+      <c r="D380" s="4">
+        <v>29.409706931196101</v>
+      </c>
+      <c r="E380" s="6">
+        <v>20</v>
+      </c>
+      <c r="F380" s="3">
+        <f t="shared" si="7"/>
+        <v>23.527765544956882</v>
+      </c>
+      <c r="G380" s="1"/>
+      <c r="H380" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B381" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C381" s="8">
+        <v>143</v>
+      </c>
+      <c r="D381" s="4">
+        <v>55.9955220392497</v>
+      </c>
+      <c r="E381" s="6">
+        <v>20</v>
+      </c>
+      <c r="F381" s="3">
+        <f t="shared" si="7"/>
+        <v>44.796417631399763</v>
+      </c>
+      <c r="G381" s="1"/>
+      <c r="H381" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B382" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C382" s="8">
+        <v>21</v>
+      </c>
+      <c r="D382" s="4">
+        <v>184.30079494655001</v>
+      </c>
+      <c r="E382" s="6">
+        <v>20</v>
+      </c>
+      <c r="F382" s="3">
+        <f t="shared" si="7"/>
+        <v>147.44063595724</v>
+      </c>
+      <c r="G382" s="1"/>
+      <c r="H382" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B383" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C383" s="8">
+        <v>40</v>
+      </c>
+      <c r="D383" s="4">
+        <v>150.7933625</v>
+      </c>
+      <c r="E383" s="6">
+        <v>20</v>
+      </c>
+      <c r="F383" s="3">
+        <f t="shared" si="7"/>
+        <v>120.63469000000001</v>
+      </c>
+      <c r="G383" s="1"/>
+      <c r="H383" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B384" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C384" s="8">
+        <v>160</v>
+      </c>
+      <c r="D384" s="4">
+        <v>24.623067252345201</v>
+      </c>
+      <c r="E384" s="6">
+        <v>20</v>
+      </c>
+      <c r="F384" s="3">
+        <f t="shared" si="7"/>
+        <v>19.698453801876163</v>
+      </c>
+      <c r="G384" s="1"/>
+      <c r="H384" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B385" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C385" s="8">
+        <v>149</v>
+      </c>
+      <c r="D385" s="4">
+        <v>56.478408165389901</v>
+      </c>
+      <c r="E385" s="6">
+        <v>20</v>
+      </c>
+      <c r="F385" s="3">
+        <f t="shared" si="7"/>
+        <v>45.182726532311918</v>
+      </c>
+      <c r="G385" s="1"/>
+      <c r="H385" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B386" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C386" s="8">
+        <v>42</v>
+      </c>
+      <c r="D386" s="4">
+        <v>48.850502623906699</v>
+      </c>
+      <c r="E386" s="6">
+        <v>20</v>
+      </c>
+      <c r="F386" s="3">
+        <f t="shared" si="7"/>
+        <v>39.080402099125358</v>
+      </c>
+      <c r="G386" s="1"/>
+      <c r="H386" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B387" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C387" s="8">
+        <v>160</v>
+      </c>
+      <c r="D387" s="4">
+        <v>38.550371323529397</v>
+      </c>
+      <c r="E387" s="6">
+        <v>20</v>
+      </c>
+      <c r="F387" s="3">
+        <f t="shared" si="7"/>
+        <v>30.840297058823516</v>
+      </c>
+      <c r="G387" s="1"/>
+      <c r="H387" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B388" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C388" s="8">
+        <v>160</v>
+      </c>
+      <c r="D388" s="4">
+        <v>39.9884284416041</v>
+      </c>
+      <c r="E388" s="6">
+        <v>20</v>
+      </c>
+      <c r="F388" s="3">
+        <f t="shared" si="7"/>
+        <v>31.990742753283278</v>
+      </c>
+      <c r="G388" s="1"/>
+      <c r="H388" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B389" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C389" s="8">
+        <v>56</v>
+      </c>
+      <c r="D389" s="4">
+        <v>55.469909420289902</v>
+      </c>
+      <c r="E389" s="6">
+        <v>20</v>
+      </c>
+      <c r="F389" s="3">
+        <f t="shared" si="7"/>
+        <v>44.37592753623192</v>
+      </c>
+      <c r="G389" s="1"/>
+      <c r="H389" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B390" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C390" s="8">
+        <v>192</v>
+      </c>
+      <c r="D390" s="4">
+        <v>33.324485795454599</v>
+      </c>
+      <c r="E390" s="6">
+        <v>20</v>
+      </c>
+      <c r="F390" s="3">
+        <f t="shared" si="7"/>
+        <v>26.659588636363679</v>
+      </c>
+      <c r="G390" s="1"/>
+      <c r="H390" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B391" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C391" s="8">
+        <v>142</v>
+      </c>
+      <c r="D391" s="4">
+        <v>73.443744980077994</v>
+      </c>
+      <c r="E391" s="6">
+        <v>20</v>
+      </c>
+      <c r="F391" s="3">
+        <f t="shared" si="7"/>
+        <v>58.754995984062397</v>
+      </c>
+      <c r="G391" s="1"/>
+      <c r="H391" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B392" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C392" s="8">
+        <v>42</v>
+      </c>
+      <c r="D392" s="4">
+        <v>45.808328834447202</v>
+      </c>
+      <c r="E392" s="6">
+        <v>20</v>
+      </c>
+      <c r="F392" s="3">
+        <f t="shared" si="7"/>
+        <v>36.64666306755776</v>
+      </c>
+      <c r="G392" s="1"/>
+      <c r="H392" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B393" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C393" s="8">
+        <v>40</v>
+      </c>
+      <c r="D393" s="4">
+        <v>120.753558265306</v>
+      </c>
+      <c r="E393" s="6">
+        <v>20</v>
+      </c>
+      <c r="F393" s="3">
+        <f t="shared" si="7"/>
+        <v>96.602846612244804</v>
+      </c>
+      <c r="G393" s="1"/>
+      <c r="H393" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B394" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C394" s="8">
+        <v>160</v>
+      </c>
+      <c r="D394" s="4">
+        <v>24.623067252345201</v>
+      </c>
+      <c r="E394" s="6">
+        <v>20</v>
+      </c>
+      <c r="F394" s="3">
+        <f t="shared" si="7"/>
+        <v>19.698453801876163</v>
+      </c>
+      <c r="G394" s="1"/>
+      <c r="H394" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B395" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C395" s="8">
+        <v>158</v>
+      </c>
+      <c r="D395" s="4">
+        <v>36.169485334497601</v>
+      </c>
+      <c r="E395" s="6">
+        <v>20</v>
+      </c>
+      <c r="F395" s="3">
+        <f t="shared" ref="F395:F430" si="8">D395-(D395*E395)/100</f>
+        <v>28.935588267598082</v>
+      </c>
+      <c r="G395" s="1"/>
+      <c r="H395" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B396" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C396" s="8">
+        <v>149</v>
+      </c>
+      <c r="D396" s="4">
+        <v>30.586636513592801</v>
+      </c>
+      <c r="E396" s="6">
+        <v>20</v>
+      </c>
+      <c r="F396" s="3">
+        <f t="shared" si="8"/>
+        <v>24.46930921087424</v>
+      </c>
+      <c r="G396" s="1"/>
+      <c r="H396" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B397" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C397" s="8">
+        <v>184</v>
+      </c>
+      <c r="D397" s="4">
+        <v>41.908045731707297</v>
+      </c>
+      <c r="E397" s="6">
+        <v>20</v>
+      </c>
+      <c r="F397" s="3">
+        <f t="shared" si="8"/>
+        <v>33.526436585365836</v>
+      </c>
+      <c r="G397" s="1"/>
+      <c r="H397" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B398" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C398" s="8">
+        <v>32</v>
+      </c>
+      <c r="D398" s="4">
+        <v>41.328781249999999</v>
+      </c>
+      <c r="E398" s="6">
+        <v>20</v>
+      </c>
+      <c r="F398" s="3">
+        <f t="shared" si="8"/>
+        <v>33.063024999999996</v>
+      </c>
+      <c r="G398" s="1"/>
+      <c r="H398" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B399" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C399" s="8">
+        <v>123.5</v>
+      </c>
+      <c r="D399" s="4">
+        <v>44.123338752035998</v>
+      </c>
+      <c r="E399" s="6">
+        <v>20</v>
+      </c>
+      <c r="F399" s="3">
+        <f t="shared" si="8"/>
+        <v>35.298671001628797</v>
+      </c>
+      <c r="G399" s="1"/>
+      <c r="H399" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B400" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C400" s="8">
+        <v>32</v>
+      </c>
+      <c r="D400" s="4">
+        <v>193.917265625</v>
+      </c>
+      <c r="E400" s="6">
+        <v>20</v>
+      </c>
+      <c r="F400" s="3">
+        <f t="shared" si="8"/>
+        <v>155.1338125</v>
+      </c>
+      <c r="G400" s="1"/>
+      <c r="H400" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B401" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C401" s="8">
+        <v>120</v>
+      </c>
+      <c r="D401" s="4">
+        <v>65.133742187500005</v>
+      </c>
+      <c r="E401" s="6">
+        <v>20</v>
+      </c>
+      <c r="F401" s="3">
+        <f t="shared" si="8"/>
+        <v>52.106993750000001</v>
+      </c>
+      <c r="G401" s="1"/>
+      <c r="H401" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B402" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C402" s="8">
+        <v>152</v>
+      </c>
+      <c r="D402" s="4">
+        <v>69.744289430102498</v>
+      </c>
+      <c r="E402" s="6">
+        <v>20</v>
+      </c>
+      <c r="F402" s="3">
+        <f t="shared" si="8"/>
+        <v>55.795431544082</v>
+      </c>
+      <c r="G402" s="1"/>
+      <c r="H402" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B403" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C403" s="8">
+        <v>8</v>
+      </c>
+      <c r="D403" s="4">
+        <v>568.30643750000002</v>
+      </c>
+      <c r="E403" s="6">
+        <v>20</v>
+      </c>
+      <c r="F403" s="3">
+        <f t="shared" si="8"/>
+        <v>454.64515</v>
+      </c>
+      <c r="G403" s="1"/>
+      <c r="H403" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B404" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C404" s="8">
+        <v>32</v>
+      </c>
+      <c r="D404" s="4">
+        <v>125.63765625000001</v>
+      </c>
+      <c r="E404" s="6">
+        <v>20</v>
+      </c>
+      <c r="F404" s="3">
+        <f t="shared" si="8"/>
+        <v>100.510125</v>
+      </c>
+      <c r="G404" s="1"/>
+      <c r="H404" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B405" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C405" s="8">
+        <v>40</v>
+      </c>
+      <c r="D405" s="4">
+        <v>190.33821875000001</v>
+      </c>
+      <c r="E405" s="6">
+        <v>20</v>
+      </c>
+      <c r="F405" s="3">
+        <f t="shared" si="8"/>
+        <v>152.27057500000001</v>
+      </c>
+      <c r="G405" s="1"/>
+      <c r="H405" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B406" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C406" s="8">
+        <v>32</v>
+      </c>
+      <c r="D406" s="4">
+        <v>117.456953125</v>
+      </c>
+      <c r="E406" s="6">
+        <v>20</v>
+      </c>
+      <c r="F406" s="3">
+        <f t="shared" si="8"/>
+        <v>93.965562500000004</v>
+      </c>
+      <c r="G406" s="1"/>
+      <c r="H406" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B407" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C407" s="8">
+        <v>160</v>
+      </c>
+      <c r="D407" s="4">
+        <v>37.816337955678897</v>
+      </c>
+      <c r="E407" s="6">
+        <v>20</v>
+      </c>
+      <c r="F407" s="3">
+        <f t="shared" si="8"/>
+        <v>30.253070364543117</v>
+      </c>
+      <c r="G407" s="1"/>
+      <c r="H407" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B408" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C408" s="8">
+        <v>32</v>
+      </c>
+      <c r="D408" s="4">
+        <v>133.06625</v>
+      </c>
+      <c r="E408" s="6">
+        <v>20</v>
+      </c>
+      <c r="F408" s="3">
+        <f t="shared" si="8"/>
+        <v>106.453</v>
+      </c>
+      <c r="G408" s="1"/>
+      <c r="H408" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B409" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C409" s="8">
+        <v>112</v>
+      </c>
+      <c r="D409" s="4">
+        <v>38.1262040816327</v>
+      </c>
+      <c r="E409" s="6">
+        <v>20</v>
+      </c>
+      <c r="F409" s="3">
+        <f t="shared" si="8"/>
+        <v>30.500963265306162</v>
+      </c>
+      <c r="G409" s="1"/>
+      <c r="H409" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B410" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C410" s="8">
+        <v>32</v>
+      </c>
+      <c r="D410" s="4">
+        <v>133.06625</v>
+      </c>
+      <c r="E410" s="6">
+        <v>20</v>
+      </c>
+      <c r="F410" s="3">
+        <f t="shared" si="8"/>
+        <v>106.453</v>
+      </c>
+      <c r="G410" s="1"/>
+      <c r="H410" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B411" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C411" s="8">
+        <v>64</v>
+      </c>
+      <c r="D411" s="4">
+        <v>117.83454618240199</v>
+      </c>
+      <c r="E411" s="6">
+        <v>20</v>
+      </c>
+      <c r="F411" s="3">
+        <f t="shared" si="8"/>
+        <v>94.267636945921595</v>
+      </c>
+      <c r="G411" s="1"/>
+      <c r="H411" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B412" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C412" s="8">
+        <v>109</v>
+      </c>
+      <c r="D412" s="4">
+        <v>37.513066301147703</v>
+      </c>
+      <c r="E412" s="6">
+        <v>20</v>
+      </c>
+      <c r="F412" s="3">
+        <f t="shared" si="8"/>
+        <v>30.010453040918161</v>
+      </c>
+      <c r="G412" s="1"/>
+      <c r="H412" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B413" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C413" s="8">
+        <v>149</v>
+      </c>
+      <c r="D413" s="4">
+        <v>38.136531325795602</v>
+      </c>
+      <c r="E413" s="6">
+        <v>20</v>
+      </c>
+      <c r="F413" s="3">
+        <f t="shared" si="8"/>
+        <v>30.509225060636481</v>
+      </c>
+      <c r="G413" s="1"/>
+      <c r="H413" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B414" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C414" s="8">
+        <v>152</v>
+      </c>
+      <c r="D414" s="4">
+        <v>45.8342666666667</v>
+      </c>
+      <c r="E414" s="6">
+        <v>20</v>
+      </c>
+      <c r="F414" s="3">
+        <f t="shared" si="8"/>
+        <v>36.667413333333357</v>
+      </c>
+      <c r="G414" s="1"/>
+      <c r="H414" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B415" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C415" s="8">
+        <v>152</v>
+      </c>
+      <c r="D415" s="4">
+        <v>45.8342666666667</v>
+      </c>
+      <c r="E415" s="6">
+        <v>20</v>
+      </c>
+      <c r="F415" s="3">
+        <f t="shared" si="8"/>
+        <v>36.667413333333357</v>
+      </c>
+      <c r="G415" s="1"/>
+      <c r="H415" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B416" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C416" s="8">
+        <v>176</v>
+      </c>
+      <c r="D416" s="4">
+        <v>37.708358442287597</v>
+      </c>
+      <c r="E416" s="6">
+        <v>20</v>
+      </c>
+      <c r="F416" s="3">
+        <f t="shared" si="8"/>
+        <v>30.166686753830078</v>
+      </c>
+      <c r="G416" s="1"/>
+      <c r="H416" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B417" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C417" s="8">
+        <v>8</v>
+      </c>
+      <c r="D417" s="4">
+        <v>45.381328947368402</v>
+      </c>
+      <c r="E417" s="6">
+        <v>20</v>
+      </c>
+      <c r="F417" s="3">
+        <f t="shared" si="8"/>
+        <v>36.305063157894722</v>
+      </c>
+      <c r="G417" s="1"/>
+      <c r="H417" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B418" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C418" s="8">
+        <v>176</v>
+      </c>
+      <c r="D418" s="4">
+        <v>40.715735160242801</v>
+      </c>
+      <c r="E418" s="6">
+        <v>20</v>
+      </c>
+      <c r="F418" s="3">
+        <f t="shared" si="8"/>
+        <v>32.572588128194241</v>
+      </c>
+      <c r="G418" s="1"/>
+      <c r="H418" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B419" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C419" s="8">
+        <v>112</v>
+      </c>
+      <c r="D419" s="4">
+        <v>76.236698941018005</v>
+      </c>
+      <c r="E419" s="6">
+        <v>20</v>
+      </c>
+      <c r="F419" s="3">
+        <f t="shared" si="8"/>
+        <v>60.989359152814401</v>
+      </c>
+      <c r="G419" s="1"/>
+      <c r="H419" s="7"/>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B420" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C420" s="8">
+        <v>160</v>
+      </c>
+      <c r="D420" s="4">
+        <v>36.180745590840402</v>
+      </c>
+      <c r="E420" s="6">
+        <v>20</v>
+      </c>
+      <c r="F420" s="3">
+        <f t="shared" si="8"/>
+        <v>28.944596472672323</v>
+      </c>
+      <c r="G420" s="1"/>
+      <c r="H420" s="7"/>
+    </row>
+    <row r="421" spans="1:8">
+      <c r="A421" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B421" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C421" s="8">
+        <v>56</v>
+      </c>
+      <c r="D421" s="4">
+        <v>126.253335287997</v>
+      </c>
+      <c r="E421" s="6">
+        <v>20</v>
+      </c>
+      <c r="F421" s="3">
+        <f t="shared" si="8"/>
+        <v>101.0026682303976</v>
+      </c>
+      <c r="G421" s="1"/>
+      <c r="H421" s="7"/>
+    </row>
+    <row r="422" spans="1:8">
+      <c r="A422" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B422" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C422" s="8">
+        <v>88</v>
+      </c>
+      <c r="D422" s="4">
+        <v>58.202100517725498</v>
+      </c>
+      <c r="E422" s="6">
+        <v>20</v>
+      </c>
+      <c r="F422" s="3">
+        <f t="shared" si="8"/>
+        <v>46.561680414180401</v>
+      </c>
+      <c r="G422" s="1"/>
+      <c r="H422" s="7"/>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B423" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C423" s="8"/>
+      <c r="D423" s="4"/>
+      <c r="E423" s="6">
+        <v>20</v>
+      </c>
+      <c r="F423" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G423" s="1"/>
+      <c r="H423" s="7"/>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B424" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C424" s="8">
+        <v>134</v>
+      </c>
+      <c r="D424" s="4">
+        <v>64.567513868277601</v>
+      </c>
+      <c r="E424" s="6">
+        <v>20</v>
+      </c>
+      <c r="F424" s="3">
+        <f t="shared" si="8"/>
+        <v>51.654011094622078</v>
+      </c>
+      <c r="G424" s="1"/>
+      <c r="H424" s="7"/>
+    </row>
+    <row r="425" spans="1:8">
+      <c r="A425" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B425" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C425" s="8"/>
+      <c r="D425" s="4"/>
+      <c r="E425" s="6">
+        <v>20</v>
+      </c>
+      <c r="F425" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G425" s="1"/>
+      <c r="H425" s="7"/>
+    </row>
+    <row r="426" spans="1:8">
+      <c r="A426" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B426" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C426" s="8">
+        <v>24</v>
+      </c>
+      <c r="D426" s="4">
+        <v>46.805258559453698</v>
+      </c>
+      <c r="E426" s="6">
+        <v>20</v>
+      </c>
+      <c r="F426" s="3">
+        <f t="shared" si="8"/>
+        <v>37.44420684756296</v>
+      </c>
+      <c r="G426" s="1"/>
+      <c r="H426" s="7"/>
+    </row>
+    <row r="427" spans="1:8">
+      <c r="A427" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B427" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C427" s="20">
+        <v>176</v>
+      </c>
+      <c r="D427" s="21">
+        <v>34.029804565098601</v>
+      </c>
+      <c r="E427" s="22">
+        <v>20</v>
+      </c>
+      <c r="F427" s="23">
+        <f t="shared" si="8"/>
+        <v>27.22384365207888</v>
+      </c>
+      <c r="G427" s="24"/>
+      <c r="H427" s="25"/>
+    </row>
+    <row r="428" spans="1:8">
+      <c r="A428" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B428" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C428" s="26">
+        <v>168</v>
+      </c>
+      <c r="D428" s="4">
+        <v>21.595788888888901</v>
+      </c>
+      <c r="E428" s="6">
+        <v>20</v>
+      </c>
+      <c r="F428" s="3">
+        <f t="shared" si="8"/>
+        <v>17.276631111111122</v>
+      </c>
+      <c r="G428" s="1"/>
+      <c r="H428" s="1"/>
+    </row>
+    <row r="429" spans="1:8">
+      <c r="A429" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B429" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C429" s="26"/>
+      <c r="D429" s="4"/>
+      <c r="E429" s="6">
+        <v>20</v>
+      </c>
+      <c r="F429" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G429" s="1"/>
+      <c r="H429" s="1"/>
+    </row>
+    <row r="430" spans="1:8">
+      <c r="A430" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B430" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C430" s="26">
+        <v>44</v>
+      </c>
+      <c r="D430" s="4">
+        <v>56.7523172043011</v>
+      </c>
+      <c r="E430" s="6">
+        <v>20</v>
+      </c>
+      <c r="F430" s="3">
+        <f t="shared" si="8"/>
+        <v>45.401853763440883</v>
+      </c>
+      <c r="G430" s="1"/>
+      <c r="H430" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G357">
-    <filterColumn colId="0">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="0"/>
+    <filterColumn colId="1"/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
@@ -10090,6 +11860,65 @@
     <hyperlink ref="H344" r:id="rId302"/>
     <hyperlink ref="H345" r:id="rId303"/>
     <hyperlink ref="H346" r:id="rId304"/>
+    <hyperlink ref="G358" r:id="rId305"/>
+    <hyperlink ref="H358" r:id="rId306"/>
+    <hyperlink ref="H359" r:id="rId307"/>
+    <hyperlink ref="H361" r:id="rId308"/>
+    <hyperlink ref="H362" r:id="rId309"/>
+    <hyperlink ref="H363" r:id="rId310"/>
+    <hyperlink ref="H364" r:id="rId311"/>
+    <hyperlink ref="H365" r:id="rId312"/>
+    <hyperlink ref="H367" r:id="rId313"/>
+    <hyperlink ref="H368" r:id="rId314"/>
+    <hyperlink ref="H369" r:id="rId315"/>
+    <hyperlink ref="H370" r:id="rId316"/>
+    <hyperlink ref="H371" r:id="rId317"/>
+    <hyperlink ref="H373" r:id="rId318"/>
+    <hyperlink ref="H374" r:id="rId319"/>
+    <hyperlink ref="H375" r:id="rId320"/>
+    <hyperlink ref="H376" r:id="rId321"/>
+    <hyperlink ref="H377" r:id="rId322"/>
+    <hyperlink ref="H378" r:id="rId323"/>
+    <hyperlink ref="H379" r:id="rId324"/>
+    <hyperlink ref="H380" r:id="rId325"/>
+    <hyperlink ref="H381" r:id="rId326"/>
+    <hyperlink ref="H382" r:id="rId327"/>
+    <hyperlink ref="H383" r:id="rId328"/>
+    <hyperlink ref="H384" r:id="rId329"/>
+    <hyperlink ref="H385" r:id="rId330"/>
+    <hyperlink ref="H386" r:id="rId331"/>
+    <hyperlink ref="H387" r:id="rId332"/>
+    <hyperlink ref="H388" r:id="rId333"/>
+    <hyperlink ref="H389" r:id="rId334"/>
+    <hyperlink ref="H390" r:id="rId335"/>
+    <hyperlink ref="H391" r:id="rId336"/>
+    <hyperlink ref="H392" r:id="rId337"/>
+    <hyperlink ref="H393" r:id="rId338"/>
+    <hyperlink ref="H394" r:id="rId339"/>
+    <hyperlink ref="H395" r:id="rId340"/>
+    <hyperlink ref="H396" r:id="rId341"/>
+    <hyperlink ref="H397" r:id="rId342"/>
+    <hyperlink ref="H398" r:id="rId343"/>
+    <hyperlink ref="H399" r:id="rId344"/>
+    <hyperlink ref="H400" r:id="rId345"/>
+    <hyperlink ref="H401" r:id="rId346"/>
+    <hyperlink ref="H402" r:id="rId347"/>
+    <hyperlink ref="H403" r:id="rId348"/>
+    <hyperlink ref="H404" r:id="rId349"/>
+    <hyperlink ref="H405" r:id="rId350"/>
+    <hyperlink ref="H406" r:id="rId351"/>
+    <hyperlink ref="H407" r:id="rId352"/>
+    <hyperlink ref="H408" r:id="rId353"/>
+    <hyperlink ref="H409" r:id="rId354"/>
+    <hyperlink ref="H410" r:id="rId355"/>
+    <hyperlink ref="H411" r:id="rId356"/>
+    <hyperlink ref="H412" r:id="rId357"/>
+    <hyperlink ref="H413" r:id="rId358"/>
+    <hyperlink ref="H414" r:id="rId359"/>
+    <hyperlink ref="H415" r:id="rId360"/>
+    <hyperlink ref="H416" r:id="rId361"/>
+    <hyperlink ref="H417" r:id="rId362"/>
+    <hyperlink ref="H418" r:id="rId363"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$432</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Foglio3!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="147">
   <si>
     <t>Tecnico</t>
   </si>
@@ -455,6 +455,12 @@
   </si>
   <si>
     <t>IRTE0000127 - DI MAURO FEDERICO</t>
+  </si>
+  <si>
+    <t>IRTE0000125 - QUADARELLA EDOARDO</t>
+  </si>
+  <si>
+    <t>IRTE0000126 - CANTONE LUCA</t>
   </si>
 </sst>
 </file>
@@ -643,7 +649,16 @@
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -933,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -9802,17 +9817,17 @@
         <v>46203</v>
       </c>
       <c r="C359" s="8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D359" s="4">
-        <v>41.328781249999999</v>
+        <v>41.366274358974302</v>
       </c>
       <c r="E359" s="6">
         <v>20</v>
       </c>
       <c r="F359" s="3">
         <f t="shared" si="7"/>
-        <v>33.063024999999996</v>
+        <v>33.09301948717944</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>65</v>
@@ -9901,14 +9916,14 @@
         <v>160</v>
       </c>
       <c r="D363" s="4">
-        <v>19.9667666666667</v>
+        <v>22.551385416666701</v>
       </c>
       <c r="E363" s="6">
         <v>20</v>
       </c>
       <c r="F363" s="3">
         <f t="shared" si="7"/>
-        <v>15.97341333333336</v>
+        <v>18.041108333333362</v>
       </c>
       <c r="G363" s="1"/>
       <c r="H363" s="7" t="s">
@@ -9951,14 +9966,14 @@
         <v>152</v>
       </c>
       <c r="D365" s="4">
-        <v>38.278795454545502</v>
+        <v>40.097431818181803</v>
       </c>
       <c r="E365" s="6">
         <v>20</v>
       </c>
       <c r="F365" s="3">
         <f t="shared" si="7"/>
-        <v>30.623036363636402</v>
+        <v>32.077945454545443</v>
       </c>
       <c r="G365" s="1"/>
       <c r="H365" s="7" t="s">
@@ -9999,14 +10014,14 @@
         <v>160</v>
       </c>
       <c r="D367" s="4">
-        <v>29.782658901267201</v>
+        <v>29.911889838767198</v>
       </c>
       <c r="E367" s="6">
         <v>20</v>
       </c>
       <c r="F367" s="3">
         <f t="shared" si="7"/>
-        <v>23.826127121013762</v>
+        <v>23.929511871013759</v>
       </c>
       <c r="G367" s="1"/>
       <c r="H367" s="7" t="s">
@@ -10099,14 +10114,14 @@
         <v>136</v>
       </c>
       <c r="D371" s="4">
-        <v>19.9667666666667</v>
+        <v>22.551385416666701</v>
       </c>
       <c r="E371" s="6">
         <v>20</v>
       </c>
       <c r="F371" s="3">
         <f t="shared" si="7"/>
-        <v>15.97341333333336</v>
+        <v>18.041108333333362</v>
       </c>
       <c r="G371" s="1"/>
       <c r="H371" s="7" t="s">
@@ -10172,14 +10187,14 @@
         <v>160</v>
       </c>
       <c r="D374" s="4">
-        <v>38.0179628378378</v>
+        <v>38.1497195945946</v>
       </c>
       <c r="E374" s="6">
         <v>20</v>
       </c>
       <c r="F374" s="3">
         <f t="shared" si="7"/>
-        <v>30.41437027027024</v>
+        <v>30.519775675675682</v>
       </c>
       <c r="G374" s="1"/>
       <c r="H374" s="7" t="s">
@@ -10222,14 +10237,14 @@
         <v>168</v>
       </c>
       <c r="D376" s="4">
-        <v>38.531518601076797</v>
+        <v>38.153817717882603</v>
       </c>
       <c r="E376" s="6">
         <v>20</v>
       </c>
       <c r="F376" s="3">
         <f t="shared" si="7"/>
-        <v>30.825214880861438</v>
+        <v>30.523054174306083</v>
       </c>
       <c r="G376" s="1"/>
       <c r="H376" s="7" t="s">
@@ -10269,17 +10284,17 @@
         <v>46203</v>
       </c>
       <c r="C378" s="8">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D378" s="4">
-        <v>45.807323229949901</v>
+        <v>35.770392597853501</v>
       </c>
       <c r="E378" s="6">
         <v>20</v>
       </c>
       <c r="F378" s="3">
         <f t="shared" si="7"/>
-        <v>36.645858583959921</v>
+        <v>28.616314078282802</v>
       </c>
       <c r="G378" s="1"/>
       <c r="H378" s="7" t="s">
@@ -10322,14 +10337,14 @@
         <v>160</v>
       </c>
       <c r="D380" s="4">
-        <v>29.409706931196101</v>
+        <v>29.165948058428299</v>
       </c>
       <c r="E380" s="6">
         <v>20</v>
       </c>
       <c r="F380" s="3">
         <f t="shared" si="7"/>
-        <v>23.527765544956882</v>
+        <v>23.332758446742638</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="7" t="s">
@@ -10394,17 +10409,17 @@
         <v>46203</v>
       </c>
       <c r="C383" s="8">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="D383" s="4">
-        <v>150.7933625</v>
+        <v>41.516246794871698</v>
       </c>
       <c r="E383" s="6">
         <v>20</v>
       </c>
       <c r="F383" s="3">
         <f t="shared" si="7"/>
-        <v>120.63469000000001</v>
+        <v>33.212997435897357</v>
       </c>
       <c r="G383" s="1"/>
       <c r="H383" s="7" t="s">
@@ -10572,14 +10587,14 @@
         <v>192</v>
       </c>
       <c r="D390" s="4">
-        <v>33.324485795454599</v>
+        <v>33.7656789772727</v>
       </c>
       <c r="E390" s="6">
         <v>20</v>
       </c>
       <c r="F390" s="3">
         <f t="shared" si="7"/>
-        <v>26.659588636363679</v>
+        <v>27.01254318181816</v>
       </c>
       <c r="G390" s="1"/>
       <c r="H390" s="7" t="s">
@@ -10703,7 +10718,7 @@
         <v>20</v>
       </c>
       <c r="F395" s="3">
-        <f t="shared" ref="F395:F430" si="8">D395-(D395*E395)/100</f>
+        <f t="shared" ref="F395:F431" si="8">D395-(D395*E395)/100</f>
         <v>28.935588267598082</v>
       </c>
       <c r="G395" s="1"/>
@@ -10794,17 +10809,17 @@
         <v>46203</v>
       </c>
       <c r="C399" s="8">
-        <v>123.5</v>
+        <v>147.5</v>
       </c>
       <c r="D399" s="4">
-        <v>44.123338752035998</v>
+        <v>36.656800106447498</v>
       </c>
       <c r="E399" s="6">
         <v>20</v>
       </c>
       <c r="F399" s="3">
         <f t="shared" si="8"/>
-        <v>35.298671001628797</v>
+        <v>29.325440085158</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="7" t="s">
@@ -10819,17 +10834,17 @@
         <v>46203</v>
       </c>
       <c r="C400" s="8">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="D400" s="4">
-        <v>193.917265625</v>
+        <v>40.981722560975598</v>
       </c>
       <c r="E400" s="6">
         <v>20</v>
       </c>
       <c r="F400" s="3">
         <f t="shared" si="8"/>
-        <v>155.1338125</v>
+        <v>32.78537804878048</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="7" t="s">
@@ -10894,17 +10909,17 @@
         <v>46203</v>
       </c>
       <c r="C403" s="8">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D403" s="4">
-        <v>568.30643750000002</v>
+        <v>37.570714843749997</v>
       </c>
       <c r="E403" s="6">
         <v>20</v>
       </c>
       <c r="F403" s="3">
         <f t="shared" si="8"/>
-        <v>454.64515</v>
+        <v>30.056571874999996</v>
       </c>
       <c r="G403" s="1"/>
       <c r="H403" s="7" t="s">
@@ -10919,17 +10934,17 @@
         <v>46203</v>
       </c>
       <c r="C404" s="8">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="D404" s="4">
-        <v>125.63765625000001</v>
+        <v>30.195953947368402</v>
       </c>
       <c r="E404" s="6">
         <v>20</v>
       </c>
       <c r="F404" s="3">
         <f t="shared" si="8"/>
-        <v>100.510125</v>
+        <v>24.156763157894723</v>
       </c>
       <c r="G404" s="1"/>
       <c r="H404" s="7" t="s">
@@ -10944,17 +10959,17 @@
         <v>46203</v>
       </c>
       <c r="C405" s="8">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="D405" s="4">
-        <v>190.33821875000001</v>
+        <v>38.653761718749998</v>
       </c>
       <c r="E405" s="6">
         <v>20</v>
       </c>
       <c r="F405" s="3">
         <f t="shared" si="8"/>
-        <v>152.27057500000001</v>
+        <v>30.923009374999999</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="7" t="s">
@@ -10969,17 +10984,17 @@
         <v>46203</v>
       </c>
       <c r="C406" s="8">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="D406" s="4">
-        <v>117.456953125</v>
+        <v>32.210850069252103</v>
       </c>
       <c r="E406" s="6">
         <v>20</v>
       </c>
       <c r="F406" s="3">
         <f t="shared" si="8"/>
-        <v>93.965562500000004</v>
+        <v>25.768680055401681</v>
       </c>
       <c r="G406" s="1"/>
       <c r="H406" s="7" t="s">
@@ -10997,14 +11012,14 @@
         <v>160</v>
       </c>
       <c r="D407" s="4">
-        <v>37.816337955678897</v>
+        <v>37.651633136965103</v>
       </c>
       <c r="E407" s="6">
         <v>20</v>
       </c>
       <c r="F407" s="3">
         <f t="shared" si="8"/>
-        <v>30.253070364543117</v>
+        <v>30.121306509572083</v>
       </c>
       <c r="G407" s="1"/>
       <c r="H407" s="7" t="s">
@@ -11019,17 +11034,17 @@
         <v>46203</v>
       </c>
       <c r="C408" s="8">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="D408" s="4">
-        <v>133.06625</v>
+        <v>30.767169938801</v>
       </c>
       <c r="E408" s="6">
         <v>20</v>
       </c>
       <c r="F408" s="3">
         <f t="shared" si="8"/>
-        <v>106.453</v>
+        <v>24.613735951040802</v>
       </c>
       <c r="G408" s="1"/>
       <c r="H408" s="7" t="s">
@@ -11044,17 +11059,17 @@
         <v>46203</v>
       </c>
       <c r="C409" s="8">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D409" s="4">
-        <v>38.1262040816327</v>
+        <v>36.677877929687497</v>
       </c>
       <c r="E409" s="6">
         <v>20</v>
       </c>
       <c r="F409" s="3">
         <f t="shared" si="8"/>
-        <v>30.500963265306162</v>
+        <v>29.342302343749999</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="7" t="s">
@@ -11069,17 +11084,17 @@
         <v>46203</v>
       </c>
       <c r="C410" s="8">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="D410" s="4">
-        <v>133.06625</v>
+        <v>30.7965655431966</v>
       </c>
       <c r="E410" s="6">
         <v>20</v>
       </c>
       <c r="F410" s="3">
         <f t="shared" si="8"/>
-        <v>106.453</v>
+        <v>24.637252434557279</v>
       </c>
       <c r="G410" s="1"/>
       <c r="H410" s="7" t="s">
@@ -11094,17 +11109,17 @@
         <v>46203</v>
       </c>
       <c r="C411" s="8">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="D411" s="4">
-        <v>117.83454618240199</v>
+        <v>38.041305898033997</v>
       </c>
       <c r="E411" s="6">
         <v>20</v>
       </c>
       <c r="F411" s="3">
         <f t="shared" si="8"/>
-        <v>94.267636945921595</v>
+        <v>30.433044718427197</v>
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="7" t="s">
@@ -11122,14 +11137,14 @@
         <v>109</v>
       </c>
       <c r="D412" s="4">
-        <v>37.513066301147703</v>
+        <v>38.082156668120199</v>
       </c>
       <c r="E412" s="6">
         <v>20</v>
       </c>
       <c r="F412" s="3">
         <f t="shared" si="8"/>
-        <v>30.010453040918161</v>
+        <v>30.46572533449616</v>
       </c>
       <c r="G412" s="1"/>
       <c r="H412" s="7" t="s">
@@ -11222,14 +11237,14 @@
         <v>176</v>
       </c>
       <c r="D416" s="4">
-        <v>37.708358442287597</v>
+        <v>38.809050381644298</v>
       </c>
       <c r="E416" s="6">
         <v>20</v>
       </c>
       <c r="F416" s="3">
         <f t="shared" si="8"/>
-        <v>30.166686753830078</v>
+        <v>31.047240305315437</v>
       </c>
       <c r="G416" s="1"/>
       <c r="H416" s="7" t="s">
@@ -11340,17 +11355,17 @@
         <v>46203</v>
       </c>
       <c r="C421" s="8">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="D421" s="4">
-        <v>126.253335287997</v>
+        <v>40.7914578629034</v>
       </c>
       <c r="E421" s="6">
         <v>20</v>
       </c>
       <c r="F421" s="3">
         <f t="shared" si="8"/>
-        <v>101.0026682303976</v>
+        <v>32.63316629032272</v>
       </c>
       <c r="G421" s="1"/>
       <c r="H421" s="7"/>
@@ -11363,17 +11378,17 @@
         <v>46203</v>
       </c>
       <c r="C422" s="8">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="D422" s="4">
-        <v>58.202100517725498</v>
+        <v>39.2081634824929</v>
       </c>
       <c r="E422" s="6">
         <v>20</v>
       </c>
       <c r="F422" s="3">
         <f t="shared" si="8"/>
-        <v>46.561680414180401</v>
+        <v>31.366530785994321</v>
       </c>
       <c r="G422" s="1"/>
       <c r="H422" s="7"/>
@@ -11446,7 +11461,7 @@
       <c r="B426" s="10">
         <v>46203</v>
       </c>
-      <c r="C426" s="8">
+      <c r="C426" s="20">
         <v>24</v>
       </c>
       <c r="D426" s="4">
@@ -11469,21 +11484,21 @@
       <c r="B427" s="10">
         <v>46203</v>
       </c>
-      <c r="C427" s="20">
-        <v>176</v>
-      </c>
-      <c r="D427" s="21">
-        <v>34.029804565098601</v>
-      </c>
-      <c r="E427" s="22">
-        <v>20</v>
-      </c>
-      <c r="F427" s="23">
+      <c r="C427" s="26">
+        <v>184</v>
+      </c>
+      <c r="D427" s="4">
+        <v>34.027072212706102</v>
+      </c>
+      <c r="E427" s="6">
+        <v>20</v>
+      </c>
+      <c r="F427" s="3">
         <f t="shared" si="8"/>
-        <v>27.22384365207888</v>
-      </c>
-      <c r="G427" s="24"/>
-      <c r="H427" s="25"/>
+        <v>27.221657770164882</v>
+      </c>
+      <c r="G427" s="1"/>
+      <c r="H427" s="7"/>
     </row>
     <row r="428" spans="1:8">
       <c r="A428" s="1" t="s">
@@ -11493,17 +11508,17 @@
         <v>46203</v>
       </c>
       <c r="C428" s="26">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D428" s="4">
-        <v>21.595788888888901</v>
+        <v>24.8809433396465</v>
       </c>
       <c r="E428" s="6">
         <v>20</v>
       </c>
       <c r="F428" s="3">
         <f t="shared" si="8"/>
-        <v>17.276631111111122</v>
+        <v>19.9047546717172</v>
       </c>
       <c r="G428" s="1"/>
       <c r="H428" s="1"/>
@@ -11529,29 +11544,75 @@
     </row>
     <row r="430" spans="1:8">
       <c r="A430" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B430" s="10">
         <v>46203</v>
       </c>
       <c r="C430" s="26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D430" s="4">
-        <v>56.7523172043011</v>
+        <v>40.981722560975598</v>
       </c>
       <c r="E430" s="6">
         <v>20</v>
       </c>
       <c r="F430" s="3">
         <f t="shared" si="8"/>
-        <v>45.401853763440883</v>
+        <v>32.78537804878048</v>
       </c>
       <c r="G430" s="1"/>
       <c r="H430" s="1"/>
     </row>
+    <row r="431" spans="1:8">
+      <c r="A431" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B431" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C431" s="26">
+        <v>24</v>
+      </c>
+      <c r="D431" s="4">
+        <v>41.516246794871698</v>
+      </c>
+      <c r="E431" s="6">
+        <v>20</v>
+      </c>
+      <c r="F431" s="3">
+        <f t="shared" si="8"/>
+        <v>33.212997435897357</v>
+      </c>
+      <c r="G431" s="1"/>
+      <c r="H431" s="1"/>
+    </row>
+    <row r="432" spans="1:8">
+      <c r="A432" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B432" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C432" s="26">
+        <v>44</v>
+      </c>
+      <c r="D432" s="4">
+        <v>56.7523172043011</v>
+      </c>
+      <c r="E432" s="6">
+        <v>20</v>
+      </c>
+      <c r="F432" s="3">
+        <f>D432-(D432*E432)/100</f>
+        <v>45.401853763440883</v>
+      </c>
+      <c r="G432" s="1"/>
+      <c r="H432" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G357">
+  <autoFilter ref="A1:G432">
     <filterColumn colId="0"/>
     <filterColumn colId="1"/>
   </autoFilter>
@@ -11926,7 +11987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D1:L104"/>
+  <dimension ref="D1:L118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -13606,8 +13667,244 @@
         <v>38.165462682006002</v>
       </c>
     </row>
+    <row r="109" spans="4:12">
+      <c r="D109" s="27">
+        <v>46174</v>
+      </c>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="28"/>
+      <c r="L109" s="28"/>
+    </row>
+    <row r="110" spans="4:12">
+      <c r="D110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="4:12">
+      <c r="D111" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F111" s="8">
+        <v>184</v>
+      </c>
+      <c r="G111" s="4">
+        <v>41.908045731707297</v>
+      </c>
+      <c r="I111" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J111" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K111" s="8">
+        <v>160</v>
+      </c>
+      <c r="L111" s="4">
+        <v>37.651633136965103</v>
+      </c>
+    </row>
+    <row r="112" spans="4:12">
+      <c r="D112" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F112" s="8">
+        <v>176</v>
+      </c>
+      <c r="G112" s="4">
+        <v>40.715735160242801</v>
+      </c>
+      <c r="I112" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J112" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K112" s="8">
+        <v>128</v>
+      </c>
+      <c r="L112" s="4">
+        <v>36.677877929687497</v>
+      </c>
+    </row>
+    <row r="113" spans="4:12">
+      <c r="D113" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F113" s="8">
+        <v>152</v>
+      </c>
+      <c r="G113" s="4">
+        <v>40.097431818181803</v>
+      </c>
+      <c r="I113" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K113" s="8">
+        <v>176</v>
+      </c>
+      <c r="L113" s="4">
+        <v>35.770392597853501</v>
+      </c>
+    </row>
+    <row r="114" spans="4:12">
+      <c r="D114" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E114" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F114" s="8">
+        <v>176</v>
+      </c>
+      <c r="G114" s="4">
+        <v>38.809050381644298</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J114" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K114" s="8">
+        <v>184</v>
+      </c>
+      <c r="L114" s="4">
+        <v>34.027072212706102</v>
+      </c>
+    </row>
+    <row r="115" spans="4:12">
+      <c r="D115" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F115" s="8">
+        <v>160</v>
+      </c>
+      <c r="G115" s="4">
+        <v>38.550371323529397</v>
+      </c>
+      <c r="I115" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J115" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K115" s="8">
+        <v>192</v>
+      </c>
+      <c r="L115" s="4">
+        <v>33.7656789772727</v>
+      </c>
+    </row>
+    <row r="116" spans="4:12">
+      <c r="D116" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F116" s="8">
+        <v>152</v>
+      </c>
+      <c r="G116" s="4">
+        <v>38.420708333333302</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J116" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K116" s="8">
+        <v>93</v>
+      </c>
+      <c r="L116" s="4">
+        <v>31.535950354609898</v>
+      </c>
+    </row>
+    <row r="117" spans="4:12">
+      <c r="D117" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F117" s="8">
+        <v>168</v>
+      </c>
+      <c r="G117" s="4">
+        <v>38.153817717882603</v>
+      </c>
+      <c r="I117" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J117" s="10">
+        <v>46203</v>
+      </c>
+      <c r="K117" s="26">
+        <v>149</v>
+      </c>
+      <c r="L117" s="4">
+        <v>30.586636513592801</v>
+      </c>
+    </row>
+    <row r="118" spans="4:12">
+      <c r="D118" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="10">
+        <v>46203</v>
+      </c>
+      <c r="F118" s="8">
+        <v>160</v>
+      </c>
+      <c r="G118" s="4">
+        <v>38.1497195945946</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="D109:L109"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D25:L25"/>
     <mergeCell ref="D1:L1"/>

--- a/Avanzamento.xlsx
+++ b/Avanzamento.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$G$507</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Foglio3!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="147">
   <si>
     <t>Tecnico</t>
   </si>
@@ -948,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H507"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
@@ -11611,8 +11611,1837 @@
       <c r="G432" s="1"/>
       <c r="H432" s="1"/>
     </row>
+    <row r="433" spans="1:8">
+      <c r="A433" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B433" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C433" s="8">
+        <v>144.5</v>
+      </c>
+      <c r="D433" s="11">
+        <v>28.153887913715799</v>
+      </c>
+      <c r="E433" s="12">
+        <v>20</v>
+      </c>
+      <c r="F433" s="13">
+        <f t="shared" ref="F433:F496" si="9">D433-(D433*E433)/100</f>
+        <v>22.523110330972639</v>
+      </c>
+      <c r="G433" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H433" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B434" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C434" s="8">
+        <v>48</v>
+      </c>
+      <c r="D434" s="4">
+        <v>32.0919762293763</v>
+      </c>
+      <c r="E434" s="6">
+        <v>20</v>
+      </c>
+      <c r="F434" s="3">
+        <f t="shared" si="9"/>
+        <v>25.67358098350104</v>
+      </c>
+      <c r="G434" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B435" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C435" s="8"/>
+      <c r="D435" s="4"/>
+      <c r="E435" s="6">
+        <v>20</v>
+      </c>
+      <c r="F435" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G435" s="1"/>
+      <c r="H435" s="7"/>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B436" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C436" s="8">
+        <v>172</v>
+      </c>
+      <c r="D436" s="4">
+        <v>21.712323210900099</v>
+      </c>
+      <c r="E436" s="6">
+        <v>20</v>
+      </c>
+      <c r="F436" s="3">
+        <f t="shared" si="9"/>
+        <v>17.36985856872008</v>
+      </c>
+      <c r="G436" s="1"/>
+      <c r="H436" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B437" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C437" s="8">
+        <v>104</v>
+      </c>
+      <c r="D437" s="4">
+        <v>37.312329791927603</v>
+      </c>
+      <c r="E437" s="6">
+        <v>20</v>
+      </c>
+      <c r="F437" s="3">
+        <f t="shared" si="9"/>
+        <v>29.849863833542081</v>
+      </c>
+      <c r="G437" s="1"/>
+      <c r="H437" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B438" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C438" s="8">
+        <v>176</v>
+      </c>
+      <c r="D438" s="4">
+        <v>39.615972222222197</v>
+      </c>
+      <c r="E438" s="6">
+        <v>20</v>
+      </c>
+      <c r="F438" s="3">
+        <f t="shared" si="9"/>
+        <v>31.692777777777756</v>
+      </c>
+      <c r="G438" s="1"/>
+      <c r="H438" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C439" s="8">
+        <v>124</v>
+      </c>
+      <c r="D439" s="4">
+        <v>26.1953326976158</v>
+      </c>
+      <c r="E439" s="6">
+        <v>20</v>
+      </c>
+      <c r="F439" s="3">
+        <f t="shared" si="9"/>
+        <v>20.956266158092639</v>
+      </c>
+      <c r="G439" s="1"/>
+      <c r="H439" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B440" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C440" s="8">
+        <v>172</v>
+      </c>
+      <c r="D440" s="4">
+        <v>31.096308641975298</v>
+      </c>
+      <c r="E440" s="6">
+        <v>20</v>
+      </c>
+      <c r="F440" s="3">
+        <f t="shared" si="9"/>
+        <v>24.877046913580237</v>
+      </c>
+      <c r="G440" s="1"/>
+      <c r="H440" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B441" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C441" s="8">
+        <v>95</v>
+      </c>
+      <c r="D441" s="4">
+        <v>31.253578239716902</v>
+      </c>
+      <c r="E441" s="6">
+        <v>20</v>
+      </c>
+      <c r="F441" s="3">
+        <f t="shared" si="9"/>
+        <v>25.002862591773521</v>
+      </c>
+      <c r="G441" s="1"/>
+      <c r="H441" s="7"/>
+    </row>
+    <row r="442" spans="1:8">
+      <c r="A442" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B442" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C442" s="8">
+        <v>143</v>
+      </c>
+      <c r="D442" s="4">
+        <v>23.0535655985095</v>
+      </c>
+      <c r="E442" s="6">
+        <v>20</v>
+      </c>
+      <c r="F442" s="3">
+        <f t="shared" si="9"/>
+        <v>18.442852478807602</v>
+      </c>
+      <c r="G442" s="1"/>
+      <c r="H442" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8">
+      <c r="A443" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B443" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C443" s="8">
+        <v>172</v>
+      </c>
+      <c r="D443" s="4">
+        <v>43.7208255160511</v>
+      </c>
+      <c r="E443" s="6">
+        <v>20</v>
+      </c>
+      <c r="F443" s="3">
+        <f t="shared" si="9"/>
+        <v>34.976660412840879</v>
+      </c>
+      <c r="G443" s="1"/>
+      <c r="H443" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B444" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C444" s="8">
+        <v>181</v>
+      </c>
+      <c r="D444" s="4">
+        <v>43.756536794376601</v>
+      </c>
+      <c r="E444" s="6">
+        <v>20</v>
+      </c>
+      <c r="F444" s="3">
+        <f t="shared" si="9"/>
+        <v>35.005229435501278</v>
+      </c>
+      <c r="G444" s="1"/>
+      <c r="H444" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8">
+      <c r="A445" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B445" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C445" s="8">
+        <v>153</v>
+      </c>
+      <c r="D445" s="4">
+        <v>131.04528296604099</v>
+      </c>
+      <c r="E445" s="6">
+        <v>20</v>
+      </c>
+      <c r="F445" s="3">
+        <f t="shared" si="9"/>
+        <v>104.83622637283278</v>
+      </c>
+      <c r="G445" s="1"/>
+      <c r="H445" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8">
+      <c r="A446" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B446" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C446" s="8">
+        <v>176</v>
+      </c>
+      <c r="D446" s="4">
+        <v>39.615972222222197</v>
+      </c>
+      <c r="E446" s="6">
+        <v>20</v>
+      </c>
+      <c r="F446" s="3">
+        <f t="shared" si="9"/>
+        <v>31.692777777777756</v>
+      </c>
+      <c r="G446" s="1"/>
+      <c r="H446" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8">
+      <c r="A447" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B447" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C447" s="8">
+        <v>152</v>
+      </c>
+      <c r="D447" s="4">
+        <v>36.7184390243902</v>
+      </c>
+      <c r="E447" s="6">
+        <v>20</v>
+      </c>
+      <c r="F447" s="3">
+        <f t="shared" si="9"/>
+        <v>29.374751219512159</v>
+      </c>
+      <c r="G447" s="1"/>
+      <c r="H447" s="7"/>
+    </row>
+    <row r="448" spans="1:8">
+      <c r="A448" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B448" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C448" s="8">
+        <v>148</v>
+      </c>
+      <c r="D448" s="4">
+        <v>39.119060714285702</v>
+      </c>
+      <c r="E448" s="6">
+        <v>20</v>
+      </c>
+      <c r="F448" s="3">
+        <f t="shared" si="9"/>
+        <v>31.295248571428562</v>
+      </c>
+      <c r="G448" s="1"/>
+      <c r="H448" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B449" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C449" s="8">
+        <v>192</v>
+      </c>
+      <c r="D449" s="4">
+        <v>34.924171686747002</v>
+      </c>
+      <c r="E449" s="6">
+        <v>20</v>
+      </c>
+      <c r="F449" s="3">
+        <f t="shared" si="9"/>
+        <v>27.939337349397601</v>
+      </c>
+      <c r="G449" s="1"/>
+      <c r="H449" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B450" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C450" s="8">
+        <v>131.5</v>
+      </c>
+      <c r="D450" s="4">
+        <v>29.679957665399801</v>
+      </c>
+      <c r="E450" s="6">
+        <v>20</v>
+      </c>
+      <c r="F450" s="3">
+        <f t="shared" si="9"/>
+        <v>23.743966132319841</v>
+      </c>
+      <c r="G450" s="1"/>
+      <c r="H450" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B451" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C451" s="8">
+        <v>104</v>
+      </c>
+      <c r="D451" s="4">
+        <v>38.65</v>
+      </c>
+      <c r="E451" s="6">
+        <v>20</v>
+      </c>
+      <c r="F451" s="3">
+        <f t="shared" si="9"/>
+        <v>30.919999999999998</v>
+      </c>
+      <c r="G451" s="1"/>
+      <c r="H451" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8">
+      <c r="A452" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B452" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C452" s="8">
+        <v>152</v>
+      </c>
+      <c r="D452" s="4">
+        <v>44.4738871645866</v>
+      </c>
+      <c r="E452" s="6">
+        <v>20</v>
+      </c>
+      <c r="F452" s="3">
+        <f t="shared" si="9"/>
+        <v>35.579109731669277</v>
+      </c>
+      <c r="G452" s="1"/>
+      <c r="H452" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8">
+      <c r="A453" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B453" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C453" s="8">
+        <v>155</v>
+      </c>
+      <c r="D453" s="4">
+        <v>36.615065022272397</v>
+      </c>
+      <c r="E453" s="6">
+        <v>20</v>
+      </c>
+      <c r="F453" s="3">
+        <f t="shared" si="9"/>
+        <v>29.292052017817916</v>
+      </c>
+      <c r="G453" s="1"/>
+      <c r="H453" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8">
+      <c r="A454" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B454" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C454" s="8">
+        <v>165</v>
+      </c>
+      <c r="D454" s="4">
+        <v>46.666219814814802</v>
+      </c>
+      <c r="E454" s="6">
+        <v>20</v>
+      </c>
+      <c r="F454" s="3">
+        <f t="shared" si="9"/>
+        <v>37.332975851851842</v>
+      </c>
+      <c r="G454" s="1"/>
+      <c r="H454" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8">
+      <c r="A455" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B455" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C455" s="8">
+        <v>136</v>
+      </c>
+      <c r="D455" s="4">
+        <v>30.298845630906101</v>
+      </c>
+      <c r="E455" s="6">
+        <v>20</v>
+      </c>
+      <c r="F455" s="3">
+        <f t="shared" si="9"/>
+        <v>24.239076504724881</v>
+      </c>
+      <c r="G455" s="1"/>
+      <c r="H455" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8">
+      <c r="A456" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B456" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C456" s="8">
+        <v>154</v>
+      </c>
+      <c r="D456" s="4">
+        <v>55.246318385650198</v>
+      </c>
+      <c r="E456" s="6">
+        <v>20</v>
+      </c>
+      <c r="F456" s="3">
+        <f t="shared" si="9"/>
+        <v>44.197054708520156</v>
+      </c>
+      <c r="G456" s="1"/>
+      <c r="H456" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8">
+      <c r="A457" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B457" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C457" s="8">
+        <v>23</v>
+      </c>
+      <c r="D457" s="4">
+        <v>45.295991136814798</v>
+      </c>
+      <c r="E457" s="6">
+        <v>20</v>
+      </c>
+      <c r="F457" s="3">
+        <f t="shared" si="9"/>
+        <v>36.236792909451836</v>
+      </c>
+      <c r="G457" s="1"/>
+      <c r="H457" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8">
+      <c r="A458" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B458" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C458" s="8">
+        <v>128</v>
+      </c>
+      <c r="D458" s="4">
+        <v>47.375443548386997</v>
+      </c>
+      <c r="E458" s="6">
+        <v>20</v>
+      </c>
+      <c r="F458" s="3">
+        <f t="shared" si="9"/>
+        <v>37.900354838709596</v>
+      </c>
+      <c r="G458" s="1"/>
+      <c r="H458" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8">
+      <c r="A459" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B459" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C459" s="8">
+        <v>172</v>
+      </c>
+      <c r="D459" s="4">
+        <v>21.712323210900099</v>
+      </c>
+      <c r="E459" s="6">
+        <v>20</v>
+      </c>
+      <c r="F459" s="3">
+        <f t="shared" si="9"/>
+        <v>17.36985856872008</v>
+      </c>
+      <c r="G459" s="1"/>
+      <c r="H459" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8">
+      <c r="A460" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B460" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C460" s="8">
+        <v>177</v>
+      </c>
+      <c r="D460" s="4">
+        <v>55.246318385650198</v>
+      </c>
+      <c r="E460" s="6">
+        <v>20</v>
+      </c>
+      <c r="F460" s="3">
+        <f t="shared" si="9"/>
+        <v>44.197054708520156</v>
+      </c>
+      <c r="G460" s="1"/>
+      <c r="H460" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8">
+      <c r="A461" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B461" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C461" s="8">
+        <v>40</v>
+      </c>
+      <c r="D461" s="4">
+        <v>245.91114999999999</v>
+      </c>
+      <c r="E461" s="6">
+        <v>20</v>
+      </c>
+      <c r="F461" s="3">
+        <f t="shared" si="9"/>
+        <v>196.72891999999999</v>
+      </c>
+      <c r="G461" s="1"/>
+      <c r="H461" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B462" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C462" s="8">
+        <v>140</v>
+      </c>
+      <c r="D462" s="4">
+        <v>38.07</v>
+      </c>
+      <c r="E462" s="6">
+        <v>20</v>
+      </c>
+      <c r="F462" s="3">
+        <f t="shared" si="9"/>
+        <v>30.456</v>
+      </c>
+      <c r="G462" s="1"/>
+      <c r="H462" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8">
+      <c r="A463" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B463" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C463" s="8">
+        <v>165</v>
+      </c>
+      <c r="D463" s="4">
+        <v>46.9028138888889</v>
+      </c>
+      <c r="E463" s="6">
+        <v>20</v>
+      </c>
+      <c r="F463" s="3">
+        <f t="shared" si="9"/>
+        <v>37.522251111111117</v>
+      </c>
+      <c r="G463" s="1"/>
+      <c r="H463" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8">
+      <c r="A464" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B464" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C464" s="8"/>
+      <c r="D464" s="4"/>
+      <c r="E464" s="6">
+        <v>20</v>
+      </c>
+      <c r="F464" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G464" s="1"/>
+      <c r="H464" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8">
+      <c r="A465" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B465" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C465" s="8">
+        <v>170</v>
+      </c>
+      <c r="D465" s="4">
+        <v>33.4496632653061</v>
+      </c>
+      <c r="E465" s="6">
+        <v>20</v>
+      </c>
+      <c r="F465" s="3">
+        <f t="shared" si="9"/>
+        <v>26.75973061224488</v>
+      </c>
+      <c r="G465" s="1"/>
+      <c r="H465" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8">
+      <c r="A466" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B466" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C466" s="8">
+        <v>160</v>
+      </c>
+      <c r="D466" s="4">
+        <v>64.331657785846403</v>
+      </c>
+      <c r="E466" s="6">
+        <v>20</v>
+      </c>
+      <c r="F466" s="3">
+        <f t="shared" si="9"/>
+        <v>51.465326228677121</v>
+      </c>
+      <c r="G466" s="1"/>
+      <c r="H466" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8">
+      <c r="A467" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B467" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C467" s="8">
+        <v>48</v>
+      </c>
+      <c r="D467" s="4">
+        <v>211.04569817073201</v>
+      </c>
+      <c r="E467" s="6">
+        <v>20</v>
+      </c>
+      <c r="F467" s="3">
+        <f t="shared" si="9"/>
+        <v>168.83655853658561</v>
+      </c>
+      <c r="G467" s="1"/>
+      <c r="H467" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8">
+      <c r="A468" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B468" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C468" s="8">
+        <v>31</v>
+      </c>
+      <c r="D468" s="4">
+        <v>45.074837037604603</v>
+      </c>
+      <c r="E468" s="6">
+        <v>20</v>
+      </c>
+      <c r="F468" s="3">
+        <f t="shared" si="9"/>
+        <v>36.059869630083682</v>
+      </c>
+      <c r="G468" s="1"/>
+      <c r="H468" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8">
+      <c r="A469" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B469" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C469" s="8">
+        <v>164</v>
+      </c>
+      <c r="D469" s="4">
+        <v>21.726779733527401</v>
+      </c>
+      <c r="E469" s="6">
+        <v>20</v>
+      </c>
+      <c r="F469" s="3">
+        <f t="shared" si="9"/>
+        <v>17.381423786821919</v>
+      </c>
+      <c r="G469" s="1"/>
+      <c r="H469" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8">
+      <c r="A470" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B470" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C470" s="8">
+        <v>160</v>
+      </c>
+      <c r="D470" s="4">
+        <v>32.354506838565001</v>
+      </c>
+      <c r="E470" s="6">
+        <v>20</v>
+      </c>
+      <c r="F470" s="3">
+        <f t="shared" si="9"/>
+        <v>25.883605470852</v>
+      </c>
+      <c r="G470" s="1"/>
+      <c r="H470" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8">
+      <c r="A471" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B471" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C471" s="8">
+        <v>155</v>
+      </c>
+      <c r="D471" s="4">
+        <v>30.719612903225801</v>
+      </c>
+      <c r="E471" s="6">
+        <v>20</v>
+      </c>
+      <c r="F471" s="3">
+        <f t="shared" si="9"/>
+        <v>24.575690322580641</v>
+      </c>
+      <c r="G471" s="1"/>
+      <c r="H471" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8">
+      <c r="A472" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B472" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C472" s="8">
+        <v>108</v>
+      </c>
+      <c r="D472" s="4">
+        <v>41.736368159203998</v>
+      </c>
+      <c r="E472" s="6">
+        <v>20</v>
+      </c>
+      <c r="F472" s="3">
+        <f t="shared" si="9"/>
+        <v>33.389094527363198</v>
+      </c>
+      <c r="G472" s="1"/>
+      <c r="H472" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8">
+      <c r="A473" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B473" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C473" s="8">
+        <v>39</v>
+      </c>
+      <c r="D473" s="4">
+        <v>35.828716619634399</v>
+      </c>
+      <c r="E473" s="6">
+        <v>20</v>
+      </c>
+      <c r="F473" s="3">
+        <f t="shared" si="9"/>
+        <v>28.66297329570752</v>
+      </c>
+      <c r="G473" s="1"/>
+      <c r="H473" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8">
+      <c r="A474" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B474" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C474" s="8">
+        <v>115.5</v>
+      </c>
+      <c r="D474" s="4">
+        <v>31.151367870062199</v>
+      </c>
+      <c r="E474" s="6">
+        <v>20</v>
+      </c>
+      <c r="F474" s="3">
+        <f t="shared" si="9"/>
+        <v>24.921094296049759</v>
+      </c>
+      <c r="G474" s="1"/>
+      <c r="H474" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8">
+      <c r="A475" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B475" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C475" s="8">
+        <v>120</v>
+      </c>
+      <c r="D475" s="4">
+        <v>35.410083333333397</v>
+      </c>
+      <c r="E475" s="6">
+        <v>20</v>
+      </c>
+      <c r="F475" s="3">
+        <f t="shared" si="9"/>
+        <v>28.328066666666718</v>
+      </c>
+      <c r="G475" s="1"/>
+      <c r="H475" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8">
+      <c r="A476" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B476" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C476" s="8">
+        <v>176</v>
+      </c>
+      <c r="D476" s="4">
+        <v>55.683137544208698</v>
+      </c>
+      <c r="E476" s="6">
+        <v>20</v>
+      </c>
+      <c r="F476" s="3">
+        <f t="shared" si="9"/>
+        <v>44.546510035366957</v>
+      </c>
+      <c r="G476" s="1"/>
+      <c r="H476" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8">
+      <c r="A477" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B477" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C477" s="8">
+        <v>160</v>
+      </c>
+      <c r="D477" s="4">
+        <v>55.767135166629998</v>
+      </c>
+      <c r="E477" s="6">
+        <v>20</v>
+      </c>
+      <c r="F477" s="3">
+        <f t="shared" si="9"/>
+        <v>44.613708133304002</v>
+      </c>
+      <c r="G477" s="1"/>
+      <c r="H477" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8">
+      <c r="A478" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B478" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C478" s="8">
+        <v>112</v>
+      </c>
+      <c r="D478" s="4">
+        <v>37.097142857142899</v>
+      </c>
+      <c r="E478" s="6">
+        <v>20</v>
+      </c>
+      <c r="F478" s="3">
+        <f t="shared" si="9"/>
+        <v>29.67771428571432</v>
+      </c>
+      <c r="G478" s="1"/>
+      <c r="H478" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8">
+      <c r="A479" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B479" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C479" s="8">
+        <v>104</v>
+      </c>
+      <c r="D479" s="4">
+        <v>29.185508082497201</v>
+      </c>
+      <c r="E479" s="6">
+        <v>20</v>
+      </c>
+      <c r="F479" s="3">
+        <f t="shared" si="9"/>
+        <v>23.348406465997762</v>
+      </c>
+      <c r="G479" s="1"/>
+      <c r="H479" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8">
+      <c r="A480" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B480" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C480" s="8">
+        <v>95</v>
+      </c>
+      <c r="D480" s="4">
+        <v>37.373856826646097</v>
+      </c>
+      <c r="E480" s="6">
+        <v>20</v>
+      </c>
+      <c r="F480" s="3">
+        <f t="shared" si="9"/>
+        <v>29.899085461316879</v>
+      </c>
+      <c r="G480" s="1"/>
+      <c r="H480" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8">
+      <c r="A481" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B481" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C481" s="8">
+        <v>80</v>
+      </c>
+      <c r="D481" s="4">
+        <v>41.603309006211198</v>
+      </c>
+      <c r="E481" s="6">
+        <v>20</v>
+      </c>
+      <c r="F481" s="3">
+        <f t="shared" si="9"/>
+        <v>33.28264720496896</v>
+      </c>
+      <c r="G481" s="1"/>
+      <c r="H481" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B482" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C482" s="8">
+        <v>186</v>
+      </c>
+      <c r="D482" s="4">
+        <v>36.507125994677097</v>
+      </c>
+      <c r="E482" s="6">
+        <v>20</v>
+      </c>
+      <c r="F482" s="3">
+        <f t="shared" si="9"/>
+        <v>29.205700795741677</v>
+      </c>
+      <c r="G482" s="1"/>
+      <c r="H482" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B483" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C483" s="8">
+        <v>24</v>
+      </c>
+      <c r="D483" s="4">
+        <v>104.95541666666701</v>
+      </c>
+      <c r="E483" s="6">
+        <v>20</v>
+      </c>
+      <c r="F483" s="3">
+        <f t="shared" si="9"/>
+        <v>83.964333333333599</v>
+      </c>
+      <c r="G483" s="1"/>
+      <c r="H483" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B484" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C484" s="8">
+        <v>194</v>
+      </c>
+      <c r="D484" s="4">
+        <v>38.9126364060809</v>
+      </c>
+      <c r="E484" s="6">
+        <v>20</v>
+      </c>
+      <c r="F484" s="3">
+        <f t="shared" si="9"/>
+        <v>31.13010912486472</v>
+      </c>
+      <c r="G484" s="1"/>
+      <c r="H484" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B485" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C485" s="8">
+        <v>96</v>
+      </c>
+      <c r="D485" s="4">
+        <v>51.216453480848898</v>
+      </c>
+      <c r="E485" s="6">
+        <v>20</v>
+      </c>
+      <c r="F485" s="3">
+        <f t="shared" si="9"/>
+        <v>40.973162784679118</v>
+      </c>
+      <c r="G485" s="1"/>
+      <c r="H485" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B486" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C486" s="8">
+        <v>150</v>
+      </c>
+      <c r="D486" s="4">
+        <v>38.293937924802698</v>
+      </c>
+      <c r="E486" s="6">
+        <v>20</v>
+      </c>
+      <c r="F486" s="3">
+        <f t="shared" si="9"/>
+        <v>30.635150339842159</v>
+      </c>
+      <c r="G486" s="1"/>
+      <c r="H486" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B487" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C487" s="8">
+        <v>130</v>
+      </c>
+      <c r="D487" s="4">
+        <v>31.068295128194599</v>
+      </c>
+      <c r="E487" s="6">
+        <v>20</v>
+      </c>
+      <c r="F487" s="3">
+        <f t="shared" si="9"/>
+        <v>24.854636102555681</v>
+      </c>
+      <c r="G487" s="1"/>
+      <c r="H487" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
+      <c r="A488" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B488" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C488" s="8">
+        <v>166</v>
+      </c>
+      <c r="D488" s="4">
+        <v>123.409739773857</v>
+      </c>
+      <c r="E488" s="6">
+        <v>20</v>
+      </c>
+      <c r="F488" s="3">
+        <f t="shared" si="9"/>
+        <v>98.727791819085596</v>
+      </c>
+      <c r="G488" s="1"/>
+      <c r="H488" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B489" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C489" s="8">
+        <v>176</v>
+      </c>
+      <c r="D489" s="4">
+        <v>50.809995974853898</v>
+      </c>
+      <c r="E489" s="6">
+        <v>20</v>
+      </c>
+      <c r="F489" s="3">
+        <f t="shared" si="9"/>
+        <v>40.647996779883115</v>
+      </c>
+      <c r="G489" s="1"/>
+      <c r="H489" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="A490" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B490" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C490" s="8">
+        <v>168</v>
+      </c>
+      <c r="D490" s="4">
+        <v>51.829164772727303</v>
+      </c>
+      <c r="E490" s="6">
+        <v>20</v>
+      </c>
+      <c r="F490" s="3">
+        <f t="shared" si="9"/>
+        <v>41.463331818181842</v>
+      </c>
+      <c r="G490" s="1"/>
+      <c r="H490" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B491" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C491" s="8">
+        <v>40</v>
+      </c>
+      <c r="D491" s="4">
+        <v>32.281159413580198</v>
+      </c>
+      <c r="E491" s="6">
+        <v>20</v>
+      </c>
+      <c r="F491" s="3">
+        <f t="shared" si="9"/>
+        <v>25.824927530864159</v>
+      </c>
+      <c r="G491" s="1"/>
+      <c r="H491" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B492" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C492" s="8">
+        <v>5</v>
+      </c>
+      <c r="D492" s="4">
+        <v>42.908999999999999</v>
+      </c>
+      <c r="E492" s="6">
+        <v>20</v>
+      </c>
+      <c r="F492" s="3">
+        <f t="shared" si="9"/>
+        <v>34.327199999999998</v>
+      </c>
+      <c r="G492" s="1"/>
+      <c r="H492" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B493" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C493" s="8">
+        <v>108</v>
+      </c>
+      <c r="D493" s="4">
+        <v>42.604784618573802</v>
+      </c>
+      <c r="E493" s="6">
+        <v>20</v>
+      </c>
+      <c r="F493" s="3">
+        <f t="shared" si="9"/>
+        <v>34.083827694859039</v>
+      </c>
+      <c r="G493" s="1"/>
+      <c r="H493" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B494" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C494" s="8">
+        <v>166</v>
+      </c>
+      <c r="D494" s="4">
+        <v>62.963926721918597</v>
+      </c>
+      <c r="E494" s="6">
+        <v>20</v>
+      </c>
+      <c r="F494" s="3">
+        <f t="shared" si="9"/>
+        <v>50.371141377534876</v>
+      </c>
+      <c r="G494" s="1"/>
+      <c r="H494" s="7"/>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B495" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C495" s="8">
+        <v>144</v>
+      </c>
+      <c r="D495" s="4">
+        <v>29.810972222222201</v>
+      </c>
+      <c r="E495" s="6">
+        <v>20</v>
+      </c>
+      <c r="F495" s="3">
+        <f t="shared" si="9"/>
+        <v>23.848777777777762</v>
+      </c>
+      <c r="G495" s="1"/>
+      <c r="H495" s="7"/>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B496" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C496" s="8">
+        <v>103</v>
+      </c>
+      <c r="D496" s="4">
+        <v>39.8784361081104</v>
+      </c>
+      <c r="E496" s="6">
+        <v>20</v>
+      </c>
+      <c r="F496" s="3">
+        <f t="shared" si="9"/>
+        <v>31.902748886488318</v>
+      </c>
+      <c r="G496" s="1"/>
+      <c r="H496" s="7"/>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B497" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C497" s="8">
+        <v>127</v>
+      </c>
+      <c r="D497" s="4">
+        <v>46.705566274470101</v>
+      </c>
+      <c r="E497" s="6">
+        <v>20</v>
+      </c>
+      <c r="F497" s="3">
+        <f t="shared" ref="F497:F507" si="10">D497-(D497*E497)/100</f>
+        <v>37.364453019576082</v>
+      </c>
+      <c r="G497" s="1"/>
+      <c r="H497" s="7"/>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B498" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C498" s="8">
+        <v>13</v>
+      </c>
+      <c r="D498" s="4">
+        <v>39.099424015009397</v>
+      </c>
+      <c r="E498" s="6">
+        <v>20</v>
+      </c>
+      <c r="F498" s="3">
+        <f t="shared" si="10"/>
+        <v>31.279539212007517</v>
+      </c>
+      <c r="G498" s="1"/>
+      <c r="H498" s="7"/>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B499" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C499" s="8">
+        <v>163</v>
+      </c>
+      <c r="D499" s="4">
+        <v>48.2186392857501</v>
+      </c>
+      <c r="E499" s="6">
+        <v>20</v>
+      </c>
+      <c r="F499" s="3">
+        <f t="shared" si="10"/>
+        <v>38.574911428600082</v>
+      </c>
+      <c r="G499" s="1"/>
+      <c r="H499" s="7"/>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B500" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C500" s="8"/>
+      <c r="D500" s="4"/>
+      <c r="E500" s="6">
+        <v>20</v>
+      </c>
+      <c r="F500" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G500" s="1"/>
+      <c r="H500" s="7"/>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B501" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C501" s="20">
+        <v>66</v>
+      </c>
+      <c r="D501" s="4">
+        <v>33.444482699300501</v>
+      </c>
+      <c r="E501" s="6">
+        <v>20</v>
+      </c>
+      <c r="F501" s="3">
+        <f t="shared" si="10"/>
+        <v>26.755586159440401</v>
+      </c>
+      <c r="G501" s="1"/>
+      <c r="H501" s="7"/>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B502" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C502" s="26">
+        <v>171</v>
+      </c>
+      <c r="D502" s="4">
+        <v>33.508970365640998</v>
+      </c>
+      <c r="E502" s="6">
+        <v>20</v>
+      </c>
+      <c r="F502" s="3">
+        <f t="shared" si="10"/>
+        <v>26.8071762925128</v>
+      </c>
+      <c r="G502" s="1"/>
+      <c r="H502" s="7"/>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B503" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C503" s="26">
+        <v>160</v>
+      </c>
+      <c r="D503" s="4">
+        <v>35.2698234856556</v>
+      </c>
+      <c r="E503" s="6">
+        <v>20</v>
+      </c>
+      <c r="F503" s="3">
+        <f t="shared" si="10"/>
+        <v>28.215858788524478</v>
+      </c>
+      <c r="G503" s="1"/>
+      <c r="H503" s="1"/>
+    </row>
+    <row r="504" spans="1:8">
+      <c r="A504" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B504" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C504" s="26"/>
+      <c r="D504" s="4"/>
+      <c r="E504" s="6">
+        <v>20</v>
+      </c>
+      <c r="F504" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G504" s="1"/>
+      <c r="H504" s="1"/>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B505" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C505" s="26">
+        <v>112</v>
+      </c>
+      <c r="D505" s="4">
+        <v>35.798830718736099</v>
+      </c>
+      <c r="E505" s="6">
+        <v>20</v>
+      </c>
+      <c r="F505" s="3">
+        <f t="shared" si="10"/>
+        <v>28.639064574988879</v>
+      </c>
+      <c r="G505" s="1"/>
+      <c r="H505" s="1"/>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="A506" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B506" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C506" s="26">
+        <v>104</v>
+      </c>
+      <c r="D506" s="4">
+        <v>47.375443548386997</v>
+      </c>
+      <c r="E506" s="6">
+        <v>20</v>
+      </c>
+      <c r="F506" s="3">
+        <f t="shared" si="10"/>
+        <v>37.900354838709596</v>
+      </c>
+      <c r="G506" s="1"/>
+      <c r="H506" s="1"/>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B507" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C507" s="26">
+        <v>24</v>
+      </c>
+      <c r="D507" s="4">
+        <v>55.246318385650198</v>
+      </c>
+      <c r="E507" s="6">
+        <v>20</v>
+      </c>
+      <c r="F507" s="3">
+        <f>D507-(D507*E507)/100</f>
+        <v>44.197054708520156</v>
+      </c>
+      <c r="G507" s="1"/>
+      <c r="H507" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G432">
+  <autoFilter ref="A1:G507">
     <filterColumn colId="0"/>
     <filterColumn colId="1"/>
   </autoFilter>
@@ -11980,6 +13809,65 @@
     <hyperlink ref="H416" r:id="rId361"/>
     <hyperlink ref="H417" r:id="rId362"/>
     <hyperlink ref="H418" r:id="rId363"/>
+    <hyperlink ref="G433" r:id="rId364"/>
+    <hyperlink ref="H433" r:id="rId365"/>
+    <hyperlink ref="H434" r:id="rId366"/>
+    <hyperlink ref="H436" r:id="rId367"/>
+    <hyperlink ref="H437" r:id="rId368"/>
+    <hyperlink ref="H438" r:id="rId369"/>
+    <hyperlink ref="H439" r:id="rId370"/>
+    <hyperlink ref="H440" r:id="rId371"/>
+    <hyperlink ref="H442" r:id="rId372"/>
+    <hyperlink ref="H443" r:id="rId373"/>
+    <hyperlink ref="H444" r:id="rId374"/>
+    <hyperlink ref="H445" r:id="rId375"/>
+    <hyperlink ref="H446" r:id="rId376"/>
+    <hyperlink ref="H448" r:id="rId377"/>
+    <hyperlink ref="H449" r:id="rId378"/>
+    <hyperlink ref="H450" r:id="rId379"/>
+    <hyperlink ref="H451" r:id="rId380"/>
+    <hyperlink ref="H452" r:id="rId381"/>
+    <hyperlink ref="H453" r:id="rId382"/>
+    <hyperlink ref="H454" r:id="rId383"/>
+    <hyperlink ref="H455" r:id="rId384"/>
+    <hyperlink ref="H456" r:id="rId385"/>
+    <hyperlink ref="H457" r:id="rId386"/>
+    <hyperlink ref="H458" r:id="rId387"/>
+    <hyperlink ref="H459" r:id="rId388"/>
+    <hyperlink ref="H460" r:id="rId389"/>
+    <hyperlink ref="H461" r:id="rId390"/>
+    <hyperlink ref="H462" r:id="rId391"/>
+    <hyperlink ref="H463" r:id="rId392"/>
+    <hyperlink ref="H464" r:id="rId393"/>
+    <hyperlink ref="H465" r:id="rId394"/>
+    <hyperlink ref="H466" r:id="rId395"/>
+    <hyperlink ref="H467" r:id="rId396"/>
+    <hyperlink ref="H468" r:id="rId397"/>
+    <hyperlink ref="H469" r:id="rId398"/>
+    <hyperlink ref="H470" r:id="rId399"/>
+    <hyperlink ref="H471" r:id="rId400"/>
+    <hyperlink ref="H472" r:id="rId401"/>
+    <hyperlink ref="H473" r:id="rId402"/>
+    <hyperlink ref="H474" r:id="rId403"/>
+    <hyperlink ref="H475" r:id="rId404"/>
+    <hyperlink ref="H476" r:id="rId405"/>
+    <hyperlink ref="H477" r:id="rId406"/>
+    <hyperlink ref="H478" r:id="rId407"/>
+    <hyperlink ref="H479" r:id="rId408"/>
+    <hyperlink ref="H480" r:id="rId409"/>
+    <hyperlink ref="H481" r:id="rId410"/>
+    <hyperlink ref="H482" r:id="rId411"/>
+    <hyperlink ref="H483" r:id="rId412"/>
+    <hyperlink ref="H484" r:id="rId413"/>
+    <hyperlink ref="H485" r:id="rId414"/>
+    <hyperlink ref="H486" r:id="rId415"/>
+    <hyperlink ref="H487" r:id="rId416"/>
+    <hyperlink ref="H488" r:id="rId417"/>
+    <hyperlink ref="H489" r:id="rId418"/>
+    <hyperlink ref="H490" r:id="rId419"/>
+    <hyperlink ref="H491" r:id="rId420"/>
+    <hyperlink ref="H492" r:id="rId421"/>
+    <hyperlink ref="H493" r:id="rId422"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11987,7 +13875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D1:L118"/>
+  <dimension ref="D1:L132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -13902,8 +15790,246 @@
         <v>38.1497195945946</v>
       </c>
     </row>
+    <row r="122" spans="4:12">
+      <c r="D122" s="27">
+        <v>46204</v>
+      </c>
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
+      <c r="H122" s="28"/>
+      <c r="I122" s="28"/>
+      <c r="J122" s="28"/>
+      <c r="K122" s="28"/>
+      <c r="L122" s="28"/>
+    </row>
+    <row r="123" spans="4:12">
+      <c r="D123" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L123" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="4:12">
+      <c r="D124" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E124" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F124" s="8">
+        <v>108</v>
+      </c>
+      <c r="G124" s="4">
+        <v>42.604784618573802</v>
+      </c>
+      <c r="I124" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J124" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K124" s="8">
+        <v>155</v>
+      </c>
+      <c r="L124" s="4">
+        <v>36.615065022272397</v>
+      </c>
+    </row>
+    <row r="125" spans="4:12">
+      <c r="D125" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F125" s="8">
+        <v>108</v>
+      </c>
+      <c r="G125" s="4">
+        <v>41.736368159203998</v>
+      </c>
+      <c r="I125" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J125" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K125" s="8">
+        <v>186</v>
+      </c>
+      <c r="L125" s="4">
+        <v>36.507125994677097</v>
+      </c>
+    </row>
+    <row r="126" spans="4:12">
+      <c r="D126" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F126" s="8">
+        <v>148</v>
+      </c>
+      <c r="G126" s="4">
+        <v>39.119060714285702</v>
+      </c>
+      <c r="I126" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K126" s="8">
+        <v>192</v>
+      </c>
+      <c r="L126" s="4">
+        <v>34.924171686747002</v>
+      </c>
+    </row>
+    <row r="127" spans="4:12">
+      <c r="D127" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E127" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F127" s="8">
+        <v>194</v>
+      </c>
+      <c r="G127" s="4">
+        <v>38.9126364060809</v>
+      </c>
+      <c r="I127" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J127" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K127" s="8">
+        <v>171</v>
+      </c>
+      <c r="L127" s="4">
+        <v>33.508970365640998</v>
+      </c>
+    </row>
+    <row r="128" spans="4:12">
+      <c r="D128" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F128" s="8">
+        <v>104</v>
+      </c>
+      <c r="G128" s="4">
+        <v>38.65</v>
+      </c>
+      <c r="I128" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J128" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K128" s="8">
+        <v>170</v>
+      </c>
+      <c r="L128" s="4">
+        <v>33.4496632653061</v>
+      </c>
+    </row>
+    <row r="129" spans="4:12">
+      <c r="D129" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" s="10">
+        <v>46234</v>
+      </c>
+      <c r="F129" s="8">
+        <v>140</v>
+      </c>
+      <c r="G129" s="4">
+        <v>38.07</v>
+      </c>
+      <c r="I129" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J129" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K129" s="8">
+        <v>40</v>
+      </c>
+      <c r="L129" s="4">
+        <v>32.281159413580198</v>
+      </c>
+    </row>
+    <row r="130" spans="4:12">
+      <c r="I130" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J130" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K130" s="8">
+        <v>95</v>
+      </c>
+      <c r="L130" s="4">
+        <v>31.253578239716902</v>
+      </c>
+    </row>
+    <row r="131" spans="4:12">
+      <c r="I131" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J131" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K131" s="8">
+        <v>172</v>
+      </c>
+      <c r="L131" s="4">
+        <v>31.096308641975298</v>
+      </c>
+    </row>
+    <row r="132" spans="4:12">
+      <c r="I132" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J132" s="10">
+        <v>46234</v>
+      </c>
+      <c r="K132" s="26">
+        <v>155</v>
+      </c>
+      <c r="L132" s="4">
+        <v>30.719612903225801</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="D122:L122"/>
     <mergeCell ref="D109:L109"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D25:L25"/>
@@ -13942,58 +16068,58 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B2" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C2" s="8">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D2" s="4">
-        <v>46.194493749999999</v>
+        <v>42.604784618573802</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B3" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="8">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4">
-        <v>44.903615728305802</v>
+        <v>41.736368159203998</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B4" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C4" s="8">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D4" s="4">
-        <v>44.902997023809498</v>
+        <v>39.119060714285702</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="B5" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C5" s="8">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D5" s="4">
-        <v>42.479528125000002</v>
+        <v>38.9126364060809</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14001,153 +16127,153 @@
         <v>19</v>
       </c>
       <c r="B6" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C6" s="8">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="D6" s="4">
-        <v>42.335981090293998</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B7" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C7" s="8">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D7" s="4">
-        <v>39.814689156314699</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="16" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B8" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C8" s="8">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D8" s="4">
-        <v>39.1587380818318</v>
+        <v>36.615065022272397</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="16" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B9" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C9" s="8">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D9" s="4">
-        <v>37.598206081081102</v>
+        <v>36.507125994677097</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="16" t="s">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="B10" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C10" s="8">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4">
-        <v>35.5917846645753</v>
+        <v>34.924171686747002</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="16" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="B11" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C11" s="8">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D11" s="4">
-        <v>35.147493750000002</v>
+        <v>33.508970365640998</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B12" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C12" s="8">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D12" s="4">
-        <v>33.4537949404762</v>
+        <v>33.4496632653061</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B13" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C13" s="8">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4">
-        <v>32.186248637203597</v>
+        <v>32.281159413580198</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="B14" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C14" s="8">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="D14" s="4">
-        <v>32.183252734025302</v>
+        <v>31.253578239716902</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="B15" s="10">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C15" s="8">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D15" s="4">
-        <v>31.106949346212499</v>
+        <v>31.096308641975298</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="16" t="s">
-        <v>21</v>
+      <c r="A16" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="B16" s="10">
-        <v>46142</v>
-      </c>
-      <c r="C16" s="8">
-        <v>136</v>
+        <v>46234</v>
+      </c>
+      <c r="C16" s="26">
+        <v>155</v>
       </c>
       <c r="D16" s="4">
-        <v>30.212524501078299</v>
+        <v>30.719612903225801</v>
       </c>
     </row>
   </sheetData>
